--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="723" firstSheet="6" activeTab="4"/>
+    <workbookView windowHeight="17655" tabRatio="723" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="761">
   <si>
     <t>id</t>
   </si>
@@ -1313,6 +1313,18 @@
     <t>每隔{Time_S}秒再攻击一次</t>
   </si>
   <si>
+    <t>击杀{KillNum}生物，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
     <t>每隔{Time_S}秒自动拾取附近魔晶</t>
   </si>
   <si>
@@ -1328,7 +1340,7 @@
     <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
   </si>
   <si>
-    <t>死亡后生成魔晶</t>
+    <t>死亡后{Percentage}%生成魔晶</t>
   </si>
   <si>
     <t>想要给魔物换个新名字！</t>
@@ -1784,6 +1796,18 @@
     <t>人类-魔法师（冰）</t>
   </si>
   <si>
+    <t>测试骷髅战士</t>
+  </si>
+  <si>
+    <t>Test Skeleton Warrior</t>
+  </si>
+  <si>
+    <t>测试骷髅投手</t>
+  </si>
+  <si>
+    <t>Test Skeleton Hurler</t>
+  </si>
+  <si>
     <t>没头脑的爪牙</t>
   </si>
   <si>
@@ -2132,6 +2156,9 @@
     <t>终焉议会议案：转生为人类</t>
   </si>
   <si>
+    <t>奖励新增：人类装备</t>
+  </si>
+  <si>
     <t>解锁种族：骷髅</t>
   </si>
   <si>
@@ -2156,6 +2183,9 @@
     <t>终焉议会议案：转生为骷髅</t>
   </si>
   <si>
+    <t>奖励新增：骷髅装备</t>
+  </si>
+  <si>
     <t>解锁种族：史莱姆</t>
   </si>
   <si>
@@ -2180,6 +2210,9 @@
     <t>终焉议会议案：生为史莱姆</t>
   </si>
   <si>
+    <t>奖励新增：史莱姆装备</t>
+  </si>
+  <si>
     <t>解锁种族：魅魔</t>
   </si>
   <si>
@@ -2207,6 +2240,9 @@
     <t>终焉议会议案：转生为魅魔</t>
   </si>
   <si>
+    <t>奖励新增：魅魔装备</t>
+  </si>
+  <si>
     <t>解锁种族：牛头人</t>
   </si>
   <si>
@@ -2231,6 +2267,9 @@
     <t>终焉议会议案：转生为牛头人</t>
   </si>
   <si>
+    <t>奖励新增：牛头人装备</t>
+  </si>
+  <si>
     <t>解锁种族：哥布林</t>
   </si>
   <si>
@@ -2258,6 +2297,9 @@
     <t>终焉议会议案：转生为哥布林</t>
   </si>
   <si>
+    <t>奖励新增：哥布林装备</t>
+  </si>
+  <si>
     <t>解锁种族：兽人</t>
   </si>
   <si>
@@ -2280,6 +2322,9 @@
   </si>
   <si>
     <t>终焉议会议案：转生兽人</t>
+  </si>
+  <si>
+    <t>奖励新增：兽人装备</t>
   </si>
 </sst>
 </file>
@@ -2933,11 +2978,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -5188,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5196,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5204,7 +5252,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5212,10 +5260,10 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C7" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5223,10 +5271,10 @@
         <v>1020010001</v>
       </c>
       <c r="B8" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C8" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5234,10 +5282,10 @@
         <v>1030010001</v>
       </c>
       <c r="B9" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C9" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5245,10 +5293,10 @@
         <v>1030020001</v>
       </c>
       <c r="B10" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C10" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:4">
@@ -5256,7 +5304,7 @@
         <v>2000000001</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5264,7 +5312,7 @@
         <v>2000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -5330,103 +5378,103 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:4">
       <c r="A5">
         <v>100000002</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>594</v>
+      <c r="B5" s="8" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:4">
       <c r="A6">
         <v>100000003</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>595</v>
+      <c r="B6" s="9" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:4">
       <c r="A7">
         <v>100000004</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>596</v>
+      <c r="B7" s="9" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:4">
       <c r="A8">
         <v>100000005</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>597</v>
+      <c r="B8" s="8" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:4">
       <c r="A9">
         <v>100000006</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>598</v>
+      <c r="B9" s="8" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:4">
       <c r="A10">
         <v>200000001</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>599</v>
+      <c r="B10" s="9" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:4">
       <c r="A11">
         <v>200000002</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>600</v>
+      <c r="B11" s="9" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:4">
       <c r="A12">
         <v>200000003</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>601</v>
+      <c r="B12" s="9" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:4">
       <c r="A13">
         <v>200000004</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>602</v>
+      <c r="B13" s="9" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:4">
       <c r="A14">
         <v>200000005</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>603</v>
+      <c r="B14" s="9" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:4">
       <c r="A15">
         <v>200000006</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>604</v>
+      <c r="B15" s="8" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:4">
       <c r="A16">
         <v>200000007</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>605</v>
+      <c r="B16" s="8" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5434,7 +5482,7 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5442,7 +5490,7 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5450,7 +5498,7 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5458,7 +5506,7 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5466,7 +5514,7 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5474,7 +5522,7 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5482,7 +5530,7 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5490,7 +5538,7 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -5498,7 +5546,7 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -5506,7 +5554,7 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5514,7 +5562,7 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5522,7 +5570,7 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5530,7 +5578,7 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -5538,7 +5586,7 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5546,7 +5594,7 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -5554,7 +5602,7 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5562,7 +5610,7 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5570,7 +5618,7 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -5637,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5645,7 +5693,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5653,7 +5701,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5661,7 +5709,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5669,7 +5717,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5677,7 +5725,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5685,7 +5733,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5693,7 +5741,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5701,7 +5749,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5709,7 +5757,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5717,7 +5765,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5725,7 +5773,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5733,7 +5781,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -5797,11 +5845,11 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>637</v>
+      <c r="B4" s="7" t="s">
+        <v>645</v>
       </c>
       <c r="C4" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5809,10 +5857,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="C5" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5820,10 +5868,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C6" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5831,10 +5879,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C7" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5842,10 +5890,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C8" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -5911,10 +5959,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>647</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>648</v>
+        <v>655</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:4">
@@ -5922,10 +5970,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>649</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>650</v>
+        <v>657</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:4">
@@ -5933,10 +5981,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>651</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>652</v>
+        <v>659</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:4">
@@ -5944,10 +5992,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>653</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>654</v>
+        <v>661</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:4">
@@ -5955,10 +6003,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>655</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>656</v>
+        <v>663</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:4">
@@ -5966,10 +6014,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>657</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>658</v>
+        <v>665</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:4">
@@ -5977,10 +6025,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>659</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>660</v>
+        <v>667</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:4">
@@ -5988,10 +6036,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>661</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:4">
@@ -5999,10 +6047,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>663</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>664</v>
+        <v>671</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:4">
@@ -6010,10 +6058,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>665</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>666</v>
+        <v>673</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -6089,10 +6137,10 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>91</v>
       </c>
     </row>
@@ -6100,33 +6148,33 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>667</v>
+      <c r="B6" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>668</v>
+      <c r="B7" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>669</v>
+      <c r="B8" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6134,10 +6182,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C9" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -6149,7 +6197,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -6205,10 +6253,10 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D4" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6216,10 +6264,10 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="D5" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6227,10 +6275,10 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D6" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6238,10 +6286,10 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="D7" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6249,10 +6297,10 @@
         <v>100200002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="D8" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6260,10 +6308,10 @@
         <v>100200003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D9" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6271,10 +6319,10 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="D10" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6282,10 +6330,10 @@
         <v>100400001</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="D11" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6293,10 +6341,10 @@
         <v>100401000</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D12" t="s">
         <v>680</v>
-      </c>
-      <c r="D12" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6304,10 +6352,10 @@
         <v>100401001</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="D13" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6315,10 +6363,10 @@
         <v>100402000</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D14" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6326,10 +6374,10 @@
         <v>100402001</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="D15" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6337,10 +6385,10 @@
         <v>100403000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="D16" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6348,10 +6396,10 @@
         <v>100403001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D17" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -6359,10 +6407,10 @@
         <v>100404001</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D18" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -6370,10 +6418,10 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="D19" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6381,10 +6429,10 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="D20" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6392,10 +6440,10 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D21" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -6403,10 +6451,10 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="D22" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6414,10 +6462,10 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="D23" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6425,10 +6473,10 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D24" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6436,10 +6484,10 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D25" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6447,10 +6495,10 @@
         <v>300100101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="D26" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6458,10 +6506,10 @@
         <v>300100102</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="D27" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6469,560 +6517,637 @@
         <v>300100201</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="D28" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
+        <v>300100301</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D29" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
         <v>300200000</v>
       </c>
-      <c r="B29" t="s">
-        <v>696</v>
-      </c>
-      <c r="D29" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30">
-        <v>300200001</v>
-      </c>
       <c r="B30" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="D30" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="D31" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="D32" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
+        <v>300200003</v>
+      </c>
+      <c r="B33" t="s">
+        <v>708</v>
+      </c>
+      <c r="D33" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
         <v>300200004</v>
       </c>
-      <c r="B33" t="s">
-        <v>700</v>
-      </c>
-      <c r="D33" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="1">
-        <v>300200101</v>
-      </c>
       <c r="B34" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="D34" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="D35" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
-        <v>300200201</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>703</v>
+        <v>300200102</v>
+      </c>
+      <c r="B36" t="s">
+        <v>711</v>
       </c>
       <c r="D36" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
+        <v>300200201</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D37" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1">
+        <v>300200301</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D38" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1">
         <v>300300000</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="D37" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38">
-        <v>300300001</v>
-      </c>
-      <c r="B38" t="s">
-        <v>705</v>
-      </c>
-      <c r="D38" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39">
-        <v>300300002</v>
-      </c>
-      <c r="B39" t="s">
-        <v>706</v>
+      <c r="B39" s="1" t="s">
+        <v>714</v>
       </c>
       <c r="D39" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="D40" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="D41" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
+        <v>300300003</v>
+      </c>
+      <c r="B42" t="s">
+        <v>717</v>
+      </c>
+      <c r="D42" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>300300004</v>
+      </c>
+      <c r="B43" t="s">
+        <v>718</v>
+      </c>
+      <c r="D43" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
         <v>300300101</v>
       </c>
-      <c r="B42" t="s">
-        <v>709</v>
-      </c>
-      <c r="D42" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="43" ht="14" customHeight="1" spans="1:4">
-      <c r="A43">
+      <c r="B44" t="s">
+        <v>719</v>
+      </c>
+      <c r="D44" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:4">
+      <c r="A45">
         <v>300300102</v>
       </c>
-      <c r="B43" t="s">
-        <v>710</v>
-      </c>
-      <c r="D43" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1" spans="1:4">
-      <c r="A44" s="1">
+      <c r="B45" t="s">
+        <v>720</v>
+      </c>
+      <c r="D45" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:4">
+      <c r="A46" s="1">
         <v>300300201</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="D44" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1">
+      <c r="B46" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D46" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:4">
+      <c r="A47" s="1">
+        <v>300300301</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D47" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1">
         <v>300400000</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="D45" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46">
-        <v>300400001</v>
-      </c>
-      <c r="B46" t="s">
-        <v>713</v>
-      </c>
-      <c r="D46" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47">
-        <v>300400002</v>
-      </c>
-      <c r="B47" t="s">
-        <v>714</v>
-      </c>
-      <c r="D47" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48">
-        <v>300400003</v>
-      </c>
-      <c r="B48" t="s">
-        <v>715</v>
+      <c r="B48" s="1" t="s">
+        <v>723</v>
       </c>
       <c r="D48" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="D49" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D50" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="D51" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
+        <v>300400004</v>
+      </c>
+      <c r="B52" t="s">
+        <v>727</v>
+      </c>
+      <c r="D52" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>300400005</v>
+      </c>
+      <c r="B53" t="s">
+        <v>728</v>
+      </c>
+      <c r="D53" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>300400101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>729</v>
+      </c>
+      <c r="D54" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
         <v>300400102</v>
       </c>
-      <c r="B52" t="s">
-        <v>719</v>
-      </c>
-      <c r="D52" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="1">
-        <v>300400201</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="D53" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="1">
-        <v>300500000</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="D54" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1">
-        <v>300500001</v>
-      </c>
       <c r="B55" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="D55" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
-        <v>300500002</v>
-      </c>
-      <c r="B56" t="s">
-        <v>723</v>
+        <v>300400201</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>731</v>
       </c>
       <c r="D56" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
-        <v>300500003</v>
-      </c>
-      <c r="B57" t="s">
-        <v>724</v>
+        <v>300400301</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>732</v>
       </c>
       <c r="D57" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
-        <v>300500004</v>
-      </c>
-      <c r="B58" t="s">
-        <v>725</v>
+        <v>300500000</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>733</v>
       </c>
       <c r="D58" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59">
-        <v>300500101</v>
+      <c r="A59" s="1">
+        <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="D59" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60">
-        <v>300500102</v>
+      <c r="A60" s="1">
+        <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="D60" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
-        <v>300500201</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>728</v>
+        <v>300500003</v>
+      </c>
+      <c r="B61" t="s">
+        <v>736</v>
       </c>
       <c r="D61" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1">
-        <v>300600000</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>729</v>
+        <v>300500004</v>
+      </c>
+      <c r="B62" t="s">
+        <v>737</v>
       </c>
       <c r="D62" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="1">
-        <v>300600001</v>
+      <c r="A63">
+        <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="D63" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="1">
-        <v>300600002</v>
+      <c r="A64">
+        <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="D64" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="1">
-        <v>300600003</v>
-      </c>
-      <c r="B65" t="s">
-        <v>732</v>
+        <v>300500201</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>740</v>
       </c>
       <c r="D65" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="1">
-        <v>300600004</v>
-      </c>
-      <c r="B66" t="s">
-        <v>733</v>
+        <v>300500301</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="D66" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="1">
-        <v>300600005</v>
-      </c>
-      <c r="B67" t="s">
-        <v>734</v>
+        <v>300600000</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>742</v>
       </c>
       <c r="D67" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68">
-        <v>300600101</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>735</v>
+      <c r="A68" s="1">
+        <v>300600001</v>
+      </c>
+      <c r="B68" t="s">
+        <v>743</v>
       </c>
       <c r="D68" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69">
-        <v>300600102</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>736</v>
+      <c r="A69" s="1">
+        <v>300600002</v>
+      </c>
+      <c r="B69" t="s">
+        <v>744</v>
       </c>
       <c r="D69" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1">
-        <v>300600201</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>737</v>
+        <v>300600003</v>
+      </c>
+      <c r="B70" t="s">
+        <v>745</v>
       </c>
       <c r="D70" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="1">
-        <v>300700000</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>738</v>
+        <v>300600004</v>
+      </c>
+      <c r="B71" t="s">
+        <v>746</v>
       </c>
       <c r="D71" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1">
-        <v>300700001</v>
+        <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="D72" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="1">
-        <v>300700002</v>
-      </c>
-      <c r="B73" t="s">
-        <v>740</v>
+      <c r="A73">
+        <v>300600101</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>748</v>
       </c>
       <c r="D73" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1">
-        <v>300700003</v>
-      </c>
-      <c r="B74" t="s">
-        <v>741</v>
+      <c r="A74">
+        <v>300600102</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>749</v>
       </c>
       <c r="D74" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="1">
-        <v>300700004</v>
-      </c>
-      <c r="B75" t="s">
-        <v>742</v>
+        <v>300600201</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="D75" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76">
-        <v>300700101</v>
-      </c>
-      <c r="B76" t="s">
-        <v>743</v>
+      <c r="A76" s="1">
+        <v>300600301</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>751</v>
       </c>
       <c r="D76" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77">
-        <v>300700102</v>
-      </c>
-      <c r="B77" t="s">
-        <v>744</v>
+      <c r="A77" s="1">
+        <v>300700000</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>752</v>
       </c>
       <c r="D77" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="1">
+        <v>300700001</v>
+      </c>
+      <c r="B78" t="s">
+        <v>753</v>
+      </c>
+      <c r="D78" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1">
+        <v>300700002</v>
+      </c>
+      <c r="B79" t="s">
+        <v>754</v>
+      </c>
+      <c r="D79" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1">
+        <v>300700003</v>
+      </c>
+      <c r="B80" t="s">
+        <v>755</v>
+      </c>
+      <c r="D80" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1">
+        <v>300700004</v>
+      </c>
+      <c r="B81" t="s">
+        <v>756</v>
+      </c>
+      <c r="D81" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>300700101</v>
+      </c>
+      <c r="B82" t="s">
+        <v>757</v>
+      </c>
+      <c r="D82" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>300700102</v>
+      </c>
+      <c r="B83" t="s">
+        <v>758</v>
+      </c>
+      <c r="D83" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1">
         <v>300700201</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="D78" t="s">
-        <v>672</v>
+      <c r="B84" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D84" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1">
+        <v>300700301</v>
+      </c>
+      <c r="B85" t="s">
+        <v>760</v>
+      </c>
+      <c r="D85" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -9366,7 +9491,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="35.375" customWidth="1"/>
@@ -9628,10 +9753,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>13000100001</v>
-      </c>
-      <c r="B23" t="s">
-        <v>403</v>
+        <v>12000400001</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>387</v>
@@ -9639,10 +9764,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>13000200001</v>
-      </c>
-      <c r="B24" t="s">
-        <v>404</v>
+        <v>12000500001</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="D24" t="s">
         <v>387</v>
@@ -9650,10 +9775,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>13000300001</v>
-      </c>
-      <c r="B25" t="s">
-        <v>405</v>
+        <v>12000600001</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
       </c>
       <c r="D25" t="s">
         <v>387</v>
@@ -9661,10 +9786,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>13000400001</v>
-      </c>
-      <c r="B26" t="s">
-        <v>406</v>
+        <v>12000700001</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
       </c>
       <c r="D26" t="s">
         <v>387</v>
@@ -9672,10 +9797,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>13000500001</v>
+        <v>13000100001</v>
       </c>
       <c r="B27" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D27" t="s">
         <v>387</v>
@@ -9683,10 +9808,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>13000600001</v>
+        <v>13000200001</v>
       </c>
       <c r="B28" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D28" t="s">
         <v>387</v>
@@ -9694,287 +9819,375 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>13000700001</v>
+        <v>13000300001</v>
       </c>
       <c r="B29" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D29" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="9">
-        <v>10001000010000</v>
+      <c r="A30">
+        <v>13000400001</v>
       </c>
       <c r="B30" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D30" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="9">
-        <v>10002000010000</v>
+      <c r="A31">
+        <v>13000500001</v>
       </c>
       <c r="B31" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D31" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="9">
-        <v>10003000010000</v>
+      <c r="A32">
+        <v>13000600001</v>
       </c>
       <c r="B32" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D32" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="9">
-        <v>10004000010000</v>
+      <c r="A33">
+        <v>13000700001</v>
       </c>
       <c r="B33" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D33" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="9">
-        <v>10005000010000</v>
+      <c r="A34" s="10">
+        <v>10001000010000</v>
       </c>
       <c r="B34" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D34" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="9">
-        <v>20001000010000</v>
+      <c r="A35" s="10">
+        <v>10002000010000</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D35" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="9">
-        <v>20002000010000</v>
+      <c r="A36" s="10">
+        <v>10003000010000</v>
       </c>
       <c r="B36" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D36" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="9">
-        <v>20003000010000</v>
+      <c r="A37" s="10">
+        <v>10004000010000</v>
       </c>
       <c r="B37" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D37" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="9">
-        <v>20004000010000</v>
+      <c r="A38" s="10">
+        <v>10005000010000</v>
       </c>
       <c r="B38" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D38" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="9">
-        <v>30001000010000</v>
+      <c r="A39" s="10">
+        <v>20001000010000</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>412</v>
       </c>
       <c r="D39" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="9">
-        <v>30002000010000</v>
+      <c r="A40" s="10">
+        <v>20002000010000</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>413</v>
       </c>
       <c r="D40" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="9">
-        <v>30003000010000</v>
+      <c r="A41" s="10">
+        <v>20003000010000</v>
       </c>
       <c r="B41" t="s">
-        <v>210</v>
+        <v>414</v>
       </c>
       <c r="D41" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="9">
-        <v>30004000010000</v>
+      <c r="A42" s="10">
+        <v>20004000010000</v>
       </c>
       <c r="B42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D42" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="9">
-        <v>110001000010000</v>
+      <c r="A43" s="10">
+        <v>30001000010000</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="9">
-        <v>110002000010000</v>
+      <c r="A44" s="10">
+        <v>30002000010000</v>
       </c>
       <c r="B44" t="s">
-        <v>418</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="9">
-        <v>110003000010000</v>
+      <c r="A45" s="10">
+        <v>30003000010000</v>
       </c>
       <c r="B45" t="s">
-        <v>419</v>
+        <v>210</v>
       </c>
       <c r="D45" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="9">
-        <v>120001000010000</v>
+      <c r="A46" s="10">
+        <v>30004000010000</v>
       </c>
       <c r="B46" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D46" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="9">
-        <v>120002000010000</v>
+      <c r="A47" s="10">
+        <v>110001000010000</v>
       </c>
       <c r="B47" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D47" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="9">
-        <v>120003000010000</v>
+      <c r="A48" s="10">
+        <v>110002000010000</v>
       </c>
       <c r="B48" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D48" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="9">
-        <v>130001000010000</v>
+      <c r="A49" s="10">
+        <v>110003000010000</v>
       </c>
       <c r="B49" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D49" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="9">
-        <v>130003000010000</v>
+      <c r="A50" s="10">
+        <v>120001000010000</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D50" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="9">
-        <v>130004000010000</v>
+      <c r="A51" s="10">
+        <v>120002000010000</v>
       </c>
       <c r="B51" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D51" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="9">
-        <v>130005000010000</v>
+      <c r="A52" s="10">
+        <v>120003000010000</v>
       </c>
       <c r="B52" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D52" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="9">
-        <v>130006000010000</v>
+      <c r="A53" s="10">
+        <v>120004000010000</v>
       </c>
       <c r="B53" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D53" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="9">
+      <c r="A54" s="10">
+        <v>120005000010000</v>
+      </c>
+      <c r="B54" t="s">
+        <v>424</v>
+      </c>
+      <c r="D54" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="10">
+        <v>120006000010000</v>
+      </c>
+      <c r="B55" t="s">
+        <v>425</v>
+      </c>
+      <c r="D55" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="10">
+        <v>120007000010000</v>
+      </c>
+      <c r="B56" t="s">
+        <v>426</v>
+      </c>
+      <c r="D56" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="10">
+        <v>130001000010000</v>
+      </c>
+      <c r="B57" t="s">
+        <v>427</v>
+      </c>
+      <c r="D57" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="10">
+        <v>130003000010000</v>
+      </c>
+      <c r="B58" t="s">
+        <v>428</v>
+      </c>
+      <c r="D58" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="10">
+        <v>130004000010000</v>
+      </c>
+      <c r="B59" t="s">
+        <v>429</v>
+      </c>
+      <c r="D59" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="10">
+        <v>130005000010000</v>
+      </c>
+      <c r="B60" t="s">
+        <v>430</v>
+      </c>
+      <c r="D60" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="10">
+        <v>130006000010000</v>
+      </c>
+      <c r="B61" t="s">
+        <v>431</v>
+      </c>
+      <c r="D61" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="10">
         <v>130007000010000</v>
       </c>
-      <c r="B54" t="s">
-        <v>428</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="B62" t="s">
+        <v>432</v>
+      </c>
+      <c r="D62" t="s">
         <v>387</v>
       </c>
     </row>
@@ -10043,10 +10256,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10054,10 +10267,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10065,10 +10278,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D6" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10076,10 +10289,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D7" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10087,10 +10300,10 @@
         <v>100001</v>
       </c>
       <c r="B8" t="s">
+        <v>438</v>
+      </c>
+      <c r="D8" t="s">
         <v>434</v>
-      </c>
-      <c r="D8" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10098,10 +10311,10 @@
         <v>100002</v>
       </c>
       <c r="B9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D9" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10109,10 +10322,10 @@
         <v>100003</v>
       </c>
       <c r="B10" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D10" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10120,10 +10333,10 @@
         <v>100004</v>
       </c>
       <c r="B11" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D11" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10131,10 +10344,10 @@
         <v>200001</v>
       </c>
       <c r="B12" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D12" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10142,10 +10355,10 @@
         <v>200002</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D13" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10153,10 +10366,10 @@
         <v>200003</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D14" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10164,10 +10377,10 @@
         <v>200004</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D15" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10175,10 +10388,10 @@
         <v>200005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D16" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10186,10 +10399,10 @@
         <v>200006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D17" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -10197,10 +10410,10 @@
         <v>200007</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D18" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -10208,10 +10421,10 @@
         <v>200008</v>
       </c>
       <c r="B19" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D19" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -10219,10 +10432,10 @@
         <v>200009</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D20" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -10230,10 +10443,10 @@
         <v>200010</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D21" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -10241,10 +10454,10 @@
         <v>200011</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D22" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -10252,10 +10465,10 @@
         <v>200012</v>
       </c>
       <c r="B23" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D23" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -10263,10 +10476,10 @@
         <v>200013</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D24" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -10274,10 +10487,10 @@
         <v>200014</v>
       </c>
       <c r="B25" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D25" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -10345,13 +10558,13 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10359,13 +10572,13 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10373,13 +10586,13 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6" t="s">
         <v>458</v>
-      </c>
-      <c r="D6" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10387,13 +10600,13 @@
         <v>20001</v>
       </c>
       <c r="B7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D7" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10401,13 +10614,13 @@
         <v>20002</v>
       </c>
       <c r="B8" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D8" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10415,13 +10628,13 @@
         <v>20003</v>
       </c>
       <c r="B9" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D9" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10429,13 +10642,13 @@
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D10" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10443,13 +10656,13 @@
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C11" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10457,13 +10670,13 @@
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C12" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D12" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10471,13 +10684,13 @@
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C13" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D13" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10485,13 +10698,13 @@
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D14" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10499,13 +10712,13 @@
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D15" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10513,13 +10726,13 @@
         <v>50001</v>
       </c>
       <c r="B16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C16" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10527,13 +10740,13 @@
         <v>50002</v>
       </c>
       <c r="B17" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C17" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D17" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -10541,13 +10754,13 @@
         <v>50003</v>
       </c>
       <c r="B18" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C18" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D18" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -10555,13 +10768,13 @@
         <v>60001</v>
       </c>
       <c r="B19" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C19" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D19" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -10569,13 +10782,13 @@
         <v>60002</v>
       </c>
       <c r="B20" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C20" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D20" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -10583,13 +10796,13 @@
         <v>60003</v>
       </c>
       <c r="B21" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C21" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D21" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -10597,13 +10810,13 @@
         <v>70001</v>
       </c>
       <c r="B22" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C22" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D22" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -10611,13 +10824,13 @@
         <v>70002</v>
       </c>
       <c r="B23" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C23" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -10625,13 +10838,13 @@
         <v>70003</v>
       </c>
       <c r="B24" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D24" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -10699,13 +10912,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10713,10 +10926,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10724,10 +10937,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D6" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10735,10 +10948,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D7" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -10750,7 +10963,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -10806,13 +11019,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C4" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10820,13 +11033,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10834,13 +11047,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C6" t="s">
+        <v>511</v>
+      </c>
+      <c r="D6" t="s">
         <v>507</v>
-      </c>
-      <c r="D6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10848,13 +11061,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C7" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D7" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10862,13 +11075,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C8" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D8" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10876,13 +11089,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C9" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10890,13 +11103,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C10" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D10" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10904,13 +11117,13 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D11" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10918,13 +11131,13 @@
         <v>1002</v>
       </c>
       <c r="B12" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C12" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D12" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10932,13 +11145,13 @@
         <v>1003</v>
       </c>
       <c r="B13" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D13" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10946,13 +11159,13 @@
         <v>1004</v>
       </c>
       <c r="B14" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C14" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D14" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10960,13 +11173,13 @@
         <v>2001</v>
       </c>
       <c r="B15" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C15" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D15" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10974,13 +11187,13 @@
         <v>2002</v>
       </c>
       <c r="B16" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C16" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D16" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10988,13 +11201,13 @@
         <v>2003</v>
       </c>
       <c r="B17" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D17" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11002,13 +11215,13 @@
         <v>2004</v>
       </c>
       <c r="B18" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C18" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11016,13 +11229,13 @@
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C19" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D19" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11030,13 +11243,13 @@
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C20" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D20" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11044,13 +11257,13 @@
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C21" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -11058,13 +11271,13 @@
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C22" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D22" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11072,13 +11285,13 @@
         <v>4001</v>
       </c>
       <c r="B23" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C23" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D23" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11086,13 +11299,13 @@
         <v>4002</v>
       </c>
       <c r="B24" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C24" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D24" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11100,13 +11313,13 @@
         <v>4003</v>
       </c>
       <c r="B25" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C25" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11114,13 +11327,13 @@
         <v>4004</v>
       </c>
       <c r="B26" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C26" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D26" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11128,13 +11341,13 @@
         <v>4005</v>
       </c>
       <c r="B27" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C27" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D27" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11142,13 +11355,13 @@
         <v>5001</v>
       </c>
       <c r="B28" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C28" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11156,13 +11369,13 @@
         <v>5002</v>
       </c>
       <c r="B29" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C29" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D29" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11170,13 +11383,13 @@
         <v>5003</v>
       </c>
       <c r="B30" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C30" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D30" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11184,13 +11397,13 @@
         <v>5004</v>
       </c>
       <c r="B31" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C31" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D31" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11198,13 +11411,13 @@
         <v>6001</v>
       </c>
       <c r="B32" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C32" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D32" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11212,13 +11425,13 @@
         <v>6002</v>
       </c>
       <c r="B33" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C33" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D33" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11226,13 +11439,13 @@
         <v>6003</v>
       </c>
       <c r="B34" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C34" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D34" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11240,13 +11453,13 @@
         <v>6004</v>
       </c>
       <c r="B35" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C35" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D35" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -11254,13 +11467,13 @@
         <v>6005</v>
       </c>
       <c r="B36" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C36" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D36" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -11268,13 +11481,13 @@
         <v>7001</v>
       </c>
       <c r="B37" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C37" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D37" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -11282,13 +11495,13 @@
         <v>7002</v>
       </c>
       <c r="B38" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C38" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D38" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -11296,13 +11509,13 @@
         <v>7003</v>
       </c>
       <c r="B39" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C39" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D39" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -11310,13 +11523,13 @@
         <v>7004</v>
       </c>
       <c r="B40" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C40" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D40" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -11324,13 +11537,13 @@
         <v>101001</v>
       </c>
       <c r="B41" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C41" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D41" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -11338,13 +11551,13 @@
         <v>102001</v>
       </c>
       <c r="B42" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C42" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D42" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -11352,13 +11565,13 @@
         <v>103001</v>
       </c>
       <c r="B43" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C43" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D43" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -11366,13 +11579,41 @@
         <v>103002</v>
       </c>
       <c r="B44" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C44" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D44" t="s">
-        <v>503</v>
+        <v>507</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1">
+        <v>900001</v>
+      </c>
+      <c r="B45" t="s">
+        <v>584</v>
+      </c>
+      <c r="C45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D45" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1">
+        <v>900002</v>
+      </c>
+      <c r="B46" t="s">
+        <v>586</v>
+      </c>
+      <c r="C46" t="s">
+        <v>587</v>
+      </c>
+      <c r="D46" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="723" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="723" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="807">
   <si>
     <t>id</t>
   </si>
@@ -1253,6 +1253,130 @@
     <t>再补一刀</t>
   </si>
   <si>
+    <t>尸堆养料-HP</t>
+  </si>
+  <si>
+    <t>尸堆养料-DR</t>
+  </si>
+  <si>
+    <t>尸堆养料-ATK</t>
+  </si>
+  <si>
+    <t>尸堆养料-ASPD</t>
+  </si>
+  <si>
+    <t>痛楚馈赠-HP</t>
+  </si>
+  <si>
+    <t>Gift of Agony(HP)</t>
+  </si>
+  <si>
+    <t>痛楚馈赠-DR</t>
+  </si>
+  <si>
+    <t>Gift of Agony(DR)</t>
+  </si>
+  <si>
+    <t>痛楚馈赠-ATK</t>
+  </si>
+  <si>
+    <t>Gift of Agony(ATK)</t>
+  </si>
+  <si>
+    <t>痛楚馈赠-ASPD</t>
+  </si>
+  <si>
+    <t>Gift of Agony(ASPD)</t>
+  </si>
+  <si>
+    <t>濒死狂宴-HP</t>
+  </si>
+  <si>
+    <t>Feast of the Dying(HP)</t>
+  </si>
+  <si>
+    <t>濒死狂宴-DR</t>
+  </si>
+  <si>
+    <t>Feast of the Dying(DR)</t>
+  </si>
+  <si>
+    <t>濒死狂宴-ATK</t>
+  </si>
+  <si>
+    <t>Feast of the Dying(ATK)</t>
+  </si>
+  <si>
+    <t>濒死狂宴-ASPD</t>
+  </si>
+  <si>
+    <t>Feast of the Dying(ASPD)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收尸费</t>
+    </r>
+  </si>
+  <si>
+    <t>Corpse Tax</t>
+  </si>
+  <si>
+    <t>痛觉提款机</t>
+  </si>
+  <si>
+    <t>Pain ATM</t>
+  </si>
+  <si>
+    <t>暴力小费</t>
+  </si>
+  <si>
+    <t>Violence Tip</t>
+  </si>
+  <si>
+    <t>鞭尸成瘾</t>
+  </si>
+  <si>
+    <t>Corpse Kicker</t>
+  </si>
+  <si>
+    <t>碰瓷反杀</t>
+  </si>
+  <si>
+    <t>Blood Bait</t>
+  </si>
+  <si>
+    <t>越打越嗨</t>
+  </si>
+  <si>
+    <r>
+      <t>Rage Spiral</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
     <t>拾晶不昧</t>
   </si>
   <si>
@@ -1313,16 +1437,58 @@
     <t>每隔{Time_S}秒再攻击一次</t>
   </si>
   <si>
-    <t>击杀{KillNum}生物，生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，攻击速度增加{Percentage}%</t>
+    <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，立即攻击一次</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+  </si>
+  <si>
+    <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
   </si>
   <si>
     <t>每隔{Time_S}秒自动拾取附近魔晶</t>
@@ -2338,7 +2504,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2380,6 +2546,18 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF060A26"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF060A26"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -2848,137 +3026,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3007,6 +3185,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -5236,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>588</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5244,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>589</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5252,7 +5439,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>590</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5260,10 +5447,10 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>591</v>
+        <v>637</v>
       </c>
       <c r="C7" t="s">
-        <v>592</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5271,10 +5458,10 @@
         <v>1020010001</v>
       </c>
       <c r="B8" t="s">
-        <v>593</v>
+        <v>639</v>
       </c>
       <c r="C8" t="s">
-        <v>594</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5282,10 +5469,10 @@
         <v>1030010001</v>
       </c>
       <c r="B9" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="C9" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5293,10 +5480,10 @@
         <v>1030020001</v>
       </c>
       <c r="B10" t="s">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="C10" t="s">
-        <v>598</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:4">
@@ -5304,7 +5491,7 @@
         <v>2000000001</v>
       </c>
       <c r="B11" t="s">
-        <v>599</v>
+        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5312,7 +5499,7 @@
         <v>2000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>600</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -5378,7 +5565,7 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>601</v>
+        <v>647</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:4">
@@ -5386,7 +5573,7 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:4">
@@ -5394,7 +5581,7 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:4">
@@ -5402,7 +5589,7 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:4">
@@ -5410,7 +5597,7 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:4">
@@ -5418,7 +5605,7 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:4">
@@ -5426,7 +5613,7 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:4">
@@ -5434,7 +5621,7 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:4">
@@ -5442,7 +5629,7 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>609</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:4">
@@ -5450,7 +5637,7 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>610</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:4">
@@ -5458,7 +5645,7 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>611</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:4">
@@ -5466,7 +5653,7 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>612</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:4">
@@ -5474,7 +5661,7 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>613</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5482,7 +5669,7 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>614</v>
+        <v>660</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5490,7 +5677,7 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>615</v>
+        <v>661</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5498,7 +5685,7 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>616</v>
+        <v>662</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5506,7 +5693,7 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>617</v>
+        <v>663</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5514,7 +5701,7 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>618</v>
+        <v>664</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5522,7 +5709,7 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>619</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5530,7 +5717,7 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>620</v>
+        <v>666</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5538,7 +5725,7 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>621</v>
+        <v>667</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -5546,7 +5733,7 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>622</v>
+        <v>668</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -5554,7 +5741,7 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>623</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5562,7 +5749,7 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>624</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5570,7 +5757,7 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>625</v>
+        <v>671</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5578,7 +5765,7 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>626</v>
+        <v>672</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -5586,7 +5773,7 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>627</v>
+        <v>673</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5594,7 +5781,7 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>628</v>
+        <v>674</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -5602,7 +5789,7 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>629</v>
+        <v>675</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5610,7 +5797,7 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>630</v>
+        <v>676</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5618,7 +5805,7 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>631</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -5685,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5693,7 +5880,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>633</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5701,7 +5888,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>634</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5709,7 +5896,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>635</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5717,7 +5904,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>636</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5725,7 +5912,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>637</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5733,7 +5920,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>638</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5741,7 +5928,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>639</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5749,7 +5936,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>640</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5757,7 +5944,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>641</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5765,7 +5952,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>642</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5773,7 +5960,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>643</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5781,7 +5968,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>644</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -5846,10 +6033,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>645</v>
+        <v>691</v>
       </c>
       <c r="C4" t="s">
-        <v>646</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5857,10 +6044,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="C5" t="s">
-        <v>648</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5868,10 +6055,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>649</v>
+        <v>695</v>
       </c>
       <c r="C6" t="s">
-        <v>650</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5879,10 +6066,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="C7" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5890,10 +6077,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>653</v>
+        <v>699</v>
       </c>
       <c r="C8" t="s">
-        <v>654</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -5959,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>655</v>
+        <v>701</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>656</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:4">
@@ -5970,10 +6157,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>657</v>
+        <v>703</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:4">
@@ -5981,10 +6168,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:4">
@@ -5992,10 +6179,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>662</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:4">
@@ -6003,10 +6190,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>663</v>
+        <v>709</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>664</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:4">
@@ -6014,10 +6201,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>665</v>
+        <v>711</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>666</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:4">
@@ -6025,10 +6212,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>667</v>
+        <v>713</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:4">
@@ -6036,10 +6223,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>670</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:4">
@@ -6047,10 +6234,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:4">
@@ -6058,10 +6245,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>673</v>
+        <v>719</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>674</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -6149,10 +6336,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>675</v>
+        <v>721</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>675</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6160,10 +6347,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6171,10 +6358,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>677</v>
+        <v>723</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>677</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6182,10 +6369,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>678</v>
+        <v>724</v>
       </c>
       <c r="C9" t="s">
-        <v>678</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -6253,10 +6440,10 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>679</v>
+        <v>725</v>
       </c>
       <c r="D4" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6264,10 +6451,10 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>681</v>
+        <v>727</v>
       </c>
       <c r="D5" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6275,10 +6462,10 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>682</v>
+        <v>728</v>
       </c>
       <c r="D6" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6286,10 +6473,10 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>683</v>
+        <v>729</v>
       </c>
       <c r="D7" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6297,10 +6484,10 @@
         <v>100200002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>684</v>
+        <v>730</v>
       </c>
       <c r="D8" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6308,10 +6495,10 @@
         <v>100200003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>685</v>
+        <v>731</v>
       </c>
       <c r="D9" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6319,10 +6506,10 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>686</v>
+        <v>732</v>
       </c>
       <c r="D10" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6330,10 +6517,10 @@
         <v>100400001</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>687</v>
+        <v>733</v>
       </c>
       <c r="D11" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6341,10 +6528,10 @@
         <v>100401000</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>688</v>
+        <v>734</v>
       </c>
       <c r="D12" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6352,10 +6539,10 @@
         <v>100401001</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>689</v>
+        <v>735</v>
       </c>
       <c r="D13" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6363,10 +6550,10 @@
         <v>100402000</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>690</v>
+        <v>736</v>
       </c>
       <c r="D14" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6374,10 +6561,10 @@
         <v>100402001</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>691</v>
+        <v>737</v>
       </c>
       <c r="D15" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6385,10 +6572,10 @@
         <v>100403000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>692</v>
+        <v>738</v>
       </c>
       <c r="D16" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6396,10 +6583,10 @@
         <v>100403001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>693</v>
+        <v>739</v>
       </c>
       <c r="D17" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -6407,10 +6594,10 @@
         <v>100404001</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>690</v>
+        <v>736</v>
       </c>
       <c r="D18" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -6418,10 +6605,10 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>694</v>
+        <v>740</v>
       </c>
       <c r="D19" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6429,10 +6616,10 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>695</v>
+        <v>741</v>
       </c>
       <c r="D20" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6440,10 +6627,10 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>696</v>
+        <v>742</v>
       </c>
       <c r="D21" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -6451,10 +6638,10 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="D22" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6462,10 +6649,10 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>698</v>
+        <v>744</v>
       </c>
       <c r="D23" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6473,10 +6660,10 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="D24" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6484,10 +6671,10 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>700</v>
+        <v>746</v>
       </c>
       <c r="D25" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6495,10 +6682,10 @@
         <v>300100101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
       <c r="D26" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6506,10 +6693,10 @@
         <v>300100102</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>702</v>
+        <v>748</v>
       </c>
       <c r="D27" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6517,10 +6704,10 @@
         <v>300100201</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>703</v>
+        <v>749</v>
       </c>
       <c r="D28" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -6528,10 +6715,10 @@
         <v>300100301</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D29" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -6539,10 +6726,10 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="D30" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6550,10 +6737,10 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="D31" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6561,10 +6748,10 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>707</v>
+        <v>753</v>
       </c>
       <c r="D32" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -6572,10 +6759,10 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>708</v>
+        <v>754</v>
       </c>
       <c r="D33" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -6583,10 +6770,10 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>709</v>
+        <v>755</v>
       </c>
       <c r="D34" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -6594,10 +6781,10 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>710</v>
+        <v>756</v>
       </c>
       <c r="D35" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -6605,10 +6792,10 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>711</v>
+        <v>757</v>
       </c>
       <c r="D36" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -6616,10 +6803,10 @@
         <v>300200201</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>712</v>
+        <v>758</v>
       </c>
       <c r="D37" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -6627,10 +6814,10 @@
         <v>300200301</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>713</v>
+        <v>759</v>
       </c>
       <c r="D38" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -6638,10 +6825,10 @@
         <v>300300000</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>714</v>
+        <v>760</v>
       </c>
       <c r="D39" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -6649,10 +6836,10 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>715</v>
+        <v>761</v>
       </c>
       <c r="D40" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -6660,10 +6847,10 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>716</v>
+        <v>762</v>
       </c>
       <c r="D41" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -6671,10 +6858,10 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>717</v>
+        <v>763</v>
       </c>
       <c r="D42" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -6682,10 +6869,10 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>718</v>
+        <v>764</v>
       </c>
       <c r="D43" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -6693,10 +6880,10 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>719</v>
+        <v>765</v>
       </c>
       <c r="D44" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -6704,10 +6891,10 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>720</v>
+        <v>766</v>
       </c>
       <c r="D45" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -6715,10 +6902,10 @@
         <v>300300201</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>721</v>
+        <v>767</v>
       </c>
       <c r="D46" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -6726,10 +6913,10 @@
         <v>300300301</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>722</v>
+        <v>768</v>
       </c>
       <c r="D47" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -6737,10 +6924,10 @@
         <v>300400000</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>723</v>
+        <v>769</v>
       </c>
       <c r="D48" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -6748,10 +6935,10 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>724</v>
+        <v>770</v>
       </c>
       <c r="D49" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -6759,10 +6946,10 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="D50" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -6770,10 +6957,10 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
+        <v>772</v>
+      </c>
+      <c r="D51" t="s">
         <v>726</v>
-      </c>
-      <c r="D51" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -6781,10 +6968,10 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>727</v>
+        <v>773</v>
       </c>
       <c r="D52" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -6792,10 +6979,10 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>728</v>
+        <v>774</v>
       </c>
       <c r="D53" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6803,10 +6990,10 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>729</v>
+        <v>775</v>
       </c>
       <c r="D54" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -6814,10 +7001,10 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>730</v>
+        <v>776</v>
       </c>
       <c r="D55" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -6825,10 +7012,10 @@
         <v>300400201</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>731</v>
+        <v>777</v>
       </c>
       <c r="D56" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -6836,10 +7023,10 @@
         <v>300400301</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>732</v>
+        <v>778</v>
       </c>
       <c r="D57" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -6847,10 +7034,10 @@
         <v>300500000</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="D58" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -6858,10 +7045,10 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>734</v>
+        <v>780</v>
       </c>
       <c r="D59" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -6869,10 +7056,10 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>735</v>
+        <v>781</v>
       </c>
       <c r="D60" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -6880,10 +7067,10 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>736</v>
+        <v>782</v>
       </c>
       <c r="D61" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -6891,10 +7078,10 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>737</v>
+        <v>783</v>
       </c>
       <c r="D62" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -6902,10 +7089,10 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>738</v>
+        <v>784</v>
       </c>
       <c r="D63" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -6913,10 +7100,10 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>739</v>
+        <v>785</v>
       </c>
       <c r="D64" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -6924,10 +7111,10 @@
         <v>300500201</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>740</v>
+        <v>786</v>
       </c>
       <c r="D65" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -6935,10 +7122,10 @@
         <v>300500301</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>741</v>
+        <v>787</v>
       </c>
       <c r="D66" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -6946,10 +7133,10 @@
         <v>300600000</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>742</v>
+        <v>788</v>
       </c>
       <c r="D67" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -6957,10 +7144,10 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="D68" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -6968,10 +7155,10 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="D69" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -6979,10 +7166,10 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="D70" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -6990,10 +7177,10 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="D71" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -7001,10 +7188,10 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>747</v>
+        <v>793</v>
       </c>
       <c r="D72" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -7012,10 +7199,10 @@
         <v>300600101</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="D73" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -7023,10 +7210,10 @@
         <v>300600102</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="D74" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -7034,10 +7221,10 @@
         <v>300600201</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="D75" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -7045,10 +7232,10 @@
         <v>300600301</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="D76" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -7056,10 +7243,10 @@
         <v>300700000</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
       <c r="D77" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -7067,10 +7254,10 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>753</v>
+        <v>799</v>
       </c>
       <c r="D78" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -7078,10 +7265,10 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>754</v>
+        <v>800</v>
       </c>
       <c r="D79" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -7089,10 +7276,10 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="D80" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -7100,10 +7287,10 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>756</v>
+        <v>802</v>
       </c>
       <c r="D81" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -7111,10 +7298,10 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>757</v>
+        <v>803</v>
       </c>
       <c r="D82" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -7122,10 +7309,10 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="D83" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -7133,10 +7320,10 @@
         <v>300700201</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>759</v>
+        <v>805</v>
       </c>
       <c r="D84" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -7144,10 +7331,10 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="D85" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -9491,7 +9678,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="35.375" customWidth="1"/>
@@ -9751,443 +9938,793 @@
         <v>387</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" ht="14.25" spans="1:4">
       <c r="A23">
-        <v>12000400001</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
+        <v>12001100001</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>403</v>
       </c>
       <c r="D23" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" ht="14.25" spans="1:4">
       <c r="A24">
-        <v>12000500001</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
+        <v>12001200001</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>404</v>
       </c>
       <c r="D24" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" ht="14.25" spans="1:4">
       <c r="A25">
-        <v>12000600001</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
+        <v>12001300001</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>405</v>
       </c>
       <c r="D25" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" ht="14.25" spans="1:4">
       <c r="A26">
-        <v>12000700001</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
+        <v>12001400001</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>406</v>
       </c>
       <c r="D26" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" ht="17.25" spans="1:4">
       <c r="A27">
-        <v>13000100001</v>
-      </c>
-      <c r="B27" t="s">
-        <v>403</v>
+        <v>12002100001</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>408</v>
       </c>
       <c r="D27" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" ht="17.25" spans="1:4">
       <c r="A28">
-        <v>13000200001</v>
-      </c>
-      <c r="B28" t="s">
-        <v>404</v>
+        <v>12002200001</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>410</v>
       </c>
       <c r="D28" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" ht="17.25" spans="1:4">
       <c r="A29">
-        <v>13000300001</v>
-      </c>
-      <c r="B29" t="s">
-        <v>405</v>
+        <v>12002300001</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>412</v>
       </c>
       <c r="D29" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" ht="17.25" spans="1:4">
       <c r="A30">
-        <v>13000400001</v>
-      </c>
-      <c r="B30" t="s">
-        <v>406</v>
+        <v>12002400001</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>414</v>
       </c>
       <c r="D30" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" ht="17.25" spans="1:4">
       <c r="A31">
-        <v>13000500001</v>
-      </c>
-      <c r="B31" t="s">
-        <v>407</v>
+        <v>12003100001</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>416</v>
       </c>
       <c r="D31" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" ht="17.25" spans="1:4">
       <c r="A32">
-        <v>13000600001</v>
-      </c>
-      <c r="B32" t="s">
-        <v>408</v>
+        <v>12003200001</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>418</v>
       </c>
       <c r="D32" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" ht="17.25" spans="1:4">
       <c r="A33">
-        <v>13000700001</v>
-      </c>
-      <c r="B33" t="s">
-        <v>409</v>
+        <v>12003300001</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>420</v>
       </c>
       <c r="D33" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="10">
-        <v>10001000010000</v>
-      </c>
-      <c r="B34" t="s">
-        <v>410</v>
+    <row r="34" ht="17.25" spans="1:4">
+      <c r="A34">
+        <v>12003400001</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>422</v>
       </c>
       <c r="D34" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="10">
-        <v>10002000010000</v>
-      </c>
-      <c r="B35" t="s">
-        <v>410</v>
+    <row r="35" ht="17.25" spans="1:4">
+      <c r="A35">
+        <v>12010100001</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>424</v>
       </c>
       <c r="D35" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="10">
-        <v>10003000010000</v>
-      </c>
-      <c r="B36" t="s">
-        <v>411</v>
+    <row r="36" ht="17.25" spans="1:4">
+      <c r="A36">
+        <v>12010200001</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>426</v>
       </c>
       <c r="D36" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="10">
-        <v>10004000010000</v>
-      </c>
-      <c r="B37" t="s">
-        <v>411</v>
+    <row r="37" ht="17.25" spans="1:4">
+      <c r="A37">
+        <v>12010300001</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>428</v>
       </c>
       <c r="D37" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="10">
-        <v>10005000010000</v>
-      </c>
-      <c r="B38" t="s">
-        <v>411</v>
+    <row r="38" ht="17.25" spans="1:4">
+      <c r="A38">
+        <v>12011100001</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>430</v>
       </c>
       <c r="D38" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="10">
-        <v>20001000010000</v>
-      </c>
-      <c r="B39" t="s">
-        <v>412</v>
+    <row r="39" ht="17.25" spans="1:4">
+      <c r="A39">
+        <v>12011200001</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>432</v>
       </c>
       <c r="D39" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="10">
-        <v>20002000010000</v>
-      </c>
-      <c r="B40" t="s">
-        <v>413</v>
+    <row r="40" ht="17.25" spans="1:4">
+      <c r="A40">
+        <v>12011300001</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="D40" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="10">
-        <v>20003000010000</v>
+      <c r="A41">
+        <v>13000100001</v>
       </c>
       <c r="B41" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="D41" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="10">
-        <v>20004000010000</v>
+      <c r="A42">
+        <v>13000200001</v>
       </c>
       <c r="B42" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="D42" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="10">
-        <v>30001000010000</v>
+      <c r="A43">
+        <v>13000300001</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
+        <v>437</v>
       </c>
       <c r="D43" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="10">
-        <v>30002000010000</v>
+      <c r="A44">
+        <v>13000400001</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>438</v>
       </c>
       <c r="D44" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="10">
-        <v>30003000010000</v>
+      <c r="A45">
+        <v>13000500001</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>439</v>
       </c>
       <c r="D45" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="10">
-        <v>30004000010000</v>
+      <c r="A46">
+        <v>13000600001</v>
       </c>
       <c r="B46" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="D46" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="10">
-        <v>110001000010000</v>
+      <c r="A47">
+        <v>13000700001</v>
       </c>
       <c r="B47" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D47" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="10">
-        <v>110002000010000</v>
+      <c r="A48" s="13">
+        <v>10001000010000</v>
       </c>
       <c r="B48" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="D48" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="10">
-        <v>110003000010000</v>
+      <c r="A49" s="13">
+        <v>10002000010000</v>
       </c>
       <c r="B49" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="D49" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="10">
-        <v>120001000010000</v>
+      <c r="A50" s="13">
+        <v>10003000010000</v>
       </c>
       <c r="B50" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="D50" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="10">
-        <v>120002000010000</v>
+      <c r="A51" s="13">
+        <v>10004000010000</v>
       </c>
       <c r="B51" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="D51" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="10">
-        <v>120003000010000</v>
+      <c r="A52" s="13">
+        <v>10005000010000</v>
       </c>
       <c r="B52" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="D52" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="10">
-        <v>120004000010000</v>
+      <c r="A53" s="13">
+        <v>20001000010000</v>
       </c>
       <c r="B53" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D53" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="10">
-        <v>120005000010000</v>
+      <c r="A54" s="13">
+        <v>20002000010000</v>
       </c>
       <c r="B54" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="D54" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="10">
-        <v>120006000010000</v>
+      <c r="A55" s="13">
+        <v>20003000010000</v>
       </c>
       <c r="B55" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="D55" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="10">
-        <v>120007000010000</v>
+      <c r="A56" s="13">
+        <v>20004000010000</v>
       </c>
       <c r="B56" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D56" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="10">
-        <v>130001000010000</v>
+      <c r="A57" s="13">
+        <v>30001000010000</v>
       </c>
       <c r="B57" t="s">
-        <v>427</v>
+        <v>204</v>
       </c>
       <c r="D57" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="10">
-        <v>130003000010000</v>
+      <c r="A58" s="13">
+        <v>30002000010000</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>208</v>
       </c>
       <c r="D58" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="10">
-        <v>130004000010000</v>
+      <c r="A59" s="13">
+        <v>30003000010000</v>
       </c>
       <c r="B59" t="s">
-        <v>429</v>
+        <v>210</v>
       </c>
       <c r="D59" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="10">
-        <v>130005000010000</v>
+      <c r="A60" s="13">
+        <v>30004000010000</v>
       </c>
       <c r="B60" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D60" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="10">
-        <v>130006000010000</v>
+      <c r="A61" s="13">
+        <v>110001000010000</v>
       </c>
       <c r="B61" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="D61" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="10">
+      <c r="A62" s="13">
+        <v>110002000010000</v>
+      </c>
+      <c r="B62" t="s">
+        <v>450</v>
+      </c>
+      <c r="D62" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="13">
+        <v>110003000010000</v>
+      </c>
+      <c r="B63" t="s">
+        <v>451</v>
+      </c>
+      <c r="D63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="13">
+        <v>120001000010000</v>
+      </c>
+      <c r="B64" t="s">
+        <v>452</v>
+      </c>
+      <c r="D64" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="13">
+        <v>120002000010000</v>
+      </c>
+      <c r="B65" t="s">
+        <v>453</v>
+      </c>
+      <c r="D65" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="13">
+        <v>120003000010000</v>
+      </c>
+      <c r="B66" t="s">
+        <v>454</v>
+      </c>
+      <c r="D66" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="13">
+        <v>120011000010000</v>
+      </c>
+      <c r="B67" t="s">
+        <v>455</v>
+      </c>
+      <c r="D67" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="13">
+        <v>120012000010000</v>
+      </c>
+      <c r="B68" t="s">
+        <v>456</v>
+      </c>
+      <c r="D68" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="13">
+        <v>120013000010000</v>
+      </c>
+      <c r="B69" t="s">
+        <v>457</v>
+      </c>
+      <c r="D69" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="13">
+        <v>120014000010000</v>
+      </c>
+      <c r="B70" t="s">
+        <v>458</v>
+      </c>
+      <c r="D70" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="13">
+        <v>120021000010000</v>
+      </c>
+      <c r="B71" t="s">
+        <v>459</v>
+      </c>
+      <c r="D71" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="13">
+        <v>120022000010000</v>
+      </c>
+      <c r="B72" t="s">
+        <v>460</v>
+      </c>
+      <c r="D72" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="13">
+        <v>120023000010000</v>
+      </c>
+      <c r="B73" t="s">
+        <v>461</v>
+      </c>
+      <c r="D73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="13">
+        <v>120024000010000</v>
+      </c>
+      <c r="B74" t="s">
+        <v>462</v>
+      </c>
+      <c r="D74" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="13">
+        <v>120031000010000</v>
+      </c>
+      <c r="B75" t="s">
+        <v>463</v>
+      </c>
+      <c r="D75" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="13">
+        <v>120032000010000</v>
+      </c>
+      <c r="B76" t="s">
+        <v>464</v>
+      </c>
+      <c r="D76" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="13">
+        <v>120033000010000</v>
+      </c>
+      <c r="B77" t="s">
+        <v>465</v>
+      </c>
+      <c r="D77" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="13">
+        <v>120034000010000</v>
+      </c>
+      <c r="B78" t="s">
+        <v>466</v>
+      </c>
+      <c r="D78" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="13">
+        <v>120101000010000</v>
+      </c>
+      <c r="B79" t="s">
+        <v>467</v>
+      </c>
+      <c r="D79" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="13">
+        <v>120102000010000</v>
+      </c>
+      <c r="B80" t="s">
+        <v>468</v>
+      </c>
+      <c r="D80" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="13">
+        <v>120103000010000</v>
+      </c>
+      <c r="B81" t="s">
+        <v>469</v>
+      </c>
+      <c r="D81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="13">
+        <v>120111000010000</v>
+      </c>
+      <c r="B82" t="s">
+        <v>470</v>
+      </c>
+      <c r="D82" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="13">
+        <v>120112000010000</v>
+      </c>
+      <c r="B83" t="s">
+        <v>471</v>
+      </c>
+      <c r="D83" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="13">
+        <v>120113000010000</v>
+      </c>
+      <c r="B84" t="s">
+        <v>472</v>
+      </c>
+      <c r="D84" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="13">
+        <v>130001000010000</v>
+      </c>
+      <c r="B85" t="s">
+        <v>473</v>
+      </c>
+      <c r="D85" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="13">
+        <v>130003000010000</v>
+      </c>
+      <c r="B86" t="s">
+        <v>474</v>
+      </c>
+      <c r="D86" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="13">
+        <v>130004000010000</v>
+      </c>
+      <c r="B87" t="s">
+        <v>475</v>
+      </c>
+      <c r="D87" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="13">
+        <v>130005000010000</v>
+      </c>
+      <c r="B88" t="s">
+        <v>476</v>
+      </c>
+      <c r="D88" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="13">
+        <v>130006000010000</v>
+      </c>
+      <c r="B89" t="s">
+        <v>477</v>
+      </c>
+      <c r="D89" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="13">
         <v>130007000010000</v>
       </c>
-      <c r="B62" t="s">
-        <v>432</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="B90" t="s">
+        <v>478</v>
+      </c>
+      <c r="D90" t="s">
         <v>387</v>
       </c>
     </row>
@@ -10256,10 +10793,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>433</v>
+        <v>479</v>
       </c>
       <c r="D4" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10267,10 +10804,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="D5" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10278,10 +10815,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="D6" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10289,10 +10826,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>437</v>
+        <v>483</v>
       </c>
       <c r="D7" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10300,10 +10837,10 @@
         <v>100001</v>
       </c>
       <c r="B8" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="D8" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10311,10 +10848,10 @@
         <v>100002</v>
       </c>
       <c r="B9" t="s">
-        <v>439</v>
+        <v>485</v>
       </c>
       <c r="D9" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10322,10 +10859,10 @@
         <v>100003</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="D10" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10333,10 +10870,10 @@
         <v>100004</v>
       </c>
       <c r="B11" t="s">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="D11" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10344,10 +10881,10 @@
         <v>200001</v>
       </c>
       <c r="B12" t="s">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="D12" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10355,10 +10892,10 @@
         <v>200002</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="D13" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10366,10 +10903,10 @@
         <v>200003</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="D14" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10377,10 +10914,10 @@
         <v>200004</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>445</v>
+        <v>491</v>
       </c>
       <c r="D15" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10388,10 +10925,10 @@
         <v>200005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>446</v>
+        <v>492</v>
       </c>
       <c r="D16" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10399,10 +10936,10 @@
         <v>200006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>447</v>
+        <v>493</v>
       </c>
       <c r="D17" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -10410,10 +10947,10 @@
         <v>200007</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>448</v>
+        <v>494</v>
       </c>
       <c r="D18" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -10421,10 +10958,10 @@
         <v>200008</v>
       </c>
       <c r="B19" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="D19" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -10432,10 +10969,10 @@
         <v>200009</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="D20" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -10443,10 +10980,10 @@
         <v>200010</v>
       </c>
       <c r="B21" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="D21" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -10454,10 +10991,10 @@
         <v>200011</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="D22" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -10465,10 +11002,10 @@
         <v>200012</v>
       </c>
       <c r="B23" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="D23" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -10476,10 +11013,10 @@
         <v>200013</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="D24" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -10487,10 +11024,10 @@
         <v>200014</v>
       </c>
       <c r="B25" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="D25" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -10558,13 +11095,13 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="C4" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
       <c r="D4" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10572,13 +11109,13 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
       <c r="C5" t="s">
-        <v>460</v>
+        <v>506</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10586,13 +11123,13 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="C6" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c r="D6" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10600,13 +11137,13 @@
         <v>20001</v>
       </c>
       <c r="B7" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="C7" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="D7" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10614,13 +11151,13 @@
         <v>20002</v>
       </c>
       <c r="B8" t="s">
-        <v>465</v>
+        <v>511</v>
       </c>
       <c r="C8" t="s">
-        <v>466</v>
+        <v>512</v>
       </c>
       <c r="D8" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10628,13 +11165,13 @@
         <v>20003</v>
       </c>
       <c r="B9" t="s">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="D9" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10642,13 +11179,13 @@
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>516</v>
       </c>
       <c r="D10" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10656,13 +11193,13 @@
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>518</v>
       </c>
       <c r="D11" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10670,13 +11207,13 @@
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>473</v>
+        <v>519</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="D12" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10684,13 +11221,13 @@
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>475</v>
+        <v>521</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="D13" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10698,13 +11235,13 @@
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>477</v>
+        <v>523</v>
       </c>
       <c r="C14" t="s">
-        <v>478</v>
+        <v>524</v>
       </c>
       <c r="D14" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10712,13 +11249,13 @@
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>479</v>
+        <v>525</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>526</v>
       </c>
       <c r="D15" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10726,13 +11263,13 @@
         <v>50001</v>
       </c>
       <c r="B16" t="s">
-        <v>481</v>
+        <v>527</v>
       </c>
       <c r="C16" t="s">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="D16" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10740,13 +11277,13 @@
         <v>50002</v>
       </c>
       <c r="B17" t="s">
-        <v>483</v>
+        <v>529</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>530</v>
       </c>
       <c r="D17" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -10754,13 +11291,13 @@
         <v>50003</v>
       </c>
       <c r="B18" t="s">
-        <v>485</v>
+        <v>531</v>
       </c>
       <c r="C18" t="s">
-        <v>486</v>
+        <v>532</v>
       </c>
       <c r="D18" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -10768,13 +11305,13 @@
         <v>60001</v>
       </c>
       <c r="B19" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="C19" t="s">
-        <v>488</v>
+        <v>534</v>
       </c>
       <c r="D19" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -10782,13 +11319,13 @@
         <v>60002</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
       <c r="C20" t="s">
-        <v>490</v>
+        <v>536</v>
       </c>
       <c r="D20" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -10796,13 +11333,13 @@
         <v>60003</v>
       </c>
       <c r="B21" t="s">
-        <v>491</v>
+        <v>537</v>
       </c>
       <c r="C21" t="s">
-        <v>492</v>
+        <v>538</v>
       </c>
       <c r="D21" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -10810,13 +11347,13 @@
         <v>70001</v>
       </c>
       <c r="B22" t="s">
-        <v>493</v>
+        <v>539</v>
       </c>
       <c r="C22" t="s">
-        <v>494</v>
+        <v>540</v>
       </c>
       <c r="D22" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -10824,13 +11361,13 @@
         <v>70002</v>
       </c>
       <c r="B23" t="s">
-        <v>495</v>
+        <v>541</v>
       </c>
       <c r="C23" t="s">
-        <v>496</v>
+        <v>542</v>
       </c>
       <c r="D23" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -10838,13 +11375,13 @@
         <v>70003</v>
       </c>
       <c r="B24" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="C24" t="s">
-        <v>498</v>
+        <v>544</v>
       </c>
       <c r="D24" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -10912,13 +11449,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>499</v>
+        <v>545</v>
       </c>
       <c r="C4" t="s">
-        <v>500</v>
+        <v>546</v>
       </c>
       <c r="D4" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10926,10 +11463,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>502</v>
+        <v>548</v>
       </c>
       <c r="D5" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10937,10 +11474,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="D6" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10948,10 +11485,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>504</v>
+        <v>550</v>
       </c>
       <c r="D7" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -11019,13 +11556,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>505</v>
+        <v>551</v>
       </c>
       <c r="C4" t="s">
-        <v>506</v>
+        <v>552</v>
       </c>
       <c r="D4" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -11033,13 +11570,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>508</v>
+        <v>554</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="D5" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -11047,13 +11584,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>510</v>
+        <v>556</v>
       </c>
       <c r="C6" t="s">
-        <v>511</v>
+        <v>557</v>
       </c>
       <c r="D6" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -11061,13 +11598,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>512</v>
+        <v>558</v>
       </c>
       <c r="C7" t="s">
-        <v>513</v>
+        <v>559</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -11075,13 +11612,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
       <c r="C8" t="s">
-        <v>515</v>
+        <v>561</v>
       </c>
       <c r="D8" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11089,13 +11626,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="C9" t="s">
-        <v>517</v>
+        <v>563</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -11103,13 +11640,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>518</v>
+        <v>564</v>
       </c>
       <c r="C10" t="s">
-        <v>519</v>
+        <v>565</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11117,13 +11654,13 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="C11" t="s">
-        <v>521</v>
+        <v>567</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11131,13 +11668,13 @@
         <v>1002</v>
       </c>
       <c r="B12" t="s">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="C12" t="s">
-        <v>523</v>
+        <v>569</v>
       </c>
       <c r="D12" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -11145,13 +11682,13 @@
         <v>1003</v>
       </c>
       <c r="B13" t="s">
-        <v>524</v>
+        <v>570</v>
       </c>
       <c r="C13" t="s">
-        <v>525</v>
+        <v>571</v>
       </c>
       <c r="D13" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -11159,13 +11696,13 @@
         <v>1004</v>
       </c>
       <c r="B14" t="s">
-        <v>526</v>
+        <v>572</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="D14" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -11173,13 +11710,13 @@
         <v>2001</v>
       </c>
       <c r="B15" t="s">
-        <v>528</v>
+        <v>574</v>
       </c>
       <c r="C15" t="s">
-        <v>529</v>
+        <v>575</v>
       </c>
       <c r="D15" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -11187,13 +11724,13 @@
         <v>2002</v>
       </c>
       <c r="B16" t="s">
-        <v>530</v>
+        <v>576</v>
       </c>
       <c r="C16" t="s">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="D16" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -11201,13 +11738,13 @@
         <v>2003</v>
       </c>
       <c r="B17" t="s">
-        <v>532</v>
+        <v>578</v>
       </c>
       <c r="C17" t="s">
-        <v>533</v>
+        <v>579</v>
       </c>
       <c r="D17" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -11215,13 +11752,13 @@
         <v>2004</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>580</v>
       </c>
       <c r="C18" t="s">
-        <v>535</v>
+        <v>581</v>
       </c>
       <c r="D18" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -11229,13 +11766,13 @@
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>536</v>
+        <v>582</v>
       </c>
       <c r="C19" t="s">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="D19" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -11243,13 +11780,13 @@
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>538</v>
+        <v>584</v>
       </c>
       <c r="C20" t="s">
-        <v>539</v>
+        <v>585</v>
       </c>
       <c r="D20" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -11257,13 +11794,13 @@
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>540</v>
+        <v>586</v>
       </c>
       <c r="C21" t="s">
-        <v>541</v>
+        <v>587</v>
       </c>
       <c r="D21" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -11271,13 +11808,13 @@
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>542</v>
+        <v>588</v>
       </c>
       <c r="C22" t="s">
-        <v>543</v>
+        <v>589</v>
       </c>
       <c r="D22" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -11285,13 +11822,13 @@
         <v>4001</v>
       </c>
       <c r="B23" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="C23" t="s">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="D23" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -11299,13 +11836,13 @@
         <v>4002</v>
       </c>
       <c r="B24" t="s">
-        <v>546</v>
+        <v>592</v>
       </c>
       <c r="C24" t="s">
-        <v>547</v>
+        <v>593</v>
       </c>
       <c r="D24" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -11313,13 +11850,13 @@
         <v>4003</v>
       </c>
       <c r="B25" t="s">
-        <v>548</v>
+        <v>594</v>
       </c>
       <c r="C25" t="s">
-        <v>549</v>
+        <v>595</v>
       </c>
       <c r="D25" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -11327,13 +11864,13 @@
         <v>4004</v>
       </c>
       <c r="B26" t="s">
-        <v>550</v>
+        <v>596</v>
       </c>
       <c r="C26" t="s">
-        <v>551</v>
+        <v>597</v>
       </c>
       <c r="D26" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -11341,13 +11878,13 @@
         <v>4005</v>
       </c>
       <c r="B27" t="s">
-        <v>552</v>
+        <v>598</v>
       </c>
       <c r="C27" t="s">
+        <v>599</v>
+      </c>
+      <c r="D27" t="s">
         <v>553</v>
-      </c>
-      <c r="D27" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -11355,13 +11892,13 @@
         <v>5001</v>
       </c>
       <c r="B28" t="s">
-        <v>554</v>
+        <v>600</v>
       </c>
       <c r="C28" t="s">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="D28" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -11369,13 +11906,13 @@
         <v>5002</v>
       </c>
       <c r="B29" t="s">
-        <v>556</v>
+        <v>602</v>
       </c>
       <c r="C29" t="s">
-        <v>557</v>
+        <v>603</v>
       </c>
       <c r="D29" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -11383,13 +11920,13 @@
         <v>5003</v>
       </c>
       <c r="B30" t="s">
-        <v>558</v>
+        <v>604</v>
       </c>
       <c r="C30" t="s">
-        <v>559</v>
+        <v>605</v>
       </c>
       <c r="D30" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -11397,13 +11934,13 @@
         <v>5004</v>
       </c>
       <c r="B31" t="s">
-        <v>560</v>
+        <v>606</v>
       </c>
       <c r="C31" t="s">
-        <v>561</v>
+        <v>607</v>
       </c>
       <c r="D31" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -11411,13 +11948,13 @@
         <v>6001</v>
       </c>
       <c r="B32" t="s">
-        <v>562</v>
+        <v>608</v>
       </c>
       <c r="C32" t="s">
-        <v>563</v>
+        <v>609</v>
       </c>
       <c r="D32" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -11425,13 +11962,13 @@
         <v>6002</v>
       </c>
       <c r="B33" t="s">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="C33" t="s">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="D33" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -11439,13 +11976,13 @@
         <v>6003</v>
       </c>
       <c r="B34" t="s">
-        <v>566</v>
+        <v>612</v>
       </c>
       <c r="C34" t="s">
-        <v>567</v>
+        <v>613</v>
       </c>
       <c r="D34" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -11453,13 +11990,13 @@
         <v>6004</v>
       </c>
       <c r="B35" t="s">
-        <v>568</v>
+        <v>614</v>
       </c>
       <c r="C35" t="s">
-        <v>569</v>
+        <v>615</v>
       </c>
       <c r="D35" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -11467,13 +12004,13 @@
         <v>6005</v>
       </c>
       <c r="B36" t="s">
-        <v>570</v>
+        <v>616</v>
       </c>
       <c r="C36" t="s">
-        <v>571</v>
+        <v>617</v>
       </c>
       <c r="D36" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -11481,13 +12018,13 @@
         <v>7001</v>
       </c>
       <c r="B37" t="s">
-        <v>572</v>
+        <v>618</v>
       </c>
       <c r="C37" t="s">
-        <v>573</v>
+        <v>619</v>
       </c>
       <c r="D37" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -11495,13 +12032,13 @@
         <v>7002</v>
       </c>
       <c r="B38" t="s">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="C38" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="D38" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -11509,13 +12046,13 @@
         <v>7003</v>
       </c>
       <c r="B39" t="s">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="C39" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="D39" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -11523,13 +12060,13 @@
         <v>7004</v>
       </c>
       <c r="B40" t="s">
-        <v>578</v>
+        <v>624</v>
       </c>
       <c r="C40" t="s">
-        <v>579</v>
+        <v>625</v>
       </c>
       <c r="D40" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -11537,13 +12074,13 @@
         <v>101001</v>
       </c>
       <c r="B41" t="s">
-        <v>580</v>
+        <v>626</v>
       </c>
       <c r="C41" t="s">
-        <v>521</v>
+        <v>567</v>
       </c>
       <c r="D41" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -11551,13 +12088,13 @@
         <v>102001</v>
       </c>
       <c r="B42" t="s">
-        <v>581</v>
+        <v>627</v>
       </c>
       <c r="C42" t="s">
-        <v>523</v>
+        <v>569</v>
       </c>
       <c r="D42" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -11565,13 +12102,13 @@
         <v>103001</v>
       </c>
       <c r="B43" t="s">
-        <v>582</v>
+        <v>628</v>
       </c>
       <c r="C43" t="s">
-        <v>525</v>
+        <v>571</v>
       </c>
       <c r="D43" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -11579,13 +12116,13 @@
         <v>103002</v>
       </c>
       <c r="B44" t="s">
-        <v>583</v>
+        <v>629</v>
       </c>
       <c r="C44" t="s">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="D44" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -11593,13 +12130,13 @@
         <v>900001</v>
       </c>
       <c r="B45" t="s">
-        <v>584</v>
+        <v>630</v>
       </c>
       <c r="C45" t="s">
-        <v>585</v>
+        <v>631</v>
       </c>
       <c r="D45" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -11607,13 +12144,13 @@
         <v>900002</v>
       </c>
       <c r="B46" t="s">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="C46" t="s">
-        <v>587</v>
+        <v>633</v>
       </c>
       <c r="D46" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="723"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="9" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="1308">
   <si>
     <t>id</t>
   </si>
@@ -3001,15 +3001,27 @@
     <t>生命</t>
   </si>
   <si>
-    <t>魔法</t>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>魔力</t>
+  </si>
+  <si>
+    <t>MP</t>
   </si>
   <si>
     <t>护甲</t>
   </si>
   <si>
+    <t>DR</t>
+  </si>
+  <si>
     <t>攻击力</t>
   </si>
   <si>
+    <t>ATK</t>
+  </si>
+  <si>
     <t>移动速度</t>
   </si>
   <si>
@@ -3020,6 +3032,18 @@
   </si>
   <si>
     <t>复活CD</t>
+  </si>
+  <si>
+    <t>魔力回复%</t>
+  </si>
+  <si>
+    <t>MPR</t>
+  </si>
+  <si>
+    <t>魔力回复</t>
+  </si>
+  <si>
+    <t>MPF</t>
   </si>
   <si>
     <t>没头脑</t>
@@ -7315,8 +7339,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="26.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -7367,7 +7395,9 @@
       <c r="B4" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="C4"/>
+      <c r="C4" t="s">
+        <v>985</v>
+      </c>
       <c r="D4" t="s">
         <v>903</v>
       </c>
@@ -7376,10 +7406,12 @@
       <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>985</v>
-      </c>
-      <c r="C5"/>
+      <c r="B5" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="C5" t="s">
+        <v>987</v>
+      </c>
       <c r="D5" t="s">
         <v>903</v>
       </c>
@@ -7389,9 +7421,11 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>986</v>
-      </c>
-      <c r="C6"/>
+        <v>988</v>
+      </c>
+      <c r="C6" t="s">
+        <v>989</v>
+      </c>
       <c r="D6" t="s">
         <v>903</v>
       </c>
@@ -7401,9 +7435,11 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>987</v>
-      </c>
-      <c r="C7"/>
+        <v>990</v>
+      </c>
+      <c r="C7" t="s">
+        <v>991</v>
+      </c>
       <c r="D7" t="s">
         <v>903</v>
       </c>
@@ -7413,9 +7449,8 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>988</v>
-      </c>
-      <c r="C8"/>
+        <v>992</v>
+      </c>
       <c r="D8" t="s">
         <v>903</v>
       </c>
@@ -7425,9 +7460,8 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>989</v>
-      </c>
-      <c r="C9"/>
+        <v>993</v>
+      </c>
       <c r="D9" t="s">
         <v>903</v>
       </c>
@@ -7437,9 +7471,8 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>990</v>
-      </c>
-      <c r="C10"/>
+        <v>994</v>
+      </c>
       <c r="D10" t="s">
         <v>903</v>
       </c>
@@ -7460,9 +7493,37 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="D12" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" spans="1:4">
+      <c r="A13" s="9">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D13" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" spans="1:4">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="D14" t="s">
         <v>903</v>
       </c>
     </row>
@@ -7530,10 +7591,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="C4" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7541,10 +7602,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7552,10 +7613,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C6" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7563,10 +7624,10 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="C7" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7574,10 +7635,10 @@
         <v>1020010001</v>
       </c>
       <c r="B8" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="C8" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7585,10 +7646,10 @@
         <v>1030010001</v>
       </c>
       <c r="B9" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="C9" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7596,10 +7657,10 @@
         <v>1030020001</v>
       </c>
       <c r="B10" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="C10" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:4">
@@ -7607,10 +7668,10 @@
         <v>2000000001</v>
       </c>
       <c r="B11" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="C11" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7618,10 +7679,10 @@
         <v>2000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="C12" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -7687,10 +7748,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="C4" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -7698,10 +7759,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="C5" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -7709,10 +7770,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="C6" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -7720,10 +7781,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C7" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -7731,10 +7792,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="C8" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -7742,10 +7803,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="C9" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -7753,10 +7814,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="C10" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -7764,10 +7825,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C11" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -7775,10 +7836,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="C12" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -7786,10 +7847,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="C13" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -7797,10 +7858,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C14" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -7808,10 +7869,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C15" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -7819,10 +7880,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="C16" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7830,10 +7891,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="C17" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7841,10 +7902,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C18" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7852,10 +7913,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="C19" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7863,10 +7924,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C20" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7874,10 +7935,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C21" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7885,10 +7946,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C22" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7896,10 +7957,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C23" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7907,10 +7968,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="C24" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7918,10 +7979,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="C25" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7929,10 +7990,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C26" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7940,10 +8001,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="C27" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7951,10 +8012,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C28" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7962,10 +8023,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C29" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7973,10 +8034,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="C30" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7984,10 +8045,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C31" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7995,10 +8056,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="C32" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8006,10 +8067,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="C33" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8017,10 +8078,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="C34" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -8087,10 +8148,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="C4" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8098,10 +8159,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="C5" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8109,10 +8170,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="C6" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8120,10 +8181,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C7" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8131,10 +8192,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C8" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8142,10 +8203,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C9" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8153,10 +8214,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8164,10 +8225,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C11" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8175,10 +8236,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C12" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8186,10 +8247,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C13" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8197,10 +8258,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C14" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8208,10 +8269,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C15" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8219,10 +8280,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C16" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -8287,10 +8348,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C4" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8298,10 +8359,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C5" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8309,10 +8370,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8320,10 +8381,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C7" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8331,10 +8392,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="C8" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -8400,10 +8461,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8411,10 +8472,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8422,10 +8483,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8433,10 +8494,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8444,10 +8505,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8455,10 +8516,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8466,10 +8527,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8477,10 +8538,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8488,10 +8549,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8499,10 +8560,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
@@ -8568,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8579,7 +8640,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8590,10 +8651,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8601,10 +8662,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8612,10 +8673,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8623,10 +8684,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="C9" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>
@@ -8694,13 +8755,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="C4" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="D4" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8708,13 +8769,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="D5" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8722,13 +8783,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="C6" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8736,13 +8797,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="C7" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="D7" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8750,13 +8811,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="C8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D8" t="s">
         <v>1147</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8764,13 +8825,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="C9" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="D9" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8778,13 +8839,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="C10" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="D10" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8792,13 +8853,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="C11" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="D11" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8806,13 +8867,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="C12" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="D12" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8820,13 +8881,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="C13" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="D13" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8834,13 +8895,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="C14" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="D14" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8848,13 +8909,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="C15" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D15" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8862,13 +8923,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="C16" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="D16" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8876,13 +8937,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="C17" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D17" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -8890,13 +8951,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="C18" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="D18" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -8904,13 +8965,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C19" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="D19" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -8918,13 +8979,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C20" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D20" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -8932,13 +8993,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C21" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D21" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -8946,13 +9007,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="C22" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="D22" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -8960,13 +9021,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="C23" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D23" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -8974,13 +9035,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="C24" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D24" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -8988,13 +9049,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="C25" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="D25" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9002,13 +9063,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="C26" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D26" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9016,13 +9077,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C27" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D27" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9030,13 +9091,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="C28" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D28" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9044,13 +9105,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C29" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D29" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9058,13 +9119,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C30" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D30" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9072,13 +9133,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C31" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D31" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9086,13 +9147,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="C32" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="D32" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9100,13 +9161,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="C33" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="D33" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9114,13 +9175,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="C34" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="D34" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9128,13 +9189,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="C35" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="D35" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9142,13 +9203,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="C36" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D36" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9156,13 +9217,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="C37" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D37" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9170,13 +9231,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="C38" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="D38" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9184,13 +9245,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="C39" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D39" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9198,13 +9259,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="C40" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="D40" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9212,13 +9273,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="C41" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="D41" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9226,13 +9287,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="C42" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="D42" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9240,13 +9301,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="C43" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="D43" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9254,13 +9315,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="C44" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D44" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9268,13 +9329,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="C45" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="D45" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9282,13 +9343,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="C46" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="D46" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9296,13 +9357,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="C47" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="D47" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9310,13 +9371,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="C48" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D48" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9324,13 +9385,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="C49" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="D49" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9338,13 +9399,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="C50" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="D50" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9352,13 +9413,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C51" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D51" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9366,13 +9427,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="C52" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="D52" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9380,13 +9441,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="C53" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="D53" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9394,13 +9455,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="C54" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="D54" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9408,13 +9469,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="C55" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="D55" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9422,13 +9483,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="C56" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="D56" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9436,13 +9497,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="C57" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="D57" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9450,13 +9511,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="C58" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="D58" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9464,13 +9525,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="C59" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D59" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9478,13 +9539,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="C60" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="D60" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9492,13 +9553,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="C61" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="D61" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9506,13 +9567,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="C62" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="D62" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9520,13 +9581,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="C63" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="D63" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9534,13 +9595,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="C64" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="D64" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9548,13 +9609,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="C65" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="D65" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9562,13 +9623,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="C66" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D66" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9576,13 +9637,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="C67" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="D67" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9590,13 +9651,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C68" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="D68" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9604,13 +9665,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C69" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="D69" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9618,13 +9679,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="C70" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="D70" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9632,13 +9693,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="C71" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="D71" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9646,13 +9707,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="C72" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="D72" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9660,13 +9721,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="C73" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="D73" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9674,13 +9735,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="C74" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="D74" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9688,13 +9749,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="C75" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="D75" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9702,13 +9763,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="C76" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="D76" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9716,13 +9777,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="C77" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="D77" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9730,13 +9791,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="C78" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="D78" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9744,13 +9805,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="C79" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="D79" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9758,13 +9819,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="C80" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="D80" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9772,13 +9833,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="C81" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D81" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9786,13 +9847,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="C82" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="D82" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9800,13 +9861,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="C83" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="D83" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -9814,13 +9875,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="C84" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D84" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -9828,13 +9889,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="C85" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="D85" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="9" activeTab="10"/>
+    <workbookView windowHeight="17655" tabRatio="723" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="1310">
   <si>
     <t>id</t>
   </si>
@@ -1013,6 +1013,12 @@
   </si>
   <si>
     <t>Weapon</t>
+  </si>
+  <si>
+    <t>肖像</t>
+  </si>
+  <si>
+    <t>Portrait</t>
   </si>
   <si>
     <t>Crystal</t>
@@ -7237,13 +7243,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7251,13 +7257,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C5" t="s">
+        <v>907</v>
+      </c>
+      <c r="D5" t="s">
         <v>905</v>
-      </c>
-      <c r="D5" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7265,13 +7271,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C6" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D6" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7279,13 +7285,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C7" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D7" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7293,13 +7299,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C8" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D8" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7307,13 +7313,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C9" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D9" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7321,13 +7327,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C10" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D10" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -7393,13 +7399,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7407,13 +7413,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C5" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D5" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7421,13 +7427,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D6" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7435,13 +7441,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C7" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D7" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7449,10 +7455,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D8" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7460,10 +7466,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D9" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7471,10 +7477,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D10" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7482,10 +7488,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D11" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:4">
@@ -7493,10 +7499,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D12" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:4">
@@ -7504,13 +7510,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D13" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:4">
@@ -7518,13 +7524,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -7591,10 +7597,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7602,10 +7608,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C5" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7613,10 +7619,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C6" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7624,10 +7630,10 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C7" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7635,10 +7641,10 @@
         <v>1020010001</v>
       </c>
       <c r="B8" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C8" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7646,10 +7652,10 @@
         <v>1030010001</v>
       </c>
       <c r="B9" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C9" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7657,10 +7663,10 @@
         <v>1030020001</v>
       </c>
       <c r="B10" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C10" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:4">
@@ -7668,10 +7674,10 @@
         <v>2000000001</v>
       </c>
       <c r="B11" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C11" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7679,10 +7685,10 @@
         <v>2000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C12" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -7748,10 +7754,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -7759,10 +7765,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C5" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -7770,10 +7776,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -7781,10 +7787,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C7" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -7792,10 +7798,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C8" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -7803,10 +7809,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C9" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -7814,10 +7820,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C10" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -7825,10 +7831,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C11" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -7836,10 +7842,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C12" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -7847,10 +7853,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C13" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -7858,10 +7864,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C14" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -7869,10 +7875,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C15" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -7880,10 +7886,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C16" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7891,10 +7897,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C17" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7902,10 +7908,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C18" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7913,10 +7919,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C19" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7924,10 +7930,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C20" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7935,10 +7941,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C21" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7946,10 +7952,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C22" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7957,10 +7963,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C23" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7968,10 +7974,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C24" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7979,10 +7985,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C25" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7990,10 +7996,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C26" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8001,10 +8007,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C27" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8012,10 +8018,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C28" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8023,10 +8029,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C29" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8034,10 +8040,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C30" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8045,10 +8051,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C31" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8056,10 +8062,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C32" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8067,10 +8073,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C33" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8078,10 +8084,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C34" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -8148,10 +8154,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8159,10 +8165,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8170,10 +8176,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C6" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8181,10 +8187,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8192,10 +8198,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C8" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8203,10 +8209,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C9" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8214,10 +8220,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8225,10 +8231,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C11" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8236,10 +8242,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C12" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8247,10 +8253,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C13" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8258,10 +8264,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C14" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8269,10 +8275,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8280,10 +8286,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C16" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -8348,10 +8354,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8359,10 +8365,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8370,10 +8376,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8381,10 +8387,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C7" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8392,10 +8398,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C8" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -8461,10 +8467,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C4" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8472,10 +8478,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8483,10 +8489,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8494,10 +8500,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8505,10 +8511,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8516,10 +8522,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8527,10 +8533,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8538,10 +8544,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8549,10 +8555,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8560,10 +8566,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -8629,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8640,7 +8646,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8651,10 +8657,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8662,10 +8668,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8673,10 +8679,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8684,10 +8690,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="C9" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -8755,13 +8761,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C4" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D4" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8769,13 +8775,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D5" t="s">
         <v>1149</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8783,13 +8789,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D6" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8797,13 +8803,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D7" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8811,13 +8817,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C8" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D8" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8825,13 +8831,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C9" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D9" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8839,13 +8845,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="C10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8853,13 +8859,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C11" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D11" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8867,13 +8873,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C12" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D12" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8881,13 +8887,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C13" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D13" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8895,13 +8901,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C14" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D14" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8909,13 +8915,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C15" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D15" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8923,13 +8929,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C16" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D16" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8937,13 +8943,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C17" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D17" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -8951,13 +8957,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C18" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D18" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -8965,13 +8971,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C19" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D19" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -8979,13 +8985,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C20" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D20" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -8993,13 +8999,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C21" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D21" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9007,13 +9013,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C22" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D22" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9021,13 +9027,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C23" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D23" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9035,13 +9041,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C24" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D24" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9049,13 +9055,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C25" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D25" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9063,13 +9069,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C26" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D26" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9077,13 +9083,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C27" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D27" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9091,13 +9097,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C28" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D28" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9105,13 +9111,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C29" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D29" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9119,13 +9125,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C30" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D30" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9133,13 +9139,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C31" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D31" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9147,13 +9153,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C32" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="D32" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9161,13 +9167,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C33" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D33" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9175,13 +9181,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C34" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D34" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9189,13 +9195,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C35" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D35" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9203,13 +9209,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C36" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D36" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9217,13 +9223,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C37" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D37" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9231,13 +9237,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C38" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D38" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9245,13 +9251,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C39" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="D39" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9259,13 +9265,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C40" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D40" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9273,13 +9279,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C41" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D41" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9287,13 +9293,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C42" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D42" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9301,13 +9307,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C43" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D43" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9315,13 +9321,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C44" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D44" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9329,13 +9335,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C45" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D45" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9343,13 +9349,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C46" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D46" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9357,13 +9363,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C47" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D47" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9371,13 +9377,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C48" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D48" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9385,13 +9391,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C49" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D49" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9399,13 +9405,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C50" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D50" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9413,13 +9419,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C51" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D51" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9427,13 +9433,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C52" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D52" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9441,13 +9447,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C53" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D53" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9455,13 +9461,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C54" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D54" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9469,13 +9475,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="C55" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="D55" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9483,13 +9489,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C56" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D56" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9497,13 +9503,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="C57" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D57" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9511,13 +9517,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C58" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D58" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9525,13 +9531,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C59" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D59" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9539,13 +9545,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C60" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D60" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9553,13 +9559,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C61" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D61" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9567,13 +9573,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C62" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D62" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9581,13 +9587,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C63" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D63" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9595,13 +9601,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C64" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D64" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9609,13 +9615,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C65" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D65" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9623,13 +9629,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C66" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D66" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9637,13 +9643,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C67" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D67" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9651,13 +9657,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C68" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D68" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9665,13 +9671,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C69" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D69" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9679,13 +9685,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C70" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D70" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9693,13 +9699,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C71" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D71" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9707,13 +9713,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C72" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D72" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9721,13 +9727,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C73" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D73" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9735,13 +9741,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C74" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D74" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9749,13 +9755,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C75" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D75" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9763,13 +9769,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C76" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D76" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9777,13 +9783,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C77" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D77" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9791,13 +9797,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C78" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D78" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9805,13 +9811,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C79" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D79" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9819,13 +9825,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C80" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D80" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9833,13 +9839,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C81" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D81" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9847,13 +9853,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C82" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="D82" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9861,13 +9867,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C83" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D83" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -9875,13 +9881,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C84" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D84" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -9889,13 +9895,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C85" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D85" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -10079,7 +10085,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -10225,6 +10231,20 @@
         <v>322</v>
       </c>
       <c r="D10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>101</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" t="s">
         <v>310</v>
       </c>
     </row>
@@ -10296,10 +10316,10 @@
         <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10307,11 +10327,11 @@
         <v>100001</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10319,13 +10339,13 @@
         <v>10100001</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10333,13 +10353,13 @@
         <v>10100002</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10347,13 +10367,13 @@
         <v>10100003</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10361,13 +10381,13 @@
         <v>10100004</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10375,13 +10395,13 @@
         <v>10200001</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10389,13 +10409,13 @@
         <v>10200002</v>
       </c>
       <c r="B11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10403,13 +10423,13 @@
         <v>10200003</v>
       </c>
       <c r="B12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10417,13 +10437,13 @@
         <v>10200004</v>
       </c>
       <c r="B13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10431,13 +10451,13 @@
         <v>10300001</v>
       </c>
       <c r="B14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10445,13 +10465,13 @@
         <v>10300002</v>
       </c>
       <c r="B15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10459,13 +10479,13 @@
         <v>10300003</v>
       </c>
       <c r="B16" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -10473,13 +10493,13 @@
         <v>10300004</v>
       </c>
       <c r="B17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -10487,13 +10507,13 @@
         <v>11000001</v>
       </c>
       <c r="B18" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D18" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -10501,13 +10521,13 @@
         <v>11000002</v>
       </c>
       <c r="B19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -10515,13 +10535,13 @@
         <v>11000003</v>
       </c>
       <c r="B20" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C20" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D20" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -10529,13 +10549,13 @@
         <v>11000004</v>
       </c>
       <c r="B21" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C21" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D21" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -10543,13 +10563,13 @@
         <v>11000005</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -10557,13 +10577,13 @@
         <v>11000006</v>
       </c>
       <c r="B23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C23" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D23" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -10571,13 +10591,13 @@
         <v>11000007</v>
       </c>
       <c r="B24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C24" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D24" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -10585,13 +10605,13 @@
         <v>11000008</v>
       </c>
       <c r="B25" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C25" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -10599,13 +10619,13 @@
         <v>11000009</v>
       </c>
       <c r="B26" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -10613,13 +10633,13 @@
         <v>11010001</v>
       </c>
       <c r="B27" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D27" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -10627,13 +10647,13 @@
         <v>20100001</v>
       </c>
       <c r="B28" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C28" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D28" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -10641,13 +10661,13 @@
         <v>20100002</v>
       </c>
       <c r="B29" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C29" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D29" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -10655,13 +10675,13 @@
         <v>20100003</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C30" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -10669,13 +10689,13 @@
         <v>20100004</v>
       </c>
       <c r="B31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C31" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -10683,13 +10703,13 @@
         <v>20100005</v>
       </c>
       <c r="B32" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D32" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -10697,13 +10717,13 @@
         <v>20100006</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C33" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D33" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -10711,13 +10731,13 @@
         <v>20100007</v>
       </c>
       <c r="B34" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C34" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D34" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -10725,13 +10745,13 @@
         <v>20200001</v>
       </c>
       <c r="B35" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C35" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D35" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -10739,13 +10759,13 @@
         <v>20200002</v>
       </c>
       <c r="B36" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C36" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D36" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -10753,13 +10773,13 @@
         <v>20200003</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C37" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -10767,13 +10787,13 @@
         <v>20200004</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C38" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -10781,13 +10801,13 @@
         <v>20200005</v>
       </c>
       <c r="B39" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -10795,13 +10815,13 @@
         <v>20200006</v>
       </c>
       <c r="B40" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C40" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D40" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -10809,13 +10829,13 @@
         <v>20200007</v>
       </c>
       <c r="B41" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C41" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D41" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -10823,13 +10843,13 @@
         <v>20200008</v>
       </c>
       <c r="B42" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C42" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -10837,13 +10857,13 @@
         <v>20200009</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C43" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -10851,13 +10871,13 @@
         <v>20200010</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C44" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D44" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -10865,13 +10885,13 @@
         <v>20200011</v>
       </c>
       <c r="B45" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C45" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D45" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -10879,13 +10899,13 @@
         <v>20300001</v>
       </c>
       <c r="B46" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D46" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -10893,13 +10913,13 @@
         <v>20300002</v>
       </c>
       <c r="B47" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C47" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D47" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -10907,13 +10927,13 @@
         <v>20300003</v>
       </c>
       <c r="B48" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -10921,13 +10941,13 @@
         <v>20300004</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C49" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D49" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -10935,13 +10955,13 @@
         <v>20300005</v>
       </c>
       <c r="B50" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C50" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -10949,13 +10969,13 @@
         <v>21000001</v>
       </c>
       <c r="B51" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C51" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D51" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -10963,13 +10983,13 @@
         <v>21000002</v>
       </c>
       <c r="B52" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D52" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -10977,13 +10997,13 @@
         <v>21000003</v>
       </c>
       <c r="B53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C53" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D53" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -10991,13 +11011,13 @@
         <v>21000004</v>
       </c>
       <c r="B54" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C54" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D54" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -11005,13 +11025,13 @@
         <v>21000005</v>
       </c>
       <c r="B55" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C55" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D55" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -11019,13 +11039,13 @@
         <v>21000006</v>
       </c>
       <c r="B56" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C56" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -11033,13 +11053,13 @@
         <v>21000007</v>
       </c>
       <c r="B57" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C57" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -11047,13 +11067,13 @@
         <v>21000008</v>
       </c>
       <c r="B58" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C58" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D58" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -11061,13 +11081,13 @@
         <v>21000009</v>
       </c>
       <c r="B59" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C59" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D59" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -11075,13 +11095,13 @@
         <v>21000010</v>
       </c>
       <c r="B60" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C60" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -11089,13 +11109,13 @@
         <v>21010001</v>
       </c>
       <c r="B61" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C61" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -11103,13 +11123,13 @@
         <v>21010002</v>
       </c>
       <c r="B62" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C62" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -11117,13 +11137,13 @@
         <v>21010003</v>
       </c>
       <c r="B63" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C63" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -11131,13 +11151,13 @@
         <v>21010004</v>
       </c>
       <c r="B64" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C64" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -11145,13 +11165,13 @@
         <v>21010005</v>
       </c>
       <c r="B65" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C65" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -11159,13 +11179,13 @@
         <v>21010006</v>
       </c>
       <c r="B66" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C66" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -11173,13 +11193,13 @@
         <v>21010007</v>
       </c>
       <c r="B67" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C67" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -11187,13 +11207,13 @@
         <v>21010008</v>
       </c>
       <c r="B68" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C68" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D68" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -11201,13 +11221,13 @@
         <v>21010009</v>
       </c>
       <c r="B69" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C69" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D69" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -11215,13 +11235,13 @@
         <v>21010010</v>
       </c>
       <c r="B70" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C70" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D70" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -11229,13 +11249,13 @@
         <v>21010011</v>
       </c>
       <c r="B71" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C71" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D71" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -11243,13 +11263,13 @@
         <v>21010012</v>
       </c>
       <c r="B72" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C72" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D72" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -11257,13 +11277,13 @@
         <v>21010013</v>
       </c>
       <c r="B73" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C73" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D73" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -11271,13 +11291,13 @@
         <v>21010014</v>
       </c>
       <c r="B74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C74" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D74" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -11285,13 +11305,13 @@
         <v>21010015</v>
       </c>
       <c r="B75" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C75" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D75" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -11299,13 +11319,13 @@
         <v>21010016</v>
       </c>
       <c r="B76" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C76" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D76" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -11313,13 +11333,13 @@
         <v>21010017</v>
       </c>
       <c r="B77" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C77" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D77" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -11327,13 +11347,13 @@
         <v>21010018</v>
       </c>
       <c r="B78" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C78" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D78" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -11341,13 +11361,13 @@
         <v>21010019</v>
       </c>
       <c r="B79" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C79" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D79" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -11355,13 +11375,13 @@
         <v>21010020</v>
       </c>
       <c r="B80" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C80" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D80" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -11369,13 +11389,13 @@
         <v>30100001</v>
       </c>
       <c r="B81" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C81" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D81" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -11383,13 +11403,13 @@
         <v>30100002</v>
       </c>
       <c r="B82" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C82" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D82" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -11397,13 +11417,13 @@
         <v>30100003</v>
       </c>
       <c r="B83" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C83" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D83" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -11411,13 +11431,13 @@
         <v>30100004</v>
       </c>
       <c r="B84" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C84" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D84" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -11425,13 +11445,13 @@
         <v>30100005</v>
       </c>
       <c r="B85" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C85" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D85" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -11439,13 +11459,13 @@
         <v>30100006</v>
       </c>
       <c r="B86" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C86" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D86" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -11453,13 +11473,13 @@
         <v>30100007</v>
       </c>
       <c r="B87" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C87" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D87" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -11467,13 +11487,13 @@
         <v>30100008</v>
       </c>
       <c r="B88" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C88" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D88" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -11481,13 +11501,13 @@
         <v>30100009</v>
       </c>
       <c r="B89" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C89" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D89" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -11495,13 +11515,13 @@
         <v>30100010</v>
       </c>
       <c r="B90" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C90" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D90" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -11509,13 +11529,13 @@
         <v>30100011</v>
       </c>
       <c r="B91" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C91" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D91" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -11523,13 +11543,13 @@
         <v>30100012</v>
       </c>
       <c r="B92" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C92" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D92" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -11537,13 +11557,13 @@
         <v>30100013</v>
       </c>
       <c r="B93" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C93" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D93" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -11551,13 +11571,13 @@
         <v>30100014</v>
       </c>
       <c r="B94" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C94" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D94" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -11565,13 +11585,13 @@
         <v>30100015</v>
       </c>
       <c r="B95" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C95" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D95" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -11579,13 +11599,13 @@
         <v>30100016</v>
       </c>
       <c r="B96" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C96" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D96" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -11593,13 +11613,13 @@
         <v>30100017</v>
       </c>
       <c r="B97" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C97" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D97" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -11607,13 +11627,13 @@
         <v>30100018</v>
       </c>
       <c r="B98" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C98" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D98" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -11621,13 +11641,13 @@
         <v>30100019</v>
       </c>
       <c r="B99" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C99" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D99" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -11635,13 +11655,13 @@
         <v>30100020</v>
       </c>
       <c r="B100" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C100" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D100" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -11649,13 +11669,13 @@
         <v>40100001</v>
       </c>
       <c r="B101" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C101" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D101" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -11663,13 +11683,13 @@
         <v>40200001</v>
       </c>
       <c r="B102" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C102" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D102" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -11677,13 +11697,13 @@
         <v>40200002</v>
       </c>
       <c r="B103" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C103" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D103" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -11691,13 +11711,13 @@
         <v>40200003</v>
       </c>
       <c r="B104" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C104" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D104" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -11705,13 +11725,13 @@
         <v>40200004</v>
       </c>
       <c r="B105" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C105" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D105" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -11719,13 +11739,13 @@
         <v>40200005</v>
       </c>
       <c r="B106" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C106" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D106" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -11733,13 +11753,13 @@
         <v>40200006</v>
       </c>
       <c r="B107" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C107" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D107" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -11747,13 +11767,13 @@
         <v>40300001</v>
       </c>
       <c r="B108" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C108" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D108" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -11761,13 +11781,13 @@
         <v>40300002</v>
       </c>
       <c r="B109" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C109" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -11775,13 +11795,13 @@
         <v>40300003</v>
       </c>
       <c r="B110" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C110" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D110" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -11789,13 +11809,13 @@
         <v>40300004</v>
       </c>
       <c r="B111" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C111" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D111" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -11803,13 +11823,13 @@
         <v>41000001</v>
       </c>
       <c r="B112" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C112" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D112" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -11817,13 +11837,13 @@
         <v>41000002</v>
       </c>
       <c r="B113" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C113" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D113" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -11831,13 +11851,13 @@
         <v>41000003</v>
       </c>
       <c r="B114" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C114" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D114" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -11845,13 +11865,13 @@
         <v>41000004</v>
       </c>
       <c r="B115" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C115" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D115" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -11859,13 +11879,13 @@
         <v>41000005</v>
       </c>
       <c r="B116" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C116" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D116" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -11873,13 +11893,13 @@
         <v>50100001</v>
       </c>
       <c r="B117" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C117" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D117" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -11887,13 +11907,13 @@
         <v>50100002</v>
       </c>
       <c r="B118" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C118" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D118" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -11901,13 +11921,13 @@
         <v>50100003</v>
       </c>
       <c r="B119" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C119" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D119" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -11915,13 +11935,13 @@
         <v>50200001</v>
       </c>
       <c r="B120" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C120" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D120" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -11929,13 +11949,13 @@
         <v>50200002</v>
       </c>
       <c r="B121" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C121" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D121" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -11943,13 +11963,13 @@
         <v>50200003</v>
       </c>
       <c r="B122" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C122" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D122" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -11957,13 +11977,13 @@
         <v>50300001</v>
       </c>
       <c r="B123" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C123" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D123" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -11971,13 +11991,13 @@
         <v>50300002</v>
       </c>
       <c r="B124" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C124" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D124" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -11985,13 +12005,13 @@
         <v>50500001</v>
       </c>
       <c r="B125" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C125" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D125" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -11999,13 +12019,13 @@
         <v>50500002</v>
       </c>
       <c r="B126" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C126" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D126" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -12013,13 +12033,13 @@
         <v>50500003</v>
       </c>
       <c r="B127" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C127" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D127" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -12027,13 +12047,13 @@
         <v>50500004</v>
       </c>
       <c r="B128" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C128" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D128" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -12041,13 +12061,13 @@
         <v>50500005</v>
       </c>
       <c r="B129" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C129" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D129" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -12055,13 +12075,13 @@
         <v>51010001</v>
       </c>
       <c r="B130" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C130" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D130" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -12075,7 +12095,7 @@
         <v>269</v>
       </c>
       <c r="D131" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -12083,13 +12103,13 @@
         <v>51010003</v>
       </c>
       <c r="B132" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C132" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D132" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -12097,13 +12117,13 @@
         <v>60100001</v>
       </c>
       <c r="B133" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C133" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D133" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -12111,13 +12131,13 @@
         <v>60100002</v>
       </c>
       <c r="B134" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C134" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D134" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -12125,13 +12145,13 @@
         <v>60100003</v>
       </c>
       <c r="B135" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C135" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D135" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -12139,13 +12159,13 @@
         <v>60100004</v>
       </c>
       <c r="B136" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C136" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D136" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -12153,13 +12173,13 @@
         <v>60100005</v>
       </c>
       <c r="B137" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C137" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D137" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -12167,13 +12187,13 @@
         <v>60100006</v>
       </c>
       <c r="B138" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C138" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D138" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -12181,13 +12201,13 @@
         <v>60100007</v>
       </c>
       <c r="B139" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C139" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D139" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -12195,13 +12215,13 @@
         <v>60100008</v>
       </c>
       <c r="B140" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C140" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D140" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -12209,13 +12229,13 @@
         <v>60100009</v>
       </c>
       <c r="B141" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C141" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D141" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -12223,13 +12243,13 @@
         <v>60100010</v>
       </c>
       <c r="B142" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C142" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D142" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -12237,13 +12257,13 @@
         <v>60200001</v>
       </c>
       <c r="B143" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C143" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D143" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -12251,13 +12271,13 @@
         <v>60200002</v>
       </c>
       <c r="B144" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C144" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D144" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -12265,13 +12285,13 @@
         <v>60300001</v>
       </c>
       <c r="B145" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C145" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D145" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -12279,13 +12299,13 @@
         <v>60300002</v>
       </c>
       <c r="B146" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C146" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D146" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -12293,13 +12313,13 @@
         <v>60300003</v>
       </c>
       <c r="B147" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C147" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D147" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -12307,13 +12327,13 @@
         <v>60300004</v>
       </c>
       <c r="B148" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C148" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D148" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -12321,13 +12341,13 @@
         <v>60300005</v>
       </c>
       <c r="B149" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C149" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D149" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -12335,13 +12355,13 @@
         <v>61010001</v>
       </c>
       <c r="B150" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C150" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D150" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -12349,13 +12369,13 @@
         <v>61010002</v>
       </c>
       <c r="B151" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C151" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D151" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -12363,13 +12383,13 @@
         <v>61010003</v>
       </c>
       <c r="B152" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C152" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D152" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -12377,13 +12397,13 @@
         <v>61010004</v>
       </c>
       <c r="B153" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C153" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D153" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -12391,13 +12411,13 @@
         <v>61010005</v>
       </c>
       <c r="B154" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C154" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D154" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -12405,13 +12425,13 @@
         <v>61010006</v>
       </c>
       <c r="B155" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C155" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D155" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -12419,13 +12439,13 @@
         <v>61010007</v>
       </c>
       <c r="B156" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C156" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D156" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -12433,13 +12453,13 @@
         <v>61010008</v>
       </c>
       <c r="B157" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C157" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D157" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -12447,13 +12467,13 @@
         <v>61010009</v>
       </c>
       <c r="B158" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C158" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D158" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -12461,13 +12481,13 @@
         <v>61010010</v>
       </c>
       <c r="B159" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C159" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D159" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -12475,13 +12495,13 @@
         <v>61010011</v>
       </c>
       <c r="B160" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C160" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D160" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -12489,13 +12509,13 @@
         <v>61010012</v>
       </c>
       <c r="B161" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C161" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D161" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -12503,13 +12523,13 @@
         <v>61010013</v>
       </c>
       <c r="B162" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C162" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D162" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -12517,13 +12537,13 @@
         <v>61010014</v>
       </c>
       <c r="B163" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C163" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D163" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -12531,13 +12551,13 @@
         <v>61010015</v>
       </c>
       <c r="B164" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C164" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D164" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -12545,13 +12565,13 @@
         <v>61010016</v>
       </c>
       <c r="B165" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C165" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D165" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -12559,13 +12579,13 @@
         <v>61010017</v>
       </c>
       <c r="B166" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C166" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D166" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -12573,13 +12593,13 @@
         <v>61010018</v>
       </c>
       <c r="B167" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C167" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D167" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -12587,13 +12607,13 @@
         <v>61010019</v>
       </c>
       <c r="B168" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C168" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D168" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -12601,13 +12621,13 @@
         <v>61010020</v>
       </c>
       <c r="B169" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C169" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D169" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -12615,13 +12635,13 @@
         <v>70100001</v>
       </c>
       <c r="B170" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C170" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D170" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -12629,13 +12649,13 @@
         <v>70200001</v>
       </c>
       <c r="B171" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C171" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D171" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -12643,13 +12663,13 @@
         <v>70200002</v>
       </c>
       <c r="B172" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C172" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D172" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -12657,13 +12677,13 @@
         <v>70300001</v>
       </c>
       <c r="B173" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C173" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D173" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -12671,13 +12691,13 @@
         <v>70300002</v>
       </c>
       <c r="B174" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C174" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D174" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -12685,13 +12705,13 @@
         <v>70300003</v>
       </c>
       <c r="B175" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C175" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D175" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -12699,13 +12719,13 @@
         <v>70300004</v>
       </c>
       <c r="B176" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C176" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D176" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -12713,13 +12733,13 @@
         <v>71000001</v>
       </c>
       <c r="B177" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C177" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D177" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -12727,13 +12747,13 @@
         <v>71000002</v>
       </c>
       <c r="B178" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C178" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D178" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -12741,13 +12761,13 @@
         <v>71000003</v>
       </c>
       <c r="B179" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C179" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D179" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -12755,13 +12775,13 @@
         <v>71010001</v>
       </c>
       <c r="B180" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C180" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D180" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -12769,13 +12789,13 @@
         <v>71010002</v>
       </c>
       <c r="B181" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C181" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D181" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -12783,13 +12803,13 @@
         <v>71010003</v>
       </c>
       <c r="B182" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C182" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D182" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -12797,13 +12817,13 @@
         <v>71010004</v>
       </c>
       <c r="B183" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C183" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D183" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -12811,13 +12831,13 @@
         <v>71010005</v>
       </c>
       <c r="B184" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C184" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D184" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -12825,13 +12845,13 @@
         <v>71010006</v>
       </c>
       <c r="B185" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C185" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D185" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -12899,13 +12919,13 @@
         <v>1000100001</v>
       </c>
       <c r="B4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -12913,13 +12933,13 @@
         <v>1000200001</v>
       </c>
       <c r="B5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C5" t="s">
+        <v>655</v>
+      </c>
+      <c r="D5" t="s">
         <v>653</v>
-      </c>
-      <c r="D5" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -12927,13 +12947,13 @@
         <v>1000300001</v>
       </c>
       <c r="B6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D6" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -12941,13 +12961,13 @@
         <v>1000400001</v>
       </c>
       <c r="B7" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D7" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -12955,13 +12975,13 @@
         <v>1000500001</v>
       </c>
       <c r="B8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -12969,13 +12989,13 @@
         <v>2000100001</v>
       </c>
       <c r="B9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D9" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -12983,13 +13003,13 @@
         <v>2000200001</v>
       </c>
       <c r="B10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C10" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D10" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -12997,13 +13017,13 @@
         <v>2000300001</v>
       </c>
       <c r="B11" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C11" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D11" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13011,13 +13031,13 @@
         <v>2000400001</v>
       </c>
       <c r="B12" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C12" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D12" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -13031,7 +13051,7 @@
         <v>294</v>
       </c>
       <c r="D13" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -13045,7 +13065,7 @@
         <v>303</v>
       </c>
       <c r="D14" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -13053,13 +13073,13 @@
         <v>3000300001</v>
       </c>
       <c r="B15" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C15" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D15" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -13073,7 +13093,7 @@
         <v>299</v>
       </c>
       <c r="D16" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -13081,13 +13101,13 @@
         <v>11000100001</v>
       </c>
       <c r="B17" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C17" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D17" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -13095,13 +13115,13 @@
         <v>11000200001</v>
       </c>
       <c r="B18" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C18" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D18" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -13109,13 +13129,13 @@
         <v>11000300001</v>
       </c>
       <c r="B19" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C19" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D19" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -13123,13 +13143,13 @@
         <v>12000100001</v>
       </c>
       <c r="B20" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C20" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D20" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -13137,13 +13157,13 @@
         <v>12000200001</v>
       </c>
       <c r="B21" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C21" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D21" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -13151,13 +13171,13 @@
         <v>12000300001</v>
       </c>
       <c r="B22" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C22" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D22" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:4">
@@ -13165,13 +13185,13 @@
         <v>12001100001</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C23" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D23" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:4">
@@ -13179,13 +13199,13 @@
         <v>12001200001</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C24" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D24" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:4">
@@ -13193,13 +13213,13 @@
         <v>12001300001</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C25" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:4">
@@ -13207,13 +13227,13 @@
         <v>12001400001</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C26" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D26" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1" spans="1:4">
@@ -13221,13 +13241,13 @@
         <v>12002100001</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1" spans="1:4">
@@ -13235,13 +13255,13 @@
         <v>12002200001</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D28" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:4">
@@ -13249,13 +13269,13 @@
         <v>12002300001</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D29" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1" spans="1:4">
@@ -13263,13 +13283,13 @@
         <v>12002400001</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D30" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" spans="1:4">
@@ -13277,13 +13297,13 @@
         <v>12003100001</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D31" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1" spans="1:4">
@@ -13291,13 +13311,13 @@
         <v>12003200001</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D32" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1" spans="1:4">
@@ -13305,13 +13325,13 @@
         <v>12003300001</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D33" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" spans="1:4">
@@ -13319,13 +13339,13 @@
         <v>12003400001</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D34" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="1:4">
@@ -13333,13 +13353,13 @@
         <v>12010100001</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D35" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" ht="17.25" customHeight="1" spans="1:4">
@@ -13347,13 +13367,13 @@
         <v>12010200001</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D36" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" ht="17.25" customHeight="1" spans="1:4">
@@ -13361,13 +13381,13 @@
         <v>12010300001</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D37" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="1:4">
@@ -13375,13 +13395,13 @@
         <v>12011100001</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D38" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="1:4">
@@ -13389,13 +13409,13 @@
         <v>12011200001</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D39" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="1:4">
@@ -13403,13 +13423,13 @@
         <v>12011300001</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D40" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -13417,13 +13437,13 @@
         <v>13000100001</v>
       </c>
       <c r="B41" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C41" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D41" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -13431,13 +13451,13 @@
         <v>13000200001</v>
       </c>
       <c r="B42" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C42" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D42" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -13445,13 +13465,13 @@
         <v>13000300001</v>
       </c>
       <c r="B43" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C43" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D43" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -13459,13 +13479,13 @@
         <v>13000400001</v>
       </c>
       <c r="B44" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C44" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D44" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -13473,13 +13493,13 @@
         <v>13000500001</v>
       </c>
       <c r="B45" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C45" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D45" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -13487,13 +13507,13 @@
         <v>13000600001</v>
       </c>
       <c r="B46" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C46" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D46" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -13501,13 +13521,13 @@
         <v>13000700001</v>
       </c>
       <c r="B47" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C47" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D47" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -13515,13 +13535,13 @@
         <v>10001000010000</v>
       </c>
       <c r="B48" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C48" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D48" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -13529,13 +13549,13 @@
         <v>10002000010000</v>
       </c>
       <c r="B49" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C49" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D49" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -13543,13 +13563,13 @@
         <v>10003000010000</v>
       </c>
       <c r="B50" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C50" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D50" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -13557,13 +13577,13 @@
         <v>10004000010000</v>
       </c>
       <c r="B51" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C51" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D51" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -13571,13 +13591,13 @@
         <v>10005000010000</v>
       </c>
       <c r="B52" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C52" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D52" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -13585,13 +13605,13 @@
         <v>20001000010000</v>
       </c>
       <c r="B53" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C53" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D53" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -13599,13 +13619,13 @@
         <v>20002000010000</v>
       </c>
       <c r="B54" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C54" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D54" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -13613,13 +13633,13 @@
         <v>20003000010000</v>
       </c>
       <c r="B55" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C55" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D55" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -13627,13 +13647,13 @@
         <v>20004000010000</v>
       </c>
       <c r="B56" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C56" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D56" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -13647,7 +13667,7 @@
         <v>297</v>
       </c>
       <c r="D57" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -13661,7 +13681,7 @@
         <v>305</v>
       </c>
       <c r="D58" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -13675,7 +13695,7 @@
         <v>309</v>
       </c>
       <c r="D59" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -13683,13 +13703,13 @@
         <v>30004000010000</v>
       </c>
       <c r="B60" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C60" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D60" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -13697,13 +13717,13 @@
         <v>110001000010000</v>
       </c>
       <c r="B61" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C61" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D61" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -13711,13 +13731,13 @@
         <v>110002000010000</v>
       </c>
       <c r="B62" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C62" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D62" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -13725,13 +13745,13 @@
         <v>110003000010000</v>
       </c>
       <c r="B63" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C63" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D63" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -13739,13 +13759,13 @@
         <v>120001000010000</v>
       </c>
       <c r="B64" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C64" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D64" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -13753,13 +13773,13 @@
         <v>120002000010000</v>
       </c>
       <c r="B65" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C65" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D65" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -13767,13 +13787,13 @@
         <v>120003000010000</v>
       </c>
       <c r="B66" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C66" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D66" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -13781,13 +13801,13 @@
         <v>120011000010000</v>
       </c>
       <c r="B67" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C67" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D67" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -13795,13 +13815,13 @@
         <v>120012000010000</v>
       </c>
       <c r="B68" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C68" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D68" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -13809,13 +13829,13 @@
         <v>120013000010000</v>
       </c>
       <c r="B69" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C69" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D69" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -13823,13 +13843,13 @@
         <v>120014000010000</v>
       </c>
       <c r="B70" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C70" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D70" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -13837,13 +13857,13 @@
         <v>120021000010000</v>
       </c>
       <c r="B71" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C71" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D71" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -13851,13 +13871,13 @@
         <v>120022000010000</v>
       </c>
       <c r="B72" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C72" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D72" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -13865,13 +13885,13 @@
         <v>120023000010000</v>
       </c>
       <c r="B73" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C73" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D73" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -13879,13 +13899,13 @@
         <v>120024000010000</v>
       </c>
       <c r="B74" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C74" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D74" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -13893,13 +13913,13 @@
         <v>120031000010000</v>
       </c>
       <c r="B75" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C75" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D75" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -13907,13 +13927,13 @@
         <v>120032000010000</v>
       </c>
       <c r="B76" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C76" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D76" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -13921,13 +13941,13 @@
         <v>120033000010000</v>
       </c>
       <c r="B77" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C77" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D77" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -13935,13 +13955,13 @@
         <v>120034000010000</v>
       </c>
       <c r="B78" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C78" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D78" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -13949,13 +13969,13 @@
         <v>120101000010000</v>
       </c>
       <c r="B79" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C79" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D79" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -13963,13 +13983,13 @@
         <v>120102000010000</v>
       </c>
       <c r="B80" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C80" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D80" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -13977,13 +13997,13 @@
         <v>120103000010000</v>
       </c>
       <c r="B81" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C81" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D81" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -13991,13 +14011,13 @@
         <v>120111000010000</v>
       </c>
       <c r="B82" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C82" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D82" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -14005,13 +14025,13 @@
         <v>120112000010000</v>
       </c>
       <c r="B83" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C83" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D83" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -14019,13 +14039,13 @@
         <v>120113000010000</v>
       </c>
       <c r="B84" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C84" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D84" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -14033,13 +14053,13 @@
         <v>130001000010000</v>
       </c>
       <c r="B85" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C85" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D85" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -14047,13 +14067,13 @@
         <v>130003000010000</v>
       </c>
       <c r="B86" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C86" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D86" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -14061,13 +14081,13 @@
         <v>130004000010000</v>
       </c>
       <c r="B87" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C87" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D87" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -14075,13 +14095,13 @@
         <v>130005000010000</v>
       </c>
       <c r="B88" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C88" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D88" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -14089,13 +14109,13 @@
         <v>130006000010000</v>
       </c>
       <c r="B89" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C89" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D89" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -14103,13 +14123,13 @@
         <v>130007000010000</v>
       </c>
       <c r="B90" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C90" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D90" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -14177,13 +14197,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C4" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14191,13 +14211,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C5" t="s">
+        <v>810</v>
+      </c>
+      <c r="D5" t="s">
         <v>808</v>
-      </c>
-      <c r="D5" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14205,13 +14225,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C6" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D6" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14219,13 +14239,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C7" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D7" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14233,13 +14253,13 @@
         <v>100001</v>
       </c>
       <c r="B8" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C8" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D8" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14247,13 +14267,13 @@
         <v>100002</v>
       </c>
       <c r="B9" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C9" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D9" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -14261,13 +14281,13 @@
         <v>100003</v>
       </c>
       <c r="B10" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C10" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D10" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -14275,13 +14295,13 @@
         <v>100004</v>
       </c>
       <c r="B11" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C11" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D11" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -14289,13 +14309,13 @@
         <v>200001</v>
       </c>
       <c r="B12" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C12" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D12" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14303,13 +14323,13 @@
         <v>200002</v>
       </c>
       <c r="B13" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C13" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D13" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -14317,13 +14337,13 @@
         <v>200003</v>
       </c>
       <c r="B14" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C14" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D14" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -14331,13 +14351,13 @@
         <v>200004</v>
       </c>
       <c r="B15" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C15" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D15" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -14345,13 +14365,13 @@
         <v>200005</v>
       </c>
       <c r="B16" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C16" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D16" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14359,13 +14379,13 @@
         <v>200006</v>
       </c>
       <c r="B17" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C17" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D17" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -14373,13 +14393,13 @@
         <v>200007</v>
       </c>
       <c r="B18" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C18" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D18" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -14387,13 +14407,13 @@
         <v>200008</v>
       </c>
       <c r="B19" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C19" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D19" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14401,13 +14421,13 @@
         <v>200009</v>
       </c>
       <c r="B20" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C20" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D20" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -14415,13 +14435,13 @@
         <v>200010</v>
       </c>
       <c r="B21" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C21" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D21" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -14429,13 +14449,13 @@
         <v>200011</v>
       </c>
       <c r="B22" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C22" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D22" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -14443,13 +14463,13 @@
         <v>200012</v>
       </c>
       <c r="B23" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C23" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D23" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -14457,13 +14477,13 @@
         <v>200013</v>
       </c>
       <c r="B24" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C24" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D24" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -14471,13 +14491,13 @@
         <v>200014</v>
       </c>
       <c r="B25" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C25" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D25" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -14545,13 +14565,13 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14559,13 +14579,13 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C5" t="s">
+        <v>855</v>
+      </c>
+      <c r="D5" t="s">
         <v>853</v>
-      </c>
-      <c r="D5" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14573,13 +14593,13 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C6" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D6" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14587,13 +14607,13 @@
         <v>20001</v>
       </c>
       <c r="B7" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C7" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D7" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14601,13 +14621,13 @@
         <v>20002</v>
       </c>
       <c r="B8" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C8" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14615,13 +14635,13 @@
         <v>20003</v>
       </c>
       <c r="B9" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C9" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D9" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -14629,13 +14649,13 @@
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C10" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D10" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -14643,13 +14663,13 @@
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C11" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D11" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -14657,13 +14677,13 @@
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C12" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14671,13 +14691,13 @@
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C13" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D13" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -14685,13 +14705,13 @@
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C14" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -14699,13 +14719,13 @@
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C15" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D15" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -14713,13 +14733,13 @@
         <v>50001</v>
       </c>
       <c r="B16" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C16" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D16" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14727,13 +14747,13 @@
         <v>50002</v>
       </c>
       <c r="B17" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C17" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D17" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -14741,13 +14761,13 @@
         <v>50003</v>
       </c>
       <c r="B18" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C18" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D18" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -14755,13 +14775,13 @@
         <v>60001</v>
       </c>
       <c r="B19" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C19" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D19" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14769,13 +14789,13 @@
         <v>60002</v>
       </c>
       <c r="B20" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C20" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D20" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -14783,13 +14803,13 @@
         <v>60003</v>
       </c>
       <c r="B21" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C21" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D21" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -14797,13 +14817,13 @@
         <v>70001</v>
       </c>
       <c r="B22" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C22" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D22" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -14811,13 +14831,13 @@
         <v>70002</v>
       </c>
       <c r="B23" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C23" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D23" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -14825,13 +14845,13 @@
         <v>70003</v>
       </c>
       <c r="B24" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C24" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D24" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -14899,13 +14919,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14913,13 +14933,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C5" t="s">
+        <v>898</v>
+      </c>
+      <c r="D5" t="s">
         <v>896</v>
-      </c>
-      <c r="D5" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14927,13 +14947,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C6" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D6" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14941,13 +14961,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C7" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D7" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -15015,13 +15035,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15029,13 +15049,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C5" t="s">
+        <v>907</v>
+      </c>
+      <c r="D5" t="s">
         <v>905</v>
-      </c>
-      <c r="D5" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15043,13 +15063,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C6" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D6" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15057,13 +15077,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C7" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D7" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -15071,13 +15091,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C8" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D8" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -15085,13 +15105,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C9" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D9" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -15099,13 +15119,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C10" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D10" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -15113,13 +15133,13 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C11" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D11" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -15127,13 +15147,13 @@
         <v>1002</v>
       </c>
       <c r="B12" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C12" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D12" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15141,13 +15161,13 @@
         <v>1003</v>
       </c>
       <c r="B13" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C13" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D13" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -15155,13 +15175,13 @@
         <v>1004</v>
       </c>
       <c r="B14" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C14" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -15169,13 +15189,13 @@
         <v>2001</v>
       </c>
       <c r="B15" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C15" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D15" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -15183,13 +15203,13 @@
         <v>2002</v>
       </c>
       <c r="B16" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C16" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D16" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -15197,13 +15217,13 @@
         <v>2003</v>
       </c>
       <c r="B17" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -15211,13 +15231,13 @@
         <v>2004</v>
       </c>
       <c r="B18" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C18" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D18" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -15225,13 +15245,13 @@
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C19" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -15239,13 +15259,13 @@
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C20" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D20" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -15253,13 +15273,13 @@
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C21" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D21" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -15267,13 +15287,13 @@
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C22" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D22" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -15281,13 +15301,13 @@
         <v>4001</v>
       </c>
       <c r="B23" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C23" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D23" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -15295,13 +15315,13 @@
         <v>4002</v>
       </c>
       <c r="B24" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C24" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D24" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -15309,13 +15329,13 @@
         <v>4003</v>
       </c>
       <c r="B25" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C25" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D25" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -15323,13 +15343,13 @@
         <v>4004</v>
       </c>
       <c r="B26" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C26" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D26" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -15337,13 +15357,13 @@
         <v>4005</v>
       </c>
       <c r="B27" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C27" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D27" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -15351,13 +15371,13 @@
         <v>5001</v>
       </c>
       <c r="B28" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C28" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D28" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -15365,13 +15385,13 @@
         <v>5002</v>
       </c>
       <c r="B29" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C29" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D29" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -15379,13 +15399,13 @@
         <v>5003</v>
       </c>
       <c r="B30" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C30" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D30" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -15393,13 +15413,13 @@
         <v>5004</v>
       </c>
       <c r="B31" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C31" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D31" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -15407,13 +15427,13 @@
         <v>6001</v>
       </c>
       <c r="B32" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C32" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D32" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -15421,13 +15441,13 @@
         <v>6002</v>
       </c>
       <c r="B33" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C33" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D33" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -15435,13 +15455,13 @@
         <v>6003</v>
       </c>
       <c r="B34" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C34" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D34" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -15449,13 +15469,13 @@
         <v>6004</v>
       </c>
       <c r="B35" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C35" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D35" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -15463,13 +15483,13 @@
         <v>6005</v>
       </c>
       <c r="B36" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C36" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D36" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -15477,13 +15497,13 @@
         <v>7001</v>
       </c>
       <c r="B37" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C37" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D37" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -15491,13 +15511,13 @@
         <v>7002</v>
       </c>
       <c r="B38" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C38" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D38" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -15505,13 +15525,13 @@
         <v>7003</v>
       </c>
       <c r="B39" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C39" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D39" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -15519,13 +15539,13 @@
         <v>7004</v>
       </c>
       <c r="B40" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C40" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D40" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -15533,13 +15553,13 @@
         <v>101001</v>
       </c>
       <c r="B41" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C41" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D41" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -15547,13 +15567,13 @@
         <v>102001</v>
       </c>
       <c r="B42" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C42" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D42" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -15561,13 +15581,13 @@
         <v>103001</v>
       </c>
       <c r="B43" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C43" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D43" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -15575,13 +15595,13 @@
         <v>103002</v>
       </c>
       <c r="B44" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C44" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D44" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -15589,13 +15609,13 @@
         <v>900001</v>
       </c>
       <c r="B45" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C45" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D45" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -15603,13 +15623,13 @@
         <v>900002</v>
       </c>
       <c r="B46" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C46" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D46" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="723" activeTab="2"/>
+    <workbookView windowHeight="17655" tabRatio="723" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -10257,12 +10257,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10448,195 +10448,117 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>10300001</v>
-      </c>
-      <c r="B14" t="s">
-        <v>344</v>
-      </c>
-      <c r="C14" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" t="s">
-        <v>326</v>
-      </c>
+        <v>10200005</v>
+      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>10300002</v>
-      </c>
-      <c r="B15" t="s">
-        <v>346</v>
-      </c>
-      <c r="C15" t="s">
-        <v>347</v>
-      </c>
-      <c r="D15" t="s">
-        <v>326</v>
-      </c>
+        <v>10200006</v>
+      </c>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>10300003</v>
-      </c>
-      <c r="B16" t="s">
-        <v>348</v>
-      </c>
-      <c r="C16" t="s">
-        <v>349</v>
-      </c>
-      <c r="D16" t="s">
-        <v>326</v>
-      </c>
+        <v>10200007</v>
+      </c>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>10300004</v>
-      </c>
-      <c r="B17" t="s">
-        <v>350</v>
-      </c>
-      <c r="C17" t="s">
-        <v>351</v>
-      </c>
-      <c r="D17" t="s">
-        <v>326</v>
-      </c>
+        <v>10200008</v>
+      </c>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>11000001</v>
-      </c>
-      <c r="B18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C18" t="s">
-        <v>353</v>
-      </c>
-      <c r="D18" t="s">
-        <v>326</v>
-      </c>
+        <v>10200009</v>
+      </c>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>11000002</v>
-      </c>
-      <c r="B19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C19" t="s">
-        <v>355</v>
-      </c>
-      <c r="D19" t="s">
-        <v>326</v>
-      </c>
+        <v>10200010</v>
+      </c>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>11000003</v>
-      </c>
-      <c r="B20" t="s">
-        <v>356</v>
-      </c>
-      <c r="C20" t="s">
-        <v>357</v>
-      </c>
-      <c r="D20" t="s">
-        <v>326</v>
-      </c>
+        <v>10200011</v>
+      </c>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>11000004</v>
-      </c>
-      <c r="B21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C21" t="s">
-        <v>359</v>
-      </c>
-      <c r="D21" t="s">
-        <v>326</v>
-      </c>
+        <v>10200012</v>
+      </c>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>11000005</v>
-      </c>
-      <c r="B22" t="s">
-        <v>360</v>
-      </c>
-      <c r="C22" t="s">
-        <v>361</v>
-      </c>
-      <c r="D22" t="s">
-        <v>326</v>
-      </c>
+        <v>10200013</v>
+      </c>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>11000006</v>
-      </c>
-      <c r="B23" t="s">
-        <v>362</v>
-      </c>
-      <c r="C23" t="s">
-        <v>363</v>
-      </c>
-      <c r="D23" t="s">
-        <v>326</v>
-      </c>
+        <v>10200014</v>
+      </c>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>11000007</v>
-      </c>
-      <c r="B24" t="s">
-        <v>364</v>
-      </c>
-      <c r="C24" t="s">
-        <v>365</v>
-      </c>
-      <c r="D24" t="s">
-        <v>326</v>
-      </c>
+        <v>10200015</v>
+      </c>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>11000008</v>
-      </c>
-      <c r="B25" t="s">
-        <v>366</v>
-      </c>
-      <c r="C25" t="s">
-        <v>367</v>
-      </c>
-      <c r="D25" t="s">
-        <v>326</v>
-      </c>
+        <v>10200016</v>
+      </c>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>11000009</v>
-      </c>
-      <c r="B26" t="s">
-        <v>368</v>
-      </c>
-      <c r="C26" t="s">
-        <v>369</v>
-      </c>
-      <c r="D26" t="s">
-        <v>326</v>
-      </c>
+        <v>10200017</v>
+      </c>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>11010001</v>
+        <v>10300001</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="C27" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="D27" t="s">
         <v>326</v>
@@ -10644,13 +10566,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>20100001</v>
+        <v>10300002</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="D28" t="s">
         <v>326</v>
@@ -10658,13 +10580,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>20100002</v>
+        <v>10300003</v>
       </c>
       <c r="B29" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="C29" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="D29" t="s">
         <v>326</v>
@@ -10672,13 +10594,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>20100003</v>
+        <v>10300004</v>
       </c>
       <c r="B30" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="D30" t="s">
         <v>326</v>
@@ -10686,13 +10608,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>20100004</v>
+        <v>11000001</v>
       </c>
       <c r="B31" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="C31" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="D31" t="s">
         <v>326</v>
@@ -10700,13 +10622,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>20100005</v>
+        <v>11000002</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="C32" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D32" t="s">
         <v>326</v>
@@ -10714,13 +10636,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>20100006</v>
+        <v>11000003</v>
       </c>
       <c r="B33" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="C33" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="D33" t="s">
         <v>326</v>
@@ -10728,13 +10650,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>20100007</v>
+        <v>11000004</v>
       </c>
       <c r="B34" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="C34" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="D34" t="s">
         <v>326</v>
@@ -10742,13 +10664,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>20200001</v>
+        <v>11000005</v>
       </c>
       <c r="B35" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="C35" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="D35" t="s">
         <v>326</v>
@@ -10756,13 +10678,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>20200002</v>
+        <v>11000006</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D36" t="s">
         <v>326</v>
@@ -10770,13 +10692,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>20200003</v>
+        <v>11000007</v>
       </c>
       <c r="B37" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="C37" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="D37" t="s">
         <v>326</v>
@@ -10784,13 +10706,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>20200004</v>
+        <v>11000008</v>
       </c>
       <c r="B38" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D38" t="s">
         <v>326</v>
@@ -10798,13 +10720,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>20200005</v>
+        <v>11000009</v>
       </c>
       <c r="B39" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="C39" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="D39" t="s">
         <v>326</v>
@@ -10812,13 +10734,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>20200006</v>
+        <v>11010001</v>
       </c>
       <c r="B40" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="D40" t="s">
         <v>326</v>
@@ -10826,13 +10748,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>20200007</v>
+        <v>20100001</v>
       </c>
       <c r="B41" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C41" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="D41" t="s">
         <v>326</v>
@@ -10840,13 +10762,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>20200008</v>
+        <v>20100002</v>
       </c>
       <c r="B42" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="C42" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="D42" t="s">
         <v>326</v>
@@ -10854,13 +10776,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>20200009</v>
+        <v>20100003</v>
       </c>
       <c r="B43" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="D43" t="s">
         <v>326</v>
@@ -10868,13 +10790,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>20200010</v>
+        <v>20100004</v>
       </c>
       <c r="B44" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="C44" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="D44" t="s">
         <v>326</v>
@@ -10882,13 +10804,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>20200011</v>
+        <v>20100005</v>
       </c>
       <c r="B45" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="C45" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="D45" t="s">
         <v>326</v>
@@ -10896,13 +10818,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>20300001</v>
+        <v>20100006</v>
       </c>
       <c r="B46" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="C46" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="D46" t="s">
         <v>326</v>
@@ -10910,13 +10832,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>20300002</v>
+        <v>20100007</v>
       </c>
       <c r="B47" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="C47" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="D47" t="s">
         <v>326</v>
@@ -10924,13 +10846,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>20300003</v>
+        <v>20200001</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="C48" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="D48" t="s">
         <v>326</v>
@@ -10938,13 +10860,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>20300004</v>
+        <v>20200002</v>
       </c>
       <c r="B49" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="C49" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="D49" t="s">
         <v>326</v>
@@ -10952,13 +10874,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>20300005</v>
+        <v>20200003</v>
       </c>
       <c r="B50" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="C50" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="D50" t="s">
         <v>326</v>
@@ -10966,13 +10888,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>21000001</v>
+        <v>20200004</v>
       </c>
       <c r="B51" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="C51" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="D51" t="s">
         <v>326</v>
@@ -10980,13 +10902,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>21000002</v>
+        <v>20200005</v>
       </c>
       <c r="B52" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="C52" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="D52" t="s">
         <v>326</v>
@@ -10994,13 +10916,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>21000003</v>
+        <v>20200006</v>
       </c>
       <c r="B53" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="C53" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="D53" t="s">
         <v>326</v>
@@ -11008,13 +10930,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>21000004</v>
+        <v>20200007</v>
       </c>
       <c r="B54" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="C54" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="D54" t="s">
         <v>326</v>
@@ -11022,13 +10944,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>21000005</v>
+        <v>20200008</v>
       </c>
       <c r="B55" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C55" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D55" t="s">
         <v>326</v>
@@ -11036,13 +10958,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>21000006</v>
+        <v>20200009</v>
       </c>
       <c r="B56" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="C56" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="D56" t="s">
         <v>326</v>
@@ -11050,13 +10972,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>21000007</v>
+        <v>20200010</v>
       </c>
       <c r="B57" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="C57" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="D57" t="s">
         <v>326</v>
@@ -11064,13 +10986,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>21000008</v>
+        <v>20200011</v>
       </c>
       <c r="B58" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="C58" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="D58" t="s">
         <v>326</v>
@@ -11078,13 +11000,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>21000009</v>
+        <v>20300001</v>
       </c>
       <c r="B59" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C59" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="D59" t="s">
         <v>326</v>
@@ -11092,13 +11014,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>21000010</v>
+        <v>20300002</v>
       </c>
       <c r="B60" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="C60" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="D60" t="s">
         <v>326</v>
@@ -11106,13 +11028,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>21010001</v>
+        <v>20300003</v>
       </c>
       <c r="B61" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="C61" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
       <c r="D61" t="s">
         <v>326</v>
@@ -11120,13 +11042,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>21010002</v>
+        <v>20300004</v>
       </c>
       <c r="B62" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="C62" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="D62" t="s">
         <v>326</v>
@@ -11134,13 +11056,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>21010003</v>
+        <v>20300005</v>
       </c>
       <c r="B63" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="C63" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="D63" t="s">
         <v>326</v>
@@ -11148,13 +11070,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>21010004</v>
+        <v>21000001</v>
       </c>
       <c r="B64" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="C64" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -11162,13 +11084,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>21010005</v>
+        <v>21000002</v>
       </c>
       <c r="B65" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="C65" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="D65" t="s">
         <v>326</v>
@@ -11176,13 +11098,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>21010006</v>
+        <v>21000003</v>
       </c>
       <c r="B66" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="C66" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="D66" t="s">
         <v>326</v>
@@ -11190,13 +11112,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>21010007</v>
+        <v>21000004</v>
       </c>
       <c r="B67" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C67" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="D67" t="s">
         <v>326</v>
@@ -11204,13 +11126,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>21010008</v>
+        <v>21000005</v>
       </c>
       <c r="B68" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C68" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="D68" t="s">
         <v>326</v>
@@ -11218,13 +11140,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>21010009</v>
+        <v>21000006</v>
       </c>
       <c r="B69" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="C69" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="D69" t="s">
         <v>326</v>
@@ -11232,13 +11154,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>21010010</v>
+        <v>21000007</v>
       </c>
       <c r="B70" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="D70" t="s">
         <v>326</v>
@@ -11246,13 +11168,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>21010011</v>
+        <v>21000008</v>
       </c>
       <c r="B71" t="s">
-        <v>364</v>
+        <v>432</v>
       </c>
       <c r="C71" t="s">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="D71" t="s">
         <v>326</v>
@@ -11260,13 +11182,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>21010012</v>
+        <v>21000009</v>
       </c>
       <c r="B72" t="s">
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="C72" t="s">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="D72" t="s">
         <v>326</v>
@@ -11274,13 +11196,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>21010013</v>
+        <v>21000010</v>
       </c>
       <c r="B73" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C73" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="D73" t="s">
         <v>326</v>
@@ -11288,13 +11210,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>21010014</v>
+        <v>21010001</v>
       </c>
       <c r="B74" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C74" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D74" t="s">
         <v>326</v>
@@ -11302,13 +11224,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>21010015</v>
+        <v>21010002</v>
       </c>
       <c r="B75" t="s">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="C75" t="s">
-        <v>451</v>
+        <v>357</v>
       </c>
       <c r="D75" t="s">
         <v>326</v>
@@ -11316,13 +11238,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>21010016</v>
+        <v>21010003</v>
       </c>
       <c r="B76" t="s">
-        <v>452</v>
+        <v>358</v>
       </c>
       <c r="C76" t="s">
-        <v>453</v>
+        <v>359</v>
       </c>
       <c r="D76" t="s">
         <v>326</v>
@@ -11330,13 +11252,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>21010017</v>
+        <v>21010004</v>
       </c>
       <c r="B77" t="s">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="C77" t="s">
-        <v>455</v>
+        <v>361</v>
       </c>
       <c r="D77" t="s">
         <v>326</v>
@@ -11344,13 +11266,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>21010018</v>
+        <v>21010005</v>
       </c>
       <c r="B78" t="s">
-        <v>456</v>
+        <v>362</v>
       </c>
       <c r="C78" t="s">
-        <v>457</v>
+        <v>363</v>
       </c>
       <c r="D78" t="s">
         <v>326</v>
@@ -11358,13 +11280,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>21010019</v>
+        <v>21010006</v>
       </c>
       <c r="B79" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="C79" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="D79" t="s">
         <v>326</v>
@@ -11372,13 +11294,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>21010020</v>
+        <v>21010007</v>
       </c>
       <c r="B80" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C80" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="D80" t="s">
         <v>326</v>
@@ -11386,13 +11308,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>30100001</v>
+        <v>21010008</v>
       </c>
       <c r="B81" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="C81" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="D81" t="s">
         <v>326</v>
@@ -11400,13 +11322,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>30100002</v>
+        <v>21010009</v>
       </c>
       <c r="B82" t="s">
-        <v>374</v>
+        <v>444</v>
       </c>
       <c r="C82" t="s">
-        <v>375</v>
+        <v>445</v>
       </c>
       <c r="D82" t="s">
         <v>326</v>
@@ -11414,13 +11336,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>30100003</v>
+        <v>21010010</v>
       </c>
       <c r="B83" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="C83" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D83" t="s">
         <v>326</v>
@@ -11428,13 +11350,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>30100004</v>
+        <v>21010011</v>
       </c>
       <c r="B84" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C84" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D84" t="s">
         <v>326</v>
@@ -11442,13 +11364,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>30100005</v>
+        <v>21010012</v>
       </c>
       <c r="B85" t="s">
-        <v>466</v>
+        <v>366</v>
       </c>
       <c r="C85" t="s">
-        <v>467</v>
+        <v>367</v>
       </c>
       <c r="D85" t="s">
         <v>326</v>
@@ -11456,13 +11378,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>30100006</v>
+        <v>21010013</v>
       </c>
       <c r="B86" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="C86" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="D86" t="s">
         <v>326</v>
@@ -11470,13 +11392,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>30100007</v>
+        <v>21010014</v>
       </c>
       <c r="B87" t="s">
-        <v>470</v>
+        <v>368</v>
       </c>
       <c r="C87" t="s">
-        <v>471</v>
+        <v>369</v>
       </c>
       <c r="D87" t="s">
         <v>326</v>
@@ -11484,13 +11406,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>30100008</v>
+        <v>21010015</v>
       </c>
       <c r="B88" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="C88" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="D88" t="s">
         <v>326</v>
@@ -11498,13 +11420,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>30100009</v>
+        <v>21010016</v>
       </c>
       <c r="B89" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="C89" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="D89" t="s">
         <v>326</v>
@@ -11512,13 +11434,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>30100010</v>
+        <v>21010017</v>
       </c>
       <c r="B90" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="C90" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="D90" t="s">
         <v>326</v>
@@ -11526,13 +11448,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>30100011</v>
+        <v>21010018</v>
       </c>
       <c r="B91" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="C91" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="D91" t="s">
         <v>326</v>
@@ -11540,13 +11462,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>30100012</v>
+        <v>21010019</v>
       </c>
       <c r="B92" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="C92" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="D92" t="s">
         <v>326</v>
@@ -11554,13 +11476,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>30100013</v>
+        <v>21010020</v>
       </c>
       <c r="B93" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="C93" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="D93" t="s">
         <v>326</v>
@@ -11568,13 +11490,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>30100014</v>
+        <v>30100001</v>
       </c>
       <c r="B94" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="C94" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="D94" t="s">
         <v>326</v>
@@ -11582,13 +11504,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>30100015</v>
+        <v>30100002</v>
       </c>
       <c r="B95" t="s">
-        <v>486</v>
+        <v>374</v>
       </c>
       <c r="C95" t="s">
-        <v>487</v>
+        <v>375</v>
       </c>
       <c r="D95" t="s">
         <v>326</v>
@@ -11596,13 +11518,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>30100016</v>
+        <v>30100003</v>
       </c>
       <c r="B96" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="C96" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="D96" t="s">
         <v>326</v>
@@ -11610,13 +11532,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>30100017</v>
+        <v>30100004</v>
       </c>
       <c r="B97" t="s">
-        <v>490</v>
+        <v>372</v>
       </c>
       <c r="C97" t="s">
-        <v>491</v>
+        <v>373</v>
       </c>
       <c r="D97" t="s">
         <v>326</v>
@@ -11624,13 +11546,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>30100018</v>
+        <v>30100005</v>
       </c>
       <c r="B98" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="D98" t="s">
         <v>326</v>
@@ -11638,13 +11560,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>30100019</v>
+        <v>30100006</v>
       </c>
       <c r="B99" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="C99" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="D99" t="s">
         <v>326</v>
@@ -11652,13 +11574,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>30100020</v>
+        <v>30100007</v>
       </c>
       <c r="B100" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="C100" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="D100" t="s">
         <v>326</v>
@@ -11666,13 +11588,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>40100001</v>
+        <v>30100008</v>
       </c>
       <c r="B101" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="C101" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="D101" t="s">
         <v>326</v>
@@ -11680,13 +11602,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>40200001</v>
+        <v>30100009</v>
       </c>
       <c r="B102" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="C102" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="D102" t="s">
         <v>326</v>
@@ -11694,13 +11616,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>40200002</v>
+        <v>30100010</v>
       </c>
       <c r="B103" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="C103" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="D103" t="s">
         <v>326</v>
@@ -11708,13 +11630,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>40200003</v>
+        <v>30100011</v>
       </c>
       <c r="B104" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="C104" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="D104" t="s">
         <v>326</v>
@@ -11722,13 +11644,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>40200004</v>
+        <v>30100012</v>
       </c>
       <c r="B105" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="C105" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="D105" t="s">
         <v>326</v>
@@ -11736,13 +11658,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>40200005</v>
+        <v>30100013</v>
       </c>
       <c r="B106" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="C106" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="D106" t="s">
         <v>326</v>
@@ -11750,13 +11672,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>40200006</v>
+        <v>30100014</v>
       </c>
       <c r="B107" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="C107" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="D107" t="s">
         <v>326</v>
@@ -11764,13 +11686,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>40300001</v>
+        <v>30100015</v>
       </c>
       <c r="B108" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="C108" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="D108" t="s">
         <v>326</v>
@@ -11778,13 +11700,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>40300002</v>
+        <v>30100016</v>
       </c>
       <c r="B109" t="s">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="C109" t="s">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="D109" t="s">
         <v>326</v>
@@ -11792,13 +11714,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>40300003</v>
+        <v>30100017</v>
       </c>
       <c r="B110" t="s">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="C110" t="s">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="D110" t="s">
         <v>326</v>
@@ -11806,13 +11728,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>40300004</v>
+        <v>30100018</v>
       </c>
       <c r="B111" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="C111" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="D111" t="s">
         <v>326</v>
@@ -11820,13 +11742,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>41000001</v>
+        <v>30100019</v>
       </c>
       <c r="B112" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="C112" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="D112" t="s">
         <v>326</v>
@@ -11834,13 +11756,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>41000002</v>
+        <v>30100020</v>
       </c>
       <c r="B113" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="C113" t="s">
-        <v>522</v>
+        <v>429</v>
       </c>
       <c r="D113" t="s">
         <v>326</v>
@@ -11848,13 +11770,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>41000003</v>
+        <v>40100001</v>
       </c>
       <c r="B114" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="C114" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="D114" t="s">
         <v>326</v>
@@ -11862,13 +11784,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
-        <v>41000004</v>
+        <v>40200001</v>
       </c>
       <c r="B115" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="C115" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="D115" t="s">
         <v>326</v>
@@ -11876,13 +11798,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116">
-        <v>41000005</v>
+        <v>40200002</v>
       </c>
       <c r="B116" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="C116" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="D116" t="s">
         <v>326</v>
@@ -11890,13 +11812,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117">
-        <v>50100001</v>
+        <v>40200003</v>
       </c>
       <c r="B117" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="C117" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -11904,13 +11826,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>50100002</v>
+        <v>40200004</v>
       </c>
       <c r="B118" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C118" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="D118" t="s">
         <v>326</v>
@@ -11918,13 +11840,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>50100003</v>
+        <v>40200005</v>
       </c>
       <c r="B119" t="s">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="C119" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="D119" t="s">
         <v>326</v>
@@ -11932,13 +11854,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>50200001</v>
+        <v>40200006</v>
       </c>
       <c r="B120" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="C120" t="s">
-        <v>534</v>
+        <v>510</v>
       </c>
       <c r="D120" t="s">
         <v>326</v>
@@ -11946,13 +11868,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>50200002</v>
+        <v>40300001</v>
       </c>
       <c r="B121" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="C121" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="D121" t="s">
         <v>326</v>
@@ -11960,13 +11882,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>50200003</v>
+        <v>40300002</v>
       </c>
       <c r="B122" t="s">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="C122" t="s">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="D122" t="s">
         <v>326</v>
@@ -11974,13 +11896,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123">
-        <v>50300001</v>
+        <v>40300003</v>
       </c>
       <c r="B123" t="s">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="C123" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="D123" t="s">
         <v>326</v>
@@ -11988,13 +11910,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124">
-        <v>50300002</v>
+        <v>40300004</v>
       </c>
       <c r="B124" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="C124" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="D124" t="s">
         <v>326</v>
@@ -12002,13 +11924,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125">
-        <v>50500001</v>
+        <v>41000001</v>
       </c>
       <c r="B125" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="C125" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="D125" t="s">
         <v>326</v>
@@ -12016,13 +11938,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126">
-        <v>50500002</v>
+        <v>41000002</v>
       </c>
       <c r="B126" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="C126" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="D126" t="s">
         <v>326</v>
@@ -12030,13 +11952,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>50500003</v>
+        <v>41000003</v>
       </c>
       <c r="B127" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="C127" t="s">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="D127" t="s">
         <v>326</v>
@@ -12044,13 +11966,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>50500004</v>
+        <v>41000004</v>
       </c>
       <c r="B128" t="s">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="C128" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="D128" t="s">
         <v>326</v>
@@ -12058,13 +11980,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>50500005</v>
+        <v>41000005</v>
       </c>
       <c r="B129" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="C129" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="D129" t="s">
         <v>326</v>
@@ -12072,13 +11994,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130">
-        <v>51010001</v>
+        <v>50100001</v>
       </c>
       <c r="B130" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="C130" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="D130" t="s">
         <v>326</v>
@@ -12086,13 +12008,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131">
-        <v>51010002</v>
+        <v>50100002</v>
       </c>
       <c r="B131" t="s">
-        <v>268</v>
+        <v>484</v>
       </c>
       <c r="C131" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
@@ -12100,13 +12022,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>51010003</v>
+        <v>50100003</v>
       </c>
       <c r="B132" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="C132" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="D132" t="s">
         <v>326</v>
@@ -12114,13 +12036,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>60100001</v>
+        <v>50200001</v>
       </c>
       <c r="B133" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="C133" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="D133" t="s">
         <v>326</v>
@@ -12128,13 +12050,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>60100002</v>
+        <v>50200002</v>
       </c>
       <c r="B134" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="C134" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="D134" t="s">
         <v>326</v>
@@ -12142,13 +12064,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>60100003</v>
+        <v>50200003</v>
       </c>
       <c r="B135" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="C135" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="D135" t="s">
         <v>326</v>
@@ -12156,13 +12078,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>60100004</v>
+        <v>50300001</v>
       </c>
       <c r="B136" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="C136" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D136" t="s">
         <v>326</v>
@@ -12170,13 +12092,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>60100005</v>
+        <v>50300002</v>
       </c>
       <c r="B137" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="C137" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="D137" t="s">
         <v>326</v>
@@ -12184,13 +12106,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>60100006</v>
+        <v>50500001</v>
       </c>
       <c r="B138" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="C138" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="D138" t="s">
         <v>326</v>
@@ -12198,13 +12120,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>60100007</v>
+        <v>50500002</v>
       </c>
       <c r="B139" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="C139" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="D139" t="s">
         <v>326</v>
@@ -12212,13 +12134,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>60100008</v>
+        <v>50500003</v>
       </c>
       <c r="B140" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="C140" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="D140" t="s">
         <v>326</v>
@@ -12226,13 +12148,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>60100009</v>
+        <v>50500004</v>
       </c>
       <c r="B141" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="C141" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="D141" t="s">
         <v>326</v>
@@ -12240,13 +12162,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>60100010</v>
+        <v>50500005</v>
       </c>
       <c r="B142" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="C142" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="D142" t="s">
         <v>326</v>
@@ -12254,13 +12176,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>60200001</v>
+        <v>51010001</v>
       </c>
       <c r="B143" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="C143" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="D143" t="s">
         <v>326</v>
@@ -12268,13 +12190,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>60200002</v>
+        <v>51010002</v>
       </c>
       <c r="B144" t="s">
-        <v>575</v>
+        <v>268</v>
       </c>
       <c r="C144" t="s">
-        <v>576</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
         <v>326</v>
@@ -12282,13 +12204,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>60300001</v>
+        <v>51010003</v>
       </c>
       <c r="B145" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="C145" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="D145" t="s">
         <v>326</v>
@@ -12296,13 +12218,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>60300002</v>
+        <v>60100001</v>
       </c>
       <c r="B146" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="C146" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="D146" t="s">
         <v>326</v>
@@ -12310,13 +12232,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>60300003</v>
+        <v>60100002</v>
       </c>
       <c r="B147" t="s">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="C147" t="s">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="D147" t="s">
         <v>326</v>
@@ -12324,13 +12246,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>60300004</v>
+        <v>60100003</v>
       </c>
       <c r="B148" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="C148" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="D148" t="s">
         <v>326</v>
@@ -12338,13 +12260,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>60300005</v>
+        <v>60100004</v>
       </c>
       <c r="B149" t="s">
-        <v>585</v>
+        <v>529</v>
       </c>
       <c r="C149" t="s">
-        <v>586</v>
+        <v>530</v>
       </c>
       <c r="D149" t="s">
         <v>326</v>
@@ -12352,13 +12274,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
-        <v>61010001</v>
+        <v>60100005</v>
       </c>
       <c r="B150" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C150" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="D150" t="s">
         <v>326</v>
@@ -12366,13 +12288,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>61010002</v>
+        <v>60100006</v>
       </c>
       <c r="B151" t="s">
-        <v>370</v>
+        <v>565</v>
       </c>
       <c r="C151" t="s">
-        <v>371</v>
+        <v>566</v>
       </c>
       <c r="D151" t="s">
         <v>326</v>
@@ -12380,13 +12302,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>61010003</v>
+        <v>60100007</v>
       </c>
       <c r="B152" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="C152" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="D152" t="s">
         <v>326</v>
@@ -12394,13 +12316,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>61010004</v>
+        <v>60100008</v>
       </c>
       <c r="B153" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="C153" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="D153" t="s">
         <v>326</v>
@@ -12408,13 +12330,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>61010005</v>
+        <v>60100009</v>
       </c>
       <c r="B154" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="C154" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="D154" t="s">
         <v>326</v>
@@ -12422,13 +12344,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155">
-        <v>61010006</v>
+        <v>60100010</v>
       </c>
       <c r="B155" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="C155" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="D155" t="s">
         <v>326</v>
@@ -12436,13 +12358,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156">
-        <v>61010007</v>
+        <v>60200001</v>
       </c>
       <c r="B156" t="s">
-        <v>597</v>
+        <v>499</v>
       </c>
       <c r="C156" t="s">
-        <v>598</v>
+        <v>500</v>
       </c>
       <c r="D156" t="s">
         <v>326</v>
@@ -12450,13 +12372,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157">
-        <v>61010008</v>
+        <v>60200002</v>
       </c>
       <c r="B157" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C157" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="D157" t="s">
         <v>326</v>
@@ -12464,13 +12386,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158">
-        <v>61010009</v>
+        <v>60300001</v>
       </c>
       <c r="B158" t="s">
-        <v>354</v>
+        <v>577</v>
       </c>
       <c r="C158" t="s">
-        <v>355</v>
+        <v>578</v>
       </c>
       <c r="D158" t="s">
         <v>326</v>
@@ -12478,13 +12400,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159">
-        <v>61010010</v>
+        <v>60300002</v>
       </c>
       <c r="B159" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="C159" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="D159" t="s">
         <v>326</v>
@@ -12492,13 +12414,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160">
-        <v>61010011</v>
+        <v>60300003</v>
       </c>
       <c r="B160" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="C160" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="D160" t="s">
         <v>326</v>
@@ -12506,13 +12428,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>61010012</v>
+        <v>60300004</v>
       </c>
       <c r="B161" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="C161" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="D161" t="s">
         <v>326</v>
@@ -12520,13 +12442,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>61010013</v>
+        <v>60300005</v>
       </c>
       <c r="B162" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="C162" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="D162" t="s">
         <v>326</v>
@@ -12534,13 +12456,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>61010014</v>
+        <v>61010001</v>
       </c>
       <c r="B163" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="C163" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="D163" t="s">
         <v>326</v>
@@ -12548,13 +12470,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>61010015</v>
+        <v>61010002</v>
       </c>
       <c r="B164" t="s">
-        <v>611</v>
+        <v>370</v>
       </c>
       <c r="C164" t="s">
-        <v>612</v>
+        <v>371</v>
       </c>
       <c r="D164" t="s">
         <v>326</v>
@@ -12562,13 +12484,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>61010016</v>
+        <v>61010003</v>
       </c>
       <c r="B165" t="s">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="C165" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="D165" t="s">
         <v>326</v>
@@ -12576,13 +12498,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
-        <v>61010017</v>
+        <v>61010004</v>
       </c>
       <c r="B166" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="C166" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="D166" t="s">
         <v>326</v>
@@ -12590,13 +12512,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167">
-        <v>61010018</v>
+        <v>61010005</v>
       </c>
       <c r="B167" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="C167" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="D167" t="s">
         <v>326</v>
@@ -12604,13 +12526,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168">
-        <v>61010019</v>
+        <v>61010006</v>
       </c>
       <c r="B168" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
       <c r="C168" t="s">
-        <v>620</v>
+        <v>596</v>
       </c>
       <c r="D168" t="s">
         <v>326</v>
@@ -12618,13 +12540,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169">
-        <v>61010020</v>
+        <v>61010007</v>
       </c>
       <c r="B169" t="s">
-        <v>621</v>
+        <v>597</v>
       </c>
       <c r="C169" t="s">
-        <v>431</v>
+        <v>598</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
@@ -12632,13 +12554,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170">
-        <v>70100001</v>
+        <v>61010008</v>
       </c>
       <c r="B170" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="C170" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="D170" t="s">
         <v>326</v>
@@ -12646,13 +12568,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171">
-        <v>70200001</v>
+        <v>61010009</v>
       </c>
       <c r="B171" t="s">
-        <v>624</v>
+        <v>354</v>
       </c>
       <c r="C171" t="s">
-        <v>625</v>
+        <v>355</v>
       </c>
       <c r="D171" t="s">
         <v>326</v>
@@ -12660,13 +12582,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172">
-        <v>70200002</v>
+        <v>61010010</v>
       </c>
       <c r="B172" t="s">
-        <v>535</v>
+        <v>601</v>
       </c>
       <c r="C172" t="s">
-        <v>536</v>
+        <v>602</v>
       </c>
       <c r="D172" t="s">
         <v>326</v>
@@ -12674,13 +12596,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173">
-        <v>70300001</v>
+        <v>61010011</v>
       </c>
       <c r="B173" t="s">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="C173" t="s">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="D173" t="s">
         <v>326</v>
@@ -12688,13 +12610,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174">
-        <v>70300002</v>
+        <v>61010012</v>
       </c>
       <c r="B174" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="C174" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="D174" t="s">
         <v>326</v>
@@ -12702,13 +12624,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>70300003</v>
+        <v>61010013</v>
       </c>
       <c r="B175" t="s">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="C175" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="D175" t="s">
         <v>326</v>
@@ -12716,13 +12638,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176">
-        <v>70300004</v>
+        <v>61010014</v>
       </c>
       <c r="B176" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="C176" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="D176" t="s">
         <v>326</v>
@@ -12730,13 +12652,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177">
-        <v>71000001</v>
+        <v>61010015</v>
       </c>
       <c r="B177" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="C177" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="D177" t="s">
         <v>326</v>
@@ -12744,13 +12666,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178">
-        <v>71000002</v>
+        <v>61010016</v>
       </c>
       <c r="B178" t="s">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="C178" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="D178" t="s">
         <v>326</v>
@@ -12758,13 +12680,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179">
-        <v>71000003</v>
+        <v>61010017</v>
       </c>
       <c r="B179" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="C179" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="D179" t="s">
         <v>326</v>
@@ -12772,13 +12694,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180">
-        <v>71010001</v>
+        <v>61010018</v>
       </c>
       <c r="B180" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
       <c r="C180" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="D180" t="s">
         <v>326</v>
@@ -12786,13 +12708,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181">
-        <v>71010002</v>
+        <v>61010019</v>
       </c>
       <c r="B181" t="s">
-        <v>642</v>
+        <v>619</v>
       </c>
       <c r="C181" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="D181" t="s">
         <v>326</v>
@@ -12800,13 +12722,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182">
-        <v>71010003</v>
+        <v>61010020</v>
       </c>
       <c r="B182" t="s">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="C182" t="s">
-        <v>645</v>
+        <v>431</v>
       </c>
       <c r="D182" t="s">
         <v>326</v>
@@ -12814,13 +12736,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183">
-        <v>71010004</v>
+        <v>70100001</v>
       </c>
       <c r="B183" t="s">
-        <v>646</v>
+        <v>622</v>
       </c>
       <c r="C183" t="s">
-        <v>647</v>
+        <v>623</v>
       </c>
       <c r="D183" t="s">
         <v>326</v>
@@ -12828,13 +12750,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184">
-        <v>71010005</v>
+        <v>70200001</v>
       </c>
       <c r="B184" t="s">
-        <v>648</v>
+        <v>624</v>
       </c>
       <c r="C184" t="s">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="D184" t="s">
         <v>326</v>
@@ -12842,15 +12764,197 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185">
+        <v>70200002</v>
+      </c>
+      <c r="B185" t="s">
+        <v>535</v>
+      </c>
+      <c r="C185" t="s">
+        <v>536</v>
+      </c>
+      <c r="D185" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186">
+        <v>70300001</v>
+      </c>
+      <c r="B186" t="s">
+        <v>626</v>
+      </c>
+      <c r="C186" t="s">
+        <v>627</v>
+      </c>
+      <c r="D186" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187">
+        <v>70300002</v>
+      </c>
+      <c r="B187" t="s">
+        <v>628</v>
+      </c>
+      <c r="C187" t="s">
+        <v>629</v>
+      </c>
+      <c r="D187" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188">
+        <v>70300003</v>
+      </c>
+      <c r="B188" t="s">
+        <v>630</v>
+      </c>
+      <c r="C188" t="s">
+        <v>631</v>
+      </c>
+      <c r="D188" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189">
+        <v>70300004</v>
+      </c>
+      <c r="B189" t="s">
+        <v>632</v>
+      </c>
+      <c r="C189" t="s">
+        <v>633</v>
+      </c>
+      <c r="D189" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190">
+        <v>71000001</v>
+      </c>
+      <c r="B190" t="s">
+        <v>634</v>
+      </c>
+      <c r="C190" t="s">
+        <v>635</v>
+      </c>
+      <c r="D190" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191">
+        <v>71000002</v>
+      </c>
+      <c r="B191" t="s">
+        <v>636</v>
+      </c>
+      <c r="C191" t="s">
+        <v>637</v>
+      </c>
+      <c r="D191" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192">
+        <v>71000003</v>
+      </c>
+      <c r="B192" t="s">
+        <v>638</v>
+      </c>
+      <c r="C192" t="s">
+        <v>639</v>
+      </c>
+      <c r="D192" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193">
+        <v>71010001</v>
+      </c>
+      <c r="B193" t="s">
+        <v>640</v>
+      </c>
+      <c r="C193" t="s">
+        <v>641</v>
+      </c>
+      <c r="D193" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194">
+        <v>71010002</v>
+      </c>
+      <c r="B194" t="s">
+        <v>642</v>
+      </c>
+      <c r="C194" t="s">
+        <v>643</v>
+      </c>
+      <c r="D194" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195">
+        <v>71010003</v>
+      </c>
+      <c r="B195" t="s">
+        <v>644</v>
+      </c>
+      <c r="C195" t="s">
+        <v>645</v>
+      </c>
+      <c r="D195" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196">
+        <v>71010004</v>
+      </c>
+      <c r="B196" t="s">
+        <v>646</v>
+      </c>
+      <c r="C196" t="s">
+        <v>647</v>
+      </c>
+      <c r="D196" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197">
+        <v>71010005</v>
+      </c>
+      <c r="B197" t="s">
+        <v>648</v>
+      </c>
+      <c r="C197" t="s">
+        <v>649</v>
+      </c>
+      <c r="D197" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198">
         <v>71010006</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B198" t="s">
         <v>650</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C198" t="s">
         <v>590</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D198" t="s">
         <v>326</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="1351">
   <si>
     <t>id</t>
   </si>
@@ -1030,37 +1030,64 @@
     <t>编织戒指</t>
   </si>
   <si>
+    <t>钢头盔</t>
+  </si>
+  <si>
+    <t>Steel Helmet</t>
+  </si>
+  <si>
+    <t>大魔法师帽</t>
+  </si>
+  <si>
     <t>铁头盔</t>
   </si>
   <si>
     <t>Iron Helmet</t>
   </si>
   <si>
-    <t>钢头盔</t>
-  </si>
-  <si>
-    <t>Steel Helmet</t>
-  </si>
-  <si>
-    <t>战斗魔法师帽</t>
-  </si>
-  <si>
-    <t>Battle Mage Hat</t>
-  </si>
-  <si>
     <t>射手兜帽</t>
   </si>
   <si>
     <t>Archer Hood</t>
   </si>
   <si>
-    <t>战士上衣</t>
+    <t>魔法师帽</t>
+  </si>
+  <si>
+    <t>精英魔法师兜帽</t>
+  </si>
+  <si>
+    <t>暗杀者兜帽</t>
+  </si>
+  <si>
+    <t>骑士头盔</t>
+  </si>
+  <si>
+    <t>死灵师面具</t>
+  </si>
+  <si>
+    <t>金骑士头盔</t>
+  </si>
+  <si>
+    <t>勇者头盔</t>
+  </si>
+  <si>
+    <t>魔力帽</t>
+  </si>
+  <si>
+    <t>暗黑骑士头盔</t>
+  </si>
+  <si>
+    <t>银色骑士头盔</t>
+  </si>
+  <si>
+    <t>钢盔甲上衣</t>
   </si>
   <si>
     <t>Warrior Chest</t>
   </si>
   <si>
-    <t>战斗魔法师上衣</t>
+    <t>大魔法师上衣</t>
   </si>
   <si>
     <t>Battle Mage Robe</t>
@@ -1078,13 +1105,52 @@
     <t>Archer Garb</t>
   </si>
   <si>
-    <t>战士裤子</t>
+    <t>魔法师上衣</t>
+  </si>
+  <si>
+    <t>狩猎者上衣</t>
+  </si>
+  <si>
+    <t>精英魔法师上衣</t>
+  </si>
+  <si>
+    <t>暗杀者上衣</t>
+  </si>
+  <si>
+    <t>竞技者上衣</t>
+  </si>
+  <si>
+    <t>骑士盔甲</t>
+  </si>
+  <si>
+    <t>治疗师长袍</t>
+  </si>
+  <si>
+    <t>死灵师长袍</t>
+  </si>
+  <si>
+    <t>金骑士盔甲</t>
+  </si>
+  <si>
+    <t>勇者上衣</t>
+  </si>
+  <si>
+    <t>魔力法师上衣</t>
+  </si>
+  <si>
+    <t>暗黑骑士盔甲</t>
+  </si>
+  <si>
+    <t>银色骑士盔甲</t>
+  </si>
+  <si>
+    <t>钢盔甲裤</t>
   </si>
   <si>
     <t>Warrior Pants</t>
   </si>
   <si>
-    <t>战斗魔法师裤子</t>
+    <t>大魔法师裤</t>
   </si>
   <si>
     <t>Battle Mage Trousers</t>
@@ -1102,6 +1168,45 @@
     <t>Archer Leggings</t>
   </si>
   <si>
+    <t>魔法师裤</t>
+  </si>
+  <si>
+    <t>狩猎者裤</t>
+  </si>
+  <si>
+    <t>精英魔法师裤</t>
+  </si>
+  <si>
+    <t>暗杀者裤</t>
+  </si>
+  <si>
+    <t>竞技者裤</t>
+  </si>
+  <si>
+    <t>骑士裤</t>
+  </si>
+  <si>
+    <t>治疗师裤</t>
+  </si>
+  <si>
+    <t>死灵师裤</t>
+  </si>
+  <si>
+    <t>金骑士裤</t>
+  </si>
+  <si>
+    <t>勇者裤</t>
+  </si>
+  <si>
+    <t>魔力法师裤</t>
+  </si>
+  <si>
+    <t>暗黑骑士裤</t>
+  </si>
+  <si>
+    <t>银色骑士裤</t>
+  </si>
+  <si>
     <t>钢剑</t>
   </si>
   <si>
@@ -1156,12 +1261,33 @@
     <t>Star Staff</t>
   </si>
   <si>
+    <t>电法杖</t>
+  </si>
+  <si>
+    <t>大剑</t>
+  </si>
+  <si>
+    <t>死灵法杖</t>
+  </si>
+  <si>
     <t>木弓</t>
   </si>
   <si>
     <t>Wooden Bow</t>
   </si>
   <si>
+    <t>钢弓</t>
+  </si>
+  <si>
+    <t>红木弓</t>
+  </si>
+  <si>
+    <t>冒险者盾剑</t>
+  </si>
+  <si>
+    <t>勇者盾剑</t>
+  </si>
+  <si>
     <t>皇冠</t>
   </si>
   <si>
@@ -1180,9 +1306,6 @@
     <t>Exotic Turban</t>
   </si>
   <si>
-    <t>魔力帽</t>
-  </si>
-  <si>
     <t>Mana Cap</t>
   </si>
   <si>
@@ -1276,13 +1399,13 @@
     <t>Tattered Belt</t>
   </si>
   <si>
+    <t>破烂法裤</t>
+  </si>
+  <si>
+    <t>Azure Belt</t>
+  </si>
+  <si>
     <t>蔚蓝腰带</t>
-  </si>
-  <si>
-    <t>Azure Belt</t>
-  </si>
-  <si>
-    <t>破烂法裤</t>
   </si>
   <si>
     <t>Tattered Robe Bottoms</t>
@@ -7243,13 +7366,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
       <c r="C4" t="s">
-        <v>904</v>
+        <v>945</v>
       </c>
       <c r="D4" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7257,13 +7380,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="C5" t="s">
-        <v>907</v>
+        <v>948</v>
       </c>
       <c r="D5" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7271,13 +7394,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>908</v>
+        <v>949</v>
       </c>
       <c r="C6" t="s">
-        <v>909</v>
+        <v>950</v>
       </c>
       <c r="D6" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7285,13 +7408,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>910</v>
+        <v>951</v>
       </c>
       <c r="C7" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="D7" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7299,13 +7422,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>912</v>
+        <v>953</v>
       </c>
       <c r="C8" t="s">
-        <v>913</v>
+        <v>954</v>
       </c>
       <c r="D8" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7313,13 +7436,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>914</v>
+        <v>955</v>
       </c>
       <c r="C9" t="s">
-        <v>915</v>
+        <v>956</v>
       </c>
       <c r="D9" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7327,13 +7450,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>916</v>
+        <v>957</v>
       </c>
       <c r="C10" t="s">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="D10" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -7399,13 +7522,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>986</v>
+        <v>1027</v>
       </c>
       <c r="C4" t="s">
-        <v>987</v>
+        <v>1028</v>
       </c>
       <c r="D4" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7413,13 +7536,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>988</v>
+        <v>1029</v>
       </c>
       <c r="C5" t="s">
-        <v>989</v>
+        <v>1030</v>
       </c>
       <c r="D5" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7427,13 +7550,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>990</v>
+        <v>1031</v>
       </c>
       <c r="C6" t="s">
-        <v>991</v>
+        <v>1032</v>
       </c>
       <c r="D6" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7441,13 +7564,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>992</v>
+        <v>1033</v>
       </c>
       <c r="C7" t="s">
-        <v>993</v>
+        <v>1034</v>
       </c>
       <c r="D7" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7455,10 +7578,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>994</v>
+        <v>1035</v>
       </c>
       <c r="D8" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7466,10 +7589,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>995</v>
+        <v>1036</v>
       </c>
       <c r="D9" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7477,10 +7600,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>996</v>
+        <v>1037</v>
       </c>
       <c r="D10" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7488,10 +7611,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>662</v>
+        <v>703</v>
       </c>
       <c r="D11" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:4">
@@ -7499,10 +7622,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>997</v>
+        <v>1038</v>
       </c>
       <c r="D12" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:4">
@@ -7510,13 +7633,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>998</v>
+        <v>1039</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>999</v>
+        <v>1040</v>
       </c>
       <c r="D13" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:4">
@@ -7524,13 +7647,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1000</v>
+        <v>1041</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
       <c r="D14" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -7597,10 +7720,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1002</v>
+        <v>1043</v>
       </c>
       <c r="C4" t="s">
-        <v>1003</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7608,10 +7731,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1004</v>
+        <v>1045</v>
       </c>
       <c r="C5" t="s">
-        <v>1005</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7619,10 +7742,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1006</v>
+        <v>1047</v>
       </c>
       <c r="C6" t="s">
-        <v>1007</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7630,10 +7753,10 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>1008</v>
+        <v>1049</v>
       </c>
       <c r="C7" t="s">
-        <v>1009</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7641,10 +7764,10 @@
         <v>1020010001</v>
       </c>
       <c r="B8" t="s">
-        <v>1010</v>
+        <v>1051</v>
       </c>
       <c r="C8" t="s">
-        <v>1011</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7652,10 +7775,10 @@
         <v>1030010001</v>
       </c>
       <c r="B9" t="s">
-        <v>1012</v>
+        <v>1053</v>
       </c>
       <c r="C9" t="s">
-        <v>1013</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7663,10 +7786,10 @@
         <v>1030020001</v>
       </c>
       <c r="B10" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="C10" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" spans="1:4">
@@ -7674,10 +7797,10 @@
         <v>2000000001</v>
       </c>
       <c r="B11" t="s">
-        <v>1016</v>
+        <v>1057</v>
       </c>
       <c r="C11" t="s">
-        <v>1017</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7685,10 +7808,10 @@
         <v>2000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="C12" t="s">
-        <v>1019</v>
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -7754,10 +7877,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1020</v>
+        <v>1061</v>
       </c>
       <c r="C4" t="s">
-        <v>1021</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -7765,10 +7888,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1022</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="s">
-        <v>1023</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -7776,10 +7899,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1024</v>
+        <v>1065</v>
       </c>
       <c r="C6" t="s">
-        <v>1025</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -7787,10 +7910,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1026</v>
+        <v>1067</v>
       </c>
       <c r="C7" t="s">
-        <v>1027</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -7798,10 +7921,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1028</v>
+        <v>1069</v>
       </c>
       <c r="C8" t="s">
-        <v>1029</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -7809,10 +7932,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1030</v>
+        <v>1071</v>
       </c>
       <c r="C9" t="s">
-        <v>1031</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -7820,10 +7943,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1032</v>
+        <v>1073</v>
       </c>
       <c r="C10" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -7831,10 +7954,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1034</v>
+        <v>1075</v>
       </c>
       <c r="C11" t="s">
-        <v>1035</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -7842,10 +7965,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1036</v>
+        <v>1077</v>
       </c>
       <c r="C12" t="s">
-        <v>1037</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -7853,10 +7976,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1038</v>
+        <v>1079</v>
       </c>
       <c r="C13" t="s">
-        <v>1039</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -7864,10 +7987,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1040</v>
+        <v>1081</v>
       </c>
       <c r="C14" t="s">
-        <v>1041</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -7875,10 +7998,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1042</v>
+        <v>1083</v>
       </c>
       <c r="C15" t="s">
-        <v>1043</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -7886,10 +8009,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1044</v>
+        <v>1085</v>
       </c>
       <c r="C16" t="s">
-        <v>1044</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7897,10 +8020,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1045</v>
+        <v>1086</v>
       </c>
       <c r="C17" t="s">
-        <v>1046</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7908,10 +8031,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1047</v>
+        <v>1088</v>
       </c>
       <c r="C18" t="s">
-        <v>1048</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7919,10 +8042,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1049</v>
+        <v>1090</v>
       </c>
       <c r="C19" t="s">
-        <v>1050</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7930,10 +8053,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1051</v>
+        <v>1092</v>
       </c>
       <c r="C20" t="s">
-        <v>1052</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7941,10 +8064,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1053</v>
+        <v>1094</v>
       </c>
       <c r="C21" t="s">
-        <v>1054</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7952,10 +8075,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1055</v>
+        <v>1096</v>
       </c>
       <c r="C22" t="s">
-        <v>1056</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7963,10 +8086,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1057</v>
+        <v>1098</v>
       </c>
       <c r="C23" t="s">
-        <v>1058</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7974,10 +8097,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1059</v>
+        <v>1100</v>
       </c>
       <c r="C24" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7985,10 +8108,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="C25" t="s">
-        <v>1062</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7996,10 +8119,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1063</v>
+        <v>1104</v>
       </c>
       <c r="C26" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8007,10 +8130,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1065</v>
+        <v>1106</v>
       </c>
       <c r="C27" t="s">
-        <v>1066</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8018,10 +8141,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1067</v>
+        <v>1108</v>
       </c>
       <c r="C28" t="s">
-        <v>1068</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8029,10 +8152,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1069</v>
+        <v>1110</v>
       </c>
       <c r="C29" t="s">
-        <v>1070</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8040,10 +8163,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1071</v>
+        <v>1112</v>
       </c>
       <c r="C30" t="s">
-        <v>1072</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8051,10 +8174,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1073</v>
+        <v>1114</v>
       </c>
       <c r="C31" t="s">
-        <v>1074</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8062,10 +8185,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="C32" t="s">
-        <v>1076</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8073,10 +8196,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1077</v>
+        <v>1118</v>
       </c>
       <c r="C33" t="s">
-        <v>1078</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8084,10 +8207,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1079</v>
+        <v>1120</v>
       </c>
       <c r="C34" t="s">
-        <v>1080</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -8154,10 +8277,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1081</v>
+        <v>1122</v>
       </c>
       <c r="C4" t="s">
-        <v>1082</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8165,10 +8288,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1083</v>
+        <v>1124</v>
       </c>
       <c r="C5" t="s">
-        <v>1084</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8176,10 +8299,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="C6" t="s">
-        <v>1086</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8187,10 +8310,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1087</v>
+        <v>1128</v>
       </c>
       <c r="C7" t="s">
-        <v>1088</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8198,10 +8321,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1089</v>
+        <v>1130</v>
       </c>
       <c r="C8" t="s">
-        <v>1090</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8209,10 +8332,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="C9" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8220,10 +8343,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1093</v>
+        <v>1134</v>
       </c>
       <c r="C10" t="s">
-        <v>1094</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8231,10 +8354,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1095</v>
+        <v>1136</v>
       </c>
       <c r="C11" t="s">
-        <v>1096</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8242,10 +8365,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1097</v>
+        <v>1138</v>
       </c>
       <c r="C12" t="s">
-        <v>1098</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8253,10 +8376,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1099</v>
+        <v>1140</v>
       </c>
       <c r="C13" t="s">
-        <v>1100</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8264,10 +8387,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1101</v>
+        <v>1142</v>
       </c>
       <c r="C14" t="s">
-        <v>1102</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8275,10 +8398,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1103</v>
+        <v>1144</v>
       </c>
       <c r="C15" t="s">
-        <v>1104</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8286,10 +8409,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1105</v>
+        <v>1146</v>
       </c>
       <c r="C16" t="s">
-        <v>1106</v>
+        <v>1147</v>
       </c>
     </row>
   </sheetData>
@@ -8354,10 +8477,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1107</v>
+        <v>1148</v>
       </c>
       <c r="C4" t="s">
-        <v>1108</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8365,10 +8488,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="s">
-        <v>1110</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8376,10 +8499,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1111</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
-        <v>1112</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8387,10 +8510,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1113</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
-        <v>1114</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8398,10 +8521,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1115</v>
+        <v>1156</v>
       </c>
       <c r="C8" t="s">
-        <v>1116</v>
+        <v>1157</v>
       </c>
     </row>
   </sheetData>
@@ -8467,10 +8590,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1117</v>
+        <v>1158</v>
       </c>
       <c r="C4" t="s">
-        <v>1118</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8478,10 +8601,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1119</v>
+        <v>1160</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1120</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8489,10 +8612,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1121</v>
+        <v>1162</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1122</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8500,10 +8623,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1123</v>
+        <v>1164</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1124</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8511,10 +8634,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1125</v>
+        <v>1166</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1126</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8522,10 +8645,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1127</v>
+        <v>1168</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1128</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8533,10 +8656,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1129</v>
+        <v>1170</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1130</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8544,10 +8667,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1131</v>
+        <v>1172</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1132</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8555,10 +8678,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1133</v>
+        <v>1174</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1134</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8566,10 +8689,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1135</v>
+        <v>1176</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1136</v>
+        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -8635,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1137</v>
+        <v>1178</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8646,7 +8769,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1138</v>
+        <v>1179</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8657,10 +8780,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1139</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1140</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8668,10 +8791,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1141</v>
+        <v>1182</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1142</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8679,10 +8802,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1143</v>
+        <v>1184</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1144</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8690,10 +8813,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1145</v>
+        <v>1186</v>
       </c>
       <c r="C9" t="s">
-        <v>1146</v>
+        <v>1187</v>
       </c>
     </row>
   </sheetData>
@@ -8761,13 +8884,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1147</v>
+        <v>1188</v>
       </c>
       <c r="C4" t="s">
-        <v>1148</v>
+        <v>1189</v>
       </c>
       <c r="D4" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8775,13 +8898,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1191</v>
       </c>
       <c r="C5" t="s">
-        <v>1151</v>
+        <v>1192</v>
       </c>
       <c r="D5" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8789,13 +8912,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1193</v>
       </c>
       <c r="C6" t="s">
-        <v>1153</v>
+        <v>1194</v>
       </c>
       <c r="D6" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8803,13 +8926,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1154</v>
+        <v>1195</v>
       </c>
       <c r="C7" t="s">
-        <v>1155</v>
+        <v>1196</v>
       </c>
       <c r="D7" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8817,13 +8940,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1156</v>
+        <v>1197</v>
       </c>
       <c r="C8" t="s">
-        <v>1157</v>
+        <v>1198</v>
       </c>
       <c r="D8" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8831,13 +8954,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1158</v>
+        <v>1199</v>
       </c>
       <c r="C9" t="s">
-        <v>1159</v>
+        <v>1200</v>
       </c>
       <c r="D9" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8845,13 +8968,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1160</v>
+        <v>1201</v>
       </c>
       <c r="C10" t="s">
-        <v>1161</v>
+        <v>1202</v>
       </c>
       <c r="D10" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8859,13 +8982,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1162</v>
+        <v>1203</v>
       </c>
       <c r="C11" t="s">
-        <v>1163</v>
+        <v>1204</v>
       </c>
       <c r="D11" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8873,13 +8996,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1164</v>
+        <v>1205</v>
       </c>
       <c r="C12" t="s">
-        <v>1165</v>
+        <v>1206</v>
       </c>
       <c r="D12" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8887,13 +9010,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1166</v>
+        <v>1207</v>
       </c>
       <c r="C13" t="s">
-        <v>1167</v>
+        <v>1208</v>
       </c>
       <c r="D13" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8901,13 +9024,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1168</v>
+        <v>1209</v>
       </c>
       <c r="C14" t="s">
-        <v>1169</v>
+        <v>1210</v>
       </c>
       <c r="D14" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8915,13 +9038,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1170</v>
+        <v>1211</v>
       </c>
       <c r="C15" t="s">
-        <v>1171</v>
+        <v>1212</v>
       </c>
       <c r="D15" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8929,13 +9052,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1172</v>
+        <v>1213</v>
       </c>
       <c r="C16" t="s">
-        <v>1173</v>
+        <v>1214</v>
       </c>
       <c r="D16" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -8943,13 +9066,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1174</v>
+        <v>1215</v>
       </c>
       <c r="C17" t="s">
-        <v>1175</v>
+        <v>1216</v>
       </c>
       <c r="D17" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -8957,13 +9080,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1168</v>
+        <v>1209</v>
       </c>
       <c r="C18" t="s">
-        <v>1169</v>
+        <v>1210</v>
       </c>
       <c r="D18" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -8971,13 +9094,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1176</v>
+        <v>1217</v>
       </c>
       <c r="C19" t="s">
-        <v>1177</v>
+        <v>1218</v>
       </c>
       <c r="D19" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -8985,13 +9108,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1178</v>
+        <v>1219</v>
       </c>
       <c r="C20" t="s">
-        <v>1179</v>
+        <v>1220</v>
       </c>
       <c r="D20" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -8999,13 +9122,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1180</v>
+        <v>1221</v>
       </c>
       <c r="C21" t="s">
-        <v>1181</v>
+        <v>1222</v>
       </c>
       <c r="D21" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9013,13 +9136,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1182</v>
+        <v>1223</v>
       </c>
       <c r="C22" t="s">
-        <v>1183</v>
+        <v>1224</v>
       </c>
       <c r="D22" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9027,13 +9150,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1184</v>
+        <v>1225</v>
       </c>
       <c r="C23" t="s">
-        <v>1185</v>
+        <v>1226</v>
       </c>
       <c r="D23" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9041,13 +9164,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1186</v>
+        <v>1227</v>
       </c>
       <c r="C24" t="s">
-        <v>1187</v>
+        <v>1228</v>
       </c>
       <c r="D24" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9055,13 +9178,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1188</v>
+        <v>1229</v>
       </c>
       <c r="C25" t="s">
-        <v>1189</v>
+        <v>1230</v>
       </c>
       <c r="D25" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9069,13 +9192,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D26" t="s">
         <v>1190</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9083,13 +9206,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1192</v>
+        <v>1233</v>
       </c>
       <c r="C27" t="s">
-        <v>1193</v>
+        <v>1234</v>
       </c>
       <c r="D27" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9097,13 +9220,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1194</v>
+        <v>1235</v>
       </c>
       <c r="C28" t="s">
-        <v>1195</v>
+        <v>1236</v>
       </c>
       <c r="D28" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9111,13 +9234,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1196</v>
+        <v>1237</v>
       </c>
       <c r="C29" t="s">
-        <v>1197</v>
+        <v>1238</v>
       </c>
       <c r="D29" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9125,13 +9248,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1198</v>
+        <v>1239</v>
       </c>
       <c r="C30" t="s">
-        <v>1199</v>
+        <v>1240</v>
       </c>
       <c r="D30" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9139,13 +9262,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1200</v>
+        <v>1241</v>
       </c>
       <c r="C31" t="s">
-        <v>1201</v>
+        <v>1242</v>
       </c>
       <c r="D31" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9153,13 +9276,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1202</v>
+        <v>1243</v>
       </c>
       <c r="C32" t="s">
-        <v>1203</v>
+        <v>1244</v>
       </c>
       <c r="D32" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9167,13 +9290,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1204</v>
+        <v>1245</v>
       </c>
       <c r="C33" t="s">
-        <v>1205</v>
+        <v>1246</v>
       </c>
       <c r="D33" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9181,13 +9304,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1206</v>
+        <v>1247</v>
       </c>
       <c r="C34" t="s">
-        <v>1207</v>
+        <v>1248</v>
       </c>
       <c r="D34" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9195,13 +9318,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1208</v>
+        <v>1249</v>
       </c>
       <c r="C35" t="s">
-        <v>1209</v>
+        <v>1250</v>
       </c>
       <c r="D35" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9209,13 +9332,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1210</v>
+        <v>1251</v>
       </c>
       <c r="C36" t="s">
-        <v>1211</v>
+        <v>1252</v>
       </c>
       <c r="D36" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9223,13 +9346,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1212</v>
+        <v>1253</v>
       </c>
       <c r="C37" t="s">
-        <v>1213</v>
+        <v>1254</v>
       </c>
       <c r="D37" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9237,13 +9360,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1214</v>
+        <v>1255</v>
       </c>
       <c r="C38" t="s">
-        <v>1215</v>
+        <v>1256</v>
       </c>
       <c r="D38" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9251,13 +9374,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1216</v>
+        <v>1257</v>
       </c>
       <c r="C39" t="s">
-        <v>1217</v>
+        <v>1258</v>
       </c>
       <c r="D39" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9265,13 +9388,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1218</v>
+        <v>1259</v>
       </c>
       <c r="C40" t="s">
-        <v>1219</v>
+        <v>1260</v>
       </c>
       <c r="D40" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9279,13 +9402,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1220</v>
+        <v>1261</v>
       </c>
       <c r="C41" t="s">
-        <v>1221</v>
+        <v>1262</v>
       </c>
       <c r="D41" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9293,13 +9416,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1222</v>
+        <v>1263</v>
       </c>
       <c r="C42" t="s">
-        <v>1223</v>
+        <v>1264</v>
       </c>
       <c r="D42" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9307,13 +9430,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1224</v>
+        <v>1265</v>
       </c>
       <c r="C43" t="s">
-        <v>1225</v>
+        <v>1266</v>
       </c>
       <c r="D43" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9321,13 +9444,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1226</v>
+        <v>1267</v>
       </c>
       <c r="C44" t="s">
-        <v>1227</v>
+        <v>1268</v>
       </c>
       <c r="D44" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9335,13 +9458,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1228</v>
+        <v>1269</v>
       </c>
       <c r="C45" t="s">
-        <v>1229</v>
+        <v>1270</v>
       </c>
       <c r="D45" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9349,13 +9472,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1230</v>
+        <v>1271</v>
       </c>
       <c r="C46" t="s">
-        <v>1231</v>
+        <v>1272</v>
       </c>
       <c r="D46" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9363,13 +9486,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1232</v>
+        <v>1273</v>
       </c>
       <c r="C47" t="s">
-        <v>1233</v>
+        <v>1274</v>
       </c>
       <c r="D47" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9377,13 +9500,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1234</v>
+        <v>1275</v>
       </c>
       <c r="C48" t="s">
-        <v>1235</v>
+        <v>1276</v>
       </c>
       <c r="D48" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9391,13 +9514,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1236</v>
+        <v>1277</v>
       </c>
       <c r="C49" t="s">
-        <v>1237</v>
+        <v>1278</v>
       </c>
       <c r="D49" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9405,13 +9528,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1238</v>
+        <v>1279</v>
       </c>
       <c r="C50" t="s">
-        <v>1239</v>
+        <v>1280</v>
       </c>
       <c r="D50" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9419,13 +9542,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1240</v>
+        <v>1281</v>
       </c>
       <c r="C51" t="s">
-        <v>1241</v>
+        <v>1282</v>
       </c>
       <c r="D51" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9433,13 +9556,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1242</v>
+        <v>1283</v>
       </c>
       <c r="C52" t="s">
-        <v>1243</v>
+        <v>1284</v>
       </c>
       <c r="D52" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9447,13 +9570,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1244</v>
+        <v>1285</v>
       </c>
       <c r="C53" t="s">
-        <v>1245</v>
+        <v>1286</v>
       </c>
       <c r="D53" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9461,13 +9584,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1246</v>
+        <v>1287</v>
       </c>
       <c r="C54" t="s">
-        <v>1247</v>
+        <v>1288</v>
       </c>
       <c r="D54" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9475,13 +9598,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1248</v>
+        <v>1289</v>
       </c>
       <c r="C55" t="s">
-        <v>1249</v>
+        <v>1290</v>
       </c>
       <c r="D55" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9489,13 +9612,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1250</v>
+        <v>1291</v>
       </c>
       <c r="C56" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="D56" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9503,13 +9626,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1252</v>
+        <v>1293</v>
       </c>
       <c r="C57" t="s">
-        <v>1253</v>
+        <v>1294</v>
       </c>
       <c r="D57" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9517,13 +9640,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1254</v>
+        <v>1295</v>
       </c>
       <c r="C58" t="s">
-        <v>1255</v>
+        <v>1296</v>
       </c>
       <c r="D58" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9531,13 +9654,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1256</v>
+        <v>1297</v>
       </c>
       <c r="C59" t="s">
-        <v>1257</v>
+        <v>1298</v>
       </c>
       <c r="D59" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9545,13 +9668,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="C60" t="s">
-        <v>1259</v>
+        <v>1300</v>
       </c>
       <c r="D60" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9559,13 +9682,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1260</v>
+        <v>1301</v>
       </c>
       <c r="C61" t="s">
-        <v>1261</v>
+        <v>1302</v>
       </c>
       <c r="D61" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9573,13 +9696,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1262</v>
+        <v>1303</v>
       </c>
       <c r="C62" t="s">
-        <v>1263</v>
+        <v>1304</v>
       </c>
       <c r="D62" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9587,13 +9710,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="C63" t="s">
-        <v>1265</v>
+        <v>1306</v>
       </c>
       <c r="D63" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9601,13 +9724,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1266</v>
+        <v>1307</v>
       </c>
       <c r="C64" t="s">
-        <v>1267</v>
+        <v>1308</v>
       </c>
       <c r="D64" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9615,13 +9738,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1268</v>
+        <v>1309</v>
       </c>
       <c r="C65" t="s">
-        <v>1269</v>
+        <v>1310</v>
       </c>
       <c r="D65" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9629,13 +9752,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1270</v>
+        <v>1311</v>
       </c>
       <c r="C66" t="s">
-        <v>1271</v>
+        <v>1312</v>
       </c>
       <c r="D66" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9643,13 +9766,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1272</v>
+        <v>1313</v>
       </c>
       <c r="C67" t="s">
-        <v>1273</v>
+        <v>1314</v>
       </c>
       <c r="D67" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9657,13 +9780,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1274</v>
+        <v>1315</v>
       </c>
       <c r="C68" t="s">
-        <v>1275</v>
+        <v>1316</v>
       </c>
       <c r="D68" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9671,13 +9794,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1276</v>
+        <v>1317</v>
       </c>
       <c r="C69" t="s">
-        <v>1277</v>
+        <v>1318</v>
       </c>
       <c r="D69" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9685,13 +9808,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1278</v>
+        <v>1319</v>
       </c>
       <c r="C70" t="s">
-        <v>1279</v>
+        <v>1320</v>
       </c>
       <c r="D70" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9699,13 +9822,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1280</v>
+        <v>1321</v>
       </c>
       <c r="C71" t="s">
-        <v>1281</v>
+        <v>1322</v>
       </c>
       <c r="D71" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9713,13 +9836,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1282</v>
+        <v>1323</v>
       </c>
       <c r="C72" t="s">
-        <v>1283</v>
+        <v>1324</v>
       </c>
       <c r="D72" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9727,13 +9850,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1284</v>
+        <v>1325</v>
       </c>
       <c r="C73" t="s">
-        <v>1285</v>
+        <v>1326</v>
       </c>
       <c r="D73" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9741,13 +9864,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1286</v>
+        <v>1327</v>
       </c>
       <c r="C74" t="s">
-        <v>1287</v>
+        <v>1328</v>
       </c>
       <c r="D74" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9755,13 +9878,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1288</v>
+        <v>1329</v>
       </c>
       <c r="C75" t="s">
-        <v>1289</v>
+        <v>1330</v>
       </c>
       <c r="D75" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9769,13 +9892,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1290</v>
+        <v>1331</v>
       </c>
       <c r="C76" t="s">
-        <v>1291</v>
+        <v>1332</v>
       </c>
       <c r="D76" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9783,13 +9906,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1292</v>
+        <v>1333</v>
       </c>
       <c r="C77" t="s">
-        <v>1293</v>
+        <v>1334</v>
       </c>
       <c r="D77" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9797,13 +9920,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1294</v>
+        <v>1335</v>
       </c>
       <c r="C78" t="s">
-        <v>1295</v>
+        <v>1336</v>
       </c>
       <c r="D78" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9811,13 +9934,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1296</v>
+        <v>1337</v>
       </c>
       <c r="C79" t="s">
-        <v>1297</v>
+        <v>1338</v>
       </c>
       <c r="D79" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9825,13 +9948,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1298</v>
+        <v>1339</v>
       </c>
       <c r="C80" t="s">
-        <v>1299</v>
+        <v>1340</v>
       </c>
       <c r="D80" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9839,13 +9962,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1300</v>
+        <v>1341</v>
       </c>
       <c r="C81" t="s">
-        <v>1301</v>
+        <v>1342</v>
       </c>
       <c r="D81" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9853,13 +9976,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1302</v>
+        <v>1343</v>
       </c>
       <c r="C82" t="s">
-        <v>1303</v>
+        <v>1344</v>
       </c>
       <c r="D82" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9867,13 +9990,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1304</v>
+        <v>1345</v>
       </c>
       <c r="C83" t="s">
-        <v>1305</v>
+        <v>1346</v>
       </c>
       <c r="D83" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -9881,13 +10004,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1306</v>
+        <v>1347</v>
       </c>
       <c r="C84" t="s">
-        <v>1307</v>
+        <v>1348</v>
       </c>
       <c r="D84" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -9895,13 +10018,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1308</v>
+        <v>1349</v>
       </c>
       <c r="C85" t="s">
-        <v>1309</v>
+        <v>1350</v>
       </c>
       <c r="D85" t="s">
-        <v>1149</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -10257,7 +10380,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D198"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
@@ -10355,9 +10478,7 @@
       <c r="B7" t="s">
         <v>330</v>
       </c>
-      <c r="C7" t="s">
-        <v>331</v>
-      </c>
+      <c r="C7"/>
       <c r="D7" t="s">
         <v>326</v>
       </c>
@@ -10367,10 +10488,10 @@
         <v>10100003</v>
       </c>
       <c r="B8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" t="s">
         <v>332</v>
-      </c>
-      <c r="C8" t="s">
-        <v>333</v>
       </c>
       <c r="D8" t="s">
         <v>326</v>
@@ -10381,324 +10502,356 @@
         <v>10100004</v>
       </c>
       <c r="B9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" t="s">
         <v>334</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="14">
+        <v>10100005</v>
+      </c>
+      <c r="B10" t="s">
         <v>335</v>
       </c>
-      <c r="D9" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>10200001</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10"/>
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="14">
+        <v>10100007</v>
+      </c>
+      <c r="B11" t="s">
         <v>336</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="14">
+        <v>10100008</v>
+      </c>
+      <c r="B12" t="s">
         <v>337</v>
       </c>
-      <c r="D10" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>10200002</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12"/>
+      <c r="D12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="14">
+        <v>10100010</v>
+      </c>
+      <c r="B13" t="s">
         <v>338</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13"/>
+      <c r="D13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="14">
+        <v>10100012</v>
+      </c>
+      <c r="B14" t="s">
         <v>339</v>
       </c>
-      <c r="D11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>10200003</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C14"/>
+      <c r="D14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="14">
+        <v>10100013</v>
+      </c>
+      <c r="B15" t="s">
         <v>340</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C15"/>
+      <c r="D15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="14">
+        <v>10100014</v>
+      </c>
+      <c r="B16" t="s">
         <v>341</v>
       </c>
-      <c r="D12" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>10200004</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C16"/>
+      <c r="D16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="14">
+        <v>10100015</v>
+      </c>
+      <c r="B17" t="s">
         <v>342</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="14">
+        <v>10100016</v>
+      </c>
+      <c r="B18" t="s">
         <v>343</v>
       </c>
-      <c r="D13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>10200005</v>
-      </c>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>10200006</v>
-      </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>10200007</v>
-      </c>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>10200008</v>
-      </c>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>10200009</v>
-      </c>
-      <c r="B18"/>
       <c r="C18"/>
-      <c r="D18"/>
+      <c r="D18" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19">
-        <v>10200010</v>
-      </c>
-      <c r="B19"/>
+      <c r="A19" s="14">
+        <v>10100017</v>
+      </c>
+      <c r="B19" t="s">
+        <v>344</v>
+      </c>
       <c r="C19"/>
-      <c r="D19"/>
+      <c r="D19" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>10200011</v>
-      </c>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
+        <v>10200001</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" t="s">
+        <v>346</v>
+      </c>
+      <c r="D20" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>10200012</v>
-      </c>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
+        <v>10200002</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="C21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D21" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>10200013</v>
-      </c>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
+        <v>10200003</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C22" t="s">
+        <v>350</v>
+      </c>
+      <c r="D22" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
+        <v>10200004</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23" t="s">
+        <v>352</v>
+      </c>
+      <c r="D23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="14">
+        <v>10200005</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24"/>
+      <c r="D24" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="14">
+        <v>10200006</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="C25"/>
+      <c r="D25" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="14">
+        <v>10200007</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="14">
+        <v>10200008</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="14">
+        <v>10200009</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="14">
+        <v>10200010</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29"/>
+      <c r="D29" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="14">
+        <v>10200011</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30"/>
+      <c r="D30" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="14">
+        <v>10200012</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="14">
+        <v>10200013</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C32"/>
+      <c r="D32" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="14">
         <v>10200014</v>
       </c>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
+      <c r="B33" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33"/>
+      <c r="D33" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="14">
         <v>10200015</v>
       </c>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
+      <c r="B34" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C34"/>
+      <c r="D34" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="14">
         <v>10200016</v>
       </c>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
+      <c r="B35" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C35"/>
+      <c r="D35" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="14">
         <v>10200017</v>
       </c>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27">
-        <v>10300001</v>
-      </c>
-      <c r="B27" t="s">
-        <v>344</v>
-      </c>
-      <c r="C27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28">
-        <v>10300002</v>
-      </c>
-      <c r="B28" t="s">
-        <v>346</v>
-      </c>
-      <c r="C28" t="s">
-        <v>347</v>
-      </c>
-      <c r="D28" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
-        <v>10300003</v>
-      </c>
-      <c r="B29" t="s">
-        <v>348</v>
-      </c>
-      <c r="C29" t="s">
-        <v>349</v>
-      </c>
-      <c r="D29" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30">
-        <v>10300004</v>
-      </c>
-      <c r="B30" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D30" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31">
-        <v>11000001</v>
-      </c>
-      <c r="B31" t="s">
-        <v>352</v>
-      </c>
-      <c r="C31" t="s">
-        <v>353</v>
-      </c>
-      <c r="D31" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32">
-        <v>11000002</v>
-      </c>
-      <c r="B32" t="s">
-        <v>354</v>
-      </c>
-      <c r="C32" t="s">
-        <v>355</v>
-      </c>
-      <c r="D32" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33">
-        <v>11000003</v>
-      </c>
-      <c r="B33" t="s">
-        <v>356</v>
-      </c>
-      <c r="C33" t="s">
-        <v>357</v>
-      </c>
-      <c r="D33" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34">
-        <v>11000004</v>
-      </c>
-      <c r="B34" t="s">
-        <v>358</v>
-      </c>
-      <c r="C34" t="s">
-        <v>359</v>
-      </c>
-      <c r="D34" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35">
-        <v>11000005</v>
-      </c>
-      <c r="B35" t="s">
-        <v>360</v>
-      </c>
-      <c r="C35" t="s">
-        <v>361</v>
-      </c>
-      <c r="D35" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36">
-        <v>11000006</v>
-      </c>
-      <c r="B36" t="s">
-        <v>362</v>
-      </c>
-      <c r="C36" t="s">
-        <v>363</v>
-      </c>
+      <c r="B36" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36"/>
       <c r="D36" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>11000007</v>
-      </c>
-      <c r="B37" t="s">
-        <v>364</v>
+        <v>10300001</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>366</v>
       </c>
       <c r="C37" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
         <v>326</v>
@@ -10706,13 +10859,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>11000008</v>
-      </c>
-      <c r="B38" t="s">
-        <v>366</v>
+        <v>10300002</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>368</v>
       </c>
       <c r="C38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D38" t="s">
         <v>326</v>
@@ -10720,13 +10873,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>11000009</v>
-      </c>
-      <c r="B39" t="s">
-        <v>368</v>
+        <v>10300003</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>370</v>
       </c>
       <c r="C39" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D39" t="s">
         <v>326</v>
@@ -10734,13 +10887,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>11010001</v>
-      </c>
-      <c r="B40" t="s">
-        <v>370</v>
+        <v>10300004</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>372</v>
       </c>
       <c r="C40" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D40" t="s">
         <v>326</v>
@@ -10748,447 +10901,405 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>20100001</v>
-      </c>
-      <c r="B41" t="s">
-        <v>372</v>
-      </c>
-      <c r="C41" t="s">
-        <v>373</v>
-      </c>
+        <v>10300005</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C41"/>
       <c r="D41" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>20100002</v>
-      </c>
-      <c r="B42" t="s">
-        <v>374</v>
-      </c>
-      <c r="C42" t="s">
+        <v>10300006</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>375</v>
       </c>
+      <c r="C42"/>
       <c r="D42" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>20100003</v>
-      </c>
-      <c r="B43" t="s">
+        <v>10300007</v>
+      </c>
+      <c r="B43" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="C43" t="s">
-        <v>377</v>
-      </c>
+      <c r="C43"/>
       <c r="D43" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>20100004</v>
-      </c>
-      <c r="B44" t="s">
-        <v>378</v>
-      </c>
-      <c r="C44" t="s">
-        <v>379</v>
-      </c>
+        <v>10300008</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C44"/>
       <c r="D44" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>20100005</v>
-      </c>
-      <c r="B45" t="s">
-        <v>380</v>
-      </c>
-      <c r="C45" t="s">
-        <v>381</v>
-      </c>
+        <v>10300009</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="C45"/>
       <c r="D45" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>20100006</v>
-      </c>
-      <c r="B46" t="s">
-        <v>382</v>
-      </c>
-      <c r="C46" t="s">
-        <v>383</v>
-      </c>
+        <v>10300010</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C46"/>
       <c r="D46" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>20100007</v>
-      </c>
-      <c r="B47" t="s">
-        <v>384</v>
-      </c>
-      <c r="C47" t="s">
-        <v>385</v>
-      </c>
+        <v>10300011</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="C47"/>
       <c r="D47" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>20200001</v>
-      </c>
-      <c r="B48" t="s">
-        <v>386</v>
-      </c>
-      <c r="C48" t="s">
-        <v>387</v>
-      </c>
+        <v>10300012</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C48"/>
       <c r="D48" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>20200002</v>
-      </c>
-      <c r="B49" t="s">
-        <v>388</v>
-      </c>
-      <c r="C49" t="s">
-        <v>389</v>
-      </c>
+        <v>10300013</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="C49"/>
       <c r="D49" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>20200003</v>
-      </c>
-      <c r="B50" t="s">
-        <v>390</v>
-      </c>
-      <c r="C50" t="s">
-        <v>391</v>
-      </c>
+        <v>10300014</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="C50"/>
       <c r="D50" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>20200004</v>
-      </c>
-      <c r="B51" t="s">
-        <v>392</v>
-      </c>
-      <c r="C51" t="s">
-        <v>393</v>
-      </c>
+        <v>10300015</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="C51"/>
       <c r="D51" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>20200005</v>
-      </c>
-      <c r="B52" t="s">
-        <v>394</v>
-      </c>
-      <c r="C52" t="s">
-        <v>395</v>
-      </c>
+        <v>10300016</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="C52"/>
       <c r="D52" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>20200006</v>
-      </c>
-      <c r="B53" t="s">
+        <v>10300017</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C53"/>
+      <c r="D53" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="14">
+        <v>11000001</v>
+      </c>
+      <c r="B54" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="14">
+        <v>11000002</v>
+      </c>
+      <c r="B55" t="s">
+        <v>389</v>
+      </c>
+      <c r="C55" t="s">
+        <v>390</v>
+      </c>
+      <c r="D55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="14">
+        <v>11000003</v>
+      </c>
+      <c r="B56" t="s">
+        <v>391</v>
+      </c>
+      <c r="C56" t="s">
+        <v>392</v>
+      </c>
+      <c r="D56" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="14">
+        <v>11000004</v>
+      </c>
+      <c r="B57" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="14">
+        <v>11000005</v>
+      </c>
+      <c r="B58" t="s">
+        <v>395</v>
+      </c>
+      <c r="C58" t="s">
         <v>396</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D58" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="14">
+        <v>11000006</v>
+      </c>
+      <c r="B59" t="s">
         <v>397</v>
       </c>
-      <c r="D53" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54">
-        <v>20200007</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C59" t="s">
         <v>398</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D59" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="14">
+        <v>11000007</v>
+      </c>
+      <c r="B60" t="s">
         <v>399</v>
       </c>
-      <c r="D54" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55">
-        <v>20200008</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C60" t="s">
         <v>400</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D60" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="14">
+        <v>11000008</v>
+      </c>
+      <c r="B61" t="s">
         <v>401</v>
       </c>
-      <c r="D55" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56">
-        <v>20200009</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C61" t="s">
         <v>402</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D61" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="14">
+        <v>11000009</v>
+      </c>
+      <c r="B62" t="s">
         <v>403</v>
       </c>
-      <c r="D56" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57">
-        <v>20200010</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="C62" t="s">
         <v>404</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D62" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="14">
+        <v>11000010</v>
+      </c>
+      <c r="B63" t="s">
+        <v>393</v>
+      </c>
+      <c r="C63"/>
+      <c r="D63" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="14">
+        <v>11000011</v>
+      </c>
+      <c r="B64" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="D57" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58">
-        <v>20200011</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C64"/>
+      <c r="D64" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="14">
+        <v>11000012</v>
+      </c>
+      <c r="B65" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C65"/>
+      <c r="D65" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="14">
+        <v>11000013</v>
+      </c>
+      <c r="B66" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D58" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59">
-        <v>20300001</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="C66"/>
+      <c r="D66" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="14">
+        <v>11010001</v>
+      </c>
+      <c r="B67" t="s">
         <v>408</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C67" t="s">
         <v>409</v>
       </c>
-      <c r="D59" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60">
-        <v>20300002</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="D67" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="14">
+        <v>11010002</v>
+      </c>
+      <c r="B68" t="s">
         <v>410</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C68"/>
+      <c r="D68" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="14">
+        <v>11010003</v>
+      </c>
+      <c r="B69" t="s">
         <v>411</v>
       </c>
-      <c r="D60" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61">
-        <v>20300003</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="C69"/>
+      <c r="D69" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="14">
+        <v>11020021</v>
+      </c>
+      <c r="B70" t="s">
         <v>412</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C70"/>
+      <c r="D70" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="14">
+        <v>11020022</v>
+      </c>
+      <c r="B71" t="s">
         <v>413</v>
       </c>
-      <c r="D61" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62">
-        <v>20300004</v>
-      </c>
-      <c r="B62" t="s">
-        <v>414</v>
-      </c>
-      <c r="C62" t="s">
-        <v>415</v>
-      </c>
-      <c r="D62" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63">
-        <v>20300005</v>
-      </c>
-      <c r="B63" t="s">
-        <v>416</v>
-      </c>
-      <c r="C63" t="s">
-        <v>417</v>
-      </c>
-      <c r="D63" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64">
-        <v>21000001</v>
-      </c>
-      <c r="B64" t="s">
-        <v>418</v>
-      </c>
-      <c r="C64" t="s">
-        <v>419</v>
-      </c>
-      <c r="D64" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65">
-        <v>21000002</v>
-      </c>
-      <c r="B65" t="s">
-        <v>420</v>
-      </c>
-      <c r="C65" t="s">
-        <v>421</v>
-      </c>
-      <c r="D65" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66">
-        <v>21000003</v>
-      </c>
-      <c r="B66" t="s">
-        <v>422</v>
-      </c>
-      <c r="C66" t="s">
-        <v>423</v>
-      </c>
-      <c r="D66" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67">
-        <v>21000004</v>
-      </c>
-      <c r="B67" t="s">
-        <v>424</v>
-      </c>
-      <c r="C67" t="s">
-        <v>425</v>
-      </c>
-      <c r="D67" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68">
-        <v>21000005</v>
-      </c>
-      <c r="B68" t="s">
-        <v>426</v>
-      </c>
-      <c r="C68" t="s">
-        <v>427</v>
-      </c>
-      <c r="D68" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69">
-        <v>21000006</v>
-      </c>
-      <c r="B69" t="s">
-        <v>428</v>
-      </c>
-      <c r="C69" t="s">
-        <v>429</v>
-      </c>
-      <c r="D69" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70">
-        <v>21000007</v>
-      </c>
-      <c r="B70" t="s">
-        <v>430</v>
-      </c>
-      <c r="C70" t="s">
-        <v>431</v>
-      </c>
-      <c r="D70" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71">
-        <v>21000008</v>
-      </c>
-      <c r="B71" t="s">
-        <v>432</v>
-      </c>
-      <c r="C71" t="s">
-        <v>433</v>
-      </c>
+      <c r="C71"/>
       <c r="D71" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>21000009</v>
+        <v>20100001</v>
       </c>
       <c r="B72" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C72" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D72" t="s">
         <v>326</v>
@@ -11196,13 +11307,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>21000010</v>
+        <v>20100002</v>
       </c>
       <c r="B73" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C73" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="D73" t="s">
         <v>326</v>
@@ -11210,13 +11321,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>21010001</v>
+        <v>20100003</v>
       </c>
       <c r="B74" t="s">
-        <v>354</v>
+        <v>418</v>
       </c>
       <c r="C74" t="s">
-        <v>355</v>
+        <v>419</v>
       </c>
       <c r="D74" t="s">
         <v>326</v>
@@ -11224,13 +11335,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>21010002</v>
+        <v>20100004</v>
       </c>
       <c r="B75" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C75" t="s">
-        <v>357</v>
+        <v>420</v>
       </c>
       <c r="D75" t="s">
         <v>326</v>
@@ -11238,13 +11349,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>21010003</v>
+        <v>20100005</v>
       </c>
       <c r="B76" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="C76" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="D76" t="s">
         <v>326</v>
@@ -11252,13 +11363,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>21010004</v>
+        <v>20100006</v>
       </c>
       <c r="B77" t="s">
-        <v>360</v>
+        <v>423</v>
       </c>
       <c r="C77" t="s">
-        <v>361</v>
+        <v>424</v>
       </c>
       <c r="D77" t="s">
         <v>326</v>
@@ -11266,13 +11377,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>21010005</v>
+        <v>20100007</v>
       </c>
       <c r="B78" t="s">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="C78" t="s">
-        <v>363</v>
+        <v>426</v>
       </c>
       <c r="D78" t="s">
         <v>326</v>
@@ -11280,13 +11391,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>21010006</v>
+        <v>20200001</v>
       </c>
       <c r="B79" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C79" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D79" t="s">
         <v>326</v>
@@ -11294,13 +11405,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>21010007</v>
+        <v>20200002</v>
       </c>
       <c r="B80" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C80" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="D80" t="s">
         <v>326</v>
@@ -11308,13 +11419,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>21010008</v>
+        <v>20200003</v>
       </c>
       <c r="B81" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C81" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D81" t="s">
         <v>326</v>
@@ -11322,13 +11433,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>21010009</v>
+        <v>20200004</v>
       </c>
       <c r="B82" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C82" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D82" t="s">
         <v>326</v>
@@ -11336,13 +11447,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>21010010</v>
+        <v>20200005</v>
       </c>
       <c r="B83" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C83" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="D83" t="s">
         <v>326</v>
@@ -11350,13 +11461,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>21010011</v>
+        <v>20200006</v>
       </c>
       <c r="B84" t="s">
-        <v>364</v>
+        <v>437</v>
       </c>
       <c r="C84" t="s">
-        <v>365</v>
+        <v>438</v>
       </c>
       <c r="D84" t="s">
         <v>326</v>
@@ -11364,13 +11475,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>21010012</v>
+        <v>20200007</v>
       </c>
       <c r="B85" t="s">
-        <v>366</v>
+        <v>439</v>
       </c>
       <c r="C85" t="s">
-        <v>367</v>
+        <v>440</v>
       </c>
       <c r="D85" t="s">
         <v>326</v>
@@ -11378,13 +11489,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>21010013</v>
+        <v>20200008</v>
       </c>
       <c r="B86" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C86" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="D86" t="s">
         <v>326</v>
@@ -11392,13 +11503,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>21010014</v>
+        <v>20200009</v>
       </c>
       <c r="B87" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="C87" t="s">
-        <v>369</v>
+        <v>444</v>
       </c>
       <c r="D87" t="s">
         <v>326</v>
@@ -11406,13 +11517,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>21010015</v>
+        <v>20200010</v>
       </c>
       <c r="B88" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C88" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D88" t="s">
         <v>326</v>
@@ -11420,83 +11531,83 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>21010016</v>
+        <v>20200011</v>
       </c>
       <c r="B89" t="s">
+        <v>447</v>
+      </c>
+      <c r="C89" t="s">
+        <v>448</v>
+      </c>
+      <c r="D89" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="14">
+        <v>20300001</v>
+      </c>
+      <c r="B90" t="s">
+        <v>449</v>
+      </c>
+      <c r="C90" t="s">
+        <v>450</v>
+      </c>
+      <c r="D90" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="14">
+        <v>20300003</v>
+      </c>
+      <c r="B91" t="s">
+        <v>451</v>
+      </c>
+      <c r="C91" t="s">
         <v>452</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D91" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="14">
+        <v>20300007</v>
+      </c>
+      <c r="B92" t="s">
         <v>453</v>
       </c>
-      <c r="D89" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90">
-        <v>21010017</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="C92" t="s">
         <v>454</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D92" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="14">
+        <v>20300009</v>
+      </c>
+      <c r="B93" t="s">
         <v>455</v>
       </c>
-      <c r="D90" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91">
-        <v>21010018</v>
-      </c>
-      <c r="B91" t="s">
+      <c r="C93" t="s">
         <v>456</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D93" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="14">
+        <v>20300011</v>
+      </c>
+      <c r="B94" t="s">
         <v>457</v>
       </c>
-      <c r="D91" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92">
-        <v>21010019</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="C94" t="s">
         <v>458</v>
-      </c>
-      <c r="C92" t="s">
-        <v>459</v>
-      </c>
-      <c r="D92" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93">
-        <v>21010020</v>
-      </c>
-      <c r="B93" t="s">
-        <v>460</v>
-      </c>
-      <c r="C93" t="s">
-        <v>461</v>
-      </c>
-      <c r="D93" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94">
-        <v>30100001</v>
-      </c>
-      <c r="B94" t="s">
-        <v>462</v>
-      </c>
-      <c r="C94" t="s">
-        <v>463</v>
       </c>
       <c r="D94" t="s">
         <v>326</v>
@@ -11504,13 +11615,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>30100002</v>
+        <v>21000001</v>
       </c>
       <c r="B95" t="s">
-        <v>374</v>
+        <v>459</v>
       </c>
       <c r="C95" t="s">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="D95" t="s">
         <v>326</v>
@@ -11518,13 +11629,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>30100003</v>
+        <v>21000002</v>
       </c>
       <c r="B96" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C96" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D96" t="s">
         <v>326</v>
@@ -11532,13 +11643,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>30100004</v>
+        <v>21000003</v>
       </c>
       <c r="B97" t="s">
-        <v>372</v>
+        <v>463</v>
       </c>
       <c r="C97" t="s">
-        <v>373</v>
+        <v>464</v>
       </c>
       <c r="D97" t="s">
         <v>326</v>
@@ -11546,13 +11657,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>30100005</v>
+        <v>21000004</v>
       </c>
       <c r="B98" t="s">
+        <v>465</v>
+      </c>
+      <c r="C98" t="s">
         <v>466</v>
-      </c>
-      <c r="C98" t="s">
-        <v>467</v>
       </c>
       <c r="D98" t="s">
         <v>326</v>
@@ -11560,13 +11671,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>30100006</v>
+        <v>21000005</v>
       </c>
       <c r="B99" t="s">
+        <v>467</v>
+      </c>
+      <c r="C99" t="s">
         <v>468</v>
-      </c>
-      <c r="C99" t="s">
-        <v>469</v>
       </c>
       <c r="D99" t="s">
         <v>326</v>
@@ -11574,13 +11685,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>30100007</v>
+        <v>21000006</v>
       </c>
       <c r="B100" t="s">
+        <v>469</v>
+      </c>
+      <c r="C100" t="s">
         <v>470</v>
-      </c>
-      <c r="C100" t="s">
-        <v>471</v>
       </c>
       <c r="D100" t="s">
         <v>326</v>
@@ -11588,13 +11699,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>30100008</v>
+        <v>21000007</v>
       </c>
       <c r="B101" t="s">
+        <v>471</v>
+      </c>
+      <c r="C101" t="s">
         <v>472</v>
-      </c>
-      <c r="C101" t="s">
-        <v>473</v>
       </c>
       <c r="D101" t="s">
         <v>326</v>
@@ -11602,13 +11713,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>30100009</v>
+        <v>21000008</v>
       </c>
       <c r="B102" t="s">
+        <v>473</v>
+      </c>
+      <c r="C102" t="s">
         <v>474</v>
-      </c>
-      <c r="C102" t="s">
-        <v>475</v>
       </c>
       <c r="D102" t="s">
         <v>326</v>
@@ -11616,13 +11727,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>30100010</v>
+        <v>21000009</v>
       </c>
       <c r="B103" t="s">
+        <v>475</v>
+      </c>
+      <c r="C103" t="s">
         <v>476</v>
-      </c>
-      <c r="C103" t="s">
-        <v>477</v>
       </c>
       <c r="D103" t="s">
         <v>326</v>
@@ -11630,13 +11741,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>30100011</v>
+        <v>21000010</v>
       </c>
       <c r="B104" t="s">
+        <v>477</v>
+      </c>
+      <c r="C104" t="s">
         <v>478</v>
-      </c>
-      <c r="C104" t="s">
-        <v>479</v>
       </c>
       <c r="D104" t="s">
         <v>326</v>
@@ -11644,13 +11755,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>30100012</v>
+        <v>21010001</v>
       </c>
       <c r="B105" t="s">
-        <v>480</v>
+        <v>389</v>
       </c>
       <c r="C105" t="s">
-        <v>481</v>
+        <v>390</v>
       </c>
       <c r="D105" t="s">
         <v>326</v>
@@ -11658,13 +11769,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>30100013</v>
+        <v>21010002</v>
       </c>
       <c r="B106" t="s">
-        <v>482</v>
+        <v>391</v>
       </c>
       <c r="C106" t="s">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="D106" t="s">
         <v>326</v>
@@ -11672,13 +11783,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>30100014</v>
+        <v>21010003</v>
       </c>
       <c r="B107" t="s">
-        <v>484</v>
+        <v>393</v>
       </c>
       <c r="C107" t="s">
-        <v>485</v>
+        <v>394</v>
       </c>
       <c r="D107" t="s">
         <v>326</v>
@@ -11686,13 +11797,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>30100015</v>
+        <v>21010004</v>
       </c>
       <c r="B108" t="s">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="C108" t="s">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="D108" t="s">
         <v>326</v>
@@ -11700,13 +11811,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>30100016</v>
+        <v>21010005</v>
       </c>
       <c r="B109" t="s">
-        <v>488</v>
+        <v>397</v>
       </c>
       <c r="C109" t="s">
-        <v>489</v>
+        <v>398</v>
       </c>
       <c r="D109" t="s">
         <v>326</v>
@@ -11714,13 +11825,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>30100017</v>
+        <v>21010006</v>
       </c>
       <c r="B110" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C110" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D110" t="s">
         <v>326</v>
@@ -11728,13 +11839,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>30100018</v>
+        <v>21010007</v>
       </c>
       <c r="B111" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="C111" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="D111" t="s">
         <v>326</v>
@@ -11742,13 +11853,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>30100019</v>
+        <v>21010008</v>
       </c>
       <c r="B112" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="C112" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D112" t="s">
         <v>326</v>
@@ -11756,13 +11867,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>30100020</v>
+        <v>21010009</v>
       </c>
       <c r="B113" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="C113" t="s">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="D113" t="s">
         <v>326</v>
@@ -11770,13 +11881,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>40100001</v>
+        <v>21010010</v>
       </c>
       <c r="B114" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C114" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D114" t="s">
         <v>326</v>
@@ -11784,13 +11895,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
-        <v>40200001</v>
+        <v>21010011</v>
       </c>
       <c r="B115" t="s">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="C115" t="s">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D115" t="s">
         <v>326</v>
@@ -11798,13 +11909,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116">
-        <v>40200002</v>
+        <v>21010012</v>
       </c>
       <c r="B116" t="s">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="C116" t="s">
-        <v>502</v>
+        <v>402</v>
       </c>
       <c r="D116" t="s">
         <v>326</v>
@@ -11812,13 +11923,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117">
-        <v>40200003</v>
+        <v>21010013</v>
       </c>
       <c r="B117" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="C117" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -11826,13 +11937,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>40200004</v>
+        <v>21010014</v>
       </c>
       <c r="B118" t="s">
-        <v>505</v>
+        <v>403</v>
       </c>
       <c r="C118" t="s">
-        <v>506</v>
+        <v>404</v>
       </c>
       <c r="D118" t="s">
         <v>326</v>
@@ -11840,13 +11951,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>40200005</v>
+        <v>21010015</v>
       </c>
       <c r="B119" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C119" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="D119" t="s">
         <v>326</v>
@@ -11854,13 +11965,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>40200006</v>
+        <v>21010016</v>
       </c>
       <c r="B120" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C120" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="D120" t="s">
         <v>326</v>
@@ -11868,13 +11979,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>40300001</v>
+        <v>21010017</v>
       </c>
       <c r="B121" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C121" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="D121" t="s">
         <v>326</v>
@@ -11882,13 +11993,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>40300002</v>
+        <v>21010018</v>
       </c>
       <c r="B122" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C122" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="D122" t="s">
         <v>326</v>
@@ -11896,13 +12007,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123">
-        <v>40300003</v>
+        <v>21010019</v>
       </c>
       <c r="B123" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C123" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="D123" t="s">
         <v>326</v>
@@ -11910,13 +12021,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124">
-        <v>40300004</v>
+        <v>21010020</v>
       </c>
       <c r="B124" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C124" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="D124" t="s">
         <v>326</v>
@@ -11924,13 +12035,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125">
-        <v>41000001</v>
+        <v>30100001</v>
       </c>
       <c r="B125" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C125" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="D125" t="s">
         <v>326</v>
@@ -11938,13 +12049,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126">
-        <v>41000002</v>
+        <v>30100002</v>
       </c>
       <c r="B126" t="s">
-        <v>521</v>
+        <v>416</v>
       </c>
       <c r="C126" t="s">
-        <v>522</v>
+        <v>417</v>
       </c>
       <c r="D126" t="s">
         <v>326</v>
@@ -11952,13 +12063,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>41000003</v>
+        <v>30100003</v>
       </c>
       <c r="B127" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="C127" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D127" t="s">
         <v>326</v>
@@ -11966,13 +12077,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>41000004</v>
+        <v>30100004</v>
       </c>
       <c r="B128" t="s">
-        <v>525</v>
+        <v>414</v>
       </c>
       <c r="C128" t="s">
-        <v>526</v>
+        <v>415</v>
       </c>
       <c r="D128" t="s">
         <v>326</v>
@@ -11980,13 +12091,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>41000005</v>
+        <v>30100005</v>
       </c>
       <c r="B129" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="C129" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="D129" t="s">
         <v>326</v>
@@ -11994,13 +12105,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130">
-        <v>50100001</v>
+        <v>30100006</v>
       </c>
       <c r="B130" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="C130" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="D130" t="s">
         <v>326</v>
@@ -12008,13 +12119,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131">
-        <v>50100002</v>
+        <v>30100007</v>
       </c>
       <c r="B131" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="C131" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
@@ -12022,13 +12133,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>50100003</v>
+        <v>30100008</v>
       </c>
       <c r="B132" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="C132" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="D132" t="s">
         <v>326</v>
@@ -12036,13 +12147,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>50200001</v>
+        <v>30100009</v>
       </c>
       <c r="B133" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="C133" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="D133" t="s">
         <v>326</v>
@@ -12050,13 +12161,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>50200002</v>
+        <v>30100010</v>
       </c>
       <c r="B134" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="C134" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="D134" t="s">
         <v>326</v>
@@ -12064,13 +12175,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>50200003</v>
+        <v>30100011</v>
       </c>
       <c r="B135" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="C135" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="D135" t="s">
         <v>326</v>
@@ -12078,13 +12189,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>50300001</v>
+        <v>30100012</v>
       </c>
       <c r="B136" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="C136" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="D136" t="s">
         <v>326</v>
@@ -12092,13 +12203,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>50300002</v>
+        <v>30100013</v>
       </c>
       <c r="B137" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="C137" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="D137" t="s">
         <v>326</v>
@@ -12106,13 +12217,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>50500001</v>
+        <v>30100014</v>
       </c>
       <c r="B138" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C138" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="D138" t="s">
         <v>326</v>
@@ -12120,13 +12231,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>50500002</v>
+        <v>30100015</v>
       </c>
       <c r="B139" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="C139" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="D139" t="s">
         <v>326</v>
@@ -12134,13 +12245,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>50500003</v>
+        <v>30100016</v>
       </c>
       <c r="B140" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C140" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="D140" t="s">
         <v>326</v>
@@ -12148,13 +12259,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>50500004</v>
+        <v>30100017</v>
       </c>
       <c r="B141" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="C141" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="D141" t="s">
         <v>326</v>
@@ -12162,13 +12273,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>50500005</v>
+        <v>30100018</v>
       </c>
       <c r="B142" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="C142" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="D142" t="s">
         <v>326</v>
@@ -12176,13 +12287,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>51010001</v>
+        <v>30100019</v>
       </c>
       <c r="B143" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="C143" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="D143" t="s">
         <v>326</v>
@@ -12190,13 +12301,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>51010002</v>
+        <v>30100020</v>
       </c>
       <c r="B144" t="s">
-        <v>268</v>
+        <v>537</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>470</v>
       </c>
       <c r="D144" t="s">
         <v>326</v>
@@ -12204,13 +12315,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>51010003</v>
+        <v>40100001</v>
       </c>
       <c r="B145" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="C145" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="D145" t="s">
         <v>326</v>
@@ -12218,13 +12329,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>60100001</v>
+        <v>40200001</v>
       </c>
       <c r="B146" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="C146" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="D146" t="s">
         <v>326</v>
@@ -12232,13 +12343,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>60100002</v>
+        <v>40200002</v>
       </c>
       <c r="B147" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="C147" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="D147" t="s">
         <v>326</v>
@@ -12246,13 +12357,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>60100003</v>
+        <v>40200003</v>
       </c>
       <c r="B148" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C148" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="D148" t="s">
         <v>326</v>
@@ -12260,13 +12371,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>60100004</v>
+        <v>40200004</v>
       </c>
       <c r="B149" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="C149" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="D149" t="s">
         <v>326</v>
@@ -12274,13 +12385,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
-        <v>60100005</v>
+        <v>40200005</v>
       </c>
       <c r="B150" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="C150" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="D150" t="s">
         <v>326</v>
@@ -12288,13 +12399,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>60100006</v>
+        <v>40200006</v>
       </c>
       <c r="B151" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="C151" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="D151" t="s">
         <v>326</v>
@@ -12302,13 +12413,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>60100007</v>
+        <v>40300001</v>
       </c>
       <c r="B152" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="C152" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="D152" t="s">
         <v>326</v>
@@ -12316,13 +12427,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>60100008</v>
+        <v>40300002</v>
       </c>
       <c r="B153" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="C153" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="D153" t="s">
         <v>326</v>
@@ -12330,13 +12441,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>60100009</v>
+        <v>40300003</v>
       </c>
       <c r="B154" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="C154" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="D154" t="s">
         <v>326</v>
@@ -12344,13 +12455,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155">
-        <v>60100010</v>
+        <v>40300004</v>
       </c>
       <c r="B155" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="C155" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="D155" t="s">
         <v>326</v>
@@ -12358,13 +12469,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156">
-        <v>60200001</v>
+        <v>41000001</v>
       </c>
       <c r="B156" t="s">
-        <v>499</v>
+        <v>560</v>
       </c>
       <c r="C156" t="s">
-        <v>500</v>
+        <v>561</v>
       </c>
       <c r="D156" t="s">
         <v>326</v>
@@ -12372,13 +12483,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157">
-        <v>60200002</v>
+        <v>41000002</v>
       </c>
       <c r="B157" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C157" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D157" t="s">
         <v>326</v>
@@ -12386,13 +12497,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158">
-        <v>60300001</v>
+        <v>41000003</v>
       </c>
       <c r="B158" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C158" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="D158" t="s">
         <v>326</v>
@@ -12400,13 +12511,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159">
-        <v>60300002</v>
+        <v>41000004</v>
       </c>
       <c r="B159" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C159" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="D159" t="s">
         <v>326</v>
@@ -12414,13 +12525,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160">
-        <v>60300003</v>
+        <v>41000005</v>
       </c>
       <c r="B160" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C160" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="D160" t="s">
         <v>326</v>
@@ -12428,13 +12539,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>60300004</v>
+        <v>50100001</v>
       </c>
       <c r="B161" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="C161" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="D161" t="s">
         <v>326</v>
@@ -12442,13 +12553,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>60300005</v>
+        <v>50100002</v>
       </c>
       <c r="B162" t="s">
-        <v>585</v>
+        <v>525</v>
       </c>
       <c r="C162" t="s">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="D162" t="s">
         <v>326</v>
@@ -12456,13 +12567,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>61010001</v>
+        <v>50100003</v>
       </c>
       <c r="B163" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="C163" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="D163" t="s">
         <v>326</v>
@@ -12470,13 +12581,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>61010002</v>
+        <v>50200001</v>
       </c>
       <c r="B164" t="s">
-        <v>370</v>
+        <v>574</v>
       </c>
       <c r="C164" t="s">
-        <v>371</v>
+        <v>575</v>
       </c>
       <c r="D164" t="s">
         <v>326</v>
@@ -12484,13 +12595,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>61010003</v>
+        <v>50200002</v>
       </c>
       <c r="B165" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="C165" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="D165" t="s">
         <v>326</v>
@@ -12498,13 +12609,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
-        <v>61010004</v>
+        <v>50200003</v>
       </c>
       <c r="B166" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="C166" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="D166" t="s">
         <v>326</v>
@@ -12512,13 +12623,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167">
-        <v>61010005</v>
+        <v>50300001</v>
       </c>
       <c r="B167" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="C167" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D167" t="s">
         <v>326</v>
@@ -12526,13 +12637,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168">
-        <v>61010006</v>
+        <v>50300002</v>
       </c>
       <c r="B168" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="C168" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="D168" t="s">
         <v>326</v>
@@ -12540,13 +12651,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169">
-        <v>61010007</v>
+        <v>50500001</v>
       </c>
       <c r="B169" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C169" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
@@ -12554,13 +12665,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170">
-        <v>61010008</v>
+        <v>50500002</v>
       </c>
       <c r="B170" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C170" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="D170" t="s">
         <v>326</v>
@@ -12568,13 +12679,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171">
-        <v>61010009</v>
+        <v>50500003</v>
       </c>
       <c r="B171" t="s">
-        <v>354</v>
+        <v>588</v>
       </c>
       <c r="C171" t="s">
-        <v>355</v>
+        <v>589</v>
       </c>
       <c r="D171" t="s">
         <v>326</v>
@@ -12582,13 +12693,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172">
-        <v>61010010</v>
+        <v>50500004</v>
       </c>
       <c r="B172" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C172" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="D172" t="s">
         <v>326</v>
@@ -12596,13 +12707,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173">
-        <v>61010011</v>
+        <v>50500005</v>
       </c>
       <c r="B173" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="C173" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="D173" t="s">
         <v>326</v>
@@ -12610,13 +12721,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174">
-        <v>61010012</v>
+        <v>51010001</v>
       </c>
       <c r="B174" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="C174" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="D174" t="s">
         <v>326</v>
@@ -12624,13 +12735,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>61010013</v>
+        <v>51010002</v>
       </c>
       <c r="B175" t="s">
-        <v>607</v>
+        <v>268</v>
       </c>
       <c r="C175" t="s">
-        <v>608</v>
+        <v>269</v>
       </c>
       <c r="D175" t="s">
         <v>326</v>
@@ -12638,13 +12749,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176">
-        <v>61010014</v>
+        <v>51010003</v>
       </c>
       <c r="B176" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="C176" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="D176" t="s">
         <v>326</v>
@@ -12652,13 +12763,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177">
-        <v>61010015</v>
+        <v>60100001</v>
       </c>
       <c r="B177" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C177" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="D177" t="s">
         <v>326</v>
@@ -12666,13 +12777,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178">
-        <v>61010016</v>
+        <v>60100002</v>
       </c>
       <c r="B178" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C178" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D178" t="s">
         <v>326</v>
@@ -12680,13 +12791,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179">
-        <v>61010017</v>
+        <v>60100003</v>
       </c>
       <c r="B179" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C179" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="D179" t="s">
         <v>326</v>
@@ -12694,13 +12805,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180">
-        <v>61010018</v>
+        <v>60100004</v>
       </c>
       <c r="B180" t="s">
-        <v>617</v>
+        <v>570</v>
       </c>
       <c r="C180" t="s">
-        <v>618</v>
+        <v>571</v>
       </c>
       <c r="D180" t="s">
         <v>326</v>
@@ -12708,13 +12819,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181">
-        <v>61010019</v>
+        <v>60100005</v>
       </c>
       <c r="B181" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="C181" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="D181" t="s">
         <v>326</v>
@@ -12722,13 +12833,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182">
-        <v>61010020</v>
+        <v>60100006</v>
       </c>
       <c r="B182" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="C182" t="s">
-        <v>431</v>
+        <v>607</v>
       </c>
       <c r="D182" t="s">
         <v>326</v>
@@ -12736,13 +12847,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183">
-        <v>70100001</v>
+        <v>60100007</v>
       </c>
       <c r="B183" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="C183" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="D183" t="s">
         <v>326</v>
@@ -12750,13 +12861,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184">
-        <v>70200001</v>
+        <v>60100008</v>
       </c>
       <c r="B184" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="C184" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="D184" t="s">
         <v>326</v>
@@ -12764,13 +12875,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185">
-        <v>70200002</v>
+        <v>60100009</v>
       </c>
       <c r="B185" t="s">
-        <v>535</v>
+        <v>612</v>
       </c>
       <c r="C185" t="s">
-        <v>536</v>
+        <v>613</v>
       </c>
       <c r="D185" t="s">
         <v>326</v>
@@ -12778,13 +12889,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186">
-        <v>70300001</v>
+        <v>60100010</v>
       </c>
       <c r="B186" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C186" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="D186" t="s">
         <v>326</v>
@@ -12792,13 +12903,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187">
-        <v>70300002</v>
+        <v>60200001</v>
       </c>
       <c r="B187" t="s">
-        <v>628</v>
+        <v>540</v>
       </c>
       <c r="C187" t="s">
-        <v>629</v>
+        <v>541</v>
       </c>
       <c r="D187" t="s">
         <v>326</v>
@@ -12806,13 +12917,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188">
-        <v>70300003</v>
+        <v>60200002</v>
       </c>
       <c r="B188" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="C188" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="D188" t="s">
         <v>326</v>
@@ -12820,13 +12931,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189">
-        <v>70300004</v>
+        <v>60300001</v>
       </c>
       <c r="B189" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="C189" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="D189" t="s">
         <v>326</v>
@@ -12834,13 +12945,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190">
-        <v>71000001</v>
+        <v>60300002</v>
       </c>
       <c r="B190" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="C190" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="D190" t="s">
         <v>326</v>
@@ -12848,13 +12959,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191">
-        <v>71000002</v>
+        <v>60300003</v>
       </c>
       <c r="B191" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="C191" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="D191" t="s">
         <v>326</v>
@@ -12862,13 +12973,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192">
-        <v>71000003</v>
+        <v>60300004</v>
       </c>
       <c r="B192" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="C192" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="D192" t="s">
         <v>326</v>
@@ -12876,13 +12987,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193">
-        <v>71010001</v>
+        <v>60300005</v>
       </c>
       <c r="B193" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="C193" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
@@ -12890,13 +13001,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194">
-        <v>71010002</v>
+        <v>61010001</v>
       </c>
       <c r="B194" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="C194" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="D194" t="s">
         <v>326</v>
@@ -12904,13 +13015,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195">
-        <v>71010003</v>
+        <v>61010002</v>
       </c>
       <c r="B195" t="s">
-        <v>644</v>
+        <v>408</v>
       </c>
       <c r="C195" t="s">
-        <v>645</v>
+        <v>409</v>
       </c>
       <c r="D195" t="s">
         <v>326</v>
@@ -12918,13 +13029,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196">
-        <v>71010004</v>
+        <v>61010003</v>
       </c>
       <c r="B196" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="C196" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="D196" t="s">
         <v>326</v>
@@ -12932,13 +13043,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197">
-        <v>71010005</v>
+        <v>61010004</v>
       </c>
       <c r="B197" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="C197" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="D197" t="s">
         <v>326</v>
@@ -12946,15 +13057,449 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198">
+        <v>61010005</v>
+      </c>
+      <c r="B198" t="s">
+        <v>634</v>
+      </c>
+      <c r="C198" t="s">
+        <v>635</v>
+      </c>
+      <c r="D198" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199">
+        <v>61010006</v>
+      </c>
+      <c r="B199" t="s">
+        <v>636</v>
+      </c>
+      <c r="C199" t="s">
+        <v>637</v>
+      </c>
+      <c r="D199" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200">
+        <v>61010007</v>
+      </c>
+      <c r="B200" t="s">
+        <v>638</v>
+      </c>
+      <c r="C200" t="s">
+        <v>639</v>
+      </c>
+      <c r="D200" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201">
+        <v>61010008</v>
+      </c>
+      <c r="B201" t="s">
+        <v>640</v>
+      </c>
+      <c r="C201" t="s">
+        <v>641</v>
+      </c>
+      <c r="D201" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202">
+        <v>61010009</v>
+      </c>
+      <c r="B202" t="s">
+        <v>389</v>
+      </c>
+      <c r="C202" t="s">
+        <v>390</v>
+      </c>
+      <c r="D202" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203">
+        <v>61010010</v>
+      </c>
+      <c r="B203" t="s">
+        <v>642</v>
+      </c>
+      <c r="C203" t="s">
+        <v>643</v>
+      </c>
+      <c r="D203" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204">
+        <v>61010011</v>
+      </c>
+      <c r="B204" t="s">
+        <v>644</v>
+      </c>
+      <c r="C204" t="s">
+        <v>645</v>
+      </c>
+      <c r="D204" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205">
+        <v>61010012</v>
+      </c>
+      <c r="B205" t="s">
+        <v>646</v>
+      </c>
+      <c r="C205" t="s">
+        <v>647</v>
+      </c>
+      <c r="D205" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206">
+        <v>61010013</v>
+      </c>
+      <c r="B206" t="s">
+        <v>648</v>
+      </c>
+      <c r="C206" t="s">
+        <v>649</v>
+      </c>
+      <c r="D206" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207">
+        <v>61010014</v>
+      </c>
+      <c r="B207" t="s">
+        <v>650</v>
+      </c>
+      <c r="C207" t="s">
+        <v>651</v>
+      </c>
+      <c r="D207" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208">
+        <v>61010015</v>
+      </c>
+      <c r="B208" t="s">
+        <v>652</v>
+      </c>
+      <c r="C208" t="s">
+        <v>653</v>
+      </c>
+      <c r="D208" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209">
+        <v>61010016</v>
+      </c>
+      <c r="B209" t="s">
+        <v>654</v>
+      </c>
+      <c r="C209" t="s">
+        <v>655</v>
+      </c>
+      <c r="D209" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210">
+        <v>61010017</v>
+      </c>
+      <c r="B210" t="s">
+        <v>656</v>
+      </c>
+      <c r="C210" t="s">
+        <v>657</v>
+      </c>
+      <c r="D210" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211">
+        <v>61010018</v>
+      </c>
+      <c r="B211" t="s">
+        <v>658</v>
+      </c>
+      <c r="C211" t="s">
+        <v>659</v>
+      </c>
+      <c r="D211" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212">
+        <v>61010019</v>
+      </c>
+      <c r="B212" t="s">
+        <v>660</v>
+      </c>
+      <c r="C212" t="s">
+        <v>661</v>
+      </c>
+      <c r="D212" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213">
+        <v>61010020</v>
+      </c>
+      <c r="B213" t="s">
+        <v>662</v>
+      </c>
+      <c r="C213" t="s">
+        <v>472</v>
+      </c>
+      <c r="D213" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214">
+        <v>70100001</v>
+      </c>
+      <c r="B214" t="s">
+        <v>663</v>
+      </c>
+      <c r="C214" t="s">
+        <v>664</v>
+      </c>
+      <c r="D214" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215">
+        <v>70200001</v>
+      </c>
+      <c r="B215" t="s">
+        <v>665</v>
+      </c>
+      <c r="C215" t="s">
+        <v>666</v>
+      </c>
+      <c r="D215" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216">
+        <v>70200002</v>
+      </c>
+      <c r="B216" t="s">
+        <v>576</v>
+      </c>
+      <c r="C216" t="s">
+        <v>577</v>
+      </c>
+      <c r="D216" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217">
+        <v>70300001</v>
+      </c>
+      <c r="B217" t="s">
+        <v>667</v>
+      </c>
+      <c r="C217" t="s">
+        <v>668</v>
+      </c>
+      <c r="D217" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218">
+        <v>70300002</v>
+      </c>
+      <c r="B218" t="s">
+        <v>669</v>
+      </c>
+      <c r="C218" t="s">
+        <v>670</v>
+      </c>
+      <c r="D218" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219">
+        <v>70300003</v>
+      </c>
+      <c r="B219" t="s">
+        <v>671</v>
+      </c>
+      <c r="C219" t="s">
+        <v>672</v>
+      </c>
+      <c r="D219" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220">
+        <v>70300004</v>
+      </c>
+      <c r="B220" t="s">
+        <v>673</v>
+      </c>
+      <c r="C220" t="s">
+        <v>674</v>
+      </c>
+      <c r="D220" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221">
+        <v>71000001</v>
+      </c>
+      <c r="B221" t="s">
+        <v>675</v>
+      </c>
+      <c r="C221" t="s">
+        <v>676</v>
+      </c>
+      <c r="D221" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222">
+        <v>71000002</v>
+      </c>
+      <c r="B222" t="s">
+        <v>677</v>
+      </c>
+      <c r="C222" t="s">
+        <v>678</v>
+      </c>
+      <c r="D222" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223">
+        <v>71000003</v>
+      </c>
+      <c r="B223" t="s">
+        <v>679</v>
+      </c>
+      <c r="C223" t="s">
+        <v>680</v>
+      </c>
+      <c r="D223" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224">
+        <v>71010001</v>
+      </c>
+      <c r="B224" t="s">
+        <v>681</v>
+      </c>
+      <c r="C224" t="s">
+        <v>682</v>
+      </c>
+      <c r="D224" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225">
+        <v>71010002</v>
+      </c>
+      <c r="B225" t="s">
+        <v>683</v>
+      </c>
+      <c r="C225" t="s">
+        <v>684</v>
+      </c>
+      <c r="D225" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226">
+        <v>71010003</v>
+      </c>
+      <c r="B226" t="s">
+        <v>685</v>
+      </c>
+      <c r="C226" t="s">
+        <v>686</v>
+      </c>
+      <c r="D226" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227">
+        <v>71010004</v>
+      </c>
+      <c r="B227" t="s">
+        <v>687</v>
+      </c>
+      <c r="C227" t="s">
+        <v>688</v>
+      </c>
+      <c r="D227" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228">
+        <v>71010005</v>
+      </c>
+      <c r="B228" t="s">
+        <v>689</v>
+      </c>
+      <c r="C228" t="s">
+        <v>690</v>
+      </c>
+      <c r="D228" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229">
         <v>71010006</v>
       </c>
-      <c r="B198" t="s">
-        <v>650</v>
-      </c>
-      <c r="C198" t="s">
-        <v>590</v>
-      </c>
-      <c r="D198" t="s">
+      <c r="B229" t="s">
+        <v>691</v>
+      </c>
+      <c r="C229" t="s">
+        <v>631</v>
+      </c>
+      <c r="D229" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13023,13 +13568,13 @@
         <v>1000100001</v>
       </c>
       <c r="B4" t="s">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="C4" t="s">
-        <v>652</v>
+        <v>693</v>
       </c>
       <c r="D4" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -13037,13 +13582,13 @@
         <v>1000200001</v>
       </c>
       <c r="B5" t="s">
-        <v>654</v>
+        <v>695</v>
       </c>
       <c r="C5" t="s">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="D5" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -13051,13 +13596,13 @@
         <v>1000300001</v>
       </c>
       <c r="B6" t="s">
-        <v>656</v>
+        <v>697</v>
       </c>
       <c r="C6" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="D6" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -13065,13 +13610,13 @@
         <v>1000400001</v>
       </c>
       <c r="B7" t="s">
-        <v>658</v>
+        <v>699</v>
       </c>
       <c r="C7" t="s">
-        <v>659</v>
+        <v>700</v>
       </c>
       <c r="D7" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -13079,13 +13624,13 @@
         <v>1000500001</v>
       </c>
       <c r="B8" t="s">
-        <v>660</v>
+        <v>701</v>
       </c>
       <c r="C8" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="D8" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -13093,13 +13638,13 @@
         <v>2000100001</v>
       </c>
       <c r="B9" t="s">
-        <v>662</v>
+        <v>703</v>
       </c>
       <c r="C9" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="D9" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -13107,13 +13652,13 @@
         <v>2000200001</v>
       </c>
       <c r="B10" t="s">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="C10" t="s">
-        <v>665</v>
+        <v>706</v>
       </c>
       <c r="D10" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -13121,13 +13666,13 @@
         <v>2000300001</v>
       </c>
       <c r="B11" t="s">
-        <v>666</v>
+        <v>707</v>
       </c>
       <c r="C11" t="s">
-        <v>667</v>
+        <v>708</v>
       </c>
       <c r="D11" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13135,13 +13680,13 @@
         <v>2000400001</v>
       </c>
       <c r="B12" t="s">
-        <v>668</v>
+        <v>709</v>
       </c>
       <c r="C12" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
       <c r="D12" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -13155,7 +13700,7 @@
         <v>294</v>
       </c>
       <c r="D13" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -13169,7 +13714,7 @@
         <v>303</v>
       </c>
       <c r="D14" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -13177,13 +13722,13 @@
         <v>3000300001</v>
       </c>
       <c r="B15" t="s">
-        <v>670</v>
+        <v>711</v>
       </c>
       <c r="C15" t="s">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="D15" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -13197,7 +13742,7 @@
         <v>299</v>
       </c>
       <c r="D16" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -13205,13 +13750,13 @@
         <v>11000100001</v>
       </c>
       <c r="B17" t="s">
-        <v>672</v>
+        <v>713</v>
       </c>
       <c r="C17" t="s">
-        <v>672</v>
+        <v>713</v>
       </c>
       <c r="D17" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -13219,13 +13764,13 @@
         <v>11000200001</v>
       </c>
       <c r="B18" t="s">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="C18" t="s">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="D18" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -13233,13 +13778,13 @@
         <v>11000300001</v>
       </c>
       <c r="B19" t="s">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="C19" t="s">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="D19" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -13247,13 +13792,13 @@
         <v>12000100001</v>
       </c>
       <c r="B20" t="s">
-        <v>676</v>
+        <v>717</v>
       </c>
       <c r="C20" t="s">
-        <v>677</v>
+        <v>718</v>
       </c>
       <c r="D20" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -13261,13 +13806,13 @@
         <v>12000200001</v>
       </c>
       <c r="B21" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="C21" t="s">
-        <v>679</v>
+        <v>720</v>
       </c>
       <c r="D21" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -13275,13 +13820,13 @@
         <v>12000300001</v>
       </c>
       <c r="B22" t="s">
-        <v>680</v>
+        <v>721</v>
       </c>
       <c r="C22" t="s">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="D22" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:4">
@@ -13289,13 +13834,13 @@
         <v>12001100001</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>682</v>
+        <v>723</v>
       </c>
       <c r="C23" t="s">
-        <v>683</v>
+        <v>724</v>
       </c>
       <c r="D23" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:4">
@@ -13303,13 +13848,13 @@
         <v>12001200001</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>684</v>
+        <v>725</v>
       </c>
       <c r="C24" t="s">
-        <v>685</v>
+        <v>726</v>
       </c>
       <c r="D24" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:4">
@@ -13317,13 +13862,13 @@
         <v>12001300001</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
       <c r="C25" t="s">
-        <v>687</v>
+        <v>728</v>
       </c>
       <c r="D25" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:4">
@@ -13331,13 +13876,13 @@
         <v>12001400001</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>688</v>
+        <v>729</v>
       </c>
       <c r="C26" t="s">
-        <v>689</v>
+        <v>730</v>
       </c>
       <c r="D26" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1" spans="1:4">
@@ -13345,13 +13890,13 @@
         <v>12002100001</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>690</v>
+        <v>731</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>691</v>
+        <v>732</v>
       </c>
       <c r="D27" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1" spans="1:4">
@@ -13359,13 +13904,13 @@
         <v>12002200001</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>692</v>
+        <v>733</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>693</v>
+        <v>734</v>
       </c>
       <c r="D28" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:4">
@@ -13373,13 +13918,13 @@
         <v>12002300001</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="D29" t="s">
         <v>694</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>695</v>
-      </c>
-      <c r="D29" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1" spans="1:4">
@@ -13387,13 +13932,13 @@
         <v>12002400001</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>696</v>
+        <v>737</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>697</v>
+        <v>738</v>
       </c>
       <c r="D30" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" spans="1:4">
@@ -13401,13 +13946,13 @@
         <v>12003100001</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="D31" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1" spans="1:4">
@@ -13415,13 +13960,13 @@
         <v>12003200001</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>700</v>
+        <v>741</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>701</v>
+        <v>742</v>
       </c>
       <c r="D32" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1" spans="1:4">
@@ -13429,13 +13974,13 @@
         <v>12003300001</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>702</v>
+        <v>743</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>703</v>
+        <v>744</v>
       </c>
       <c r="D33" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" spans="1:4">
@@ -13443,13 +13988,13 @@
         <v>12003400001</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>704</v>
+        <v>745</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="D34" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="1:4">
@@ -13457,13 +14002,13 @@
         <v>12010100001</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>706</v>
+        <v>747</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>707</v>
+        <v>748</v>
       </c>
       <c r="D35" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" ht="17.25" customHeight="1" spans="1:4">
@@ -13471,13 +14016,13 @@
         <v>12010200001</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>708</v>
+        <v>749</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>709</v>
+        <v>750</v>
       </c>
       <c r="D36" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="37" ht="17.25" customHeight="1" spans="1:4">
@@ -13485,13 +14030,13 @@
         <v>12010300001</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>710</v>
+        <v>751</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>711</v>
+        <v>752</v>
       </c>
       <c r="D37" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="1:4">
@@ -13499,13 +14044,13 @@
         <v>12011100001</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>712</v>
+        <v>753</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>713</v>
+        <v>754</v>
       </c>
       <c r="D38" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="1:4">
@@ -13513,13 +14058,13 @@
         <v>12011200001</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>714</v>
+        <v>755</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>715</v>
+        <v>756</v>
       </c>
       <c r="D39" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="1:4">
@@ -13527,13 +14072,13 @@
         <v>12011300001</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>716</v>
+        <v>757</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="D40" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -13541,13 +14086,13 @@
         <v>13000100001</v>
       </c>
       <c r="B41" t="s">
-        <v>718</v>
+        <v>759</v>
       </c>
       <c r="C41" t="s">
-        <v>719</v>
+        <v>760</v>
       </c>
       <c r="D41" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -13555,13 +14100,13 @@
         <v>13000200001</v>
       </c>
       <c r="B42" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="C42" t="s">
-        <v>721</v>
+        <v>762</v>
       </c>
       <c r="D42" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -13569,13 +14114,13 @@
         <v>13000300001</v>
       </c>
       <c r="B43" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
       <c r="C43" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="D43" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -13583,13 +14128,13 @@
         <v>13000400001</v>
       </c>
       <c r="B44" t="s">
-        <v>724</v>
+        <v>765</v>
       </c>
       <c r="C44" t="s">
-        <v>725</v>
+        <v>766</v>
       </c>
       <c r="D44" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -13597,13 +14142,13 @@
         <v>13000500001</v>
       </c>
       <c r="B45" t="s">
-        <v>726</v>
+        <v>767</v>
       </c>
       <c r="C45" t="s">
-        <v>727</v>
+        <v>768</v>
       </c>
       <c r="D45" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -13611,13 +14156,13 @@
         <v>13000600001</v>
       </c>
       <c r="B46" t="s">
-        <v>728</v>
+        <v>769</v>
       </c>
       <c r="C46" t="s">
-        <v>729</v>
+        <v>770</v>
       </c>
       <c r="D46" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -13625,13 +14170,13 @@
         <v>13000700001</v>
       </c>
       <c r="B47" t="s">
-        <v>730</v>
+        <v>771</v>
       </c>
       <c r="C47" t="s">
-        <v>731</v>
+        <v>772</v>
       </c>
       <c r="D47" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -13639,13 +14184,13 @@
         <v>10001000010000</v>
       </c>
       <c r="B48" t="s">
-        <v>732</v>
+        <v>773</v>
       </c>
       <c r="C48" t="s">
-        <v>733</v>
+        <v>774</v>
       </c>
       <c r="D48" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -13653,13 +14198,13 @@
         <v>10002000010000</v>
       </c>
       <c r="B49" t="s">
-        <v>732</v>
+        <v>773</v>
       </c>
       <c r="C49" t="s">
-        <v>733</v>
+        <v>774</v>
       </c>
       <c r="D49" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -13667,13 +14212,13 @@
         <v>10003000010000</v>
       </c>
       <c r="B50" t="s">
-        <v>734</v>
+        <v>775</v>
       </c>
       <c r="C50" t="s">
-        <v>735</v>
+        <v>776</v>
       </c>
       <c r="D50" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -13681,13 +14226,13 @@
         <v>10004000010000</v>
       </c>
       <c r="B51" t="s">
-        <v>734</v>
+        <v>775</v>
       </c>
       <c r="C51" t="s">
-        <v>735</v>
+        <v>776</v>
       </c>
       <c r="D51" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -13695,13 +14240,13 @@
         <v>10005000010000</v>
       </c>
       <c r="B52" t="s">
-        <v>734</v>
+        <v>775</v>
       </c>
       <c r="C52" t="s">
-        <v>735</v>
+        <v>776</v>
       </c>
       <c r="D52" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -13709,13 +14254,13 @@
         <v>20001000010000</v>
       </c>
       <c r="B53" t="s">
-        <v>736</v>
+        <v>777</v>
       </c>
       <c r="C53" t="s">
-        <v>737</v>
+        <v>778</v>
       </c>
       <c r="D53" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -13723,13 +14268,13 @@
         <v>20002000010000</v>
       </c>
       <c r="B54" t="s">
-        <v>738</v>
+        <v>779</v>
       </c>
       <c r="C54" t="s">
-        <v>739</v>
+        <v>780</v>
       </c>
       <c r="D54" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -13737,13 +14282,13 @@
         <v>20003000010000</v>
       </c>
       <c r="B55" t="s">
-        <v>740</v>
+        <v>781</v>
       </c>
       <c r="C55" t="s">
-        <v>741</v>
+        <v>782</v>
       </c>
       <c r="D55" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -13751,13 +14296,13 @@
         <v>20004000010000</v>
       </c>
       <c r="B56" t="s">
-        <v>742</v>
+        <v>783</v>
       </c>
       <c r="C56" t="s">
-        <v>743</v>
+        <v>784</v>
       </c>
       <c r="D56" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -13771,7 +14316,7 @@
         <v>297</v>
       </c>
       <c r="D57" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -13785,7 +14330,7 @@
         <v>305</v>
       </c>
       <c r="D58" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -13799,7 +14344,7 @@
         <v>309</v>
       </c>
       <c r="D59" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -13807,13 +14352,13 @@
         <v>30004000010000</v>
       </c>
       <c r="B60" t="s">
-        <v>744</v>
+        <v>785</v>
       </c>
       <c r="C60" t="s">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="D60" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -13821,13 +14366,13 @@
         <v>110001000010000</v>
       </c>
       <c r="B61" t="s">
-        <v>746</v>
+        <v>787</v>
       </c>
       <c r="C61" t="s">
-        <v>747</v>
+        <v>788</v>
       </c>
       <c r="D61" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -13835,13 +14380,13 @@
         <v>110002000010000</v>
       </c>
       <c r="B62" t="s">
-        <v>748</v>
+        <v>789</v>
       </c>
       <c r="C62" t="s">
-        <v>749</v>
+        <v>790</v>
       </c>
       <c r="D62" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -13849,13 +14394,13 @@
         <v>110003000010000</v>
       </c>
       <c r="B63" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="C63" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
       <c r="D63" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -13863,13 +14408,13 @@
         <v>120001000010000</v>
       </c>
       <c r="B64" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="C64" t="s">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="D64" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -13877,13 +14422,13 @@
         <v>120002000010000</v>
       </c>
       <c r="B65" t="s">
-        <v>754</v>
+        <v>795</v>
       </c>
       <c r="C65" t="s">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="D65" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -13891,13 +14436,13 @@
         <v>120003000010000</v>
       </c>
       <c r="B66" t="s">
-        <v>756</v>
+        <v>797</v>
       </c>
       <c r="C66" t="s">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="D66" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -13905,13 +14450,13 @@
         <v>120011000010000</v>
       </c>
       <c r="B67" t="s">
-        <v>758</v>
+        <v>799</v>
       </c>
       <c r="C67" t="s">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="D67" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -13919,13 +14464,13 @@
         <v>120012000010000</v>
       </c>
       <c r="B68" t="s">
-        <v>760</v>
+        <v>801</v>
       </c>
       <c r="C68" t="s">
-        <v>761</v>
+        <v>802</v>
       </c>
       <c r="D68" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -13933,13 +14478,13 @@
         <v>120013000010000</v>
       </c>
       <c r="B69" t="s">
-        <v>762</v>
+        <v>803</v>
       </c>
       <c r="C69" t="s">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="D69" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -13947,13 +14492,13 @@
         <v>120014000010000</v>
       </c>
       <c r="B70" t="s">
-        <v>764</v>
+        <v>805</v>
       </c>
       <c r="C70" t="s">
-        <v>765</v>
+        <v>806</v>
       </c>
       <c r="D70" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -13961,13 +14506,13 @@
         <v>120021000010000</v>
       </c>
       <c r="B71" t="s">
-        <v>766</v>
+        <v>807</v>
       </c>
       <c r="C71" t="s">
-        <v>767</v>
+        <v>808</v>
       </c>
       <c r="D71" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -13975,13 +14520,13 @@
         <v>120022000010000</v>
       </c>
       <c r="B72" t="s">
-        <v>768</v>
+        <v>809</v>
       </c>
       <c r="C72" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
       <c r="D72" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -13989,13 +14534,13 @@
         <v>120023000010000</v>
       </c>
       <c r="B73" t="s">
-        <v>770</v>
+        <v>811</v>
       </c>
       <c r="C73" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="D73" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -14003,13 +14548,13 @@
         <v>120024000010000</v>
       </c>
       <c r="B74" t="s">
-        <v>772</v>
+        <v>813</v>
       </c>
       <c r="C74" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="D74" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -14017,13 +14562,13 @@
         <v>120031000010000</v>
       </c>
       <c r="B75" t="s">
-        <v>774</v>
+        <v>815</v>
       </c>
       <c r="C75" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
       <c r="D75" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -14031,13 +14576,13 @@
         <v>120032000010000</v>
       </c>
       <c r="B76" t="s">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="C76" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="D76" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -14045,13 +14590,13 @@
         <v>120033000010000</v>
       </c>
       <c r="B77" t="s">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="C77" t="s">
-        <v>779</v>
+        <v>820</v>
       </c>
       <c r="D77" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -14059,13 +14604,13 @@
         <v>120034000010000</v>
       </c>
       <c r="B78" t="s">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="C78" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="D78" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -14073,13 +14618,13 @@
         <v>120101000010000</v>
       </c>
       <c r="B79" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="C79" t="s">
-        <v>783</v>
+        <v>824</v>
       </c>
       <c r="D79" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -14087,13 +14632,13 @@
         <v>120102000010000</v>
       </c>
       <c r="B80" t="s">
-        <v>784</v>
+        <v>825</v>
       </c>
       <c r="C80" t="s">
-        <v>785</v>
+        <v>826</v>
       </c>
       <c r="D80" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -14101,13 +14646,13 @@
         <v>120103000010000</v>
       </c>
       <c r="B81" t="s">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="C81" t="s">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="D81" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -14115,13 +14660,13 @@
         <v>120111000010000</v>
       </c>
       <c r="B82" t="s">
-        <v>788</v>
+        <v>829</v>
       </c>
       <c r="C82" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="D82" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -14129,13 +14674,13 @@
         <v>120112000010000</v>
       </c>
       <c r="B83" t="s">
-        <v>790</v>
+        <v>831</v>
       </c>
       <c r="C83" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="D83" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -14143,13 +14688,13 @@
         <v>120113000010000</v>
       </c>
       <c r="B84" t="s">
-        <v>792</v>
+        <v>833</v>
       </c>
       <c r="C84" t="s">
-        <v>793</v>
+        <v>834</v>
       </c>
       <c r="D84" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -14157,13 +14702,13 @@
         <v>130001000010000</v>
       </c>
       <c r="B85" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="C85" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="D85" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -14171,13 +14716,13 @@
         <v>130003000010000</v>
       </c>
       <c r="B86" t="s">
-        <v>796</v>
+        <v>837</v>
       </c>
       <c r="C86" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
       <c r="D86" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -14185,13 +14730,13 @@
         <v>130004000010000</v>
       </c>
       <c r="B87" t="s">
-        <v>798</v>
+        <v>839</v>
       </c>
       <c r="C87" t="s">
-        <v>799</v>
+        <v>840</v>
       </c>
       <c r="D87" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -14199,13 +14744,13 @@
         <v>130005000010000</v>
       </c>
       <c r="B88" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="C88" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
       <c r="D88" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -14213,13 +14758,13 @@
         <v>130006000010000</v>
       </c>
       <c r="B89" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="C89" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="D89" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -14227,13 +14772,13 @@
         <v>130007000010000</v>
       </c>
       <c r="B90" t="s">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="C90" t="s">
-        <v>805</v>
+        <v>846</v>
       </c>
       <c r="D90" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -14301,13 +14846,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="C4" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="D4" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14315,13 +14860,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>809</v>
+        <v>850</v>
       </c>
       <c r="C5" t="s">
-        <v>810</v>
+        <v>851</v>
       </c>
       <c r="D5" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14329,13 +14874,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="C6" t="s">
-        <v>812</v>
+        <v>853</v>
       </c>
       <c r="D6" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14343,13 +14888,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>813</v>
+        <v>854</v>
       </c>
       <c r="C7" t="s">
-        <v>814</v>
+        <v>855</v>
       </c>
       <c r="D7" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14357,13 +14902,13 @@
         <v>100001</v>
       </c>
       <c r="B8" t="s">
-        <v>815</v>
+        <v>856</v>
       </c>
       <c r="C8" t="s">
-        <v>816</v>
+        <v>857</v>
       </c>
       <c r="D8" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14371,13 +14916,13 @@
         <v>100002</v>
       </c>
       <c r="B9" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="C9" t="s">
-        <v>818</v>
+        <v>859</v>
       </c>
       <c r="D9" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -14385,13 +14930,13 @@
         <v>100003</v>
       </c>
       <c r="B10" t="s">
-        <v>819</v>
+        <v>860</v>
       </c>
       <c r="C10" t="s">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="D10" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -14399,13 +14944,13 @@
         <v>100004</v>
       </c>
       <c r="B11" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="C11" t="s">
-        <v>822</v>
+        <v>863</v>
       </c>
       <c r="D11" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -14413,13 +14958,13 @@
         <v>200001</v>
       </c>
       <c r="B12" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="C12" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="D12" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14427,13 +14972,13 @@
         <v>200002</v>
       </c>
       <c r="B13" t="s">
-        <v>825</v>
+        <v>866</v>
       </c>
       <c r="C13" t="s">
-        <v>826</v>
+        <v>867</v>
       </c>
       <c r="D13" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -14441,13 +14986,13 @@
         <v>200003</v>
       </c>
       <c r="B14" t="s">
-        <v>827</v>
+        <v>868</v>
       </c>
       <c r="C14" t="s">
-        <v>828</v>
+        <v>869</v>
       </c>
       <c r="D14" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -14455,13 +15000,13 @@
         <v>200004</v>
       </c>
       <c r="B15" t="s">
-        <v>829</v>
+        <v>870</v>
       </c>
       <c r="C15" t="s">
-        <v>830</v>
+        <v>871</v>
       </c>
       <c r="D15" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -14469,13 +15014,13 @@
         <v>200005</v>
       </c>
       <c r="B16" t="s">
-        <v>831</v>
+        <v>872</v>
       </c>
       <c r="C16" t="s">
-        <v>832</v>
+        <v>873</v>
       </c>
       <c r="D16" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14483,13 +15028,13 @@
         <v>200006</v>
       </c>
       <c r="B17" t="s">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="C17" t="s">
-        <v>834</v>
+        <v>875</v>
       </c>
       <c r="D17" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -14497,13 +15042,13 @@
         <v>200007</v>
       </c>
       <c r="B18" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
       <c r="C18" t="s">
-        <v>836</v>
+        <v>877</v>
       </c>
       <c r="D18" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -14511,13 +15056,13 @@
         <v>200008</v>
       </c>
       <c r="B19" t="s">
-        <v>837</v>
+        <v>878</v>
       </c>
       <c r="C19" t="s">
-        <v>838</v>
+        <v>879</v>
       </c>
       <c r="D19" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14525,13 +15070,13 @@
         <v>200009</v>
       </c>
       <c r="B20" t="s">
-        <v>839</v>
+        <v>880</v>
       </c>
       <c r="C20" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
       <c r="D20" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -14539,13 +15084,13 @@
         <v>200010</v>
       </c>
       <c r="B21" t="s">
-        <v>841</v>
+        <v>882</v>
       </c>
       <c r="C21" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
       <c r="D21" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -14553,13 +15098,13 @@
         <v>200011</v>
       </c>
       <c r="B22" t="s">
-        <v>843</v>
+        <v>884</v>
       </c>
       <c r="C22" t="s">
-        <v>844</v>
+        <v>885</v>
       </c>
       <c r="D22" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -14567,13 +15112,13 @@
         <v>200012</v>
       </c>
       <c r="B23" t="s">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="C23" t="s">
-        <v>846</v>
+        <v>887</v>
       </c>
       <c r="D23" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -14581,13 +15126,13 @@
         <v>200013</v>
       </c>
       <c r="B24" t="s">
-        <v>847</v>
+        <v>888</v>
       </c>
       <c r="C24" t="s">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="D24" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -14595,13 +15140,13 @@
         <v>200014</v>
       </c>
       <c r="B25" t="s">
+        <v>890</v>
+      </c>
+      <c r="C25" t="s">
+        <v>891</v>
+      </c>
+      <c r="D25" t="s">
         <v>849</v>
-      </c>
-      <c r="C25" t="s">
-        <v>850</v>
-      </c>
-      <c r="D25" t="s">
-        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -14669,13 +15214,13 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
-        <v>851</v>
+        <v>892</v>
       </c>
       <c r="C4" t="s">
-        <v>852</v>
+        <v>893</v>
       </c>
       <c r="D4" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -14683,13 +15228,13 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>854</v>
+        <v>895</v>
       </c>
       <c r="C5" t="s">
-        <v>855</v>
+        <v>896</v>
       </c>
       <c r="D5" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -14697,13 +15242,13 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>856</v>
+        <v>897</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>898</v>
       </c>
       <c r="D6" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -14711,13 +15256,13 @@
         <v>20001</v>
       </c>
       <c r="B7" t="s">
-        <v>858</v>
+        <v>899</v>
       </c>
       <c r="C7" t="s">
-        <v>859</v>
+        <v>900</v>
       </c>
       <c r="D7" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -14725,13 +15270,13 @@
         <v>20002</v>
       </c>
       <c r="B8" t="s">
-        <v>860</v>
+        <v>901</v>
       </c>
       <c r="C8" t="s">
-        <v>861</v>
+        <v>902</v>
       </c>
       <c r="D8" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -14739,13 +15284,13 @@
         <v>20003</v>
       </c>
       <c r="B9" t="s">
-        <v>862</v>
+        <v>903</v>
       </c>
       <c r="C9" t="s">
-        <v>863</v>
+        <v>904</v>
       </c>
       <c r="D9" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -14753,13 +15298,13 @@
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="C10" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
       <c r="D10" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -14767,13 +15312,13 @@
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="C11" t="s">
-        <v>867</v>
+        <v>908</v>
       </c>
       <c r="D11" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -14781,13 +15326,13 @@
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>868</v>
+        <v>909</v>
       </c>
       <c r="C12" t="s">
-        <v>869</v>
+        <v>910</v>
       </c>
       <c r="D12" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14795,13 +15340,13 @@
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="C13" t="s">
-        <v>871</v>
+        <v>912</v>
       </c>
       <c r="D13" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -14809,13 +15354,13 @@
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>872</v>
+        <v>913</v>
       </c>
       <c r="C14" t="s">
-        <v>873</v>
+        <v>914</v>
       </c>
       <c r="D14" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -14823,13 +15368,13 @@
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>874</v>
+        <v>915</v>
       </c>
       <c r="C15" t="s">
-        <v>875</v>
+        <v>916</v>
       </c>
       <c r="D15" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -14837,13 +15382,13 @@
         <v>50001</v>
       </c>
       <c r="B16" t="s">
-        <v>876</v>
+        <v>917</v>
       </c>
       <c r="C16" t="s">
-        <v>877</v>
+        <v>918</v>
       </c>
       <c r="D16" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14851,13 +15396,13 @@
         <v>50002</v>
       </c>
       <c r="B17" t="s">
-        <v>878</v>
+        <v>919</v>
       </c>
       <c r="C17" t="s">
-        <v>879</v>
+        <v>920</v>
       </c>
       <c r="D17" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -14865,13 +15410,13 @@
         <v>50003</v>
       </c>
       <c r="B18" t="s">
-        <v>880</v>
+        <v>921</v>
       </c>
       <c r="C18" t="s">
-        <v>881</v>
+        <v>922</v>
       </c>
       <c r="D18" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -14879,13 +15424,13 @@
         <v>60001</v>
       </c>
       <c r="B19" t="s">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="C19" t="s">
-        <v>883</v>
+        <v>924</v>
       </c>
       <c r="D19" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14893,13 +15438,13 @@
         <v>60002</v>
       </c>
       <c r="B20" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="C20" t="s">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="D20" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -14907,13 +15452,13 @@
         <v>60003</v>
       </c>
       <c r="B21" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
       <c r="C21" t="s">
-        <v>887</v>
+        <v>928</v>
       </c>
       <c r="D21" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -14921,13 +15466,13 @@
         <v>70001</v>
       </c>
       <c r="B22" t="s">
-        <v>888</v>
+        <v>929</v>
       </c>
       <c r="C22" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
       <c r="D22" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -14935,13 +15480,13 @@
         <v>70002</v>
       </c>
       <c r="B23" t="s">
-        <v>890</v>
+        <v>931</v>
       </c>
       <c r="C23" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
       <c r="D23" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -14949,13 +15494,13 @@
         <v>70003</v>
       </c>
       <c r="B24" t="s">
-        <v>892</v>
+        <v>933</v>
       </c>
       <c r="C24" t="s">
-        <v>893</v>
+        <v>934</v>
       </c>
       <c r="D24" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -15023,13 +15568,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="C4" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
       <c r="D4" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15037,13 +15582,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>897</v>
+        <v>938</v>
       </c>
       <c r="C5" t="s">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="D5" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15051,13 +15596,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>899</v>
+        <v>940</v>
       </c>
       <c r="C6" t="s">
-        <v>900</v>
+        <v>941</v>
       </c>
       <c r="D6" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15065,13 +15610,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>901</v>
+        <v>942</v>
       </c>
       <c r="C7" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="D7" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>
@@ -15139,13 +15684,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
       <c r="C4" t="s">
-        <v>904</v>
+        <v>945</v>
       </c>
       <c r="D4" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15153,13 +15698,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="C5" t="s">
-        <v>907</v>
+        <v>948</v>
       </c>
       <c r="D5" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15167,13 +15712,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>908</v>
+        <v>949</v>
       </c>
       <c r="C6" t="s">
-        <v>909</v>
+        <v>950</v>
       </c>
       <c r="D6" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15181,13 +15726,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>910</v>
+        <v>951</v>
       </c>
       <c r="C7" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="D7" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -15195,13 +15740,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>912</v>
+        <v>953</v>
       </c>
       <c r="C8" t="s">
-        <v>913</v>
+        <v>954</v>
       </c>
       <c r="D8" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -15209,13 +15754,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>914</v>
+        <v>955</v>
       </c>
       <c r="C9" t="s">
-        <v>915</v>
+        <v>956</v>
       </c>
       <c r="D9" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -15223,13 +15768,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>916</v>
+        <v>957</v>
       </c>
       <c r="C10" t="s">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="D10" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -15237,13 +15782,13 @@
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>918</v>
+        <v>959</v>
       </c>
       <c r="C11" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
       <c r="D11" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -15251,13 +15796,13 @@
         <v>1002</v>
       </c>
       <c r="B12" t="s">
-        <v>920</v>
+        <v>961</v>
       </c>
       <c r="C12" t="s">
-        <v>921</v>
+        <v>962</v>
       </c>
       <c r="D12" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15265,13 +15810,13 @@
         <v>1003</v>
       </c>
       <c r="B13" t="s">
-        <v>922</v>
+        <v>963</v>
       </c>
       <c r="C13" t="s">
-        <v>923</v>
+        <v>964</v>
       </c>
       <c r="D13" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -15279,13 +15824,13 @@
         <v>1004</v>
       </c>
       <c r="B14" t="s">
-        <v>924</v>
+        <v>965</v>
       </c>
       <c r="C14" t="s">
-        <v>925</v>
+        <v>966</v>
       </c>
       <c r="D14" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -15293,13 +15838,13 @@
         <v>2001</v>
       </c>
       <c r="B15" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
       <c r="C15" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="D15" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -15307,13 +15852,13 @@
         <v>2002</v>
       </c>
       <c r="B16" t="s">
-        <v>928</v>
+        <v>969</v>
       </c>
       <c r="C16" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="D16" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -15321,13 +15866,13 @@
         <v>2003</v>
       </c>
       <c r="B17" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="C17" t="s">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="D17" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -15335,13 +15880,13 @@
         <v>2004</v>
       </c>
       <c r="B18" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
       <c r="C18" t="s">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="D18" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -15349,13 +15894,13 @@
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="C19" t="s">
-        <v>935</v>
+        <v>976</v>
       </c>
       <c r="D19" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -15363,13 +15908,13 @@
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>936</v>
+        <v>977</v>
       </c>
       <c r="C20" t="s">
-        <v>937</v>
+        <v>978</v>
       </c>
       <c r="D20" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -15377,13 +15922,13 @@
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>938</v>
+        <v>979</v>
       </c>
       <c r="C21" t="s">
-        <v>939</v>
+        <v>980</v>
       </c>
       <c r="D21" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -15391,13 +15936,13 @@
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>940</v>
+        <v>981</v>
       </c>
       <c r="C22" t="s">
-        <v>941</v>
+        <v>982</v>
       </c>
       <c r="D22" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -15405,13 +15950,13 @@
         <v>4001</v>
       </c>
       <c r="B23" t="s">
-        <v>942</v>
+        <v>983</v>
       </c>
       <c r="C23" t="s">
-        <v>943</v>
+        <v>984</v>
       </c>
       <c r="D23" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -15419,13 +15964,13 @@
         <v>4002</v>
       </c>
       <c r="B24" t="s">
-        <v>944</v>
+        <v>985</v>
       </c>
       <c r="C24" t="s">
-        <v>945</v>
+        <v>986</v>
       </c>
       <c r="D24" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -15433,13 +15978,13 @@
         <v>4003</v>
       </c>
       <c r="B25" t="s">
+        <v>987</v>
+      </c>
+      <c r="C25" t="s">
+        <v>988</v>
+      </c>
+      <c r="D25" t="s">
         <v>946</v>
-      </c>
-      <c r="C25" t="s">
-        <v>947</v>
-      </c>
-      <c r="D25" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -15447,13 +15992,13 @@
         <v>4004</v>
       </c>
       <c r="B26" t="s">
-        <v>948</v>
+        <v>989</v>
       </c>
       <c r="C26" t="s">
-        <v>949</v>
+        <v>990</v>
       </c>
       <c r="D26" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -15461,13 +16006,13 @@
         <v>4005</v>
       </c>
       <c r="B27" t="s">
-        <v>950</v>
+        <v>991</v>
       </c>
       <c r="C27" t="s">
-        <v>951</v>
+        <v>992</v>
       </c>
       <c r="D27" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -15475,13 +16020,13 @@
         <v>5001</v>
       </c>
       <c r="B28" t="s">
-        <v>952</v>
+        <v>993</v>
       </c>
       <c r="C28" t="s">
-        <v>953</v>
+        <v>994</v>
       </c>
       <c r="D28" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -15489,13 +16034,13 @@
         <v>5002</v>
       </c>
       <c r="B29" t="s">
-        <v>954</v>
+        <v>995</v>
       </c>
       <c r="C29" t="s">
-        <v>955</v>
+        <v>996</v>
       </c>
       <c r="D29" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -15503,13 +16048,13 @@
         <v>5003</v>
       </c>
       <c r="B30" t="s">
-        <v>956</v>
+        <v>997</v>
       </c>
       <c r="C30" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="D30" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -15517,13 +16062,13 @@
         <v>5004</v>
       </c>
       <c r="B31" t="s">
-        <v>958</v>
+        <v>999</v>
       </c>
       <c r="C31" t="s">
-        <v>959</v>
+        <v>1000</v>
       </c>
       <c r="D31" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -15531,13 +16076,13 @@
         <v>6001</v>
       </c>
       <c r="B32" t="s">
-        <v>960</v>
+        <v>1001</v>
       </c>
       <c r="C32" t="s">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="D32" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -15545,13 +16090,13 @@
         <v>6002</v>
       </c>
       <c r="B33" t="s">
-        <v>962</v>
+        <v>1003</v>
       </c>
       <c r="C33" t="s">
-        <v>963</v>
+        <v>1004</v>
       </c>
       <c r="D33" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -15559,13 +16104,13 @@
         <v>6003</v>
       </c>
       <c r="B34" t="s">
-        <v>964</v>
+        <v>1005</v>
       </c>
       <c r="C34" t="s">
-        <v>965</v>
+        <v>1006</v>
       </c>
       <c r="D34" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -15573,13 +16118,13 @@
         <v>6004</v>
       </c>
       <c r="B35" t="s">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="C35" t="s">
-        <v>967</v>
+        <v>1008</v>
       </c>
       <c r="D35" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -15587,13 +16132,13 @@
         <v>6005</v>
       </c>
       <c r="B36" t="s">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="C36" t="s">
-        <v>969</v>
+        <v>1010</v>
       </c>
       <c r="D36" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -15601,13 +16146,13 @@
         <v>7001</v>
       </c>
       <c r="B37" t="s">
-        <v>970</v>
+        <v>1011</v>
       </c>
       <c r="C37" t="s">
-        <v>971</v>
+        <v>1012</v>
       </c>
       <c r="D37" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -15615,13 +16160,13 @@
         <v>7002</v>
       </c>
       <c r="B38" t="s">
-        <v>972</v>
+        <v>1013</v>
       </c>
       <c r="C38" t="s">
-        <v>973</v>
+        <v>1014</v>
       </c>
       <c r="D38" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -15629,13 +16174,13 @@
         <v>7003</v>
       </c>
       <c r="B39" t="s">
-        <v>974</v>
+        <v>1015</v>
       </c>
       <c r="C39" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="D39" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -15643,13 +16188,13 @@
         <v>7004</v>
       </c>
       <c r="B40" t="s">
-        <v>976</v>
+        <v>1017</v>
       </c>
       <c r="C40" t="s">
-        <v>977</v>
+        <v>1018</v>
       </c>
       <c r="D40" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -15657,13 +16202,13 @@
         <v>101001</v>
       </c>
       <c r="B41" t="s">
-        <v>978</v>
+        <v>1019</v>
       </c>
       <c r="C41" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
       <c r="D41" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -15671,13 +16216,13 @@
         <v>102001</v>
       </c>
       <c r="B42" t="s">
-        <v>979</v>
+        <v>1020</v>
       </c>
       <c r="C42" t="s">
-        <v>921</v>
+        <v>962</v>
       </c>
       <c r="D42" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -15685,13 +16230,13 @@
         <v>103001</v>
       </c>
       <c r="B43" t="s">
-        <v>980</v>
+        <v>1021</v>
       </c>
       <c r="C43" t="s">
-        <v>923</v>
+        <v>964</v>
       </c>
       <c r="D43" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -15699,13 +16244,13 @@
         <v>103002</v>
       </c>
       <c r="B44" t="s">
-        <v>981</v>
+        <v>1022</v>
       </c>
       <c r="C44" t="s">
-        <v>925</v>
+        <v>966</v>
       </c>
       <c r="D44" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -15713,13 +16258,13 @@
         <v>900001</v>
       </c>
       <c r="B45" t="s">
-        <v>982</v>
+        <v>1023</v>
       </c>
       <c r="C45" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="D45" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -15727,13 +16272,13 @@
         <v>900002</v>
       </c>
       <c r="B46" t="s">
-        <v>984</v>
+        <v>1025</v>
       </c>
       <c r="C46" t="s">
-        <v>985</v>
+        <v>1026</v>
       </c>
       <c r="D46" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="723" activeTab="3"/>
+    <workbookView windowHeight="17655" tabRatio="723" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -16,9 +16,9 @@
     <sheet name="StoreGashaponmachineInfo" sheetId="7" r:id="rId7"/>
     <sheet name="GameWorldInfo" sheetId="8" r:id="rId8"/>
     <sheet name="CreatureInfo" sheetId="9" r:id="rId9"/>
-    <sheet name="CreatureModel" sheetId="17" r:id="rId10"/>
-    <sheet name="CreatureAttributeTypeInfo" sheetId="18" r:id="rId11"/>
-    <sheet name="NpcInfo" sheetId="10" r:id="rId12"/>
+    <sheet name="NpcInfo" sheetId="10" r:id="rId10"/>
+    <sheet name="CreatureModel" sheetId="17" r:id="rId11"/>
+    <sheet name="CreatureAttributeTypeInfo" sheetId="18" r:id="rId12"/>
     <sheet name="ConversationCouncilorInfo" sheetId="11" r:id="rId13"/>
     <sheet name="TitleInfo" sheetId="12" r:id="rId14"/>
     <sheet name="NpcRelationshipInfo" sheetId="13" r:id="rId15"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="1358">
   <si>
     <t>id</t>
   </si>
@@ -3109,6 +3109,12 @@
     <t>人类-弓箭手</t>
   </si>
   <si>
+    <t>人类-强弓手</t>
+  </si>
+  <si>
+    <t>人类-连射手</t>
+  </si>
+  <si>
     <t>人类-魔法师（火）</t>
   </si>
   <si>
@@ -3127,6 +3133,75 @@
     <t>Test Skeleton Hurler</t>
   </si>
   <si>
+    <t>没头脑</t>
+  </si>
+  <si>
+    <t>Dimwit</t>
+  </si>
+  <si>
+    <t>不高兴</t>
+  </si>
+  <si>
+    <t>Grumpy</t>
+  </si>
+  <si>
+    <t>忠诚</t>
+  </si>
+  <si>
+    <t>Loyal</t>
+  </si>
+  <si>
+    <t>冒险者</t>
+  </si>
+  <si>
+    <t>持盾战士</t>
+  </si>
+  <si>
+    <t>持盾战士-Boss-lv1</t>
+  </si>
+  <si>
+    <t>弓箭手</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>强弓手</t>
+  </si>
+  <si>
+    <t>强弓手-Boss-lv1</t>
+  </si>
+  <si>
+    <t>连射手</t>
+  </si>
+  <si>
+    <t>连射手-Boss-lv1</t>
+  </si>
+  <si>
+    <t>魔法师（火）</t>
+  </si>
+  <si>
+    <t>Mage (Fire)</t>
+  </si>
+  <si>
+    <t>魔法师（冰）</t>
+  </si>
+  <si>
+    <t>Mage (Ice)</t>
+  </si>
+  <si>
+    <t>白剑伟</t>
+  </si>
+  <si>
+    <t>Bai Jianwei</t>
+  </si>
+  <si>
+    <t>宛家伟</t>
+  </si>
+  <si>
+    <t>Wan Jiawei</t>
+  </si>
+  <si>
     <t>生命</t>
   </si>
   <si>
@@ -3173,60 +3248,6 @@
   </si>
   <si>
     <t>MPF</t>
-  </si>
-  <si>
-    <t>没头脑</t>
-  </si>
-  <si>
-    <t>Dimwit</t>
-  </si>
-  <si>
-    <t>不高兴</t>
-  </si>
-  <si>
-    <t>Grumpy</t>
-  </si>
-  <si>
-    <t>忠诚</t>
-  </si>
-  <si>
-    <t>Loyal</t>
-  </si>
-  <si>
-    <t>战士</t>
-  </si>
-  <si>
-    <t>Warrior</t>
-  </si>
-  <si>
-    <t>弓箭手</t>
-  </si>
-  <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>魔法师（火）</t>
-  </si>
-  <si>
-    <t>Mage (Fire)</t>
-  </si>
-  <si>
-    <t>魔法师（冰）</t>
-  </si>
-  <si>
-    <t>Mage (Ice)</t>
-  </si>
-  <si>
-    <t>白剑伟</t>
-  </si>
-  <si>
-    <t>Bai Jianwei</t>
-  </si>
-  <si>
-    <t>宛家伟</t>
-  </si>
-  <si>
-    <t>Wan Jiawei</t>
   </si>
   <si>
     <t>滚开！</t>
@@ -4800,6 +4821,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4807,9 +4831,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6906,10 +6927,10 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="14">
+      <c r="A125" s="11">
         <v>90001</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="11" t="s">
         <v>244</v>
       </c>
       <c r="C125"/>
@@ -6918,10 +6939,10 @@
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="14">
+      <c r="A126" s="11">
         <v>90002</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="11" t="s">
         <v>245</v>
       </c>
       <c r="C126"/>
@@ -7196,10 +7217,10 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="14">
+      <c r="A146" s="11">
         <v>2000008</v>
       </c>
-      <c r="B146" s="14" t="s">
+      <c r="B146" s="11" t="s">
         <v>280</v>
       </c>
       <c r="C146"/>
@@ -7208,10 +7229,10 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="14">
+      <c r="A147" s="11">
         <v>2000009</v>
       </c>
-      <c r="B147" s="14" t="s">
+      <c r="B147" s="11" t="s">
         <v>281</v>
       </c>
       <c r="C147"/>
@@ -7220,10 +7241,10 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="14">
+      <c r="A148" s="11">
         <v>2000010</v>
       </c>
-      <c r="B148" s="14" t="s">
+      <c r="B148" s="11" t="s">
         <v>282</v>
       </c>
       <c r="C148"/>
@@ -7309,6 +7330,211 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>1010010001</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" s="9" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>1010020001</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" s="9" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>1020010001</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="11">
+        <v>1020020001</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10" s="11" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="11">
+        <v>1020030001</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" s="11" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>1030010001</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>1030020001</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="14" ht="12" customHeight="1" spans="1:4">
+      <c r="A14">
+        <v>2000000001</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>2000000002</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D10"/>
@@ -7465,7 +7691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D14"/>
@@ -7522,10 +7748,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="C4" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="D4" t="s">
         <v>946</v>
@@ -7536,10 +7762,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1029</v>
+        <v>1054</v>
       </c>
       <c r="C5" t="s">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="D5" t="s">
         <v>946</v>
@@ -7550,10 +7776,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="D6" t="s">
         <v>946</v>
@@ -7564,10 +7790,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1033</v>
+        <v>1058</v>
       </c>
       <c r="C7" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="D7" t="s">
         <v>946</v>
@@ -7578,7 +7804,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="D8" t="s">
         <v>946</v>
@@ -7589,7 +7815,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="D9" t="s">
         <v>946</v>
@@ -7600,7 +7826,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="D10" t="s">
         <v>946</v>
@@ -7622,7 +7848,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="D12" t="s">
         <v>946</v>
@@ -7633,10 +7859,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1040</v>
+        <v>1065</v>
       </c>
       <c r="D13" t="s">
         <v>946</v>
@@ -7647,171 +7873,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1041</v>
+        <v>1066</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1042</v>
+        <v>1067</v>
       </c>
       <c r="D14" t="s">
         <v>946</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>1010010001</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>1020010001</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>1030010001</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>1030020001</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="11" ht="12" customHeight="1" spans="1:4">
-      <c r="A11">
-        <v>2000000001</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>2000000002</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -7877,10 +7945,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="C4" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -7888,10 +7956,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="C5" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -7899,10 +7967,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="C6" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -7910,10 +7978,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="C7" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -7921,10 +7989,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="C8" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -7932,10 +8000,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="C9" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -7943,10 +8011,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="C10" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -7954,10 +8022,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="C11" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -7965,10 +8033,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="C12" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -7976,10 +8044,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="C13" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -7987,10 +8055,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C14" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -7998,10 +8066,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="C15" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -8009,10 +8077,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="C16" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8020,10 +8088,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="C17" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -8031,10 +8099,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="C18" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8042,10 +8110,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="C19" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8053,10 +8121,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C20" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8064,10 +8132,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="C21" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8075,10 +8143,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="C22" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8086,10 +8154,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="C23" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8097,10 +8165,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C24" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8108,10 +8176,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="C25" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8119,10 +8187,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="C26" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8130,10 +8198,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="C27" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8141,10 +8209,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="C28" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8152,10 +8220,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="C29" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8163,10 +8231,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="C30" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8174,10 +8242,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="C31" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8185,10 +8253,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="C32" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8196,10 +8264,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="C33" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8207,10 +8275,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="C34" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
@@ -8277,10 +8345,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="C4" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8288,10 +8356,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C5" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8299,10 +8367,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="C6" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8310,10 +8378,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="C7" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8321,10 +8389,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="C8" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8332,10 +8400,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="C9" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8343,10 +8411,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="C10" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8354,10 +8422,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="C11" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8365,10 +8433,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="C12" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8376,10 +8444,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="C13" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8387,10 +8455,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="C14" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8398,10 +8466,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="C15" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8409,10 +8477,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="C16" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
     </row>
   </sheetData>
@@ -8477,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8488,10 +8556,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="C5" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8499,10 +8567,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="C6" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8510,10 +8578,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="C7" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8521,10 +8589,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C8" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>
@@ -8590,10 +8658,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="C4" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8601,10 +8669,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8612,10 +8680,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8623,10 +8691,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8634,10 +8702,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8645,10 +8713,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8656,10 +8724,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8667,10 +8735,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8678,10 +8746,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8689,10 +8757,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
     </row>
   </sheetData>
@@ -8758,7 +8826,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8769,7 +8837,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8780,10 +8848,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8791,10 +8859,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8802,10 +8870,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8813,10 +8881,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="C9" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -8884,13 +8952,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="C4" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="D4" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8898,13 +8966,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="C5" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="D5" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8912,13 +8980,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="D6" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8926,13 +8994,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="C7" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="D7" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8940,13 +9008,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D8" t="s">
         <v>1197</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8954,13 +9022,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="C9" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="D9" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8968,13 +9036,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="C10" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="D10" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8982,13 +9050,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="C11" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="D11" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8996,13 +9064,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="C12" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="D12" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -9010,13 +9078,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="C13" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="D13" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -9024,13 +9092,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="C14" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D14" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -9038,13 +9106,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="C15" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="D15" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -9052,13 +9120,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="C16" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="D16" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -9066,13 +9134,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="C17" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="D17" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9080,13 +9148,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="C18" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D18" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -9094,13 +9162,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="C19" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="D19" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9108,13 +9176,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="C20" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="D20" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -9122,13 +9190,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="C21" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="D21" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9136,13 +9204,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="C22" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="D22" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9150,13 +9218,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="C23" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="D23" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9164,13 +9232,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="C24" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="D24" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9178,13 +9246,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="C25" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="D25" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9192,13 +9260,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="C26" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="D26" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9206,13 +9274,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="C27" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="D27" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9220,13 +9288,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="C28" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="D28" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9234,13 +9302,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="C29" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="D29" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9248,13 +9316,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="C30" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="D30" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9262,13 +9330,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="C31" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="D31" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9276,13 +9344,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="C32" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="D32" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9290,13 +9358,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="C33" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="D33" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9304,13 +9372,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="C34" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="D34" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9318,13 +9386,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="C35" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="D35" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9332,13 +9400,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="C36" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="D36" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9346,13 +9414,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="C37" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="D37" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9360,13 +9428,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="C38" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="D38" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9374,13 +9442,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="C39" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="D39" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9388,13 +9456,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="C40" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="D40" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9402,13 +9470,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="C41" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="D41" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9416,13 +9484,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="C42" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="D42" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9430,13 +9498,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="C43" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="D43" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9444,13 +9512,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="C44" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="D44" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9458,13 +9526,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="C45" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="D45" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9472,13 +9540,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="C46" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="D46" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9486,13 +9554,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="C47" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
       <c r="D47" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9500,13 +9568,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="C48" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="D48" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9514,13 +9582,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="C49" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="D49" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9528,13 +9596,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="C50" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="D50" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9542,13 +9610,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="C51" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="D51" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9556,13 +9624,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="C52" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="D52" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9570,13 +9638,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="C53" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="D53" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9584,13 +9652,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="C54" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="D54" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9598,13 +9666,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="C55" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="D55" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9612,13 +9680,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="C56" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="D56" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9626,13 +9694,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="C57" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="D57" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9640,13 +9708,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="C58" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="D58" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9654,13 +9722,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="C59" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="D59" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9668,13 +9736,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="C60" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="D60" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9682,13 +9750,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="C61" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="D61" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9696,13 +9764,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="C62" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="D62" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9710,13 +9778,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="C63" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="D63" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9724,13 +9792,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="C64" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="D64" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9738,13 +9806,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1309</v>
+        <v>1316</v>
       </c>
       <c r="C65" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="D65" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9752,13 +9820,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="C66" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="D66" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9766,13 +9834,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="C67" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="D67" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9780,13 +9848,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="C68" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="D68" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9794,13 +9862,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="C69" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="D69" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9808,13 +9876,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="C70" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="D70" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9822,13 +9890,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="C71" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="D71" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9836,13 +9904,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="C72" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="D72" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9850,13 +9918,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="C73" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="D73" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9864,13 +9932,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="C74" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="D74" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9878,13 +9946,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="C75" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="D75" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9892,13 +9960,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="C76" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="D76" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9906,13 +9974,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="C77" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="D77" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9920,13 +9988,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="C78" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="D78" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -9934,13 +10002,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
       <c r="C79" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="D79" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -9948,13 +10016,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="C80" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="D80" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -9962,13 +10030,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="C81" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
       <c r="D81" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -9976,13 +10044,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="C82" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="D82" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -9990,13 +10058,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="C83" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="D83" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -10004,13 +10072,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="C84" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="D84" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -10018,13 +10086,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="C85" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="D85" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
@@ -10432,10 +10500,10 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="14">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>268</v>
       </c>
       <c r="C4" t="s">
@@ -10446,10 +10514,10 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="14">
+      <c r="A5" s="11">
         <v>100001</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>327</v>
       </c>
       <c r="C5"/>
@@ -10512,7 +10580,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="14">
+      <c r="A10" s="11">
         <v>10100005</v>
       </c>
       <c r="B10" t="s">
@@ -10524,7 +10592,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="14">
+      <c r="A11" s="11">
         <v>10100007</v>
       </c>
       <c r="B11" t="s">
@@ -10536,7 +10604,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="14">
+      <c r="A12" s="11">
         <v>10100008</v>
       </c>
       <c r="B12" t="s">
@@ -10548,7 +10616,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="14">
+      <c r="A13" s="11">
         <v>10100010</v>
       </c>
       <c r="B13" t="s">
@@ -10560,7 +10628,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="14">
+      <c r="A14" s="11">
         <v>10100012</v>
       </c>
       <c r="B14" t="s">
@@ -10572,7 +10640,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="14">
+      <c r="A15" s="11">
         <v>10100013</v>
       </c>
       <c r="B15" t="s">
@@ -10584,7 +10652,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="14">
+      <c r="A16" s="11">
         <v>10100014</v>
       </c>
       <c r="B16" t="s">
@@ -10596,7 +10664,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="14">
+      <c r="A17" s="11">
         <v>10100015</v>
       </c>
       <c r="B17" t="s">
@@ -10608,7 +10676,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="14">
+      <c r="A18" s="11">
         <v>10100016</v>
       </c>
       <c r="B18" t="s">
@@ -10620,7 +10688,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="14">
+      <c r="A19" s="11">
         <v>10100017</v>
       </c>
       <c r="B19" t="s">
@@ -10635,7 +10703,7 @@
       <c r="A20">
         <v>10200001</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="11" t="s">
         <v>345</v>
       </c>
       <c r="C20" t="s">
@@ -10649,7 +10717,7 @@
       <c r="A21">
         <v>10200002</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="11" t="s">
         <v>347</v>
       </c>
       <c r="C21" t="s">
@@ -10663,7 +10731,7 @@
       <c r="A22">
         <v>10200003</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="11" t="s">
         <v>349</v>
       </c>
       <c r="C22" t="s">
@@ -10677,7 +10745,7 @@
       <c r="A23">
         <v>10200004</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="11" t="s">
         <v>351</v>
       </c>
       <c r="C23" t="s">
@@ -10688,10 +10756,10 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="14">
+      <c r="A24" s="11">
         <v>10200005</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="11" t="s">
         <v>353</v>
       </c>
       <c r="C24"/>
@@ -10700,10 +10768,10 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="14">
+      <c r="A25" s="11">
         <v>10200006</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="11" t="s">
         <v>354</v>
       </c>
       <c r="C25"/>
@@ -10712,10 +10780,10 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="14">
+      <c r="A26" s="11">
         <v>10200007</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="11" t="s">
         <v>355</v>
       </c>
       <c r="C26"/>
@@ -10724,10 +10792,10 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="14">
+      <c r="A27" s="11">
         <v>10200008</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="11" t="s">
         <v>356</v>
       </c>
       <c r="C27"/>
@@ -10736,10 +10804,10 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="14">
+      <c r="A28" s="11">
         <v>10200009</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="11" t="s">
         <v>357</v>
       </c>
       <c r="C28"/>
@@ -10748,10 +10816,10 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="14">
+      <c r="A29" s="11">
         <v>10200010</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="11" t="s">
         <v>358</v>
       </c>
       <c r="C29"/>
@@ -10760,10 +10828,10 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="14">
+      <c r="A30" s="11">
         <v>10200011</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="11" t="s">
         <v>359</v>
       </c>
       <c r="C30"/>
@@ -10772,10 +10840,10 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="14">
+      <c r="A31" s="11">
         <v>10200012</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="11" t="s">
         <v>360</v>
       </c>
       <c r="C31"/>
@@ -10784,10 +10852,10 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="14">
+      <c r="A32" s="11">
         <v>10200013</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="11" t="s">
         <v>361</v>
       </c>
       <c r="C32"/>
@@ -10796,10 +10864,10 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="14">
+      <c r="A33" s="11">
         <v>10200014</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="11" t="s">
         <v>362</v>
       </c>
       <c r="C33"/>
@@ -10808,10 +10876,10 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="14">
+      <c r="A34" s="11">
         <v>10200015</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="11" t="s">
         <v>363</v>
       </c>
       <c r="C34"/>
@@ -10820,10 +10888,10 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="14">
+      <c r="A35" s="11">
         <v>10200016</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="11" t="s">
         <v>364</v>
       </c>
       <c r="C35"/>
@@ -10832,10 +10900,10 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="14">
+      <c r="A36" s="11">
         <v>10200017</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="11" t="s">
         <v>365</v>
       </c>
       <c r="C36"/>
@@ -10847,7 +10915,7 @@
       <c r="A37">
         <v>10300001</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="11" t="s">
         <v>366</v>
       </c>
       <c r="C37" t="s">
@@ -10861,7 +10929,7 @@
       <c r="A38">
         <v>10300002</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="11" t="s">
         <v>368</v>
       </c>
       <c r="C38" t="s">
@@ -10875,7 +10943,7 @@
       <c r="A39">
         <v>10300003</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="11" t="s">
         <v>370</v>
       </c>
       <c r="C39" t="s">
@@ -10889,7 +10957,7 @@
       <c r="A40">
         <v>10300004</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="11" t="s">
         <v>372</v>
       </c>
       <c r="C40" t="s">
@@ -10903,7 +10971,7 @@
       <c r="A41">
         <v>10300005</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="11" t="s">
         <v>374</v>
       </c>
       <c r="C41"/>
@@ -10915,7 +10983,7 @@
       <c r="A42">
         <v>10300006</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="11" t="s">
         <v>375</v>
       </c>
       <c r="C42"/>
@@ -10927,7 +10995,7 @@
       <c r="A43">
         <v>10300007</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="11" t="s">
         <v>376</v>
       </c>
       <c r="C43"/>
@@ -10939,7 +11007,7 @@
       <c r="A44">
         <v>10300008</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="11" t="s">
         <v>377</v>
       </c>
       <c r="C44"/>
@@ -10951,7 +11019,7 @@
       <c r="A45">
         <v>10300009</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="11" t="s">
         <v>378</v>
       </c>
       <c r="C45"/>
@@ -10963,7 +11031,7 @@
       <c r="A46">
         <v>10300010</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="11" t="s">
         <v>379</v>
       </c>
       <c r="C46"/>
@@ -10975,7 +11043,7 @@
       <c r="A47">
         <v>10300011</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="11" t="s">
         <v>380</v>
       </c>
       <c r="C47"/>
@@ -10987,7 +11055,7 @@
       <c r="A48">
         <v>10300012</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="11" t="s">
         <v>381</v>
       </c>
       <c r="C48"/>
@@ -10999,7 +11067,7 @@
       <c r="A49">
         <v>10300013</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="11" t="s">
         <v>382</v>
       </c>
       <c r="C49"/>
@@ -11011,7 +11079,7 @@
       <c r="A50">
         <v>10300014</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="11" t="s">
         <v>383</v>
       </c>
       <c r="C50"/>
@@ -11023,7 +11091,7 @@
       <c r="A51">
         <v>10300015</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="11" t="s">
         <v>384</v>
       </c>
       <c r="C51"/>
@@ -11035,7 +11103,7 @@
       <c r="A52">
         <v>10300016</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="11" t="s">
         <v>385</v>
       </c>
       <c r="C52"/>
@@ -11047,7 +11115,7 @@
       <c r="A53">
         <v>10300017</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="11" t="s">
         <v>386</v>
       </c>
       <c r="C53"/>
@@ -11056,7 +11124,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="14">
+      <c r="A54" s="11">
         <v>11000001</v>
       </c>
       <c r="B54" t="s">
@@ -11070,7 +11138,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="14">
+      <c r="A55" s="11">
         <v>11000002</v>
       </c>
       <c r="B55" t="s">
@@ -11084,7 +11152,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="14">
+      <c r="A56" s="11">
         <v>11000003</v>
       </c>
       <c r="B56" t="s">
@@ -11098,7 +11166,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="14">
+      <c r="A57" s="11">
         <v>11000004</v>
       </c>
       <c r="B57" t="s">
@@ -11112,7 +11180,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="14">
+      <c r="A58" s="11">
         <v>11000005</v>
       </c>
       <c r="B58" t="s">
@@ -11126,7 +11194,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="14">
+      <c r="A59" s="11">
         <v>11000006</v>
       </c>
       <c r="B59" t="s">
@@ -11140,7 +11208,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="14">
+      <c r="A60" s="11">
         <v>11000007</v>
       </c>
       <c r="B60" t="s">
@@ -11154,7 +11222,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="14">
+      <c r="A61" s="11">
         <v>11000008</v>
       </c>
       <c r="B61" t="s">
@@ -11168,7 +11236,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="14">
+      <c r="A62" s="11">
         <v>11000009</v>
       </c>
       <c r="B62" t="s">
@@ -11182,7 +11250,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="14">
+      <c r="A63" s="11">
         <v>11000010</v>
       </c>
       <c r="B63" t="s">
@@ -11194,10 +11262,10 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="14">
+      <c r="A64" s="11">
         <v>11000011</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="11" t="s">
         <v>405</v>
       </c>
       <c r="C64"/>
@@ -11206,10 +11274,10 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="14">
+      <c r="A65" s="11">
         <v>11000012</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="11" t="s">
         <v>406</v>
       </c>
       <c r="C65"/>
@@ -11218,10 +11286,10 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="14">
+      <c r="A66" s="11">
         <v>11000013</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="11" t="s">
         <v>407</v>
       </c>
       <c r="C66"/>
@@ -11230,7 +11298,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="14">
+      <c r="A67" s="11">
         <v>11010001</v>
       </c>
       <c r="B67" t="s">
@@ -11244,7 +11312,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="14">
+      <c r="A68" s="11">
         <v>11010002</v>
       </c>
       <c r="B68" t="s">
@@ -11256,7 +11324,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="14">
+      <c r="A69" s="11">
         <v>11010003</v>
       </c>
       <c r="B69" t="s">
@@ -11268,7 +11336,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="14">
+      <c r="A70" s="11">
         <v>11020021</v>
       </c>
       <c r="B70" t="s">
@@ -11280,7 +11348,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="14">
+      <c r="A71" s="11">
         <v>11020022</v>
       </c>
       <c r="B71" t="s">
@@ -11544,7 +11612,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="14">
+      <c r="A90" s="11">
         <v>20300001</v>
       </c>
       <c r="B90" t="s">
@@ -11558,7 +11626,7 @@
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="14">
+      <c r="A91" s="11">
         <v>20300003</v>
       </c>
       <c r="B91" t="s">
@@ -11572,7 +11640,7 @@
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="14">
+      <c r="A92" s="11">
         <v>20300007</v>
       </c>
       <c r="B92" t="s">
@@ -11586,7 +11654,7 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="14">
+      <c r="A93" s="11">
         <v>20300009</v>
       </c>
       <c r="B93" t="s">
@@ -11600,7 +11668,7 @@
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="14">
+      <c r="A94" s="11">
         <v>20300011</v>
       </c>
       <c r="B94" t="s">
@@ -13833,7 +13901,7 @@
       <c r="A23">
         <v>12001100001</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>723</v>
       </c>
       <c r="C23" t="s">
@@ -13847,7 +13915,7 @@
       <c r="A24">
         <v>12001200001</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>725</v>
       </c>
       <c r="C24" t="s">
@@ -13861,7 +13929,7 @@
       <c r="A25">
         <v>12001300001</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>727</v>
       </c>
       <c r="C25" t="s">
@@ -13875,7 +13943,7 @@
       <c r="A26">
         <v>12001400001</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>729</v>
       </c>
       <c r="C26" t="s">
@@ -13889,10 +13957,10 @@
       <c r="A27">
         <v>12002100001</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>732</v>
       </c>
       <c r="D27" t="s">
@@ -13903,10 +13971,10 @@
       <c r="A28">
         <v>12002200001</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>734</v>
       </c>
       <c r="D28" t="s">
@@ -13917,10 +13985,10 @@
       <c r="A29">
         <v>12002300001</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>736</v>
       </c>
       <c r="D29" t="s">
@@ -13931,10 +13999,10 @@
       <c r="A30">
         <v>12002400001</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>738</v>
       </c>
       <c r="D30" t="s">
@@ -13945,10 +14013,10 @@
       <c r="A31">
         <v>12003100001</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>740</v>
       </c>
       <c r="D31" t="s">
@@ -13959,10 +14027,10 @@
       <c r="A32">
         <v>12003200001</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>742</v>
       </c>
       <c r="D32" t="s">
@@ -13973,10 +14041,10 @@
       <c r="A33">
         <v>12003300001</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>744</v>
       </c>
       <c r="D33" t="s">
@@ -13987,10 +14055,10 @@
       <c r="A34">
         <v>12003400001</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>746</v>
       </c>
       <c r="D34" t="s">
@@ -14001,10 +14069,10 @@
       <c r="A35">
         <v>12010100001</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>747</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>748</v>
       </c>
       <c r="D35" t="s">
@@ -14015,10 +14083,10 @@
       <c r="A36">
         <v>12010200001</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>750</v>
       </c>
       <c r="D36" t="s">
@@ -14029,10 +14097,10 @@
       <c r="A37">
         <v>12010300001</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>752</v>
       </c>
       <c r="D37" t="s">
@@ -14043,10 +14111,10 @@
       <c r="A38">
         <v>12011100001</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>754</v>
       </c>
       <c r="D38" t="s">
@@ -14057,10 +14125,10 @@
       <c r="A39">
         <v>12011200001</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="13" t="s">
         <v>755</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>756</v>
       </c>
       <c r="D39" t="s">
@@ -14071,10 +14139,10 @@
       <c r="A40">
         <v>12011300001</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>758</v>
       </c>
       <c r="D40" t="s">
@@ -14180,7 +14248,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13">
+      <c r="A48" s="14">
         <v>10001000010000</v>
       </c>
       <c r="B48" t="s">
@@ -14194,7 +14262,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13">
+      <c r="A49" s="14">
         <v>10002000010000</v>
       </c>
       <c r="B49" t="s">
@@ -14208,7 +14276,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>10003000010000</v>
       </c>
       <c r="B50" t="s">
@@ -14222,7 +14290,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="13">
+      <c r="A51" s="14">
         <v>10004000010000</v>
       </c>
       <c r="B51" t="s">
@@ -14236,7 +14304,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="13">
+      <c r="A52" s="14">
         <v>10005000010000</v>
       </c>
       <c r="B52" t="s">
@@ -14250,7 +14318,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="13">
+      <c r="A53" s="14">
         <v>20001000010000</v>
       </c>
       <c r="B53" t="s">
@@ -14264,7 +14332,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>20002000010000</v>
       </c>
       <c r="B54" t="s">
@@ -14278,7 +14346,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>20003000010000</v>
       </c>
       <c r="B55" t="s">
@@ -14292,7 +14360,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="13">
+      <c r="A56" s="14">
         <v>20004000010000</v>
       </c>
       <c r="B56" t="s">
@@ -14306,7 +14374,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="13">
+      <c r="A57" s="14">
         <v>30001000010000</v>
       </c>
       <c r="B57" t="s">
@@ -14320,7 +14388,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="13">
+      <c r="A58" s="14">
         <v>30002000010000</v>
       </c>
       <c r="B58" t="s">
@@ -14334,7 +14402,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="13">
+      <c r="A59" s="14">
         <v>30003000010000</v>
       </c>
       <c r="B59" t="s">
@@ -14348,7 +14416,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="13">
+      <c r="A60" s="14">
         <v>30004000010000</v>
       </c>
       <c r="B60" t="s">
@@ -14362,7 +14430,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="13">
+      <c r="A61" s="14">
         <v>110001000010000</v>
       </c>
       <c r="B61" t="s">
@@ -14376,7 +14444,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="13">
+      <c r="A62" s="14">
         <v>110002000010000</v>
       </c>
       <c r="B62" t="s">
@@ -14390,7 +14458,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="13">
+      <c r="A63" s="14">
         <v>110003000010000</v>
       </c>
       <c r="B63" t="s">
@@ -14404,7 +14472,7 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="13">
+      <c r="A64" s="14">
         <v>120001000010000</v>
       </c>
       <c r="B64" t="s">
@@ -14418,7 +14486,7 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="13">
+      <c r="A65" s="14">
         <v>120002000010000</v>
       </c>
       <c r="B65" t="s">
@@ -14432,7 +14500,7 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="13">
+      <c r="A66" s="14">
         <v>120003000010000</v>
       </c>
       <c r="B66" t="s">
@@ -14446,7 +14514,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="13">
+      <c r="A67" s="14">
         <v>120011000010000</v>
       </c>
       <c r="B67" t="s">
@@ -14460,7 +14528,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="13">
+      <c r="A68" s="14">
         <v>120012000010000</v>
       </c>
       <c r="B68" t="s">
@@ -14474,7 +14542,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="13">
+      <c r="A69" s="14">
         <v>120013000010000</v>
       </c>
       <c r="B69" t="s">
@@ -14488,7 +14556,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="13">
+      <c r="A70" s="14">
         <v>120014000010000</v>
       </c>
       <c r="B70" t="s">
@@ -14502,7 +14570,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="13">
+      <c r="A71" s="14">
         <v>120021000010000</v>
       </c>
       <c r="B71" t="s">
@@ -14516,7 +14584,7 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="13">
+      <c r="A72" s="14">
         <v>120022000010000</v>
       </c>
       <c r="B72" t="s">
@@ -14530,7 +14598,7 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="13">
+      <c r="A73" s="14">
         <v>120023000010000</v>
       </c>
       <c r="B73" t="s">
@@ -14544,7 +14612,7 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="13">
+      <c r="A74" s="14">
         <v>120024000010000</v>
       </c>
       <c r="B74" t="s">
@@ -14558,7 +14626,7 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="13">
+      <c r="A75" s="14">
         <v>120031000010000</v>
       </c>
       <c r="B75" t="s">
@@ -14572,7 +14640,7 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="13">
+      <c r="A76" s="14">
         <v>120032000010000</v>
       </c>
       <c r="B76" t="s">
@@ -14586,7 +14654,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="13">
+      <c r="A77" s="14">
         <v>120033000010000</v>
       </c>
       <c r="B77" t="s">
@@ -14600,7 +14668,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="13">
+      <c r="A78" s="14">
         <v>120034000010000</v>
       </c>
       <c r="B78" t="s">
@@ -14614,7 +14682,7 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="13">
+      <c r="A79" s="14">
         <v>120101000010000</v>
       </c>
       <c r="B79" t="s">
@@ -14628,7 +14696,7 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="13">
+      <c r="A80" s="14">
         <v>120102000010000</v>
       </c>
       <c r="B80" t="s">
@@ -14642,7 +14710,7 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="13">
+      <c r="A81" s="14">
         <v>120103000010000</v>
       </c>
       <c r="B81" t="s">
@@ -14656,7 +14724,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="13">
+      <c r="A82" s="14">
         <v>120111000010000</v>
       </c>
       <c r="B82" t="s">
@@ -14670,7 +14738,7 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="13">
+      <c r="A83" s="14">
         <v>120112000010000</v>
       </c>
       <c r="B83" t="s">
@@ -14684,7 +14752,7 @@
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="13">
+      <c r="A84" s="14">
         <v>120113000010000</v>
       </c>
       <c r="B84" t="s">
@@ -14698,7 +14766,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="13">
+      <c r="A85" s="14">
         <v>130001000010000</v>
       </c>
       <c r="B85" t="s">
@@ -14712,7 +14780,7 @@
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="13">
+      <c r="A86" s="14">
         <v>130003000010000</v>
       </c>
       <c r="B86" t="s">
@@ -14726,7 +14794,7 @@
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="13">
+      <c r="A87" s="14">
         <v>130004000010000</v>
       </c>
       <c r="B87" t="s">
@@ -14740,7 +14808,7 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="13">
+      <c r="A88" s="14">
         <v>130005000010000</v>
       </c>
       <c r="B88" t="s">
@@ -14754,7 +14822,7 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="13">
+      <c r="A89" s="14">
         <v>130006000010000</v>
       </c>
       <c r="B89" t="s">
@@ -14768,7 +14836,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="13">
+      <c r="A90" s="14">
         <v>130007000010000</v>
       </c>
       <c r="B90" t="s">
@@ -15628,7 +15696,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -16226,42 +16294,38 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43">
-        <v>103001</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="11">
+        <v>102002</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="C43" t="s">
-        <v>964</v>
-      </c>
+      <c r="C43"/>
       <c r="D43" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44">
-        <v>103002</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="11">
+        <v>102003</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="C44" t="s">
-        <v>966</v>
-      </c>
+      <c r="C44"/>
       <c r="D44" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>900001</v>
+        <v>103001</v>
       </c>
       <c r="B45" t="s">
         <v>1023</v>
       </c>
       <c r="C45" t="s">
-        <v>1024</v>
+        <v>964</v>
       </c>
       <c r="D45" t="s">
         <v>946</v>
@@ -16269,15 +16333,43 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
+        <v>103002</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C46" t="s">
+        <v>966</v>
+      </c>
+      <c r="D46" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>900001</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D47" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
         <v>900002</v>
       </c>
-      <c r="B46" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="B48" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D48" t="s">
         <v>946</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="1364">
   <si>
     <t>id</t>
   </si>
@@ -3103,7 +3103,10 @@
     <t>Orc Mage (Ice)</t>
   </si>
   <si>
-    <t>人类-战士</t>
+    <t>人类-冒险者</t>
+  </si>
+  <si>
+    <t>人类-持盾战士</t>
   </si>
   <si>
     <t>人类-弓箭手</t>
@@ -3118,9 +3121,18 @@
     <t>人类-魔法师（火）</t>
   </si>
   <si>
+    <t>人类-魔法师（水）</t>
+  </si>
+  <si>
+    <t>Human Mage (Water)</t>
+  </si>
+  <si>
     <t>人类-魔法师（冰）</t>
   </si>
   <si>
+    <t>人类-魔法师（雷）</t>
+  </si>
+  <si>
     <t>测试骷髅战士</t>
   </si>
   <si>
@@ -3184,10 +3196,16 @@
     <t>Mage (Fire)</t>
   </si>
   <si>
+    <t>魔法师（水）</t>
+  </si>
+  <si>
+    <t>Mage (Water)</t>
+  </si>
+  <si>
     <t>魔法师（冰）</t>
   </si>
   <si>
-    <t>Mage (Ice)</t>
+    <t>魔法师（雷）</t>
   </si>
   <si>
     <t>白剑伟</t>
@@ -4131,7 +4149,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4187,6 +4205,20 @@
       <color rgb="FF6A9955"/>
       <name val="Consolas"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -4659,137 +4691,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4825,6 +4857,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7332,7 +7373,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
@@ -7388,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C4" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7399,10 +7440,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7410,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7421,11 +7462,11 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="9" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7433,11 +7474,11 @@
         <v>1010020001</v>
       </c>
       <c r="B8" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C8"/>
       <c r="D8" s="9" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7445,13 +7486,13 @@
         <v>1020010001</v>
       </c>
       <c r="B9" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C9" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7459,11 +7500,11 @@
         <v>1020020001</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C10"/>
       <c r="D10" s="11" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7471,11 +7512,11 @@
         <v>1020030001</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C11"/>
       <c r="D11" s="11" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7483,13 +7524,13 @@
         <v>1030010001</v>
       </c>
       <c r="B12" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>1044</v>
+        <v>1049</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7497,35 +7538,59 @@
         <v>1030020001</v>
       </c>
       <c r="B13" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C13" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="14" ht="12" customHeight="1" spans="1:4">
+        <v>1051</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
-        <v>2000000001</v>
+        <v>1030030001</v>
       </c>
       <c r="B14" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1049</v>
+        <v>1052</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
+        <v>1030040001</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1" spans="1:4">
+      <c r="A16">
+        <v>2000000001</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>2000000002</v>
       </c>
-      <c r="B15" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1051</v>
+      <c r="B17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
@@ -7748,10 +7813,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="C4" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="D4" t="s">
         <v>946</v>
@@ -7762,10 +7827,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="C5" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D5" t="s">
         <v>946</v>
@@ -7776,10 +7841,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D6" t="s">
         <v>946</v>
@@ -7790,10 +7855,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="C7" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D7" t="s">
         <v>946</v>
@@ -7804,7 +7869,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D8" t="s">
         <v>946</v>
@@ -7815,7 +7880,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D9" t="s">
         <v>946</v>
@@ -7826,7 +7891,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D10" t="s">
         <v>946</v>
@@ -7848,7 +7913,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="D12" t="s">
         <v>946</v>
@@ -7859,10 +7924,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="D13" t="s">
         <v>946</v>
@@ -7873,10 +7938,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="D14" t="s">
         <v>946</v>
@@ -7945,10 +8010,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="C4" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -7956,10 +8021,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="C5" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -7967,10 +8032,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="C6" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -7978,10 +8043,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="C7" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -7989,10 +8054,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="C8" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8000,10 +8065,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="C9" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -8011,10 +8076,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="C10" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -8022,10 +8087,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C11" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -8033,10 +8098,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="C12" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -8044,10 +8109,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C13" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -8055,10 +8120,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C14" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -8066,10 +8131,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="C15" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -8077,10 +8142,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="C16" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8088,10 +8153,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="C17" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -8099,10 +8164,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C18" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8110,10 +8175,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="C19" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8121,10 +8186,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8132,10 +8197,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="C21" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8143,10 +8208,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="C22" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8154,10 +8219,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="C23" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8165,10 +8230,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="C24" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8176,10 +8241,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="C25" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8187,10 +8252,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="C26" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8198,10 +8263,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="C27" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8209,10 +8274,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="C28" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8220,10 +8285,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="C29" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8231,10 +8296,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="C30" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8242,10 +8307,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="C31" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8253,10 +8318,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="C32" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8264,10 +8329,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="C33" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8275,10 +8340,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="C34" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
@@ -8345,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8356,10 +8421,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="C5" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8367,10 +8432,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="C6" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8378,10 +8443,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C7" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8389,10 +8454,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="C8" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8400,10 +8465,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="C9" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8411,10 +8476,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="C10" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8422,10 +8487,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="C11" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8433,10 +8498,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C12" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8444,10 +8509,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="C13" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8455,10 +8520,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="C14" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8466,10 +8531,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C15" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8477,10 +8542,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="C16" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
     </row>
   </sheetData>
@@ -8545,10 +8610,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8556,10 +8621,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="C5" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8567,10 +8632,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="C6" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8578,10 +8643,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="C7" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8589,10 +8654,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="C8" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>
@@ -8658,10 +8723,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="C4" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8669,10 +8734,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8680,10 +8745,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8691,10 +8756,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8702,10 +8767,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8713,10 +8778,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8724,10 +8789,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8735,10 +8800,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8746,10 +8811,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8757,10 +8822,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -8826,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8837,7 +8902,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8848,10 +8913,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8859,10 +8924,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8870,10 +8935,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8881,10 +8946,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="C9" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -8952,13 +9017,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="C4" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="D4" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8966,13 +9031,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="D5" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8980,13 +9045,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="C6" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="D6" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8994,13 +9059,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="C7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D7" t="s">
         <v>1203</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -9008,13 +9073,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C8" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="D8" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -9022,13 +9087,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="C9" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D9" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -9036,13 +9101,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="C10" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="D10" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -9050,13 +9115,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="C11" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D11" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9064,13 +9129,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="C12" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D12" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -9078,13 +9143,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="C13" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D13" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -9092,13 +9157,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="C14" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="D14" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -9106,13 +9171,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="C15" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="D15" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -9120,13 +9185,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="C16" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D16" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -9134,13 +9199,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="C17" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D17" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9148,13 +9213,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="C18" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="D18" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -9162,13 +9227,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="C19" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="D19" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9176,13 +9241,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="C20" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="D20" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -9190,13 +9255,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="C21" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D21" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9204,13 +9269,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="C22" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D22" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9218,13 +9283,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="C23" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D23" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9232,13 +9297,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="C24" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="D24" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9246,13 +9311,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C25" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D25" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9260,13 +9325,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="C26" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D26" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9274,13 +9339,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="C27" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D27" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9288,13 +9353,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="C28" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="D28" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9302,13 +9367,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="C29" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="D29" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9316,13 +9381,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="C30" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D30" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9330,13 +9395,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="C31" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="D31" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9344,13 +9409,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="C32" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="D32" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9358,13 +9423,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="C33" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="D33" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9372,13 +9437,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="C34" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="D34" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9386,13 +9451,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="C35" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="D35" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9400,13 +9465,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="C36" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D36" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9414,13 +9479,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="C37" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="D37" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9428,13 +9493,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="C38" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="D38" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9442,13 +9507,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="C39" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D39" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9456,13 +9521,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="C40" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="D40" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9470,13 +9535,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="C41" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="D41" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9484,13 +9549,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="C42" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D42" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9498,13 +9563,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="C43" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D43" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9512,13 +9577,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="C44" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="D44" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9526,13 +9591,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="C45" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="D45" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9540,13 +9605,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="C46" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="D46" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9554,13 +9619,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="C47" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D47" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9568,13 +9633,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="C48" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="D48" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9582,13 +9647,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="C49" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="D49" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9596,13 +9661,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="C50" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="D50" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9610,13 +9675,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="C51" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="D51" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9624,13 +9689,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="C52" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="D52" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9638,13 +9703,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="C53" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="D53" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9652,13 +9717,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="C54" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="D54" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9666,13 +9731,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="C55" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="D55" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9680,13 +9745,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="C56" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="D56" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9694,13 +9759,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="C57" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="D57" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9708,13 +9773,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="C58" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="D58" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9722,13 +9787,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="C59" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="D59" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9736,13 +9801,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="C60" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D60" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9750,13 +9815,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="C61" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="D61" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9764,13 +9829,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="C62" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="D62" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9778,13 +9843,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="C63" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D63" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9792,13 +9857,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="C64" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="D64" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9806,13 +9871,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="C65" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="D65" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9820,13 +9885,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="C66" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="D66" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9834,13 +9899,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="C67" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="D67" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9848,13 +9913,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="C68" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="D68" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9862,13 +9927,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="C69" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="D69" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9876,13 +9941,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="C70" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="D70" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9890,13 +9955,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="C71" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="D71" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9904,13 +9969,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C72" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="D72" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9918,13 +9983,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="C73" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="D73" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9932,13 +9997,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C74" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="D74" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -9946,13 +10011,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="C75" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="D75" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -9960,13 +10025,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="C76" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="D76" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -9974,13 +10039,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="C77" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="D77" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -9988,13 +10053,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="C78" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="D78" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -10002,13 +10067,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="C79" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="D79" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -10016,13 +10081,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="C80" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="D80" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -10030,13 +10095,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="C81" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="D81" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -10044,13 +10109,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="C82" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="D82" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -10058,13 +10123,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="C83" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="D83" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -10072,13 +10137,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="C84" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="D84" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -10086,13 +10151,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="C85" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="D85" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
@@ -13901,7 +13966,7 @@
       <c r="A23">
         <v>12001100001</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="15" t="s">
         <v>723</v>
       </c>
       <c r="C23" t="s">
@@ -13915,7 +13980,7 @@
       <c r="A24">
         <v>12001200001</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="15" t="s">
         <v>725</v>
       </c>
       <c r="C24" t="s">
@@ -13929,7 +13994,7 @@
       <c r="A25">
         <v>12001300001</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="15" t="s">
         <v>727</v>
       </c>
       <c r="C25" t="s">
@@ -13943,7 +14008,7 @@
       <c r="A26">
         <v>12001400001</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="15" t="s">
         <v>729</v>
       </c>
       <c r="C26" t="s">
@@ -13957,10 +14022,10 @@
       <c r="A27">
         <v>12002100001</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="16" t="s">
         <v>732</v>
       </c>
       <c r="D27" t="s">
@@ -13971,10 +14036,10 @@
       <c r="A28">
         <v>12002200001</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="16" t="s">
         <v>734</v>
       </c>
       <c r="D28" t="s">
@@ -13985,10 +14050,10 @@
       <c r="A29">
         <v>12002300001</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="16" t="s">
         <v>736</v>
       </c>
       <c r="D29" t="s">
@@ -13999,10 +14064,10 @@
       <c r="A30">
         <v>12002400001</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="16" t="s">
         <v>738</v>
       </c>
       <c r="D30" t="s">
@@ -14013,10 +14078,10 @@
       <c r="A31">
         <v>12003100001</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="16" t="s">
         <v>740</v>
       </c>
       <c r="D31" t="s">
@@ -14027,10 +14092,10 @@
       <c r="A32">
         <v>12003200001</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="15" t="s">
         <v>741</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="16" t="s">
         <v>742</v>
       </c>
       <c r="D32" t="s">
@@ -14041,10 +14106,10 @@
       <c r="A33">
         <v>12003300001</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="15" t="s">
         <v>743</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="16" t="s">
         <v>744</v>
       </c>
       <c r="D33" t="s">
@@ -14055,10 +14120,10 @@
       <c r="A34">
         <v>12003400001</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="15" t="s">
         <v>745</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="16" t="s">
         <v>746</v>
       </c>
       <c r="D34" t="s">
@@ -14069,10 +14134,10 @@
       <c r="A35">
         <v>12010100001</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="16" t="s">
         <v>747</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="16" t="s">
         <v>748</v>
       </c>
       <c r="D35" t="s">
@@ -14083,10 +14148,10 @@
       <c r="A36">
         <v>12010200001</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="16" t="s">
         <v>749</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="16" t="s">
         <v>750</v>
       </c>
       <c r="D36" t="s">
@@ -14097,10 +14162,10 @@
       <c r="A37">
         <v>12010300001</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="16" t="s">
         <v>751</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="16" t="s">
         <v>752</v>
       </c>
       <c r="D37" t="s">
@@ -14111,10 +14176,10 @@
       <c r="A38">
         <v>12011100001</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="16" t="s">
         <v>753</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="16" t="s">
         <v>754</v>
       </c>
       <c r="D38" t="s">
@@ -14125,10 +14190,10 @@
       <c r="A39">
         <v>12011200001</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="16" t="s">
         <v>755</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="16" t="s">
         <v>756</v>
       </c>
       <c r="D39" t="s">
@@ -14139,10 +14204,10 @@
       <c r="A40">
         <v>12011300001</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="16" t="s">
         <v>757</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="16" t="s">
         <v>758</v>
       </c>
       <c r="D40" t="s">
@@ -14248,7 +14313,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="14">
+      <c r="A48" s="17">
         <v>10001000010000</v>
       </c>
       <c r="B48" t="s">
@@ -14262,7 +14327,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="14">
+      <c r="A49" s="17">
         <v>10002000010000</v>
       </c>
       <c r="B49" t="s">
@@ -14276,7 +14341,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="14">
+      <c r="A50" s="17">
         <v>10003000010000</v>
       </c>
       <c r="B50" t="s">
@@ -14290,7 +14355,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="14">
+      <c r="A51" s="17">
         <v>10004000010000</v>
       </c>
       <c r="B51" t="s">
@@ -14304,7 +14369,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="14">
+      <c r="A52" s="17">
         <v>10005000010000</v>
       </c>
       <c r="B52" t="s">
@@ -14318,7 +14383,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="14">
+      <c r="A53" s="17">
         <v>20001000010000</v>
       </c>
       <c r="B53" t="s">
@@ -14332,7 +14397,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="14">
+      <c r="A54" s="17">
         <v>20002000010000</v>
       </c>
       <c r="B54" t="s">
@@ -14346,7 +14411,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="14">
+      <c r="A55" s="17">
         <v>20003000010000</v>
       </c>
       <c r="B55" t="s">
@@ -14360,7 +14425,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="14">
+      <c r="A56" s="17">
         <v>20004000010000</v>
       </c>
       <c r="B56" t="s">
@@ -14374,7 +14439,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="14">
+      <c r="A57" s="17">
         <v>30001000010000</v>
       </c>
       <c r="B57" t="s">
@@ -14388,7 +14453,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="14">
+      <c r="A58" s="17">
         <v>30002000010000</v>
       </c>
       <c r="B58" t="s">
@@ -14402,7 +14467,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="14">
+      <c r="A59" s="17">
         <v>30003000010000</v>
       </c>
       <c r="B59" t="s">
@@ -14416,7 +14481,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="14">
+      <c r="A60" s="17">
         <v>30004000010000</v>
       </c>
       <c r="B60" t="s">
@@ -14430,7 +14495,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="14">
+      <c r="A61" s="17">
         <v>110001000010000</v>
       </c>
       <c r="B61" t="s">
@@ -14444,7 +14509,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="14">
+      <c r="A62" s="17">
         <v>110002000010000</v>
       </c>
       <c r="B62" t="s">
@@ -14458,7 +14523,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="14">
+      <c r="A63" s="17">
         <v>110003000010000</v>
       </c>
       <c r="B63" t="s">
@@ -14472,7 +14537,7 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="14">
+      <c r="A64" s="17">
         <v>120001000010000</v>
       </c>
       <c r="B64" t="s">
@@ -14486,7 +14551,7 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="14">
+      <c r="A65" s="17">
         <v>120002000010000</v>
       </c>
       <c r="B65" t="s">
@@ -14500,7 +14565,7 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="14">
+      <c r="A66" s="17">
         <v>120003000010000</v>
       </c>
       <c r="B66" t="s">
@@ -14514,7 +14579,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="14">
+      <c r="A67" s="17">
         <v>120011000010000</v>
       </c>
       <c r="B67" t="s">
@@ -14528,7 +14593,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="14">
+      <c r="A68" s="17">
         <v>120012000010000</v>
       </c>
       <c r="B68" t="s">
@@ -14542,7 +14607,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="14">
+      <c r="A69" s="17">
         <v>120013000010000</v>
       </c>
       <c r="B69" t="s">
@@ -14556,7 +14621,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="14">
+      <c r="A70" s="17">
         <v>120014000010000</v>
       </c>
       <c r="B70" t="s">
@@ -14570,7 +14635,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="14">
+      <c r="A71" s="17">
         <v>120021000010000</v>
       </c>
       <c r="B71" t="s">
@@ -14584,7 +14649,7 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="14">
+      <c r="A72" s="17">
         <v>120022000010000</v>
       </c>
       <c r="B72" t="s">
@@ -14598,7 +14663,7 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="14">
+      <c r="A73" s="17">
         <v>120023000010000</v>
       </c>
       <c r="B73" t="s">
@@ -14612,7 +14677,7 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="14">
+      <c r="A74" s="17">
         <v>120024000010000</v>
       </c>
       <c r="B74" t="s">
@@ -14626,7 +14691,7 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="14">
+      <c r="A75" s="17">
         <v>120031000010000</v>
       </c>
       <c r="B75" t="s">
@@ -14640,7 +14705,7 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="14">
+      <c r="A76" s="17">
         <v>120032000010000</v>
       </c>
       <c r="B76" t="s">
@@ -14654,7 +14719,7 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="14">
+      <c r="A77" s="17">
         <v>120033000010000</v>
       </c>
       <c r="B77" t="s">
@@ -14668,7 +14733,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="14">
+      <c r="A78" s="17">
         <v>120034000010000</v>
       </c>
       <c r="B78" t="s">
@@ -14682,7 +14747,7 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="14">
+      <c r="A79" s="17">
         <v>120101000010000</v>
       </c>
       <c r="B79" t="s">
@@ -14696,7 +14761,7 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="14">
+      <c r="A80" s="17">
         <v>120102000010000</v>
       </c>
       <c r="B80" t="s">
@@ -14710,7 +14775,7 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="14">
+      <c r="A81" s="17">
         <v>120103000010000</v>
       </c>
       <c r="B81" t="s">
@@ -14724,7 +14789,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="14">
+      <c r="A82" s="17">
         <v>120111000010000</v>
       </c>
       <c r="B82" t="s">
@@ -14738,7 +14803,7 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="14">
+      <c r="A83" s="17">
         <v>120112000010000</v>
       </c>
       <c r="B83" t="s">
@@ -14752,7 +14817,7 @@
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="14">
+      <c r="A84" s="17">
         <v>120113000010000</v>
       </c>
       <c r="B84" t="s">
@@ -14766,7 +14831,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="14">
+      <c r="A85" s="17">
         <v>130001000010000</v>
       </c>
       <c r="B85" t="s">
@@ -14780,7 +14845,7 @@
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="14">
+      <c r="A86" s="17">
         <v>130003000010000</v>
       </c>
       <c r="B86" t="s">
@@ -14794,7 +14859,7 @@
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="14">
+      <c r="A87" s="17">
         <v>130004000010000</v>
       </c>
       <c r="B87" t="s">
@@ -14808,7 +14873,7 @@
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="14">
+      <c r="A88" s="17">
         <v>130005000010000</v>
       </c>
       <c r="B88" t="s">
@@ -14822,7 +14887,7 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="14">
+      <c r="A89" s="17">
         <v>130006000010000</v>
       </c>
       <c r="B89" t="s">
@@ -14836,7 +14901,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="14">
+      <c r="A90" s="17">
         <v>130007000010000</v>
       </c>
       <c r="B90" t="s">
@@ -15696,7 +15761,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -15846,530 +15911,566 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11">
+      <c r="A11" s="12">
         <v>1001</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
+      <c r="A12" s="12">
         <v>1002</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="12" t="s">
         <v>961</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13">
+      <c r="A13" s="12">
         <v>1003</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="12" t="s">
         <v>963</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="12" t="s">
         <v>964</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14">
+      <c r="A14" s="12">
         <v>1004</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="12" t="s">
         <v>965</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
+      <c r="A15" s="12">
         <v>2001</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="12" t="s">
         <v>967</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16">
+      <c r="A16" s="12">
         <v>2002</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="12" t="s">
         <v>969</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="12" t="s">
         <v>970</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17">
+      <c r="A17" s="12">
         <v>2003</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="12" t="s">
         <v>971</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="12" t="s">
         <v>972</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18">
+      <c r="A18" s="12">
         <v>2004</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="12" t="s">
         <v>973</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="12" t="s">
         <v>974</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19">
+      <c r="A19" s="12">
         <v>3001</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20">
+      <c r="A20" s="12">
         <v>3002</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="12" t="s">
         <v>978</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21">
+      <c r="A21" s="12">
         <v>3003</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="12" t="s">
         <v>979</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="12" t="s">
         <v>980</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22">
+      <c r="A22" s="12">
         <v>3004</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="12" t="s">
         <v>982</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23">
+      <c r="A23" s="12">
         <v>4001</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="12" t="s">
         <v>983</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="12" t="s">
         <v>984</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24">
+      <c r="A24" s="12">
         <v>4002</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="12" t="s">
         <v>985</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25">
+      <c r="A25" s="12">
         <v>4003</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="12" t="s">
         <v>988</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26">
+      <c r="A26" s="12">
         <v>4004</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27">
+      <c r="A27" s="12">
         <v>4005</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28">
+      <c r="A28" s="12">
         <v>5001</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="12" t="s">
         <v>994</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29">
+      <c r="A29" s="12">
         <v>5002</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="12" t="s">
         <v>995</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30">
+      <c r="A30" s="12">
         <v>5003</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="12" t="s">
         <v>997</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="12" t="s">
         <v>998</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31">
+      <c r="A31" s="12">
         <v>5004</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="12" t="s">
         <v>1000</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32">
+      <c r="A32" s="12">
         <v>6001</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="12" t="s">
         <v>1001</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33">
+      <c r="A33" s="12">
         <v>6002</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="12" t="s">
         <v>1003</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="12" t="s">
         <v>1004</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34">
+      <c r="A34" s="12">
         <v>6003</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="12" t="s">
         <v>1006</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35">
+      <c r="A35" s="12">
         <v>6004</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="12" t="s">
         <v>1007</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="12" t="s">
         <v>1008</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36">
+      <c r="A36" s="12">
         <v>6005</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="12" t="s">
         <v>1010</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37">
+      <c r="A37" s="12">
         <v>7001</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="12" t="s">
         <v>1012</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38">
+      <c r="A38" s="12">
         <v>7002</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39">
+      <c r="A39" s="12">
         <v>7003</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="12" t="s">
         <v>1015</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40">
+      <c r="A40" s="12">
         <v>7004</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="12" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41">
+      <c r="A41" s="13">
         <v>101001</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="13" t="s">
         <v>960</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="13" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42">
+      <c r="A42" s="14">
+        <v>101002</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="13">
         <v>102001</v>
       </c>
-      <c r="B42" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>962</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" s="13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="11">
+    <row r="44" spans="1:4">
+      <c r="A44" s="14">
         <v>102002</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C43"/>
-      <c r="D43" t="s">
+      <c r="B44" s="14" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="11">
+    <row r="45" spans="1:4">
+      <c r="A45" s="14">
         <v>102003</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C44"/>
-      <c r="D44" t="s">
+      <c r="B45" s="14" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45">
+    <row r="46" spans="1:4">
+      <c r="A46" s="13">
         <v>103001</v>
       </c>
-      <c r="B45" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" s="13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46">
+    <row r="47" spans="1:4">
+      <c r="A47" s="13">
         <v>103002</v>
       </c>
-      <c r="B46" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C46" t="s">
-        <v>966</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="B47" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47">
+    <row r="48" spans="1:4">
+      <c r="A48" s="13">
+        <v>103003</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="13">
+        <v>103004</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
         <v>900001</v>
       </c>
-      <c r="B47" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="B50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D50" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48">
+    <row r="51" spans="1:4">
+      <c r="A51">
         <v>900002</v>
       </c>
-      <c r="B48" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="B51" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D51" t="s">
         <v>946</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="723" activeTab="9"/>
+    <workbookView windowWidth="25860" windowHeight="8820" tabRatio="723" firstSheet="11" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="1362">
   <si>
     <t>id</t>
   </si>
@@ -2122,12 +2122,27 @@
     <t>木制法杖</t>
   </si>
   <si>
+    <t>content_1_cn</t>
+  </si>
+  <si>
+    <t>content_1_en</t>
+  </si>
+  <si>
+    <t>内容-1-中文</t>
+  </si>
+  <si>
+    <t>内容-1-英文</t>
+  </si>
+  <si>
     <t>减速-冰</t>
   </si>
   <si>
     <t>Slow - Ice</t>
   </si>
   <si>
+    <t>减速</t>
+  </si>
+  <si>
     <t>excel_buff_info</t>
   </si>
   <si>
@@ -2140,31 +2155,34 @@
     <t>流血</t>
   </si>
   <si>
-    <t>Bleed</t>
+    <t>持续造成伤害</t>
+  </si>
+  <si>
+    <t>Damage Over Time</t>
   </si>
   <si>
     <t>中毒</t>
   </si>
   <si>
-    <t>Poison</t>
-  </si>
-  <si>
     <t>烧伤</t>
   </si>
   <si>
-    <t>Burn</t>
-  </si>
-  <si>
     <t>闪避</t>
   </si>
   <si>
-    <t>Dodge</t>
+    <t>有50%概率闪避敌人攻击</t>
+  </si>
+  <si>
+    <t>50% chance to dodge attacks</t>
   </si>
   <si>
     <t>暴击</t>
   </si>
   <si>
-    <t>Crit</t>
+    <t>有50%概率攻击产生暴击</t>
+  </si>
+  <si>
+    <t>50% chance for critical hit</t>
   </si>
   <si>
     <t>狂暴-力</t>
@@ -2173,433 +2191,409 @@
     <t>Fury-Str</t>
   </si>
   <si>
+    <t>血量低于50% 攻击力提升</t>
+  </si>
+  <si>
+    <t>ATK boost when HP &lt; 50%</t>
+  </si>
+  <si>
     <t>狂暴-速</t>
   </si>
   <si>
     <t>Fury-Spd</t>
   </si>
   <si>
+    <t>血量低于50% 攻击速度提升</t>
+  </si>
+  <si>
+    <t>ASPD boost when HP &lt; 50%</t>
+  </si>
+  <si>
     <t>强身健体</t>
   </si>
   <si>
     <t>Gym Rat</t>
   </si>
   <si>
+    <t>所有魔物放置CD减少10%</t>
+  </si>
+  <si>
+    <t>All demon placement CD reduced 10%</t>
+  </si>
+  <si>
     <t>HP+</t>
   </si>
   <si>
+    <t>生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Increase HP by {Percentage}%</t>
+  </si>
+  <si>
     <t>DR+</t>
   </si>
   <si>
     <t>DEF+</t>
   </si>
   <si>
+    <t>护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Increase DEF by {Percentage}%</t>
+  </si>
+  <si>
     <t>ATK+</t>
   </si>
   <si>
+    <t>攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Increase ATK by {Percentage}%</t>
+  </si>
+  <si>
     <t>医者自医</t>
   </si>
   <si>
     <t>Self-Heal</t>
   </si>
   <si>
+    <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+  </si>
+  <si>
+    <t>Restore {Percentage}% HP every {Time_S}s</t>
+  </si>
+  <si>
     <t>护甲保养</t>
   </si>
   <si>
     <t>Armor Polish</t>
   </si>
   <si>
+    <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+  </si>
+  <si>
+    <t>Restore {Percentage}% DEF every {Time_S}s</t>
+  </si>
+  <si>
     <t>再补一刀</t>
   </si>
   <si>
     <t>Double Tap</t>
   </si>
   <si>
+    <t>每隔{Time_S}秒再攻击一次</t>
+  </si>
+  <si>
+    <t>Extra attack every {Time_S}s</t>
+  </si>
+  <si>
     <t>尸堆养料-HP</t>
   </si>
   <si>
     <t>Feast-HP</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% HP per {KillNum} kills</t>
+  </si>
+  <si>
     <t>尸堆养料-DR</t>
   </si>
   <si>
     <t>Feast-DEF</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% DEF per {KillNum} kills</t>
+  </si>
+  <si>
     <t>尸堆养料-ATK</t>
   </si>
   <si>
     <t>Feast-ATK</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ATK per {KillNum} kills</t>
+  </si>
+  <si>
     <t>尸堆养料-ASPD</t>
   </si>
   <si>
     <t>Feast-ASPD</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
+  </si>
+  <si>
     <t>痛楚馈赠-HP</t>
   </si>
   <si>
     <t>Gift of Agony(HP)</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>痛楚馈赠-DR</t>
   </si>
   <si>
     <t>Gift of Agony(DR)</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>痛楚馈赠-ATK</t>
   </si>
   <si>
     <t>Gift of Agony(ATK)</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>痛楚馈赠-ASPD</t>
   </si>
   <si>
     <t>Gift of Agony(ASPD)</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>濒死狂宴-HP</t>
   </si>
   <si>
     <t>Feast of the Dying(HP)</t>
   </si>
   <si>
+    <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
+  </si>
+  <si>
     <t>濒死狂宴-DR</t>
   </si>
   <si>
     <t>Feast of the Dying(DR)</t>
   </si>
   <si>
+    <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
+  </si>
+  <si>
     <t>濒死狂宴-ATK</t>
   </si>
   <si>
     <t>Feast of the Dying(ATK)</t>
   </si>
   <si>
+    <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
+  </si>
+  <si>
     <t>濒死狂宴-ASPD</t>
   </si>
   <si>
     <t>Feast of the Dying(ASPD)</t>
   </si>
   <si>
+    <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
+  </si>
+  <si>
     <t> 收尸费</t>
   </si>
   <si>
     <t>Corpse Tax</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>Drop crystal per {KillNum} kills</t>
+  </si>
+  <si>
     <t>痛觉提款机</t>
   </si>
   <si>
     <t>Pain ATM</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>暴力小费</t>
   </si>
   <si>
     <t>Violence Tip</t>
   </si>
   <si>
+    <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>Drop crystal per {AttackDamage} dmg dealt</t>
+  </si>
+  <si>
     <t>鞭尸成瘾</t>
   </si>
   <si>
     <t>Corpse Kicker</t>
   </si>
   <si>
+    <t>击杀{KillNum}次生物，立即攻击一次</t>
+  </si>
+  <si>
+    <t>Instant attack per {KillNum} kills</t>
+  </si>
+  <si>
     <t>碰瓷反杀</t>
   </si>
   <si>
     <t>Blood Bait</t>
   </si>
   <si>
+    <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+  </si>
+  <si>
+    <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+  </si>
+  <si>
     <t>越打越嗨</t>
   </si>
   <si>
     <t>Rage Spiral </t>
   </si>
   <si>
+    <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+  </si>
+  <si>
+    <t>Extra attack per {AttackDamage} dmg dealt</t>
+  </si>
+  <si>
     <t>拾晶不昧</t>
   </si>
   <si>
     <t>Honest Finder</t>
   </si>
   <si>
+    <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+  </si>
+  <si>
+    <t>Auto-collect crystals every {Time_S}s</t>
+  </si>
+  <si>
     <t>有利可图</t>
   </si>
   <si>
     <t>Opportunist</t>
   </si>
   <si>
+    <t>死亡后重生</t>
+  </si>
+  <si>
+    <t>Resurrect on Death</t>
+  </si>
+  <si>
     <t>死而复生</t>
   </si>
   <si>
     <t>Second Wind</t>
   </si>
   <si>
+    <t>死亡后爆炸</t>
+  </si>
+  <si>
+    <t>Explode on Death</t>
+  </si>
+  <si>
     <t>同归于尽</t>
   </si>
   <si>
     <t>Mutual Destruction</t>
   </si>
   <si>
+    <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+  </si>
+  <si>
+    <t>Heal allies {Percentage}% of max HP on death</t>
+  </si>
+  <si>
     <t>死得其所-HP</t>
   </si>
   <si>
     <t>Noble Death-HP</t>
   </si>
   <si>
+    <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+  </si>
+  <si>
+    <t>Shield allies {Percentage}% of max DEF on death</t>
+  </si>
+  <si>
     <t>死得其所-DR</t>
   </si>
   <si>
     <t>Noble Death-DEF</t>
   </si>
   <si>
+    <t>死亡后{Percentage}%生成魔晶</t>
+  </si>
+  <si>
+    <t>Spawn {Percentage}% chance crystal on death</t>
+  </si>
+  <si>
     <t>死亡税</t>
   </si>
   <si>
     <t>Death Tax</t>
   </si>
   <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>Slow</t>
-  </si>
-  <si>
-    <t>持续造成伤害</t>
-  </si>
-  <si>
-    <t>Damage Over Time</t>
-  </si>
-  <si>
-    <t>有50%概率闪避敌人攻击</t>
-  </si>
-  <si>
-    <t>50% chance to dodge attacks</t>
-  </si>
-  <si>
-    <t>有50%概率攻击产生暴击</t>
-  </si>
-  <si>
-    <t>50% chance for critical hit</t>
-  </si>
-  <si>
-    <t>血量低于50% 攻击力提升</t>
-  </si>
-  <si>
-    <t>ATK boost when HP &lt; 50%</t>
-  </si>
-  <si>
-    <t>血量低于50% 攻击速度提升</t>
-  </si>
-  <si>
-    <t>ASPD boost when HP &lt; 50%</t>
-  </si>
-  <si>
-    <t>所有魔物放置CD减少10%</t>
-  </si>
-  <si>
-    <t>All demon placement CD reduced 10%</t>
-  </si>
-  <si>
-    <t>生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Increase HP by {Percentage}%</t>
-  </si>
-  <si>
-    <t>护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Increase DEF by {Percentage}%</t>
-  </si>
-  <si>
-    <t>攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Increase ATK by {Percentage}%</t>
-  </si>
-  <si>
-    <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
-  </si>
-  <si>
-    <t>Restore {Percentage}% HP every {Time_S}s</t>
-  </si>
-  <si>
-    <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
-  </si>
-  <si>
-    <t>Restore {Percentage}% DEF every {Time_S}s</t>
-  </si>
-  <si>
-    <t>每隔{Time_S}秒再攻击一次</t>
-  </si>
-  <si>
-    <t>Extra attack every {Time_S}s</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% HP per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% DEF per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ATK per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
-  </si>
-  <si>
-    <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
-  </si>
-  <si>
-    <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
-  </si>
-  <si>
-    <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，掉落一次魔晶</t>
-  </si>
-  <si>
-    <t>Drop crystal per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
-  </si>
-  <si>
-    <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
-  </si>
-  <si>
-    <t>Drop crystal per {AttackDamage} dmg dealt</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}次生物，立即攻击一次</t>
-  </si>
-  <si>
-    <t>Instant attack per {KillNum} kills</t>
-  </si>
-  <si>
-    <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
-  </si>
-  <si>
-    <t>Extra attack per {UnderAttackDamage} dmg taken</t>
-  </si>
-  <si>
-    <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
-  </si>
-  <si>
-    <t>Extra attack per {AttackDamage} dmg dealt</t>
-  </si>
-  <si>
-    <t>每隔{Time_S}秒自动拾取附近魔晶</t>
-  </si>
-  <si>
-    <t>Auto-collect crystals every {Time_S}s</t>
-  </si>
-  <si>
-    <t>死亡后重生</t>
-  </si>
-  <si>
-    <t>Resurrect on Death</t>
-  </si>
-  <si>
-    <t>死亡后爆炸</t>
-  </si>
-  <si>
-    <t>Explode on Death</t>
-  </si>
-  <si>
-    <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
-  </si>
-  <si>
-    <t>Heal allies {Percentage}% of max HP on death</t>
-  </si>
-  <si>
-    <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
-  </si>
-  <si>
-    <t>Shield allies {Percentage}% of max DEF on death</t>
-  </si>
-  <si>
-    <t>死亡后{Percentage}%生成魔晶</t>
-  </si>
-  <si>
-    <t>Spawn {Percentage}% chance crystal on death</t>
-  </si>
-  <si>
     <t>想要给魔物换个新名字！</t>
   </si>
   <si>
     <t>Want to rename my minion!</t>
   </si>
   <si>
+    <t>重命名魔物</t>
+  </si>
+  <si>
+    <t>Rename Demon</t>
+  </si>
+  <si>
     <t>excel_doom_council_info</t>
-  </si>
-  <si>
-    <t>重命名魔物</t>
-  </si>
-  <si>
-    <t>Rename Demon</t>
   </si>
   <si>
     <t>想要给自己换个新名字！</t>
@@ -4142,12 +4136,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -4821,7 +4814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4869,9 +4862,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7429,10 +7419,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C4" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7440,10 +7430,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7451,10 +7441,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C6" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7462,11 +7452,11 @@
         <v>1010010001</v>
       </c>
       <c r="B7" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="9" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7474,11 +7464,11 @@
         <v>1010020001</v>
       </c>
       <c r="B8" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C8"/>
       <c r="D8" s="9" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7486,13 +7476,13 @@
         <v>1020010001</v>
       </c>
       <c r="B9" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C9" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7500,11 +7490,11 @@
         <v>1020020001</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C10"/>
       <c r="D10" s="11" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7512,11 +7502,11 @@
         <v>1020030001</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C11"/>
       <c r="D11" s="11" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7524,13 +7514,13 @@
         <v>1030010001</v>
       </c>
       <c r="B12" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C12" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D12" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7538,13 +7528,13 @@
         <v>1030020001</v>
       </c>
       <c r="B13" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C13" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D13" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7552,11 +7542,11 @@
         <v>1030030001</v>
       </c>
       <c r="B14" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7564,11 +7554,11 @@
         <v>1030040001</v>
       </c>
       <c r="B15" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1" spans="1:4">
@@ -7576,10 +7566,10 @@
         <v>2000000001</v>
       </c>
       <c r="B16" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C16" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7587,10 +7577,10 @@
         <v>2000000002</v>
       </c>
       <c r="B17" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C17" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
@@ -7657,13 +7647,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C4" t="s">
+        <v>943</v>
+      </c>
+      <c r="D4" t="s">
         <v>944</v>
-      </c>
-      <c r="C4" t="s">
-        <v>945</v>
-      </c>
-      <c r="D4" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7671,13 +7661,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C5" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7685,13 +7675,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C6" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D6" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7699,13 +7689,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C7" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D7" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7713,13 +7703,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7727,13 +7717,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C9" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="D9" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7741,13 +7731,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C10" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>
@@ -7813,13 +7803,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D4" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7827,13 +7817,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7841,13 +7831,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C6" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D6" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7855,13 +7845,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C7" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D7" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7869,10 +7859,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7880,10 +7870,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D9" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7891,10 +7881,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7902,10 +7892,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:4">
@@ -7913,10 +7903,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:4">
@@ -7924,13 +7914,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:4">
@@ -7938,13 +7928,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D14" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>
@@ -8010,10 +8000,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8021,10 +8011,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C5" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -8032,10 +8022,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C6" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -8043,10 +8033,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C7" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8054,10 +8044,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C8" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8065,10 +8055,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C9" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -8076,10 +8066,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C10" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -8087,10 +8077,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -8098,10 +8088,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C12" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -8109,10 +8099,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C13" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -8120,10 +8110,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C14" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -8131,10 +8121,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C15" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -8142,10 +8132,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C16" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8153,10 +8143,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C17" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -8164,10 +8154,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C18" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8175,10 +8165,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C19" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8186,10 +8176,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C20" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8197,10 +8187,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C21" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8208,10 +8198,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8219,10 +8209,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C23" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8230,10 +8220,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C24" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8241,10 +8231,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C25" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8252,10 +8242,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C26" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8263,10 +8253,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C27" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8274,10 +8264,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C28" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8285,10 +8275,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C29" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8296,10 +8286,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C30" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8307,10 +8297,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C31" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8318,10 +8308,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C32" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8329,10 +8319,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C33" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8340,10 +8330,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C34" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -8410,10 +8400,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C4" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8421,10 +8411,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8432,10 +8422,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C6" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8443,10 +8433,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C7" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8454,10 +8444,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C8" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8465,10 +8455,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C9" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8476,10 +8466,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C10" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8487,10 +8477,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C11" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8498,10 +8488,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C12" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8509,10 +8499,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C13" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8520,10 +8510,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C14" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8531,10 +8521,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C15" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8542,10 +8532,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C16" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -8610,10 +8600,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C4" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8621,10 +8611,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8632,10 +8622,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C6" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8643,10 +8633,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C7" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8654,10 +8644,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C8" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
   </sheetData>
@@ -8723,10 +8713,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C4" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8734,10 +8724,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8745,10 +8735,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8756,10 +8746,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8767,10 +8757,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8778,10 +8768,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8789,10 +8779,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8800,10 +8790,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8811,10 +8801,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8822,10 +8812,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
@@ -8891,7 +8881,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8902,7 +8892,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8913,10 +8903,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8924,10 +8914,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8935,10 +8925,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8946,10 +8936,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C9" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
   </sheetData>
@@ -9017,13 +9007,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="s">
         <v>1201</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9031,13 +9021,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C5" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D5" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -9045,13 +9035,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C6" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D6" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -9059,13 +9049,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C7" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D7" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -9073,13 +9063,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C8" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D8" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -9087,13 +9077,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C9" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D9" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -9101,13 +9091,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C10" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D10" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -9115,13 +9105,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C11" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D11" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9129,13 +9119,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C12" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D12" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -9143,13 +9133,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C13" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D13" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -9157,13 +9147,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C14" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D14" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -9171,13 +9161,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C15" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="D15" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -9185,13 +9175,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C16" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="D16" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -9199,13 +9189,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C17" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D17" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9213,13 +9203,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C18" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D18" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -9227,13 +9217,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C19" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D19" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9241,13 +9231,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C20" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D20" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -9255,13 +9245,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C21" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D21" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9269,13 +9259,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C22" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D22" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9283,13 +9273,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C23" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="D23" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9297,13 +9287,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C24" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="D24" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9311,13 +9301,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C25" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D25" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9325,13 +9315,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C26" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D26" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9339,13 +9329,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C27" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="D27" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9353,13 +9343,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C28" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D28" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9367,13 +9357,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C29" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="D29" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9381,13 +9371,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C30" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D30" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9395,13 +9385,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C31" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D31" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9409,13 +9399,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C32" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D32" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9423,13 +9413,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C33" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D33" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9437,13 +9427,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C34" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D34" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9451,13 +9441,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C35" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="D35" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9465,13 +9455,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C36" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D36" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9479,13 +9469,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C37" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D37" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9493,13 +9483,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C38" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D38" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9507,13 +9497,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C39" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D39" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9521,13 +9511,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C40" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D40" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9535,13 +9525,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C41" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="D41" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9549,13 +9539,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C42" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="D42" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9563,13 +9553,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C43" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="D43" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9577,13 +9567,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C44" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D44" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9591,13 +9581,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C45" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D45" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9605,13 +9595,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C46" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D46" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9619,13 +9609,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C47" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D47" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9633,13 +9623,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C48" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D48" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9647,13 +9637,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C49" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D49" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9661,13 +9651,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C50" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D50" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9675,13 +9665,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C51" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D51" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9689,13 +9679,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C52" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D52" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9703,13 +9693,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C53" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="D53" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9717,13 +9707,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C54" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D54" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9731,13 +9721,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C55" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="D55" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9745,13 +9735,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C56" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D56" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9759,13 +9749,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C57" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="D57" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9773,13 +9763,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C58" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D58" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9787,13 +9777,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C59" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="D59" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9801,13 +9791,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C60" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D60" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9815,13 +9805,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C61" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D61" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9829,13 +9819,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C62" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D62" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9843,13 +9833,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C63" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="D63" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9857,13 +9847,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C64" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="D64" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9871,13 +9861,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C65" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="D65" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9885,13 +9875,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C66" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="D66" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9899,13 +9889,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C67" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="D67" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9913,13 +9903,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C68" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D68" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9927,13 +9917,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C69" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="D69" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9941,13 +9931,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C70" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D70" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9955,13 +9945,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C71" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D71" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9969,13 +9959,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C72" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="D72" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9983,13 +9973,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C73" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D73" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9997,13 +9987,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C74" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D74" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -10011,13 +10001,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C75" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="D75" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -10025,13 +10015,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C76" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="D76" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -10039,13 +10029,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C77" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D77" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -10053,13 +10043,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C78" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="D78" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -10067,13 +10057,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C79" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D79" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -10081,13 +10071,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C80" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D80" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -10095,13 +10085,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C81" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D81" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -10109,13 +10099,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C82" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D82" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -10123,13 +10113,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C83" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D83" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -10137,13 +10127,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C84" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D84" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -10151,13 +10141,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C85" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D85" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -13645,16 +13635,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D90"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="35.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="61.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13665,10 +13656,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13681,8 +13678,14 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -13693,136 +13696,182 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1000100001</v>
       </c>
       <c r="B4" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C4" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D4" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>698</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1000200001</v>
       </c>
       <c r="B5" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C5" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D5" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>698</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1000300001</v>
       </c>
       <c r="B6" t="s">
-        <v>697</v>
-      </c>
-      <c r="C6" t="s">
-        <v>698</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="C6"/>
       <c r="D6" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>703</v>
+      </c>
+      <c r="E6" t="s">
+        <v>704</v>
+      </c>
+      <c r="F6" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1000400001</v>
       </c>
       <c r="B7" t="s">
+        <v>705</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>703</v>
+      </c>
+      <c r="E7" t="s">
+        <v>704</v>
+      </c>
+      <c r="F7" t="s">
         <v>699</v>
       </c>
-      <c r="C7" t="s">
-        <v>700</v>
-      </c>
-      <c r="D7" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>1000500001</v>
       </c>
       <c r="B8" t="s">
-        <v>701</v>
-      </c>
-      <c r="C8" t="s">
-        <v>702</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="C8"/>
       <c r="D8" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>703</v>
+      </c>
+      <c r="E8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>2000100001</v>
       </c>
       <c r="B9" t="s">
-        <v>703</v>
-      </c>
-      <c r="C9" t="s">
-        <v>704</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="C9"/>
       <c r="D9" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>708</v>
+      </c>
+      <c r="E9" t="s">
+        <v>709</v>
+      </c>
+      <c r="F9" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>2000200001</v>
       </c>
       <c r="B10" t="s">
-        <v>705</v>
-      </c>
-      <c r="C10" t="s">
-        <v>706</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="C10"/>
       <c r="D10" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>711</v>
+      </c>
+      <c r="E10" t="s">
+        <v>712</v>
+      </c>
+      <c r="F10" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>2000300001</v>
       </c>
       <c r="B11" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="C11" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="D11" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>715</v>
+      </c>
+      <c r="E11" t="s">
+        <v>716</v>
+      </c>
+      <c r="F11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>2000400001</v>
       </c>
       <c r="B12" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="C12" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="D12" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>719</v>
+      </c>
+      <c r="E12" t="s">
+        <v>720</v>
+      </c>
+      <c r="F12" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>3000100001</v>
       </c>
@@ -13833,10 +13882,16 @@
         <v>294</v>
       </c>
       <c r="D13" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>296</v>
+      </c>
+      <c r="E13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>3000200001</v>
       </c>
@@ -13847,24 +13902,36 @@
         <v>303</v>
       </c>
       <c r="D14" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>304</v>
+      </c>
+      <c r="E14" t="s">
+        <v>305</v>
+      </c>
+      <c r="F14" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>3000300001</v>
       </c>
       <c r="B15" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="C15" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="D15" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>308</v>
+      </c>
+      <c r="E15" t="s">
+        <v>309</v>
+      </c>
+      <c r="F15" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>3000400001</v>
       </c>
@@ -13875,1043 +13942,629 @@
         <v>299</v>
       </c>
       <c r="D16" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>723</v>
+      </c>
+      <c r="E16" t="s">
+        <v>724</v>
+      </c>
+      <c r="F16" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>11000100001</v>
       </c>
       <c r="B17" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="C17" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="D17" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>726</v>
+      </c>
+      <c r="E17" t="s">
+        <v>727</v>
+      </c>
+      <c r="F17" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>11000200001</v>
       </c>
       <c r="B18" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="C18" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="D18" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>730</v>
+      </c>
+      <c r="E18" t="s">
+        <v>731</v>
+      </c>
+      <c r="F18" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>11000300001</v>
       </c>
       <c r="B19" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="C19" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="D19" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>733</v>
+      </c>
+      <c r="E19" t="s">
+        <v>734</v>
+      </c>
+      <c r="F19" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>12000100001</v>
       </c>
       <c r="B20" t="s">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="C20" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="D20" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>737</v>
+      </c>
+      <c r="E20" t="s">
+        <v>738</v>
+      </c>
+      <c r="F20" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>12000200001</v>
       </c>
       <c r="B21" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="C21" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="D21" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>741</v>
+      </c>
+      <c r="E21" t="s">
+        <v>742</v>
+      </c>
+      <c r="F21" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>12000300001</v>
       </c>
       <c r="B22" t="s">
-        <v>721</v>
+        <v>743</v>
       </c>
       <c r="C22" t="s">
-        <v>722</v>
+        <v>744</v>
       </c>
       <c r="D22" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:4">
+        <v>745</v>
+      </c>
+      <c r="E22" t="s">
+        <v>746</v>
+      </c>
+      <c r="F22" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1" spans="1:6">
       <c r="A23">
         <v>12001100001</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>723</v>
+        <v>747</v>
       </c>
       <c r="C23" t="s">
-        <v>724</v>
+        <v>748</v>
       </c>
       <c r="D23" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:4">
+        <v>749</v>
+      </c>
+      <c r="E23" t="s">
+        <v>750</v>
+      </c>
+      <c r="F23" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:6">
       <c r="A24">
         <v>12001200001</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>725</v>
+        <v>751</v>
       </c>
       <c r="C24" t="s">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="D24" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1" spans="1:4">
+        <v>753</v>
+      </c>
+      <c r="E24" t="s">
+        <v>754</v>
+      </c>
+      <c r="F24" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1" spans="1:6">
       <c r="A25">
         <v>12001300001</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>727</v>
+        <v>755</v>
       </c>
       <c r="C25" t="s">
-        <v>728</v>
+        <v>756</v>
       </c>
       <c r="D25" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1" spans="1:4">
+        <v>757</v>
+      </c>
+      <c r="E25" t="s">
+        <v>758</v>
+      </c>
+      <c r="F25" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:6">
       <c r="A26">
         <v>12001400001</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="C26" t="s">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:4">
+        <v>761</v>
+      </c>
+      <c r="E26" t="s">
+        <v>762</v>
+      </c>
+      <c r="F26" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="1:6">
       <c r="A27">
         <v>12002100001</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="D27" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:4">
+        <v>765</v>
+      </c>
+      <c r="E27" t="s">
+        <v>766</v>
+      </c>
+      <c r="F27" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="1:6">
       <c r="A28">
         <v>12002200001</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>733</v>
+        <v>767</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>734</v>
+        <v>768</v>
       </c>
       <c r="D28" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:4">
+        <v>769</v>
+      </c>
+      <c r="E28" t="s">
+        <v>770</v>
+      </c>
+      <c r="F28" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1" spans="1:6">
       <c r="A29">
         <v>12002300001</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>735</v>
+        <v>771</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>736</v>
+        <v>772</v>
       </c>
       <c r="D29" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:4">
+        <v>773</v>
+      </c>
+      <c r="E29" t="s">
+        <v>774</v>
+      </c>
+      <c r="F29" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" spans="1:6">
       <c r="A30">
         <v>12002400001</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>737</v>
+        <v>775</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>738</v>
+        <v>776</v>
       </c>
       <c r="D30" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:4">
+        <v>777</v>
+      </c>
+      <c r="E30" t="s">
+        <v>778</v>
+      </c>
+      <c r="F30" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="1:6">
       <c r="A31">
         <v>12003100001</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>739</v>
+        <v>779</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="D31" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:4">
+        <v>781</v>
+      </c>
+      <c r="E31" t="s">
+        <v>782</v>
+      </c>
+      <c r="F31" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="1:6">
       <c r="A32">
         <v>12003200001</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>741</v>
+        <v>783</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>742</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="33" ht="17.25" customHeight="1" spans="1:4">
+        <v>785</v>
+      </c>
+      <c r="E32" t="s">
+        <v>786</v>
+      </c>
+      <c r="F32" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1" spans="1:6">
       <c r="A33">
         <v>12003300001</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>743</v>
+        <v>787</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>744</v>
+        <v>788</v>
       </c>
       <c r="D33" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="34" ht="17.25" customHeight="1" spans="1:4">
+        <v>789</v>
+      </c>
+      <c r="E33" t="s">
+        <v>790</v>
+      </c>
+      <c r="F33" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1" spans="1:6">
       <c r="A34">
         <v>12003400001</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="D34" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="35" ht="17.25" customHeight="1" spans="1:4">
+        <v>793</v>
+      </c>
+      <c r="E34" t="s">
+        <v>794</v>
+      </c>
+      <c r="F34" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1" spans="1:6">
       <c r="A35">
         <v>12010100001</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>747</v>
+        <v>795</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>748</v>
+        <v>796</v>
       </c>
       <c r="D35" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="36" ht="17.25" customHeight="1" spans="1:4">
+        <v>797</v>
+      </c>
+      <c r="E35" t="s">
+        <v>798</v>
+      </c>
+      <c r="F35" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1" spans="1:6">
       <c r="A36">
         <v>12010200001</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>749</v>
+        <v>799</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="37" ht="17.25" customHeight="1" spans="1:4">
+        <v>801</v>
+      </c>
+      <c r="E36" t="s">
+        <v>802</v>
+      </c>
+      <c r="F36" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1" spans="1:6">
       <c r="A37">
         <v>12010300001</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>751</v>
+        <v>803</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>752</v>
+        <v>804</v>
       </c>
       <c r="D37" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="38" ht="17.25" customHeight="1" spans="1:4">
+        <v>805</v>
+      </c>
+      <c r="E37" t="s">
+        <v>806</v>
+      </c>
+      <c r="F37" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1" spans="1:6">
       <c r="A38">
         <v>12011100001</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>753</v>
+        <v>807</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>754</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="39" ht="17.25" customHeight="1" spans="1:4">
+        <v>809</v>
+      </c>
+      <c r="E38" t="s">
+        <v>810</v>
+      </c>
+      <c r="F38" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1" spans="1:6">
       <c r="A39">
         <v>12011200001</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="D39" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="40" ht="17.25" customHeight="1" spans="1:4">
+        <v>813</v>
+      </c>
+      <c r="E39" t="s">
+        <v>814</v>
+      </c>
+      <c r="F39" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1" spans="1:6">
       <c r="A40">
         <v>12011300001</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>757</v>
+        <v>815</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>758</v>
+        <v>816</v>
       </c>
       <c r="D40" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>817</v>
+      </c>
+      <c r="E40" t="s">
+        <v>818</v>
+      </c>
+      <c r="F40" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>13000100001</v>
       </c>
       <c r="B41" t="s">
-        <v>759</v>
+        <v>819</v>
       </c>
       <c r="C41" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="D41" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>821</v>
+      </c>
+      <c r="E41" t="s">
+        <v>822</v>
+      </c>
+      <c r="F41" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>13000200001</v>
       </c>
       <c r="B42" t="s">
-        <v>761</v>
+        <v>823</v>
       </c>
       <c r="C42" t="s">
-        <v>762</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>825</v>
+      </c>
+      <c r="E42" t="s">
+        <v>826</v>
+      </c>
+      <c r="F42" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>13000300001</v>
       </c>
       <c r="B43" t="s">
-        <v>763</v>
+        <v>827</v>
       </c>
       <c r="C43" t="s">
-        <v>764</v>
+        <v>828</v>
       </c>
       <c r="D43" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>829</v>
+      </c>
+      <c r="E43" t="s">
+        <v>830</v>
+      </c>
+      <c r="F43" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>13000400001</v>
       </c>
       <c r="B44" t="s">
-        <v>765</v>
+        <v>831</v>
       </c>
       <c r="C44" t="s">
-        <v>766</v>
+        <v>832</v>
       </c>
       <c r="D44" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>833</v>
+      </c>
+      <c r="E44" t="s">
+        <v>834</v>
+      </c>
+      <c r="F44" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>13000500001</v>
       </c>
       <c r="B45" t="s">
-        <v>767</v>
+        <v>835</v>
       </c>
       <c r="C45" t="s">
-        <v>768</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>837</v>
+      </c>
+      <c r="E45" t="s">
+        <v>838</v>
+      </c>
+      <c r="F45" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>13000600001</v>
       </c>
       <c r="B46" t="s">
-        <v>769</v>
+        <v>839</v>
       </c>
       <c r="C46" t="s">
-        <v>770</v>
+        <v>840</v>
       </c>
       <c r="D46" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>841</v>
+      </c>
+      <c r="E46" t="s">
+        <v>842</v>
+      </c>
+      <c r="F46" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>13000700001</v>
       </c>
       <c r="B47" t="s">
-        <v>771</v>
+        <v>843</v>
       </c>
       <c r="C47" t="s">
-        <v>772</v>
-      </c>
-      <c r="D47" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="17">
-        <v>10001000010000</v>
-      </c>
-      <c r="B48" t="s">
-        <v>773</v>
-      </c>
-      <c r="C48" t="s">
-        <v>774</v>
-      </c>
-      <c r="D48" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="17">
-        <v>10002000010000</v>
-      </c>
-      <c r="B49" t="s">
-        <v>773</v>
-      </c>
-      <c r="C49" t="s">
-        <v>774</v>
-      </c>
-      <c r="D49" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="17">
-        <v>10003000010000</v>
-      </c>
-      <c r="B50" t="s">
-        <v>775</v>
-      </c>
-      <c r="C50" t="s">
-        <v>776</v>
-      </c>
-      <c r="D50" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="17">
-        <v>10004000010000</v>
-      </c>
-      <c r="B51" t="s">
-        <v>775</v>
-      </c>
-      <c r="C51" t="s">
-        <v>776</v>
-      </c>
-      <c r="D51" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="17">
-        <v>10005000010000</v>
-      </c>
-      <c r="B52" t="s">
-        <v>775</v>
-      </c>
-      <c r="C52" t="s">
-        <v>776</v>
-      </c>
-      <c r="D52" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="17">
-        <v>20001000010000</v>
-      </c>
-      <c r="B53" t="s">
-        <v>777</v>
-      </c>
-      <c r="C53" t="s">
-        <v>778</v>
-      </c>
-      <c r="D53" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="17">
-        <v>20002000010000</v>
-      </c>
-      <c r="B54" t="s">
-        <v>779</v>
-      </c>
-      <c r="C54" t="s">
-        <v>780</v>
-      </c>
-      <c r="D54" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="17">
-        <v>20003000010000</v>
-      </c>
-      <c r="B55" t="s">
-        <v>781</v>
-      </c>
-      <c r="C55" t="s">
-        <v>782</v>
-      </c>
-      <c r="D55" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="17">
-        <v>20004000010000</v>
-      </c>
-      <c r="B56" t="s">
-        <v>783</v>
-      </c>
-      <c r="C56" t="s">
-        <v>784</v>
-      </c>
-      <c r="D56" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="17">
-        <v>30001000010000</v>
-      </c>
-      <c r="B57" t="s">
-        <v>296</v>
-      </c>
-      <c r="C57" t="s">
-        <v>297</v>
-      </c>
-      <c r="D57" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="17">
-        <v>30002000010000</v>
-      </c>
-      <c r="B58" t="s">
-        <v>304</v>
-      </c>
-      <c r="C58" t="s">
-        <v>305</v>
-      </c>
-      <c r="D58" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="17">
-        <v>30003000010000</v>
-      </c>
-      <c r="B59" t="s">
-        <v>308</v>
-      </c>
-      <c r="C59" t="s">
-        <v>309</v>
-      </c>
-      <c r="D59" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="17">
-        <v>30004000010000</v>
-      </c>
-      <c r="B60" t="s">
-        <v>785</v>
-      </c>
-      <c r="C60" t="s">
-        <v>786</v>
-      </c>
-      <c r="D60" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="17">
-        <v>110001000010000</v>
-      </c>
-      <c r="B61" t="s">
-        <v>787</v>
-      </c>
-      <c r="C61" t="s">
-        <v>788</v>
-      </c>
-      <c r="D61" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="17">
-        <v>110002000010000</v>
-      </c>
-      <c r="B62" t="s">
-        <v>789</v>
-      </c>
-      <c r="C62" t="s">
-        <v>790</v>
-      </c>
-      <c r="D62" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="17">
-        <v>110003000010000</v>
-      </c>
-      <c r="B63" t="s">
-        <v>791</v>
-      </c>
-      <c r="C63" t="s">
-        <v>792</v>
-      </c>
-      <c r="D63" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="17">
-        <v>120001000010000</v>
-      </c>
-      <c r="B64" t="s">
-        <v>793</v>
-      </c>
-      <c r="C64" t="s">
-        <v>794</v>
-      </c>
-      <c r="D64" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="17">
-        <v>120002000010000</v>
-      </c>
-      <c r="B65" t="s">
-        <v>795</v>
-      </c>
-      <c r="C65" t="s">
-        <v>796</v>
-      </c>
-      <c r="D65" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="17">
-        <v>120003000010000</v>
-      </c>
-      <c r="B66" t="s">
-        <v>797</v>
-      </c>
-      <c r="C66" t="s">
-        <v>798</v>
-      </c>
-      <c r="D66" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="17">
-        <v>120011000010000</v>
-      </c>
-      <c r="B67" t="s">
-        <v>799</v>
-      </c>
-      <c r="C67" t="s">
-        <v>800</v>
-      </c>
-      <c r="D67" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="17">
-        <v>120012000010000</v>
-      </c>
-      <c r="B68" t="s">
-        <v>801</v>
-      </c>
-      <c r="C68" t="s">
-        <v>802</v>
-      </c>
-      <c r="D68" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="17">
-        <v>120013000010000</v>
-      </c>
-      <c r="B69" t="s">
-        <v>803</v>
-      </c>
-      <c r="C69" t="s">
-        <v>804</v>
-      </c>
-      <c r="D69" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="17">
-        <v>120014000010000</v>
-      </c>
-      <c r="B70" t="s">
-        <v>805</v>
-      </c>
-      <c r="C70" t="s">
-        <v>806</v>
-      </c>
-      <c r="D70" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="17">
-        <v>120021000010000</v>
-      </c>
-      <c r="B71" t="s">
-        <v>807</v>
-      </c>
-      <c r="C71" t="s">
-        <v>808</v>
-      </c>
-      <c r="D71" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="17">
-        <v>120022000010000</v>
-      </c>
-      <c r="B72" t="s">
-        <v>809</v>
-      </c>
-      <c r="C72" t="s">
-        <v>810</v>
-      </c>
-      <c r="D72" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="17">
-        <v>120023000010000</v>
-      </c>
-      <c r="B73" t="s">
-        <v>811</v>
-      </c>
-      <c r="C73" t="s">
-        <v>812</v>
-      </c>
-      <c r="D73" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="17">
-        <v>120024000010000</v>
-      </c>
-      <c r="B74" t="s">
-        <v>813</v>
-      </c>
-      <c r="C74" t="s">
-        <v>814</v>
-      </c>
-      <c r="D74" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="17">
-        <v>120031000010000</v>
-      </c>
-      <c r="B75" t="s">
-        <v>815</v>
-      </c>
-      <c r="C75" t="s">
-        <v>816</v>
-      </c>
-      <c r="D75" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="17">
-        <v>120032000010000</v>
-      </c>
-      <c r="B76" t="s">
-        <v>817</v>
-      </c>
-      <c r="C76" t="s">
-        <v>818</v>
-      </c>
-      <c r="D76" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="17">
-        <v>120033000010000</v>
-      </c>
-      <c r="B77" t="s">
-        <v>819</v>
-      </c>
-      <c r="C77" t="s">
-        <v>820</v>
-      </c>
-      <c r="D77" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="17">
-        <v>120034000010000</v>
-      </c>
-      <c r="B78" t="s">
-        <v>821</v>
-      </c>
-      <c r="C78" t="s">
-        <v>822</v>
-      </c>
-      <c r="D78" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="17">
-        <v>120101000010000</v>
-      </c>
-      <c r="B79" t="s">
-        <v>823</v>
-      </c>
-      <c r="C79" t="s">
-        <v>824</v>
-      </c>
-      <c r="D79" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="17">
-        <v>120102000010000</v>
-      </c>
-      <c r="B80" t="s">
-        <v>825</v>
-      </c>
-      <c r="C80" t="s">
-        <v>826</v>
-      </c>
-      <c r="D80" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="17">
-        <v>120103000010000</v>
-      </c>
-      <c r="B81" t="s">
-        <v>827</v>
-      </c>
-      <c r="C81" t="s">
-        <v>828</v>
-      </c>
-      <c r="D81" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="17">
-        <v>120111000010000</v>
-      </c>
-      <c r="B82" t="s">
-        <v>829</v>
-      </c>
-      <c r="C82" t="s">
-        <v>830</v>
-      </c>
-      <c r="D82" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="17">
-        <v>120112000010000</v>
-      </c>
-      <c r="B83" t="s">
-        <v>831</v>
-      </c>
-      <c r="C83" t="s">
-        <v>832</v>
-      </c>
-      <c r="D83" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="17">
-        <v>120113000010000</v>
-      </c>
-      <c r="B84" t="s">
-        <v>833</v>
-      </c>
-      <c r="C84" t="s">
-        <v>834</v>
-      </c>
-      <c r="D84" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="17">
-        <v>130001000010000</v>
-      </c>
-      <c r="B85" t="s">
-        <v>835</v>
-      </c>
-      <c r="C85" t="s">
-        <v>836</v>
-      </c>
-      <c r="D85" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="17">
-        <v>130003000010000</v>
-      </c>
-      <c r="B86" t="s">
-        <v>837</v>
-      </c>
-      <c r="C86" t="s">
-        <v>838</v>
-      </c>
-      <c r="D86" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="17">
-        <v>130004000010000</v>
-      </c>
-      <c r="B87" t="s">
-        <v>839</v>
-      </c>
-      <c r="C87" t="s">
-        <v>840</v>
-      </c>
-      <c r="D87" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="17">
-        <v>130005000010000</v>
-      </c>
-      <c r="B88" t="s">
-        <v>841</v>
-      </c>
-      <c r="C88" t="s">
-        <v>842</v>
-      </c>
-      <c r="D88" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="17">
-        <v>130006000010000</v>
-      </c>
-      <c r="B89" t="s">
-        <v>843</v>
-      </c>
-      <c r="C89" t="s">
         <v>844</v>
       </c>
-      <c r="D89" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="17">
-        <v>130007000010000</v>
-      </c>
-      <c r="B90" t="s">
-        <v>845</v>
-      </c>
-      <c r="C90" t="s">
-        <v>846</v>
-      </c>
-      <c r="D90" t="s">
-        <v>694</v>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -14923,16 +14576,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="3" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14943,10 +14597,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -14959,8 +14619,14 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -14971,25 +14637,37 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="4" spans="1:6">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C4" t="s">
+        <v>846</v>
+      </c>
+      <c r="D4" t="s">
         <v>847</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>848</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+    <row r="5" spans="1:6">
+      <c r="A5" s="11">
         <v>2</v>
       </c>
       <c r="B5" t="s">
@@ -14999,286 +14677,192 @@
         <v>851</v>
       </c>
       <c r="D5" t="s">
+        <v>852</v>
+      </c>
+      <c r="E5" t="s">
+        <v>853</v>
+      </c>
+      <c r="F5" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>3</v>
+    <row r="6" spans="1:6">
+      <c r="A6" s="11">
+        <v>1000000001</v>
       </c>
       <c r="B6" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C6" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D6" t="s">
+        <v>856</v>
+      </c>
+      <c r="E6" t="s">
+        <v>857</v>
+      </c>
+      <c r="F6" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>4</v>
+    <row r="7" spans="1:6">
+      <c r="A7" s="11">
+        <v>1000100001</v>
       </c>
       <c r="B7" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C7" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D7" t="s">
+        <v>860</v>
+      </c>
+      <c r="E7" t="s">
+        <v>861</v>
+      </c>
+      <c r="F7" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>100001</v>
+    <row r="8" spans="1:6">
+      <c r="A8" s="11">
+        <v>1000200001</v>
       </c>
       <c r="B8" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C8" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D8" t="s">
+        <v>864</v>
+      </c>
+      <c r="E8" t="s">
+        <v>865</v>
+      </c>
+      <c r="F8" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>100002</v>
+    <row r="9" spans="1:6">
+      <c r="A9" s="11">
+        <v>1000200002</v>
       </c>
       <c r="B9" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="C9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="D9" t="s">
+        <v>868</v>
+      </c>
+      <c r="E9" t="s">
+        <v>869</v>
+      </c>
+      <c r="F9" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>100003</v>
+    <row r="10" spans="1:6">
+      <c r="A10" s="11">
+        <v>1000200003</v>
       </c>
       <c r="B10" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="C10" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="D10" t="s">
+        <v>872</v>
+      </c>
+      <c r="E10" t="s">
+        <v>873</v>
+      </c>
+      <c r="F10" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>100004</v>
+    <row r="11" spans="1:6">
+      <c r="A11" s="11">
+        <v>1000200004</v>
       </c>
       <c r="B11" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C11" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="D11" t="s">
+        <v>876</v>
+      </c>
+      <c r="E11" t="s">
+        <v>877</v>
+      </c>
+      <c r="F11" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>200001</v>
+    <row r="12" spans="1:6">
+      <c r="A12" s="11">
+        <v>1000200005</v>
       </c>
       <c r="B12" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="C12" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="D12" t="s">
+        <v>880</v>
+      </c>
+      <c r="E12" t="s">
+        <v>881</v>
+      </c>
+      <c r="F12" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>200002</v>
+    <row r="13" spans="1:6">
+      <c r="A13" s="11">
+        <v>1000200006</v>
       </c>
       <c r="B13" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="C13" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="D13" t="s">
+        <v>884</v>
+      </c>
+      <c r="E13" t="s">
+        <v>885</v>
+      </c>
+      <c r="F13" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>200003</v>
+    <row r="14" spans="1:6">
+      <c r="A14" s="11">
+        <v>1000200007</v>
       </c>
       <c r="B14" t="s">
-        <v>868</v>
+        <v>886</v>
       </c>
       <c r="C14" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="D14" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>200004</v>
-      </c>
-      <c r="B15" t="s">
-        <v>870</v>
-      </c>
-      <c r="C15" t="s">
-        <v>871</v>
-      </c>
-      <c r="D15" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>200005</v>
-      </c>
-      <c r="B16" t="s">
-        <v>872</v>
-      </c>
-      <c r="C16" t="s">
-        <v>873</v>
-      </c>
-      <c r="D16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>200006</v>
-      </c>
-      <c r="B17" t="s">
-        <v>874</v>
-      </c>
-      <c r="C17" t="s">
-        <v>875</v>
-      </c>
-      <c r="D17" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>200007</v>
-      </c>
-      <c r="B18" t="s">
-        <v>876</v>
-      </c>
-      <c r="C18" t="s">
-        <v>877</v>
-      </c>
-      <c r="D18" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>200008</v>
-      </c>
-      <c r="B19" t="s">
-        <v>878</v>
-      </c>
-      <c r="C19" t="s">
-        <v>879</v>
-      </c>
-      <c r="D19" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>200009</v>
-      </c>
-      <c r="B20" t="s">
-        <v>880</v>
-      </c>
-      <c r="C20" t="s">
-        <v>881</v>
-      </c>
-      <c r="D20" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>200010</v>
-      </c>
-      <c r="B21" t="s">
-        <v>882</v>
-      </c>
-      <c r="C21" t="s">
-        <v>883</v>
-      </c>
-      <c r="D21" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>200011</v>
-      </c>
-      <c r="B22" t="s">
-        <v>884</v>
-      </c>
-      <c r="C22" t="s">
-        <v>885</v>
-      </c>
-      <c r="D22" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>200012</v>
-      </c>
-      <c r="B23" t="s">
-        <v>886</v>
-      </c>
-      <c r="C23" t="s">
-        <v>887</v>
-      </c>
-      <c r="D23" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>200013</v>
-      </c>
-      <c r="B24" t="s">
         <v>888</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E14" t="s">
         <v>889</v>
       </c>
-      <c r="D24" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>200014</v>
-      </c>
-      <c r="B25" t="s">
-        <v>890</v>
-      </c>
-      <c r="C25" t="s">
-        <v>891</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F14" t="s">
         <v>849</v>
       </c>
     </row>
@@ -15347,13 +14931,13 @@
         <v>10001</v>
       </c>
       <c r="B4" t="s">
+        <v>890</v>
+      </c>
+      <c r="C4" t="s">
+        <v>891</v>
+      </c>
+      <c r="D4" t="s">
         <v>892</v>
-      </c>
-      <c r="C4" t="s">
-        <v>893</v>
-      </c>
-      <c r="D4" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15361,13 +14945,13 @@
         <v>10002</v>
       </c>
       <c r="B5" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C5" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D5" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15375,13 +14959,13 @@
         <v>10003</v>
       </c>
       <c r="B6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C6" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15389,13 +14973,13 @@
         <v>20001</v>
       </c>
       <c r="B7" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C7" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D7" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -15403,13 +14987,13 @@
         <v>20002</v>
       </c>
       <c r="B8" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C8" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -15417,13 +15001,13 @@
         <v>20003</v>
       </c>
       <c r="B9" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C9" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D9" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -15431,13 +15015,13 @@
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D10" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -15445,13 +15029,13 @@
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C11" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -15459,13 +15043,13 @@
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C12" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D12" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15473,13 +15057,13 @@
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C13" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D13" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -15487,13 +15071,13 @@
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C14" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D14" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -15501,13 +15085,13 @@
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C15" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D15" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -15515,13 +15099,13 @@
         <v>50001</v>
       </c>
       <c r="B16" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D16" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -15529,13 +15113,13 @@
         <v>50002</v>
       </c>
       <c r="B17" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C17" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D17" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -15543,13 +15127,13 @@
         <v>50003</v>
       </c>
       <c r="B18" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C18" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D18" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -15557,13 +15141,13 @@
         <v>60001</v>
       </c>
       <c r="B19" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C19" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D19" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -15571,13 +15155,13 @@
         <v>60002</v>
       </c>
       <c r="B20" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C20" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D20" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -15585,13 +15169,13 @@
         <v>60003</v>
       </c>
       <c r="B21" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C21" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D21" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -15599,13 +15183,13 @@
         <v>70001</v>
       </c>
       <c r="B22" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C22" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D22" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -15613,13 +15197,13 @@
         <v>70002</v>
       </c>
       <c r="B23" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C23" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D23" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -15627,13 +15211,13 @@
         <v>70003</v>
       </c>
       <c r="B24" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C24" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D24" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -15701,13 +15285,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>933</v>
+      </c>
+      <c r="C4" t="s">
+        <v>934</v>
+      </c>
+      <c r="D4" t="s">
         <v>935</v>
-      </c>
-      <c r="C4" t="s">
-        <v>936</v>
-      </c>
-      <c r="D4" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15715,13 +15299,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C5" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15729,13 +15313,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C6" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D6" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15743,13 +15327,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C7" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D7" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -15817,13 +15401,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C4" t="s">
+        <v>943</v>
+      </c>
+      <c r="D4" t="s">
         <v>944</v>
-      </c>
-      <c r="C4" t="s">
-        <v>945</v>
-      </c>
-      <c r="D4" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15831,13 +15415,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C5" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -15845,13 +15429,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C6" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D6" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -15859,13 +15443,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C7" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D7" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -15873,13 +15457,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -15887,13 +15471,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C9" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="D9" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -15901,13 +15485,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C10" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -15915,13 +15499,13 @@
         <v>1001</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -15929,13 +15513,13 @@
         <v>1002</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15943,13 +15527,13 @@
         <v>1003</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -15957,13 +15541,13 @@
         <v>1004</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -15971,13 +15555,13 @@
         <v>2001</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -15985,13 +15569,13 @@
         <v>2002</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -15999,13 +15583,13 @@
         <v>2003</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -16013,13 +15597,13 @@
         <v>2004</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -16027,13 +15611,13 @@
         <v>3001</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -16041,13 +15625,13 @@
         <v>3002</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -16055,13 +15639,13 @@
         <v>3003</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -16069,13 +15653,13 @@
         <v>3004</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -16083,13 +15667,13 @@
         <v>4001</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -16097,13 +15681,13 @@
         <v>4002</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -16111,13 +15695,13 @@
         <v>4003</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -16125,13 +15709,13 @@
         <v>4004</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -16139,13 +15723,13 @@
         <v>4005</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -16153,13 +15737,13 @@
         <v>5001</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -16167,13 +15751,13 @@
         <v>5002</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -16181,13 +15765,13 @@
         <v>5003</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -16195,13 +15779,13 @@
         <v>5004</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -16209,13 +15793,13 @@
         <v>6001</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -16223,13 +15807,13 @@
         <v>6002</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -16237,13 +15821,13 @@
         <v>6003</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -16251,13 +15835,13 @@
         <v>6004</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -16265,13 +15849,13 @@
         <v>6005</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -16279,13 +15863,13 @@
         <v>7001</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -16293,13 +15877,13 @@
         <v>7002</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -16307,13 +15891,13 @@
         <v>7003</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -16321,13 +15905,13 @@
         <v>7004</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -16335,13 +15919,13 @@
         <v>101001</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -16349,11 +15933,11 @@
         <v>101002</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -16361,13 +15945,13 @@
         <v>102001</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -16375,11 +15959,11 @@
         <v>102002</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -16387,11 +15971,11 @@
         <v>102003</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -16399,13 +15983,13 @@
         <v>103001</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -16413,13 +15997,13 @@
         <v>103002</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -16427,11 +16011,11 @@
         <v>103003</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -16439,11 +16023,11 @@
         <v>103004</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -16451,13 +16035,13 @@
         <v>900001</v>
       </c>
       <c r="B50" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C50" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D50" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -16465,13 +16049,13 @@
         <v>900002</v>
       </c>
       <c r="B51" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C51" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D51" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25860" windowHeight="8820" tabRatio="723" firstSheet="11" activeTab="17"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="1367">
   <si>
     <t>id</t>
   </si>
@@ -3127,6 +3127,15 @@
     <t>人类-魔法师（雷）</t>
   </si>
   <si>
+    <t>人类-大魔法师（火）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（水）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（冰）</t>
+  </si>
+  <si>
     <t>测试骷髅战士</t>
   </si>
   <si>
@@ -3202,16 +3211,22 @@
     <t>魔法师（雷）</t>
   </si>
   <si>
+    <t>大魔法师（火）</t>
+  </si>
+  <si>
+    <t>大魔法师（水）</t>
+  </si>
+  <si>
+    <t>大魔法师（冰）</t>
+  </si>
+  <si>
     <t>白剑伟</t>
   </si>
   <si>
-    <t>Bai Jianwei</t>
-  </si>
-  <si>
     <t>宛家伟</t>
   </si>
   <si>
-    <t>Wan Jiawei</t>
+    <t>雷神天尊斩</t>
   </si>
   <si>
     <t>生命</t>
@@ -4201,14 +4216,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4814,7 +4829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4846,16 +4861,25 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6958,10 +6982,10 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="11">
+      <c r="A125" s="17">
         <v>90001</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="17" t="s">
         <v>244</v>
       </c>
       <c r="C125"/>
@@ -6970,10 +6994,10 @@
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="11">
+      <c r="A126" s="17">
         <v>90002</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="17" t="s">
         <v>245</v>
       </c>
       <c r="C126"/>
@@ -7248,10 +7272,10 @@
       </c>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="11">
+      <c r="A146" s="17">
         <v>2000008</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="17" t="s">
         <v>280</v>
       </c>
       <c r="C146"/>
@@ -7260,10 +7284,10 @@
       </c>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="11">
+      <c r="A147" s="17">
         <v>2000009</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="17" t="s">
         <v>281</v>
       </c>
       <c r="C147"/>
@@ -7272,10 +7296,10 @@
       </c>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="11">
+      <c r="A148" s="17">
         <v>2000010</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="17" t="s">
         <v>282</v>
       </c>
       <c r="C148"/>
@@ -7363,7 +7387,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
@@ -7419,10 +7443,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C4" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7430,10 +7454,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7441,146 +7465,186 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7">
+      <c r="A7" s="11">
         <v>1010010001</v>
       </c>
-      <c r="B7" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7" s="9" t="s">
-        <v>1037</v>
+      <c r="B7" s="12" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13" t="s">
+        <v>1040</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8">
+      <c r="A8" s="11">
         <v>1010020001</v>
       </c>
-      <c r="B8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8" s="9" t="s">
-        <v>1039</v>
+      <c r="B8" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="13" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9">
+      <c r="A9" s="11">
         <v>1020010001</v>
       </c>
-      <c r="B9" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>1040</v>
+      <c r="B9" s="12" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>1043</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11">
+      <c r="A10" s="14">
         <v>1020020001</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10" s="11" t="s">
-        <v>1043</v>
+      <c r="B10" s="15" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="15" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="11">
+      <c r="A11" s="14">
         <v>1020030001</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11" s="11" t="s">
-        <v>1045</v>
+      <c r="B11" s="15" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="15" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
+      <c r="A12" s="11">
         <v>1030010001</v>
       </c>
-      <c r="B12" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1046</v>
+      <c r="B12" s="12" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13">
+      <c r="A13" s="11">
         <v>1030020001</v>
       </c>
-      <c r="B13" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1048</v>
+      <c r="B13" s="12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>1051</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14">
+      <c r="A14" s="11">
         <v>1030030001</v>
       </c>
-      <c r="B14" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C14"/>
-      <c r="D14" t="s">
-        <v>1050</v>
+      <c r="B14" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
+      <c r="A15" s="11">
         <v>1030040001</v>
       </c>
-      <c r="B15" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="16" ht="12" customHeight="1" spans="1:4">
-      <c r="A16">
+      <c r="B15" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="13">
+        <v>1031010001</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16" s="15" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="13">
+        <v>1031010002</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" s="15" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="13">
+        <v>1031010003</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18" s="15" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="19" ht="12" customHeight="1" spans="1:4">
+      <c r="A19">
         <v>2000000001</v>
       </c>
-      <c r="B16" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
+      <c r="B19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
         <v>2000000002</v>
       </c>
-      <c r="B17" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1055</v>
+      <c r="B20" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>2000000003</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -7803,10 +7867,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="C4" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="D4" t="s">
         <v>944</v>
@@ -7817,10 +7881,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D5" t="s">
         <v>944</v>
@@ -7831,10 +7895,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C6" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="D6" t="s">
         <v>944</v>
@@ -7845,10 +7909,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="C7" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="D7" t="s">
         <v>944</v>
@@ -7859,7 +7923,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="s">
         <v>944</v>
@@ -7870,7 +7934,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="D9" t="s">
         <v>944</v>
@@ -7881,7 +7945,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="D10" t="s">
         <v>944</v>
@@ -7903,7 +7967,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="D12" t="s">
         <v>944</v>
@@ -7914,10 +7978,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D13" t="s">
         <v>944</v>
@@ -7928,10 +7992,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="D14" t="s">
         <v>944</v>
@@ -8000,10 +8064,10 @@
         <v>100000001</v>
       </c>
       <c r="B4" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="C4" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8011,10 +8075,10 @@
         <v>100000002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="C5" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4">
@@ -8022,10 +8086,10 @@
         <v>100000003</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4">
@@ -8033,10 +8097,10 @@
         <v>100000004</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C7" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8044,10 +8108,10 @@
         <v>100000005</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="C8" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8055,10 +8119,10 @@
         <v>100000006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="C9" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4">
@@ -8066,10 +8130,10 @@
         <v>200000001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="C10" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4">
@@ -8077,10 +8141,10 @@
         <v>200000002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="C11" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4">
@@ -8088,10 +8152,10 @@
         <v>200000003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="C12" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4">
@@ -8099,10 +8163,10 @@
         <v>200000004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="C13" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4">
@@ -8110,10 +8174,10 @@
         <v>200000005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="C14" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:4">
@@ -8121,10 +8185,10 @@
         <v>200000006</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="C15" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:4">
@@ -8132,10 +8196,10 @@
         <v>200000007</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8143,10 +8207,10 @@
         <v>300000001</v>
       </c>
       <c r="B17" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -8154,10 +8218,10 @@
         <v>300000002</v>
       </c>
       <c r="B18" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="C18" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8165,10 +8229,10 @@
         <v>300000003</v>
       </c>
       <c r="B19" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="C19" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8176,10 +8240,10 @@
         <v>300000004</v>
       </c>
       <c r="B20" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="C20" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8187,10 +8251,10 @@
         <v>300000005</v>
       </c>
       <c r="B21" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="C21" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8198,10 +8262,10 @@
         <v>300000006</v>
       </c>
       <c r="B22" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="C22" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8209,10 +8273,10 @@
         <v>400000001</v>
       </c>
       <c r="B23" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="C23" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8220,10 +8284,10 @@
         <v>400000002</v>
       </c>
       <c r="B24" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="C24" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8231,10 +8295,10 @@
         <v>400000003</v>
       </c>
       <c r="B25" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="C25" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8242,10 +8306,10 @@
         <v>400000004</v>
       </c>
       <c r="B26" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="C26" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8253,10 +8317,10 @@
         <v>400000005</v>
       </c>
       <c r="B27" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="C27" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8264,10 +8328,10 @@
         <v>400000006</v>
       </c>
       <c r="B28" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="C28" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8275,10 +8339,10 @@
         <v>400000007</v>
       </c>
       <c r="B29" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="C29" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8286,10 +8350,10 @@
         <v>500000001</v>
       </c>
       <c r="B30" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="C30" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8297,10 +8361,10 @@
         <v>500000002</v>
       </c>
       <c r="B31" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="C31" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8308,10 +8372,10 @@
         <v>500000003</v>
       </c>
       <c r="B32" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="C32" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8319,10 +8383,10 @@
         <v>500000004</v>
       </c>
       <c r="B33" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="C33" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8330,10 +8394,10 @@
         <v>500000005</v>
       </c>
       <c r="B34" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="C34" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
@@ -8400,10 +8464,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="C4" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8411,10 +8475,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8422,10 +8486,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="C6" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8433,10 +8497,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="C7" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8444,10 +8508,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="C8" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8455,10 +8519,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="C9" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -8466,10 +8530,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="C10" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -8477,10 +8541,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="C11" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8488,10 +8552,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="C12" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -8499,10 +8563,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="C13" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8510,10 +8574,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="C14" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -8521,10 +8585,10 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="C15" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -8532,10 +8596,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="C16" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>
@@ -8600,10 +8664,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="C4" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -8611,10 +8675,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="C5" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8622,10 +8686,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8633,10 +8697,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="C7" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8644,10 +8708,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="C8" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -8713,10 +8777,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="C4" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:4">
@@ -8724,10 +8788,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:4">
@@ -8735,10 +8799,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:4">
@@ -8746,10 +8810,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:4">
@@ -8757,10 +8821,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:4">
@@ -8768,10 +8832,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:4">
@@ -8779,10 +8843,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:4">
@@ -8790,10 +8854,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:4">
@@ -8801,10 +8865,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:4">
@@ -8812,10 +8876,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
   </sheetData>
@@ -8881,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="C4" t="s">
         <v>119</v>
@@ -8892,7 +8956,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>113</v>
@@ -8903,10 +8967,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8914,10 +8978,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8925,10 +8989,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:4">
@@ -8936,10 +9000,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="C9" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
@@ -9007,13 +9071,13 @@
         <v>100000000</v>
       </c>
       <c r="B4" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="C4" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="D4" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9021,13 +9085,13 @@
         <v>100000001</v>
       </c>
       <c r="B5" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="D5" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -9035,13 +9099,13 @@
         <v>100100001</v>
       </c>
       <c r="B6" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="D6" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -9049,13 +9113,13 @@
         <v>100200001</v>
       </c>
       <c r="B7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D7" t="s">
         <v>1206</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -9063,13 +9127,13 @@
         <v>100200002</v>
       </c>
       <c r="B8" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="C8" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="D8" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -9077,13 +9141,13 @@
         <v>100200003</v>
       </c>
       <c r="B9" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="C9" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="D9" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -9091,13 +9155,13 @@
         <v>100300001</v>
       </c>
       <c r="B10" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="C10" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D10" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -9105,13 +9169,13 @@
         <v>100400001</v>
       </c>
       <c r="B11" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="C11" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="D11" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9119,13 +9183,13 @@
         <v>100401000</v>
       </c>
       <c r="B12" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="C12" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="D12" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -9133,13 +9197,13 @@
         <v>100401001</v>
       </c>
       <c r="B13" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="C13" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="D13" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -9147,13 +9211,13 @@
         <v>100402000</v>
       </c>
       <c r="B14" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="C14" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D14" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -9161,13 +9225,13 @@
         <v>100402001</v>
       </c>
       <c r="B15" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="C15" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="D15" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -9175,13 +9239,13 @@
         <v>100403000</v>
       </c>
       <c r="B16" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="C16" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="D16" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -9189,13 +9253,13 @@
         <v>100403001</v>
       </c>
       <c r="B17" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="C17" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="D17" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9203,13 +9267,13 @@
         <v>100404001</v>
       </c>
       <c r="B18" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="C18" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D18" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -9217,13 +9281,13 @@
         <v>200000001</v>
       </c>
       <c r="B19" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="C19" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="D19" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9231,13 +9295,13 @@
         <v>200100001</v>
       </c>
       <c r="B20" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="C20" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D20" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -9245,13 +9309,13 @@
         <v>300100000</v>
       </c>
       <c r="B21" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="C21" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="D21" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9259,13 +9323,13 @@
         <v>300100001</v>
       </c>
       <c r="B22" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="C22" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D22" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9273,13 +9337,13 @@
         <v>300100002</v>
       </c>
       <c r="B23" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="C23" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D23" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9287,13 +9351,13 @@
         <v>300100003</v>
       </c>
       <c r="B24" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="C24" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="D24" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9301,13 +9365,13 @@
         <v>300100004</v>
       </c>
       <c r="B25" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="C25" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D25" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9315,13 +9379,13 @@
         <v>300100101</v>
       </c>
       <c r="B26" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="C26" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="D26" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9329,13 +9393,13 @@
         <v>300100102</v>
       </c>
       <c r="B27" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="C27" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="D27" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9343,13 +9407,13 @@
         <v>300100201</v>
       </c>
       <c r="B28" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="C28" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="D28" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9357,13 +9421,13 @@
         <v>300100301</v>
       </c>
       <c r="B29" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="C29" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="D29" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9371,13 +9435,13 @@
         <v>300200000</v>
       </c>
       <c r="B30" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="C30" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="D30" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9385,13 +9449,13 @@
         <v>300200001</v>
       </c>
       <c r="B31" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="C31" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D31" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9399,13 +9463,13 @@
         <v>300200002</v>
       </c>
       <c r="B32" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="C32" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="D32" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -9413,13 +9477,13 @@
         <v>300200003</v>
       </c>
       <c r="B33" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="C33" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D33" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -9427,13 +9491,13 @@
         <v>300200004</v>
       </c>
       <c r="B34" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="C34" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="D34" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -9441,13 +9505,13 @@
         <v>300200101</v>
       </c>
       <c r="B35" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="C35" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="D35" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -9455,13 +9519,13 @@
         <v>300200102</v>
       </c>
       <c r="B36" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="C36" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="D36" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -9469,13 +9533,13 @@
         <v>300200201</v>
       </c>
       <c r="B37" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="C37" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D37" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -9483,13 +9547,13 @@
         <v>300200301</v>
       </c>
       <c r="B38" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="C38" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="D38" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -9497,13 +9561,13 @@
         <v>300300000</v>
       </c>
       <c r="B39" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C39" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="D39" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -9511,13 +9575,13 @@
         <v>300300001</v>
       </c>
       <c r="B40" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="C40" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="D40" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -9525,13 +9589,13 @@
         <v>300300002</v>
       </c>
       <c r="B41" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C41" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="D41" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -9539,13 +9603,13 @@
         <v>300300003</v>
       </c>
       <c r="B42" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="C42" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="D42" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -9553,13 +9617,13 @@
         <v>300300004</v>
       </c>
       <c r="B43" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="C43" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="D43" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -9567,13 +9631,13 @@
         <v>300300101</v>
       </c>
       <c r="B44" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="C44" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="D44" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
@@ -9581,13 +9645,13 @@
         <v>300300102</v>
       </c>
       <c r="B45" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="C45" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="D45" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
@@ -9595,13 +9659,13 @@
         <v>300300201</v>
       </c>
       <c r="B46" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="C46" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="D46" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
@@ -9609,13 +9673,13 @@
         <v>300300301</v>
       </c>
       <c r="B47" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="C47" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="D47" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -9623,13 +9687,13 @@
         <v>300400000</v>
       </c>
       <c r="B48" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="C48" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="D48" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -9637,13 +9701,13 @@
         <v>300400001</v>
       </c>
       <c r="B49" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="C49" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="D49" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -9651,13 +9715,13 @@
         <v>300400002</v>
       </c>
       <c r="B50" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="C50" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="D50" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -9665,13 +9729,13 @@
         <v>300400003</v>
       </c>
       <c r="B51" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="C51" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="D51" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -9679,13 +9743,13 @@
         <v>300400004</v>
       </c>
       <c r="B52" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="C52" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="D52" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9693,13 +9757,13 @@
         <v>300400005</v>
       </c>
       <c r="B53" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="C53" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D53" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -9707,13 +9771,13 @@
         <v>300400101</v>
       </c>
       <c r="B54" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="C54" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="D54" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -9721,13 +9785,13 @@
         <v>300400102</v>
       </c>
       <c r="B55" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="C55" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="D55" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -9735,13 +9799,13 @@
         <v>300400201</v>
       </c>
       <c r="B56" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="C56" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="D56" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -9749,13 +9813,13 @@
         <v>300400301</v>
       </c>
       <c r="B57" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="C57" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D57" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -9763,13 +9827,13 @@
         <v>300500000</v>
       </c>
       <c r="B58" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="C58" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D58" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -9777,13 +9841,13 @@
         <v>300500001</v>
       </c>
       <c r="B59" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="C59" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="D59" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -9791,13 +9855,13 @@
         <v>300500002</v>
       </c>
       <c r="B60" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="C60" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="D60" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -9805,13 +9869,13 @@
         <v>300500003</v>
       </c>
       <c r="B61" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="C61" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="D61" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -9819,13 +9883,13 @@
         <v>300500004</v>
       </c>
       <c r="B62" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="C62" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="D62" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -9833,13 +9897,13 @@
         <v>300500101</v>
       </c>
       <c r="B63" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="C63" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="D63" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -9847,13 +9911,13 @@
         <v>300500102</v>
       </c>
       <c r="B64" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="C64" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="D64" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -9861,13 +9925,13 @@
         <v>300500201</v>
       </c>
       <c r="B65" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="C65" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="D65" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -9875,13 +9939,13 @@
         <v>300500301</v>
       </c>
       <c r="B66" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="C66" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="D66" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -9889,13 +9953,13 @@
         <v>300600000</v>
       </c>
       <c r="B67" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="C67" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="D67" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -9903,13 +9967,13 @@
         <v>300600001</v>
       </c>
       <c r="B68" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="C68" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="D68" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -9917,13 +9981,13 @@
         <v>300600002</v>
       </c>
       <c r="B69" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="C69" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D69" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -9931,13 +9995,13 @@
         <v>300600003</v>
       </c>
       <c r="B70" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="C70" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D70" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -9945,13 +10009,13 @@
         <v>300600004</v>
       </c>
       <c r="B71" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="C71" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="D71" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -9959,13 +10023,13 @@
         <v>300600005</v>
       </c>
       <c r="B72" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="C72" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="D72" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -9973,13 +10037,13 @@
         <v>300600101</v>
       </c>
       <c r="B73" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="C73" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="D73" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -9987,13 +10051,13 @@
         <v>300600102</v>
       </c>
       <c r="B74" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="C74" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="D74" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -10001,13 +10065,13 @@
         <v>300600201</v>
       </c>
       <c r="B75" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="C75" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="D75" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -10015,13 +10079,13 @@
         <v>300600301</v>
       </c>
       <c r="B76" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="C76" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="D76" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -10029,13 +10093,13 @@
         <v>300700000</v>
       </c>
       <c r="B77" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="C77" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="D77" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -10043,13 +10107,13 @@
         <v>300700001</v>
       </c>
       <c r="B78" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C78" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="D78" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -10057,13 +10121,13 @@
         <v>300700002</v>
       </c>
       <c r="B79" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="C79" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="D79" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -10071,13 +10135,13 @@
         <v>300700003</v>
       </c>
       <c r="B80" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="C80" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="D80" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -10085,13 +10149,13 @@
         <v>300700004</v>
       </c>
       <c r="B81" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="C81" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="D81" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -10099,13 +10163,13 @@
         <v>300700101</v>
       </c>
       <c r="B82" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="C82" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="D82" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -10113,13 +10177,13 @@
         <v>300700102</v>
       </c>
       <c r="B83" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="C83" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="D83" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -10127,13 +10191,13 @@
         <v>300700201</v>
       </c>
       <c r="B84" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="C84" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="D84" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -10141,13 +10205,13 @@
         <v>300700301</v>
       </c>
       <c r="B85" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="C85" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="D85" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -10555,10 +10619,10 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="11">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="17" t="s">
         <v>268</v>
       </c>
       <c r="C4" t="s">
@@ -10569,10 +10633,10 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="11">
+      <c r="A5" s="17">
         <v>100001</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="17" t="s">
         <v>327</v>
       </c>
       <c r="C5"/>
@@ -10635,7 +10699,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11">
+      <c r="A10" s="17">
         <v>10100005</v>
       </c>
       <c r="B10" t="s">
@@ -10647,7 +10711,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
         <v>10100007</v>
       </c>
       <c r="B11" t="s">
@@ -10659,7 +10723,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="11">
+      <c r="A12" s="17">
         <v>10100008</v>
       </c>
       <c r="B12" t="s">
@@ -10671,7 +10735,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="11">
+      <c r="A13" s="17">
         <v>10100010</v>
       </c>
       <c r="B13" t="s">
@@ -10683,7 +10747,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="11">
+      <c r="A14" s="17">
         <v>10100012</v>
       </c>
       <c r="B14" t="s">
@@ -10695,7 +10759,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="11">
+      <c r="A15" s="17">
         <v>10100013</v>
       </c>
       <c r="B15" t="s">
@@ -10707,7 +10771,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="11">
+      <c r="A16" s="17">
         <v>10100014</v>
       </c>
       <c r="B16" t="s">
@@ -10719,7 +10783,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="11">
+      <c r="A17" s="17">
         <v>10100015</v>
       </c>
       <c r="B17" t="s">
@@ -10731,7 +10795,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="11">
+      <c r="A18" s="17">
         <v>10100016</v>
       </c>
       <c r="B18" t="s">
@@ -10743,7 +10807,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="11">
+      <c r="A19" s="17">
         <v>10100017</v>
       </c>
       <c r="B19" t="s">
@@ -10758,7 +10822,7 @@
       <c r="A20">
         <v>10200001</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="17" t="s">
         <v>345</v>
       </c>
       <c r="C20" t="s">
@@ -10772,7 +10836,7 @@
       <c r="A21">
         <v>10200002</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="17" t="s">
         <v>347</v>
       </c>
       <c r="C21" t="s">
@@ -10786,7 +10850,7 @@
       <c r="A22">
         <v>10200003</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="17" t="s">
         <v>349</v>
       </c>
       <c r="C22" t="s">
@@ -10800,7 +10864,7 @@
       <c r="A23">
         <v>10200004</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="17" t="s">
         <v>351</v>
       </c>
       <c r="C23" t="s">
@@ -10811,10 +10875,10 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="11">
+      <c r="A24" s="17">
         <v>10200005</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="17" t="s">
         <v>353</v>
       </c>
       <c r="C24"/>
@@ -10823,10 +10887,10 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="11">
+      <c r="A25" s="17">
         <v>10200006</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="17" t="s">
         <v>354</v>
       </c>
       <c r="C25"/>
@@ -10835,10 +10899,10 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="11">
+      <c r="A26" s="17">
         <v>10200007</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="17" t="s">
         <v>355</v>
       </c>
       <c r="C26"/>
@@ -10847,10 +10911,10 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="11">
+      <c r="A27" s="17">
         <v>10200008</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="17" t="s">
         <v>356</v>
       </c>
       <c r="C27"/>
@@ -10859,10 +10923,10 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="11">
+      <c r="A28" s="17">
         <v>10200009</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="17" t="s">
         <v>357</v>
       </c>
       <c r="C28"/>
@@ -10871,10 +10935,10 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="11">
+      <c r="A29" s="17">
         <v>10200010</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="17" t="s">
         <v>358</v>
       </c>
       <c r="C29"/>
@@ -10883,10 +10947,10 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="11">
+      <c r="A30" s="17">
         <v>10200011</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="17" t="s">
         <v>359</v>
       </c>
       <c r="C30"/>
@@ -10895,10 +10959,10 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="11">
+      <c r="A31" s="17">
         <v>10200012</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="17" t="s">
         <v>360</v>
       </c>
       <c r="C31"/>
@@ -10907,10 +10971,10 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="11">
+      <c r="A32" s="17">
         <v>10200013</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="17" t="s">
         <v>361</v>
       </c>
       <c r="C32"/>
@@ -10919,10 +10983,10 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="11">
+      <c r="A33" s="17">
         <v>10200014</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="17" t="s">
         <v>362</v>
       </c>
       <c r="C33"/>
@@ -10931,10 +10995,10 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="11">
+      <c r="A34" s="17">
         <v>10200015</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="17" t="s">
         <v>363</v>
       </c>
       <c r="C34"/>
@@ -10943,10 +11007,10 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="11">
+      <c r="A35" s="17">
         <v>10200016</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="17" t="s">
         <v>364</v>
       </c>
       <c r="C35"/>
@@ -10955,10 +11019,10 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="11">
+      <c r="A36" s="17">
         <v>10200017</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="17" t="s">
         <v>365</v>
       </c>
       <c r="C36"/>
@@ -10970,7 +11034,7 @@
       <c r="A37">
         <v>10300001</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="17" t="s">
         <v>366</v>
       </c>
       <c r="C37" t="s">
@@ -10984,7 +11048,7 @@
       <c r="A38">
         <v>10300002</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="17" t="s">
         <v>368</v>
       </c>
       <c r="C38" t="s">
@@ -10998,7 +11062,7 @@
       <c r="A39">
         <v>10300003</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="17" t="s">
         <v>370</v>
       </c>
       <c r="C39" t="s">
@@ -11012,7 +11076,7 @@
       <c r="A40">
         <v>10300004</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="17" t="s">
         <v>372</v>
       </c>
       <c r="C40" t="s">
@@ -11026,7 +11090,7 @@
       <c r="A41">
         <v>10300005</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="17" t="s">
         <v>374</v>
       </c>
       <c r="C41"/>
@@ -11038,7 +11102,7 @@
       <c r="A42">
         <v>10300006</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="17" t="s">
         <v>375</v>
       </c>
       <c r="C42"/>
@@ -11050,7 +11114,7 @@
       <c r="A43">
         <v>10300007</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="17" t="s">
         <v>376</v>
       </c>
       <c r="C43"/>
@@ -11062,7 +11126,7 @@
       <c r="A44">
         <v>10300008</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="17" t="s">
         <v>377</v>
       </c>
       <c r="C44"/>
@@ -11074,7 +11138,7 @@
       <c r="A45">
         <v>10300009</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="17" t="s">
         <v>378</v>
       </c>
       <c r="C45"/>
@@ -11086,7 +11150,7 @@
       <c r="A46">
         <v>10300010</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="17" t="s">
         <v>379</v>
       </c>
       <c r="C46"/>
@@ -11098,7 +11162,7 @@
       <c r="A47">
         <v>10300011</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="17" t="s">
         <v>380</v>
       </c>
       <c r="C47"/>
@@ -11110,7 +11174,7 @@
       <c r="A48">
         <v>10300012</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="17" t="s">
         <v>381</v>
       </c>
       <c r="C48"/>
@@ -11122,7 +11186,7 @@
       <c r="A49">
         <v>10300013</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="17" t="s">
         <v>382</v>
       </c>
       <c r="C49"/>
@@ -11134,7 +11198,7 @@
       <c r="A50">
         <v>10300014</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="17" t="s">
         <v>383</v>
       </c>
       <c r="C50"/>
@@ -11146,7 +11210,7 @@
       <c r="A51">
         <v>10300015</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="17" t="s">
         <v>384</v>
       </c>
       <c r="C51"/>
@@ -11158,7 +11222,7 @@
       <c r="A52">
         <v>10300016</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="17" t="s">
         <v>385</v>
       </c>
       <c r="C52"/>
@@ -11170,7 +11234,7 @@
       <c r="A53">
         <v>10300017</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="17" t="s">
         <v>386</v>
       </c>
       <c r="C53"/>
@@ -11179,7 +11243,7 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>11000001</v>
       </c>
       <c r="B54" t="s">
@@ -11193,7 +11257,7 @@
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="11">
+      <c r="A55" s="17">
         <v>11000002</v>
       </c>
       <c r="B55" t="s">
@@ -11207,7 +11271,7 @@
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="11">
+      <c r="A56" s="17">
         <v>11000003</v>
       </c>
       <c r="B56" t="s">
@@ -11221,7 +11285,7 @@
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="11">
+      <c r="A57" s="17">
         <v>11000004</v>
       </c>
       <c r="B57" t="s">
@@ -11235,7 +11299,7 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="11">
+      <c r="A58" s="17">
         <v>11000005</v>
       </c>
       <c r="B58" t="s">
@@ -11249,7 +11313,7 @@
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="11">
+      <c r="A59" s="17">
         <v>11000006</v>
       </c>
       <c r="B59" t="s">
@@ -11263,7 +11327,7 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="11">
+      <c r="A60" s="17">
         <v>11000007</v>
       </c>
       <c r="B60" t="s">
@@ -11277,7 +11341,7 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="11">
+      <c r="A61" s="17">
         <v>11000008</v>
       </c>
       <c r="B61" t="s">
@@ -11291,7 +11355,7 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="11">
+      <c r="A62" s="17">
         <v>11000009</v>
       </c>
       <c r="B62" t="s">
@@ -11305,7 +11369,7 @@
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="11">
+      <c r="A63" s="17">
         <v>11000010</v>
       </c>
       <c r="B63" t="s">
@@ -11317,10 +11381,10 @@
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="11">
+      <c r="A64" s="17">
         <v>11000011</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="17" t="s">
         <v>405</v>
       </c>
       <c r="C64"/>
@@ -11329,10 +11393,10 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="11">
+      <c r="A65" s="17">
         <v>11000012</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="17" t="s">
         <v>406</v>
       </c>
       <c r="C65"/>
@@ -11341,10 +11405,10 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="11">
+      <c r="A66" s="17">
         <v>11000013</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="17" t="s">
         <v>407</v>
       </c>
       <c r="C66"/>
@@ -11353,7 +11417,7 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="11">
+      <c r="A67" s="17">
         <v>11010001</v>
       </c>
       <c r="B67" t="s">
@@ -11367,7 +11431,7 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="11">
+      <c r="A68" s="17">
         <v>11010002</v>
       </c>
       <c r="B68" t="s">
@@ -11379,7 +11443,7 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="11">
+      <c r="A69" s="17">
         <v>11010003</v>
       </c>
       <c r="B69" t="s">
@@ -11391,7 +11455,7 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="11">
+      <c r="A70" s="17">
         <v>11020021</v>
       </c>
       <c r="B70" t="s">
@@ -11403,7 +11467,7 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="11">
+      <c r="A71" s="17">
         <v>11020022</v>
       </c>
       <c r="B71" t="s">
@@ -11667,7 +11731,7 @@
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="11">
+      <c r="A90" s="17">
         <v>20300001</v>
       </c>
       <c r="B90" t="s">
@@ -11681,7 +11745,7 @@
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="11">
+      <c r="A91" s="17">
         <v>20300003</v>
       </c>
       <c r="B91" t="s">
@@ -11695,7 +11759,7 @@
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="11">
+      <c r="A92" s="17">
         <v>20300007</v>
       </c>
       <c r="B92" t="s">
@@ -11709,7 +11773,7 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="11">
+      <c r="A93" s="17">
         <v>20300009</v>
       </c>
       <c r="B93" t="s">
@@ -11723,7 +11787,7 @@
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="11">
+      <c r="A94" s="17">
         <v>20300011</v>
       </c>
       <c r="B94" t="s">
@@ -14075,7 +14139,7 @@
       <c r="A23">
         <v>12001100001</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="18" t="s">
         <v>747</v>
       </c>
       <c r="C23" t="s">
@@ -14095,7 +14159,7 @@
       <c r="A24">
         <v>12001200001</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="18" t="s">
         <v>751</v>
       </c>
       <c r="C24" t="s">
@@ -14115,7 +14179,7 @@
       <c r="A25">
         <v>12001300001</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="18" t="s">
         <v>755</v>
       </c>
       <c r="C25" t="s">
@@ -14135,7 +14199,7 @@
       <c r="A26">
         <v>12001400001</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="18" t="s">
         <v>759</v>
       </c>
       <c r="C26" t="s">
@@ -14155,10 +14219,10 @@
       <c r="A27">
         <v>12002100001</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="18" t="s">
         <v>763</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="19" t="s">
         <v>764</v>
       </c>
       <c r="D27" t="s">
@@ -14175,10 +14239,10 @@
       <c r="A28">
         <v>12002200001</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="19" t="s">
         <v>768</v>
       </c>
       <c r="D28" t="s">
@@ -14195,10 +14259,10 @@
       <c r="A29">
         <v>12002300001</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="18" t="s">
         <v>771</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="19" t="s">
         <v>772</v>
       </c>
       <c r="D29" t="s">
@@ -14215,10 +14279,10 @@
       <c r="A30">
         <v>12002400001</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="18" t="s">
         <v>775</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="19" t="s">
         <v>776</v>
       </c>
       <c r="D30" t="s">
@@ -14235,10 +14299,10 @@
       <c r="A31">
         <v>12003100001</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="18" t="s">
         <v>779</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="19" t="s">
         <v>780</v>
       </c>
       <c r="D31" t="s">
@@ -14255,10 +14319,10 @@
       <c r="A32">
         <v>12003200001</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="18" t="s">
         <v>783</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="19" t="s">
         <v>784</v>
       </c>
       <c r="D32" t="s">
@@ -14275,10 +14339,10 @@
       <c r="A33">
         <v>12003300001</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="19" t="s">
         <v>788</v>
       </c>
       <c r="D33" t="s">
@@ -14295,10 +14359,10 @@
       <c r="A34">
         <v>12003400001</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="18" t="s">
         <v>791</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="19" t="s">
         <v>792</v>
       </c>
       <c r="D34" t="s">
@@ -14315,10 +14379,10 @@
       <c r="A35">
         <v>12010100001</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="19" t="s">
         <v>796</v>
       </c>
       <c r="D35" t="s">
@@ -14335,10 +14399,10 @@
       <c r="A36">
         <v>12010200001</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="19" t="s">
         <v>799</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="19" t="s">
         <v>800</v>
       </c>
       <c r="D36" t="s">
@@ -14355,10 +14419,10 @@
       <c r="A37">
         <v>12010300001</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="19" t="s">
         <v>803</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="19" t="s">
         <v>804</v>
       </c>
       <c r="D37" t="s">
@@ -14375,10 +14439,10 @@
       <c r="A38">
         <v>12011100001</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="19" t="s">
         <v>807</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="19" t="s">
         <v>808</v>
       </c>
       <c r="D38" t="s">
@@ -14395,10 +14459,10 @@
       <c r="A39">
         <v>12011200001</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="19" t="s">
         <v>811</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="19" t="s">
         <v>812</v>
       </c>
       <c r="D39" t="s">
@@ -14415,10 +14479,10 @@
       <c r="A40">
         <v>12011300001</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="19" t="s">
         <v>815</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="19" t="s">
         <v>816</v>
       </c>
       <c r="D40" t="s">
@@ -14647,7 +14711,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="11">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
       <c r="B4" t="s">
@@ -14667,7 +14731,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="11">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
       <c r="B5" t="s">
@@ -14687,7 +14751,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="11">
+      <c r="A6" s="17">
         <v>1000000001</v>
       </c>
       <c r="B6" t="s">
@@ -14707,7 +14771,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="11">
+      <c r="A7" s="17">
         <v>1000100001</v>
       </c>
       <c r="B7" t="s">
@@ -14727,7 +14791,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="11">
+      <c r="A8" s="17">
         <v>1000200001</v>
       </c>
       <c r="B8" t="s">
@@ -14747,7 +14811,7 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>1000200002</v>
       </c>
       <c r="B9" t="s">
@@ -14767,7 +14831,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="11">
+      <c r="A10" s="17">
         <v>1000200003</v>
       </c>
       <c r="B10" t="s">
@@ -14787,7 +14851,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
         <v>1000200004</v>
       </c>
       <c r="B11" t="s">
@@ -14807,7 +14871,7 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="11">
+      <c r="A12" s="17">
         <v>1000200005</v>
       </c>
       <c r="B12" t="s">
@@ -14827,7 +14891,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="11">
+      <c r="A13" s="17">
         <v>1000200006</v>
       </c>
       <c r="B13" t="s">
@@ -14847,7 +14911,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="11">
+      <c r="A14" s="17">
         <v>1000200007</v>
       </c>
       <c r="B14" t="s">
@@ -15345,7 +15409,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -15495,566 +15559,602 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="12">
+      <c r="A11" s="16">
         <v>1001</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="16" t="s">
         <v>957</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="16" t="s">
         <v>958</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="12">
+      <c r="A12" s="16">
         <v>1002</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="16" t="s">
         <v>959</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="16" t="s">
         <v>960</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="12">
+      <c r="A13" s="16">
         <v>1003</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="16" t="s">
         <v>961</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="16" t="s">
         <v>962</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="12">
+      <c r="A14" s="16">
         <v>1004</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="16" t="s">
         <v>964</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="12">
+      <c r="A15" s="16">
         <v>2001</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="16" t="s">
         <v>965</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="16" t="s">
         <v>966</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="12">
+      <c r="A16" s="16">
         <v>2002</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="16" t="s">
         <v>967</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="16" t="s">
         <v>968</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12">
+      <c r="A17" s="16">
         <v>2003</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="16" t="s">
         <v>969</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="16" t="s">
         <v>970</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12">
+      <c r="A18" s="16">
         <v>2004</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="16" t="s">
         <v>971</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="16" t="s">
         <v>972</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12">
+      <c r="A19" s="16">
         <v>3001</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="16" t="s">
         <v>973</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="16" t="s">
         <v>974</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12">
+      <c r="A20" s="16">
         <v>3002</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="16" t="s">
         <v>975</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="16" t="s">
         <v>976</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12">
+      <c r="A21" s="16">
         <v>3003</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="16" t="s">
         <v>977</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="16" t="s">
         <v>978</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12">
+      <c r="A22" s="16">
         <v>3004</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="16" t="s">
         <v>979</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="16" t="s">
         <v>980</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12">
+      <c r="A23" s="16">
         <v>4001</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="16" t="s">
         <v>981</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="16" t="s">
         <v>982</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12">
+      <c r="A24" s="16">
         <v>4002</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="16" t="s">
         <v>983</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="16" t="s">
         <v>984</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12">
+      <c r="A25" s="16">
         <v>4003</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="16" t="s">
         <v>985</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="16" t="s">
         <v>986</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12">
+      <c r="A26" s="16">
         <v>4004</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="16" t="s">
         <v>987</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="16" t="s">
         <v>988</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12">
+      <c r="A27" s="16">
         <v>4005</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="16" t="s">
         <v>989</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="16" t="s">
         <v>990</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="12">
+      <c r="A28" s="16">
         <v>5001</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="16" t="s">
         <v>991</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="16" t="s">
         <v>992</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="12">
+      <c r="A29" s="16">
         <v>5002</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="16" t="s">
         <v>993</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="16" t="s">
         <v>994</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12">
+      <c r="A30" s="16">
         <v>5003</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="16" t="s">
         <v>995</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="16" t="s">
         <v>996</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12">
+      <c r="A31" s="16">
         <v>5004</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="16" t="s">
         <v>997</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="16" t="s">
         <v>998</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12">
+      <c r="A32" s="16">
         <v>6001</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="16" t="s">
         <v>999</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="16" t="s">
         <v>1000</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12">
+      <c r="A33" s="16">
         <v>6002</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="16" t="s">
         <v>1001</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="16" t="s">
         <v>1002</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="12">
+      <c r="A34" s="16">
         <v>6003</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="16" t="s">
         <v>1003</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="16" t="s">
         <v>1004</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12">
+      <c r="A35" s="16">
         <v>6004</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="16" t="s">
         <v>1005</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="16" t="s">
         <v>1006</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12">
+      <c r="A36" s="16">
         <v>6005</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="16" t="s">
         <v>1007</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="16" t="s">
         <v>1008</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12">
+      <c r="A37" s="16">
         <v>7001</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="16" t="s">
         <v>1009</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="16" t="s">
         <v>1010</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12">
+      <c r="A38" s="16">
         <v>7002</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="16" t="s">
         <v>1011</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="16" t="s">
         <v>1012</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12">
+      <c r="A39" s="16">
         <v>7003</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="16" t="s">
         <v>1013</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="16" t="s">
         <v>1014</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12">
+      <c r="A40" s="16">
         <v>7004</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="16" t="s">
         <v>1015</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="16" t="s">
         <v>1016</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="16" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="13">
+      <c r="A41" s="12">
         <v>101001</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>958</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>101002</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="15" t="s">
         <v>1018</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13" t="s">
+      <c r="C42" s="12"/>
+      <c r="D42" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13">
+      <c r="A43" s="12">
         <v>102001</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="12" t="s">
         <v>1019</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="14">
+      <c r="A44" s="15">
         <v>102002</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13" t="s">
+      <c r="C44" s="12"/>
+      <c r="D44" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="14">
+      <c r="A45" s="15">
         <v>102003</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13" t="s">
+      <c r="C45" s="12"/>
+      <c r="D45" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="13">
+      <c r="A46" s="12">
         <v>103001</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>962</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="13">
+      <c r="A47" s="12">
         <v>103002</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13">
+      <c r="A48" s="12">
         <v>103003</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="15" t="s">
         <v>1025</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13" t="s">
+      <c r="C48" s="12"/>
+      <c r="D48" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13">
+      <c r="A49" s="12">
         <v>103004</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="15" t="s">
         <v>1026</v>
       </c>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13" t="s">
+      <c r="C49" s="12"/>
+      <c r="D49" s="12" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50">
+      <c r="A50" s="15">
+        <v>103101</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="15">
+        <v>103102</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="15">
+        <v>103103</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
         <v>900001</v>
       </c>
-      <c r="B50" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="B53" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D53" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51">
+    <row r="54" spans="1:4">
+      <c r="A54">
         <v>900002</v>
       </c>
-      <c r="B51" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="B54" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D54" t="s">
         <v>944</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -8304,7 +8304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -8900,6 +8900,156 @@
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2000005001</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>慢条斯理Lv.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sloth Lv.1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低10%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -10%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2000005002</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>慢条斯理Lv.2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sloth Lv.2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低20%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -20%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2000005003</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>慢条斯理Lv.3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sloth Lv.3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低30%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -30%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2000005004</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>慢条斯理Lv.4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sloth Lv.4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低40%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -40%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2000005005</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>慢条斯理Lv.5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sloth Lv.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低50%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -50%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
@@ -13584,7 +13734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="35.375" customWidth="1" style="1" min="1" max="1"/>
@@ -14054,30 +14204,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>伤害性极强</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>Overwhelming Damage</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>所有魔物攻击力增加{Percentage}%</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>All demons gain {Percentage}% ATK</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
@@ -15000,6 +15150,36 @@
       <c r="D48" s="0" t="n"/>
       <c r="E48" s="0" t="n"/>
       <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>慢条斯理</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sloth</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>敌方进攻生物移动速度降低{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Enemy attackers' MSPD -{Percentage}%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -3405,20 +3405,20 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="0" t="n">
         <v>55007</v>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -4393,16 +4393,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000001</v>
+        <v>2000011</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>Sort: Type</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4413,16 +4413,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Reputation!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4433,16 +4433,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4453,16 +4453,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4473,16 +4473,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4493,16 +4493,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4513,16 +4513,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4533,16 +4533,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4553,16 +4553,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4573,16 +4573,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4593,16 +4593,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4613,16 +4613,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Difficulty {0}</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4633,19 +4633,39 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>{0}h {1}m</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B177" s="0" t="inlineStr">
+      <c r="B178" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="C177" s="0" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>Total Clears</t>
         </is>
       </c>
-      <c r="D177" s="0" t="inlineStr">
+      <c r="D178" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -6924,7 +6944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7060,20 +7080,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>Unlock Council of Doom</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="A7" t="n">
+        <v>100100002</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>献祭祭品数量+1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sacrifice Fodder +1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
@@ -7081,16 +7101,16 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon Renaming</t>
+          <t>Unlock Council of Doom</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -7101,16 +7121,16 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon King Renaming</t>
+          <t>Council: Demon Renaming</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -7121,16 +7141,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>100300001</v>
+        <v>100200003</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Portal: +1 World Choice</t>
+          <t>Council: Demon King Renaming</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -7141,11 +7161,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>100400000</v>
+        <v>100300001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>传送门可选择世界+1</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Portal: +1 World Choice</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -7156,16 +7181,11 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>Incubation Skip</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -7176,16 +7196,16 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Unlock R Rarity Incubation</t>
+          <t>Incubation Skip</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -7196,16 +7216,16 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>R Rarity Rate +1%</t>
+          <t>Unlock R Rarity Incubation</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -7216,16 +7236,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>R Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7236,16 +7256,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>SR Rarity Rate +1%</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -7256,16 +7276,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Unlock SSR Rarity Incubation</t>
+          <t>SR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7276,16 +7296,16 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>SSR Rarity Rate +1%</t>
+          <t>Unlock SSR Rarity Incubation</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7296,16 +7316,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>100404001</v>
+        <v>100403001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>SSR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -7316,16 +7336,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>200000001</v>
+        <v>100404001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Team Limit +1</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -7336,16 +7356,16 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>解锁一个新阵容</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Unlock New Team</t>
+          <t>Team Limit +1</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -7356,16 +7376,16 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>300100000</v>
+        <v>200100001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>解锁一个新阵容</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Unlock New Team</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -7376,16 +7396,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -7396,16 +7416,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -7416,16 +7436,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -7436,16 +7456,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -7456,16 +7476,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -7476,16 +7496,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -7496,16 +7516,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -7516,16 +7536,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -7536,16 +7556,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300200000</v>
+        <v>300100301</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -7556,16 +7576,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -7576,16 +7596,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -7596,16 +7616,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -7616,16 +7636,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -7636,16 +7656,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -7656,16 +7676,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -7676,16 +7696,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -7696,16 +7716,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -7716,16 +7736,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300300000</v>
+        <v>300200301</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -7736,16 +7756,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -7756,16 +7776,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -7776,16 +7796,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -7796,16 +7816,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -7816,16 +7836,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -7836,16 +7856,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -7856,16 +7876,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -7876,16 +7896,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -7896,16 +7916,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300400000</v>
+        <v>300300301</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -7916,16 +7936,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -7936,16 +7956,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -7956,16 +7976,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -7976,16 +7996,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -7996,16 +8016,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8016,16 +8036,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8036,16 +8056,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8056,16 +8076,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8076,16 +8096,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8096,16 +8116,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300500000</v>
+        <v>300400301</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8116,16 +8136,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8136,16 +8156,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8156,16 +8176,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8176,16 +8196,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8196,16 +8216,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8216,16 +8236,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8236,16 +8256,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8256,16 +8276,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8276,16 +8296,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300600000</v>
+        <v>300500301</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8296,16 +8316,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8316,16 +8336,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8336,16 +8356,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8356,16 +8376,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8376,16 +8396,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -8396,16 +8416,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -8416,16 +8436,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -8436,16 +8456,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -8456,16 +8476,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -8476,16 +8496,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300700000</v>
+        <v>300600301</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -8496,16 +8516,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -8516,16 +8536,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -8536,16 +8556,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -8556,16 +8576,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -8576,16 +8596,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Class: Orc Ice Mage</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -8596,16 +8616,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Incubate Orcs x5</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -8616,16 +8636,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Incubate Orcs x10</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -8636,16 +8656,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>终焉议会议案：转生兽人</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Council: Reincarnate as Orc</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -8656,14 +8676,34 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B87" s="0" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C87" s="0" t="inlineStr"/>
+      <c r="C88" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -6944,7 +6944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7080,60 +7080,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>100100002</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>献祭祭品数量+1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Sacrifice Fodder +1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n">
-        <v>100200001</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>开启终焉议会</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>Unlock Council of Doom</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="A8" t="n">
+        <v>100100003</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>献祭失败保底概率提升</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sacrifice Fail Pity Up</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n">
-        <v>100200002</v>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>终焉议会议案：魔物重命名</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>Council: Demon Renaming</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="A9" t="n">
+        <v>100100004</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>不同魔物献祭成功率提升</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cross-species Sacrifice Rate Up</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
@@ -7141,16 +7141,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon King Renaming</t>
+          <t>Unlock Council of Doom</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -7161,16 +7161,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Portal: +1 World Choice</t>
+          <t>Council: Demon Renaming</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -7181,11 +7181,16 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>100400000</v>
+        <v>100200003</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>终焉议会议案：魔王重命名</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Council: Demon King Renaming</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -7196,16 +7201,16 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>100400001</v>
+        <v>100300001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Incubation Skip</t>
+          <t>Portal: +1 World Choice</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -7216,16 +7221,11 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>Unlock R Rarity Incubation</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -7236,16 +7236,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>R Rarity Rate +1%</t>
+          <t>Incubation Skip</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7256,16 +7256,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>Unlock R Rarity Incubation</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -7276,16 +7276,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>SR Rarity Rate +1%</t>
+          <t>R Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7296,16 +7296,16 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Unlock SSR Rarity Incubation</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7316,16 +7316,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>SSR Rarity Rate +1%</t>
+          <t>SR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -7336,16 +7336,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>100404001</v>
+        <v>100403000</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>Unlock SSR Rarity Incubation</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -7356,16 +7356,16 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Team Limit +1</t>
+          <t>SSR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -7376,16 +7376,16 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>200100001</v>
+        <v>100404001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>解锁一个新阵容</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Unlock New Team</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -7396,16 +7396,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Team Limit +1</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -7416,16 +7416,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁一个新阵容</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Unlock New Team</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -7436,16 +7436,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -7456,16 +7456,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -7476,16 +7476,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -7496,16 +7496,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -7516,16 +7516,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -7536,16 +7536,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -7556,16 +7556,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -7576,16 +7576,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -7596,16 +7596,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -7616,16 +7616,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -7636,16 +7636,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -7656,16 +7656,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -7676,16 +7676,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -7696,16 +7696,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -7716,16 +7716,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -7736,16 +7736,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -7756,16 +7756,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -7776,16 +7776,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -7796,16 +7796,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -7816,16 +7816,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -7836,16 +7836,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -7856,16 +7856,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -7876,16 +7876,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -7896,16 +7896,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -7916,16 +7916,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -7936,16 +7936,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -7956,16 +7956,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -7976,16 +7976,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -7996,16 +7996,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8016,16 +8016,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8036,16 +8036,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8056,16 +8056,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8076,16 +8076,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8096,16 +8096,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8116,16 +8116,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8136,16 +8136,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8156,16 +8156,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8176,16 +8176,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8196,16 +8196,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8216,16 +8216,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8236,16 +8236,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8256,16 +8256,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8276,16 +8276,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8296,16 +8296,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8316,16 +8316,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8336,16 +8336,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8356,16 +8356,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8376,16 +8376,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8396,16 +8396,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -8416,16 +8416,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -8436,16 +8436,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -8456,16 +8456,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -8476,16 +8476,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -8496,16 +8496,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -8516,16 +8516,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -8536,16 +8536,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -8556,16 +8556,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -8576,16 +8576,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -8596,16 +8596,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -8616,16 +8616,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -8636,16 +8636,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Unlock Class: Orc Ice Mage</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -8656,16 +8656,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Incubate Orcs x5</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -8676,16 +8676,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Incubate Orcs x10</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -8696,14 +8696,54 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>终焉议会议案：转生兽人</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>Council: Reincarnate as Orc</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B88" s="0" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C88" s="0" t="inlineStr"/>
+      <c r="C90" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2830,20 +2830,20 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="0" t="n">
-        <v>50101</v>
-      </c>
-      <c r="B85" s="0" t="inlineStr">
-        <is>
-          <t>继续</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="inlineStr">
-        <is>
-          <t>Continue</t>
-        </is>
-      </c>
-      <c r="D85" s="0" t="inlineStr">
+      <c r="A85" t="n">
+        <v>50006</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>魔力不足</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Not enough mana</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -2851,16 +2851,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>51001</v>
+        <v>50101</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Abyssal Blessing</t>
+          <t>Continue</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -2871,16 +2871,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>51002</v>
+        <v>51001</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Choose an Abyssal Blessing</t>
+          <t>Abyssal Blessing</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -2891,16 +2891,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>51003</v>
+        <v>51002</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Choose an Abyssal Blessing</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -2911,16 +2911,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>52001</v>
+        <v>51003</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>Select Reward</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -2931,16 +2931,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>52002</v>
+        <v>52001</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Select Reward</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -2951,16 +2951,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>52003</v>
+        <v>52002</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>Choices Left: {0}/{1}</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2971,16 +2971,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>52004</v>
+        <v>52003</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>No Choices Left</t>
+          <t>Choices Left: {0}/{1}</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -2991,16 +2991,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>52005</v>
+        <v>52004</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>Still have choices! End selection?</t>
+          <t>No Choices Left</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -3011,16 +3011,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>53000</v>
+        <v>52005</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Doom Council</t>
+          <t>Still have choices! End selection?</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -3031,16 +3031,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>53001</v>
+        <v>53000</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>Select a Proposal</t>
+          <t>Doom Council</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -3051,16 +3051,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>53002</v>
+        <v>53001</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Submit '{0}' to Council of Doom?</t>
+          <t>Select a Proposal</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -3071,16 +3071,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>53003</v>
+        <v>53002</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>Pass Rate: {0}%</t>
+          <t>Submit '{0}' to Council of Doom?</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -3091,16 +3091,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53004</v>
+        <v>53003</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>Start Voting</t>
+          <t>Pass Rate: {0}%</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -3111,16 +3111,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53005</v>
+        <v>53004</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>Leave Council</t>
+          <t>Start Voting</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -3131,16 +3131,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53006</v>
+        <v>53005</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>Aye</t>
+          <t>Leave Council</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -3151,16 +3151,16 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53007</v>
+        <v>53006</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>Nay</t>
+          <t>Aye</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -3171,16 +3171,16 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53008</v>
+        <v>53007</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Nay</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -3191,16 +3191,16 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53009</v>
+        <v>53008</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -3211,16 +3211,16 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53010</v>
+        <v>53009</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>Violent Persuasion</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -3231,16 +3231,16 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53011</v>
+        <v>53010</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>Free Time</t>
+          <t>Violent Persuasion</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -3251,16 +3251,16 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53012</v>
+        <v>53011</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>Submit Proposal '{0}'?</t>
+          <t>Free Time</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -3271,11 +3271,16 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>是否提交议案《{0}》？</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>Submit Proposal '{0}'?</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -3286,16 +3291,11 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>Demon Lord slayers are approaching...</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3306,16 +3306,16 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>A horde of heroes is approaching...</t>
+          <t>Demon Lord slayers are approaching...</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3326,16 +3326,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>Warning! A hero party is swarming in...</t>
+          <t>A horde of heroes is approaching...</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3346,16 +3346,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>Subjugation forces detected approaching...</t>
+          <t>Warning! A hero party is swarming in...</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3366,16 +3366,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>The Allied Hero Army is closing in...</t>
+          <t>Subjugation forces detected approaching...</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3386,16 +3386,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>A horde of self-proclaimed heroes has arrived...</t>
+          <t>The Allied Hero Army is closing in...</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3406,16 +3406,16 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>Alert: Allies of justice are approaching...</t>
+          <t>A horde of self-proclaimed heroes has arrived...</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3426,16 +3426,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Upgrade</t>
+          <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3446,16 +3446,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>Begin Sacrifice</t>
+          <t>Sacrifice Upgrade</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3466,16 +3466,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>Success Rate</t>
+          <t>Begin Sacrifice</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3486,16 +3486,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>Select Sacrifice First!</t>
+          <t>Success Rate</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3506,16 +3506,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>Too Many Sacrifices!</t>
+          <t>Select Sacrifice First!</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3526,16 +3526,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>Start Sacrifice? Current Rate: {0}</t>
+          <t>Too Many Sacrifices!</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3546,16 +3546,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>62001</v>
+        <v>61003</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Research for x{0} Magic Crystals?</t>
+          <t>Start Sacrifice? Current Rate: {0}</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3566,16 +3566,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>62002</v>
+        <v>61004</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Allocate All Points First!</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3586,16 +3586,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>62003</v>
+        <v>61005</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Points Left: {0}</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3606,16 +3606,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>62004</v>
+        <v>62001</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Research for x{0} Magic Crystals?</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3626,16 +3626,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>63001</v>
+        <v>62002</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Select Rebirth Appearance</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3646,16 +3646,16 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>63002</v>
+        <v>62003</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3666,16 +3666,16 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>63003</v>
+        <v>62004</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Confirm Rebirth with this look?</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3686,14 +3686,18 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>64001</v>
+        <v>63001</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
-        </is>
-      </c>
-      <c r="C128" s="0" t="n"/>
+          <t>选择转生魔王外观</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>Select Rebirth Appearance</t>
+        </is>
+      </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3702,14 +3706,18 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>64002</v>
+        <v>63002</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="C129" s="0" t="n"/>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3718,16 +3726,16 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Bribe</t>
+          <t>Confirm Rebirth with this look?</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3738,18 +3746,14 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>80001</v>
+        <v>64001</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
-        </is>
-      </c>
-      <c r="C131" s="0" t="inlineStr">
-        <is>
-          <t>Start Evolution</t>
-        </is>
-      </c>
+          <t>成就</t>
+        </is>
+      </c>
+      <c r="C131" s="0" t="n"/>
       <c r="D131" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3758,18 +3762,14 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>80002</v>
+        <v>64002</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
-        </is>
-      </c>
-      <c r="C132" s="0" t="inlineStr">
-        <is>
-          <t>End Evolution</t>
-        </is>
-      </c>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="C132" s="0" t="n"/>
       <c r="D132" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3778,16 +3778,16 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>80003</v>
+        <v>70001</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>Complete Evolution</t>
+          <t>Bribe</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3798,16 +3798,16 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>80004</v>
+        <v>80001</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>End Evolution? Materials won't be refunded!</t>
+          <t>Start Evolution</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3818,16 +3818,16 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>80005</v>
+        <v>80002</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>End Evolution</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3838,16 +3838,16 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>80006</v>
+        <v>80003</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>Select Evolution Target</t>
+          <t>Complete Evolution</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3858,16 +3858,16 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80007</v>
+        <v>80004</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>Select Support Demon</t>
+          <t>End Evolution? Materials won't be refunded!</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3878,16 +3878,16 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80008</v>
+        <v>80005</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3898,16 +3898,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80009</v>
+        <v>80006</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>Speed Up x{0}</t>
+          <t>Select Evolution Target</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3918,16 +3918,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80010</v>
+        <v>80007</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+          <t>Select Support Demon</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3938,11 +3938,16 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>90001</v>
+        <v>80008</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>还未选择魔物</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>No Demon Selected</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3953,11 +3958,16 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>90002</v>
+        <v>80009</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
+          <t>加速进阶 x{0}</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>Speed Up x{0}</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3968,16 +3978,16 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>1000001</v>
+        <v>80010</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3988,16 +3998,11 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>1000002</v>
+        <v>90001</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C144" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
@@ -4008,16 +4013,11 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>1001001</v>
+        <v>90002</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
-        </is>
-      </c>
-      <c r="C145" s="0" t="inlineStr">
-        <is>
-          <t>Lv.{0}</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
@@ -4028,16 +4028,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>1002001</v>
+        <v>1000001</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -4048,16 +4048,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>1002002</v>
+        <v>1000002</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -4068,16 +4068,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>1003001</v>
+        <v>1001001</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -4088,16 +4088,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1003002</v>
+        <v>1002001</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -4108,16 +4108,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1004001</v>
+        <v>1002002</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4128,16 +4128,16 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1004002</v>
+        <v>1003001</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -4148,16 +4148,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1005001</v>
+        <v>1003002</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -4168,16 +4168,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1005002</v>
+        <v>1004001</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -4188,16 +4188,16 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1005003</v>
+        <v>1004002</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -4208,16 +4208,16 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>2000001</v>
+        <v>1005001</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -4228,16 +4228,16 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>2000002</v>
+        <v>1005002</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -4248,16 +4248,16 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>2000003</v>
+        <v>1005003</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -4268,16 +4268,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>2000004</v>
+        <v>2000001</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -4288,16 +4288,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>2000005</v>
+        <v>2000002</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -4308,16 +4308,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>2000006</v>
+        <v>2000003</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Sort: Team</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4328,16 +4328,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000007</v>
+        <v>2000004</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4348,11 +4348,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000008</v>
+        <v>2000005</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：等级</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4363,11 +4368,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000009</v>
+        <v>2000006</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：阵容</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Team</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4378,11 +4388,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000010</v>
+        <v>2000007</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4393,16 +4408,11 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000011</v>
+        <v>2000008</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
-        </is>
-      </c>
-      <c r="C165" s="0" t="inlineStr">
-        <is>
-          <t>Sort: Type</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4413,16 +4423,11 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000001</v>
+        <v>2000009</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
-        </is>
-      </c>
-      <c r="C166" s="0" t="inlineStr">
-        <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4433,16 +4438,11 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000002</v>
+        <v>2000010</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
-        </is>
-      </c>
-      <c r="C167" s="0" t="inlineStr">
-        <is>
-          <t>Not Enough Reputation!</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4453,16 +4453,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000003</v>
+        <v>2000011</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Sort: Type</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4473,16 +4473,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000004</v>
+        <v>3000001</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4493,16 +4493,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>3000005</v>
+        <v>3000002</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4513,16 +4513,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>4000006</v>
+        <v>3000003</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4533,16 +4533,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>4000008</v>
+        <v>3000004</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4553,16 +4553,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>4000010</v>
+        <v>3000005</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4573,16 +4573,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>4000011</v>
+        <v>4000006</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4593,16 +4593,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>4000012</v>
+        <v>4000008</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4613,16 +4613,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>4000013</v>
+        <v>4000010</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4633,16 +4633,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>4000014</v>
+        <v>4000011</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4653,19 +4653,79 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>Conquer Clears</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>Difficulty {0}</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>{0}h {1}m</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B178" s="0" t="inlineStr">
+      <c r="B181" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="C178" s="0" t="inlineStr">
+      <c r="C181" s="0" t="inlineStr">
         <is>
           <t>Total Clears</t>
         </is>
       </c>
-      <c r="D178" s="0" t="inlineStr">
+      <c r="D181" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -7100,40 +7160,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>100100003</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>献祭失败保底概率提升</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Sacrifice Fail Pity Up</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>100100004</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Cross-species Sacrifice Rate Up</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
@@ -10250,7 +10310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -10483,12 +10543,22 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.1</t>
+          <t>强身健体Lv.1</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Gym Rat Lv.1</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>减少10%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加10%</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 10% HP</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -10503,12 +10573,22 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.2</t>
+          <t>强身健体Lv.2</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Gym Rat Lv.2</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>减少20%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加20%</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 20% HP</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -10523,12 +10603,22 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.3</t>
+          <t>强身健体Lv.3</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Gym Rat Lv.3</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>减少30%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加30%</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 30% HP</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -10543,12 +10633,22 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.4</t>
+          <t>强身健体Lv.4</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Gym Rat Lv.4</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>减少40%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加40%</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 40% HP</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -10563,12 +10663,22 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.5</t>
+          <t>强身健体Lv.5</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Gym Rat Lv.5</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>减少50%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加50%</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 50% HP</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -10583,12 +10693,22 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>强征健体Lv.1</t>
+          <t>时光沙漏Lv.1</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Hourglass Lv.1</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加10%</t>
+          <t>减少10%所有魔物复活CD时间</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>All demon revive CD reduced by 10%</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -10603,12 +10723,22 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>强征健体Lv.2</t>
+          <t>时光沙漏Lv.2</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Hourglass Lv.2</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加20%</t>
+          <t>减少20%所有魔物复活CD时间</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>All demon revive CD reduced by 20%</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -10623,12 +10753,22 @@
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>强征健体Lv.3</t>
+          <t>时光沙漏Lv.3</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Hourglass Lv.3</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加30%</t>
+          <t>减少30%所有魔物复活CD时间</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>All demon revive CD reduced by 30%</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -10643,12 +10783,22 @@
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>强征健体Lv.4</t>
+          <t>时光沙漏Lv.4</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Hourglass Lv.4</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加40%</t>
+          <t>减少40%所有魔物复活CD时间</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>All demon revive CD reduced by 40%</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -10663,12 +10813,22 @@
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>强征健体Lv.5</t>
+          <t>时光沙漏Lv.5</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Hourglass Lv.5</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加50%</t>
+          <t>减少50%所有魔物复活CD时间</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>All demon revive CD reduced by 50%</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -10972,6 +11132,306 @@
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="n">
+        <v>2000006001</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>唯快不破Lv.1</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>Speed Demon Lv.1</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物攻击速度增加10%</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 10% ASPD</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="n">
+        <v>2000006002</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>唯快不破Lv.2</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>Speed Demon Lv.2</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物攻击速度增加20%</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 20% ASPD</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>2000006003</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>唯快不破Lv.3</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>Speed Demon Lv.3</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物攻击速度增加30%</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 30% ASPD</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>2000006004</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>唯快不破Lv.4</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>Speed Demon Lv.4</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物攻击速度增加40%</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 40% ASPD</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="n">
+        <v>2000006005</v>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>唯快不破Lv.5</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>Speed Demon Lv.5</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物攻击速度增加50%</t>
+        </is>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 50% ASPD</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="n">
+        <v>2000007001</v>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.1</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.1</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加10%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 10% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
+        <v>2000007002</v>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.2</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.2</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加20%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 20% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.3</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.3</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加30%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 30% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.4</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.4</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加40%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 40% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="n">
+        <v>2000007005</v>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.5</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.5</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加50%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 50% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
@@ -15610,7 +16070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="35.375" customWidth="1" style="1" min="1" max="1"/>
@@ -16104,26 +16564,26 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>11000100001</v>
+        <v>3000600001</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>慢条斯理</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>Sloth</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>敌方进攻生物移动速度降低{Percentage}%</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>Increase HP by {Percentage}%</t>
+          <t>Enemy attackers' MSPD -{Percentage}%</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -16134,26 +16594,26 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>11000200001</v>
+        <v>3000700001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>DR+</t>
+          <t>唯快不破</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>DEF+</t>
+          <t>Speed Demon</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>所有魔物攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>Increase DEF by {Percentage}%</t>
+          <t>All demons gain {Percentage}% ASPD</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -16164,26 +16624,26 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>11000300001</v>
+        <v>3000800001</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>坚不可摧</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>Indestructible</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>攻击力增加{Percentage}%</t>
+          <t>所有魔物护甲增加{Percentage}%（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>Increase ATK by {Percentage}%</t>
+          <t>All demons gain {Percentage}% DR (no bonus for demons without DR)</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -16194,26 +16654,26 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000100001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>医者自医</t>
+          <t>HP+</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Self-Heal</t>
+          <t>HP+</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% HP every {Time_S}s</t>
+          <t>Increase HP by {Percentage}%</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -16224,26 +16684,26 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000200001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>护甲保养</t>
+          <t>DR+</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Armor Polish</t>
+          <t>DEF+</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% DEF every {Time_S}s</t>
+          <t>Increase DEF by {Percentage}%</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -16254,26 +16714,26 @@
     </row>
     <row r="23" ht="14.25" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000300001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>再补一刀</t>
+          <t>ATK+</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Double Tap</t>
+          <t>ATK+</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒再攻击一次</t>
+          <t>攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>Extra attack every {Time_S}s</t>
+          <t>Increase ATK by {Percentage}%</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -16284,26 +16744,26 @@
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-HP</t>
+        <v>12000100001</v>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>医者自医</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Feast-HP</t>
+          <t>Self-Heal</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP per {KillNum} kills</t>
+          <t>Restore {Percentage}% HP every {Time_S}s</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -16314,26 +16774,26 @@
     </row>
     <row r="25" ht="14.25" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-DR</t>
+        <v>12000200001</v>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>护甲保养</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Feast-DEF</t>
+          <t>Armor Polish</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
+          <t>Restore {Percentage}% DEF every {Time_S}s</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -16344,26 +16804,26 @@
     </row>
     <row r="26" ht="14.25" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-ATK</t>
+        <v>12000300001</v>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>再补一刀</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Feast-ATK</t>
+          <t>Double Tap</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒再攻击一次</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
+          <t>Extra attack every {Time_S}s</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -16374,26 +16834,26 @@
     </row>
     <row r="27" ht="17.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001100001</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>尸堆养料-ASPD</t>
+          <t>尸堆养料-HP</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Feast-ASPD</t>
+          <t>Feast-HP</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
+          <t>Gain {Percentage}% HP per {KillNum} kills</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -16404,26 +16864,26 @@
     </row>
     <row r="28" ht="17.25" customHeight="1" s="1">
       <c r="A28" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001200001</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-HP</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(HP)</t>
+          <t>尸堆养料-DR</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>Feast-DEF</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -16434,26 +16894,26 @@
     </row>
     <row r="29" ht="17.25" customHeight="1" s="1">
       <c r="A29" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001300001</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-DR</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(DR)</t>
+          <t>尸堆养料-ATK</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>Feast-ATK</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -16464,26 +16924,26 @@
     </row>
     <row r="30" ht="17.25" customHeight="1" s="1">
       <c r="A30" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001400001</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-ATK</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(ATK)</t>
+          <t>尸堆养料-ASPD</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>Feast-ASPD</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -16494,26 +16954,26 @@
     </row>
     <row r="31" ht="17.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002100001</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-ASPD</t>
+          <t>痛楚馈赠-HP</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Gift of Agony(ASPD)</t>
+          <t>Gift of Agony(HP)</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -16524,26 +16984,26 @@
     </row>
     <row r="32" ht="17.25" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002200001</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-HP</t>
+          <t>痛楚馈赠-DR</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(HP)</t>
+          <t>Gift of Agony(DR)</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -16554,26 +17014,26 @@
     </row>
     <row r="33" ht="17.25" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002300001</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-DR</t>
+          <t>痛楚馈赠-ATK</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(DR)</t>
+          <t>Gift of Agony(ATK)</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -16584,26 +17044,26 @@
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002400001</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-ATK</t>
+          <t>痛楚馈赠-ASPD</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(ATK)</t>
+          <t>Gift of Agony(ASPD)</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -16614,26 +17074,26 @@
     </row>
     <row r="35" ht="17.25" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003100001</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-ASPD</t>
+          <t>濒死狂宴-HP</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(ASPD)</t>
+          <t>Feast of the Dying(HP)</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -16644,26 +17104,26 @@
     </row>
     <row r="36" ht="17.25" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 收尸费</t>
+        <v>12003200001</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-DR</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Corpse Tax</t>
+          <t>Feast of the Dying(DR)</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {KillNum} kills</t>
+          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -16674,26 +17134,26 @@
     </row>
     <row r="37" ht="17.25" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>痛觉提款机</t>
+        <v>12003300001</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ATK</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Pain ATM</t>
+          <t>Feast of the Dying(ATK)</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -16704,26 +17164,26 @@
     </row>
     <row r="38" ht="17.25" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>暴力小费</t>
+        <v>12003400001</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ASPD</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Violence Tip</t>
+          <t>Feast of the Dying(ASPD)</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {AttackDamage} dmg dealt</t>
+          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
@@ -16734,26 +17194,26 @@
     </row>
     <row r="39" ht="17.25" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>鞭尸成瘾</t>
+          <t xml:space="preserve"> 收尸费</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corpse Kicker</t>
+          <t>Corpse Tax</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>Instant attack per {KillNum} kills</t>
+          <t>Drop crystal per {KillNum} kills</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
@@ -16764,26 +17224,26 @@
     </row>
     <row r="40" ht="17.25" customHeight="1" s="1">
       <c r="A40" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>碰瓷反杀</t>
+          <t>痛觉提款机</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Blood Bait</t>
+          <t>Pain ATM</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
@@ -16794,26 +17254,26 @@
     </row>
     <row r="41" ht="17.25" customHeight="1" s="1">
       <c r="A41" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>越打越嗨</t>
+          <t>暴力小费</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rage Spiral </t>
+          <t>Violence Tip</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {AttackDamage} dmg dealt</t>
+          <t>Drop crystal per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
@@ -16824,26 +17284,26 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>拾晶不昧</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>Honest Finder</t>
+        <v>12011100001</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>鞭尸成瘾</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Corpse Kicker</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>Auto-collect crystals every {Time_S}s</t>
+          <t>Instant attack per {KillNum} kills</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
@@ -16854,26 +17314,26 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>13000200001</v>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t>有利可图</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>Opportunist</t>
+        <v>12011200001</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>碰瓷反杀</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Blood Bait</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>Resurrect on Death</t>
+          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
@@ -16884,26 +17344,26 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="B44" s="0" t="inlineStr">
-        <is>
-          <t>死而复生</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>Second Wind</t>
+        <v>12011300001</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>越打越嗨</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rage Spiral </t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>Explode on Death</t>
+          <t>Extra attack per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
@@ -16914,26 +17374,26 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000100001</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>同归于尽</t>
+          <t>拾晶不昧</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Mutual Destruction</t>
+          <t>Honest Finder</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>Heal allies {Percentage}% of max HP on death</t>
+          <t>Auto-collect crystals every {Time_S}s</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
@@ -16944,26 +17404,26 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000200001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>死得其所-HP</t>
+          <t>有利可图</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Noble Death-HP</t>
+          <t>Opportunist</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后重生</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>Shield allies {Percentage}% of max DEF on death</t>
+          <t>Resurrect on Death</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
@@ -16974,26 +17434,26 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000300001</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>死得其所-DR</t>
+          <t>死而复生</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Noble Death-DEF</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>Spawn {Percentage}% chance crystal on death</t>
+          <t>Explode on Death</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
@@ -17004,16 +17464,26 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000400001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>死亡税</t>
+          <t>同归于尽</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Death Tax</t>
+          <t>Mutual Destruction</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>Heal allies {Percentage}% of max HP on death</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
@@ -17024,29 +17494,79 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>3000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理</t>
+          <t>死得其所-HP</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Sloth</t>
+          <t>Noble Death-HP</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低{Percentage}%</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -{Percentage}%</t>
+          <t>Shield allies {Percentage}% of max DEF on death</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-DR</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-DEF</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>死亡后{Percentage}%生成魔晶</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>Spawn {Percentage}% chance crystal on death</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>死亡税</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>Death Tax</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="723" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="11" activeTab="18" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" state="visible" r:id="rId1"/>
@@ -7420,20 +7420,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>100310112</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>Sword &amp; Magic: Conquest Difficulty +1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>excel_research_info</t>
         </is>
@@ -8976,11 +8976,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="30.875" customWidth="1" style="1" min="2" max="2"/>
     <col width="32.5" customWidth="1" style="1" min="3" max="3"/>
+    <col width="58.375" customWidth="1" style="1" min="4" max="4"/>
+    <col width="49.875" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9080,1380 +9082,360 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="n">
+      <c r="A4" t="n">
         <v>4001001</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 I</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer I</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 10 只生物</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 10 creatures</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>生物猎手</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Creature Slayer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>累计击杀 {Name} 只生物</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Defeat a total of {Name} creatures</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>4001003</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 II</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer II</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 100 只生物</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 100 creatures</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4002001</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>时光旅人</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Time Traveler</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>累计游玩 {Time_H} 小时</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Play for a total of {Time_H} hour(s)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n">
-        <v>4001005</v>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 III</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer III</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 1000 只生物</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 1000 creatures</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="A6" t="n">
+        <v>4003001</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 10 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 10, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n">
-        <v>4001007</v>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 IV</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer IV</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 10000 只生物</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 10000 creatures</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="A7" t="n">
+        <v>4003101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 1 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 1, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n">
-        <v>4001009</v>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 V</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer V</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 100000 只生物</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 100000 creatures</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="A8" t="n">
+        <v>4003201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 2 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 2, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n">
-        <v>4001011</v>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>生物猎手 VI</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>Creature Slayer VI</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>累计击杀 1000000 只生物</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>Defeat a total of 1000000 creatures</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="A9" t="n">
+        <v>4003301</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 3 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 3, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="n">
-        <v>4002001</v>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 I</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler I</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 1 小时</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 1 hour</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="A10" t="n">
+        <v>4003401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 4 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 4, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="n">
-        <v>4002003</v>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 II</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler II</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 2 小时</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 2 hours</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="A11" t="n">
+        <v>4003501</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 5 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 5, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n">
-        <v>4002005</v>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 III</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler III</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 3 小时</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 3 hours</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="A12" t="n">
+        <v>4003601</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 6 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 6, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n">
-        <v>4002007</v>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 IV</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler IV</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 4 小时</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 4 hours</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="A13" t="n">
+        <v>4003701</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度7</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.7</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 7 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 7, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n">
-        <v>4002009</v>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 V</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler V</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 5 小时</t>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 5 hours</t>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="A14" t="n">
+        <v>4003801</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.8</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 8 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 8, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="n">
-        <v>4002011</v>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 VI</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler VI</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 6 小时</t>
-        </is>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 6 hours</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="n">
-        <v>4002013</v>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 VII</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler VII</t>
-        </is>
-      </c>
-      <c r="D16" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 7 小时</t>
-        </is>
-      </c>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 7 hours</t>
-        </is>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="n">
-        <v>4002015</v>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 VIII</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler VIII</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 8 小时</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 8 hours</t>
-        </is>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="n">
-        <v>4002017</v>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 IX</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler IX</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 9 小时</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 9 hours</t>
-        </is>
-      </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="n">
-        <v>4002019</v>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>时光旅人 X</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>Time Traveler X</t>
-        </is>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t>累计游玩 10 小时</t>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>Play for a total of 10 hours</t>
-        </is>
-      </c>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="n">
-        <v>4003001</v>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度10 I</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.10 I</t>
-        </is>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 10 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 10, 1 time</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="n">
-        <v>4003003</v>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度10 II</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.10 II</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 10 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 10, 10 times</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="n">
-        <v>4003005</v>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度10 III</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.10 III</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 10 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 10, 100 times</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="n">
-        <v>4003101</v>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度1 I</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.1 I</t>
-        </is>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 1 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 1, 1 time</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="n">
-        <v>4003103</v>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度1 II</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.1 II</t>
-        </is>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 1 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 1, 10 times</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="n">
-        <v>4003105</v>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度1 III</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.1 III</t>
-        </is>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 1 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 1, 100 times</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="n">
-        <v>4003201</v>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度2 I</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.2 I</t>
-        </is>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 2 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 2, 1 time</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="n">
-        <v>4003203</v>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度2 II</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.2 II</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 2 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 2, 10 times</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="n">
-        <v>4003205</v>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度2 III</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.2 III</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 2 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 2, 100 times</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="n">
-        <v>4003301</v>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度3 I</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.3 I</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 3 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 3, 1 time</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="n">
-        <v>4003303</v>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度3 II</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.3 II</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 3 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 3, 10 times</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="n">
-        <v>4003305</v>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度3 III</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.3 III</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 3 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 3, 100 times</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="n">
-        <v>4003401</v>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度4 I</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.4 I</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 4 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 4, 1 time</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="n">
-        <v>4003403</v>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度4 II</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.4 II</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 4 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 4, 10 times</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="n">
-        <v>4003405</v>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度4 III</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.4 III</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 4 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 4, 100 times</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="n">
-        <v>4003501</v>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度5 I</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.5 I</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 5 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 5, 1 time</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="n">
-        <v>4003503</v>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度5 II</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.5 II</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 5 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 5, 10 times</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="n">
-        <v>4003505</v>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度5 III</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.5 III</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 5 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 5, 100 times</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="n">
-        <v>4003601</v>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度6 I</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.6 I</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 6 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 6, 1 time</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="n">
-        <v>4003603</v>
-      </c>
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度6 II</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.6 II</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 6 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 6, 10 times</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="n">
-        <v>4003605</v>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度6 III</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.6 III</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 6 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 6, 100 times</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="n">
-        <v>4003701</v>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度7 I</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.7 I</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 7 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 7, 1 time</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="n">
-        <v>4003703</v>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度7 II</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.7 II</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 7 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 7, 10 times</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="n">
-        <v>4003705</v>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度7 III</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.7 III</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 7 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 7, 100 times</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="n">
-        <v>4003801</v>
-      </c>
-      <c r="B44" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度8 I</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.8 I</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 8 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 8, 1 time</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="n">
-        <v>4003803</v>
-      </c>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度8 II</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.8 II</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 8 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 8, 10 times</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="n">
-        <v>4003805</v>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度8 III</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.8 III</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 8 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 8, 100 times</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="n">
+      <c r="A15" t="n">
         <v>4003901</v>
       </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度9 I</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.9 I</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 9 通关 1 次</t>
-        </is>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 9, 1 time</t>
-        </is>
-      </c>
-      <c r="F47" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="n">
-        <v>4003903</v>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度9 II</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.9 II</t>
-        </is>
-      </c>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 9 通关 10 次</t>
-        </is>
-      </c>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 9, 10 times</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t>excel_achievement_info</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="n">
-        <v>4003905</v>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>征服者·剑与魔法·难度9 III</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>Conqueror Sword&amp;Magic Diff.9 III</t>
-        </is>
-      </c>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>在剑与魔法世界难度 9 通关 100 次</t>
-        </is>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>Clear Sword&amp;Magic difficulty 9, 100 times</t>
-        </is>
-      </c>
-      <c r="F49" s="0" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>征服者·剑与魔法·难度9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Conqueror Sword&amp;Magic Diff.9</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>在剑与魔法世界难度 9 通关 {Name} 次</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Clear Sword&amp;Magic difficulty 9, {Name} time(s)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="11" activeTab="18" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" state="visible" r:id="rId1"/>
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -3327,11 +3327,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>Are you sure you want to leave the council? Spent resources will not be refunded.</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3342,16 +3347,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord slayers are approaching...</t>
+          <t>Current Proposal Approval Rate: {0}%</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3362,16 +3367,11 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
-        </is>
-      </c>
-      <c r="C112" s="0" t="inlineStr">
-        <is>
-          <t>A horde of heroes is approaching...</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3382,16 +3382,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>Warning! A hero party is swarming in...</t>
+          <t>Demon Lord slayers are approaching...</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3402,16 +3402,16 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>Subjugation forces detected approaching...</t>
+          <t>A horde of heroes is approaching...</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3422,16 +3422,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>The Allied Hero Army is closing in...</t>
+          <t>Warning! A hero party is swarming in...</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3442,16 +3442,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>A horde of self-proclaimed heroes has arrived...</t>
+          <t>Subjugation forces detected approaching...</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3462,16 +3462,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>Alert: Allies of justice are approaching...</t>
+          <t>The Allied Hero Army is closing in...</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3482,16 +3482,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Upgrade</t>
+          <t>A horde of self-proclaimed heroes has arrived...</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3502,16 +3502,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>Begin Sacrifice</t>
+          <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3522,16 +3522,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>Success Rate</t>
+          <t>Sacrifice Upgrade</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3542,16 +3542,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Select Sacrifice First!</t>
+          <t>Begin Sacrifice</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3562,16 +3562,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Too Many Sacrifices!</t>
+          <t>Success Rate</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3582,16 +3582,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Start Sacrifice? Current Rate: {0}</t>
+          <t>Select Sacrifice First!</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3602,16 +3602,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Allocate All Points First!</t>
+          <t>Too Many Sacrifices!</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3622,16 +3622,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Points Left: {0}</t>
+          <t>Start Sacrifice? Current Rate: {0}</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3642,16 +3642,16 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Research for x{0} Magic Crystals?</t>
+          <t>Allocate All Points First!</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3662,16 +3662,16 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Points Left: {0}</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3682,16 +3682,16 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Research for x{0} Magic Crystals?</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3702,16 +3702,16 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3722,16 +3722,16 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Select Rebirth Appearance</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3742,16 +3742,16 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3762,16 +3762,16 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>Confirm Rebirth with this look?</t>
+          <t>Select Rebirth Appearance</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3782,14 +3782,18 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
-        </is>
-      </c>
-      <c r="C133" s="0" t="n"/>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3798,14 +3802,18 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="C134" s="0" t="n"/>
+          <t>是否以此外观完成转生？</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>Confirm Rebirth with this look?</t>
+        </is>
+      </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3814,18 +3822,14 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
-        </is>
-      </c>
-      <c r="C135" s="0" t="inlineStr">
-        <is>
-          <t>Bribe</t>
-        </is>
-      </c>
+          <t>成就</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="n"/>
       <c r="D135" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3834,18 +3838,14 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
-        </is>
-      </c>
-      <c r="C136" s="0" t="inlineStr">
-        <is>
-          <t>Start Evolution</t>
-        </is>
-      </c>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="n"/>
       <c r="D136" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>End Evolution</t>
+          <t>Bribe</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3874,16 +3874,16 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>Complete Evolution</t>
+          <t>Start Evolution</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3894,16 +3894,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>End Evolution? Materials won't be refunded!</t>
+          <t>End Evolution</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3914,16 +3914,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Complete Evolution</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3934,16 +3934,16 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>Select Evolution Target</t>
+          <t>End Evolution? Materials won't be refunded!</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3954,16 +3954,16 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>Select Support Demon</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3974,16 +3974,16 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected</t>
+          <t>Select Evolution Target</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3994,16 +3994,16 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>Speed Up x{0}</t>
+          <t>Select Support Demon</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
@@ -4014,16 +4014,16 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+          <t>No Demon Selected</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
@@ -4034,11 +4034,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>加速进阶 x{0}</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>Speed Up x{0}</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -4049,11 +4054,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -4064,16 +4074,11 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
-        </is>
-      </c>
-      <c r="C148" s="0" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -4084,16 +4089,11 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C149" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -4104,16 +4104,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4124,16 +4124,16 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -4144,16 +4144,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -4164,16 +4164,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -4184,16 +4184,16 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -4204,16 +4204,16 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -4224,16 +4224,16 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -4244,16 +4244,16 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -4264,16 +4264,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -4284,16 +4284,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -4304,16 +4304,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4324,16 +4324,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4344,16 +4344,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4364,16 +4364,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4384,16 +4384,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4404,16 +4404,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Sort: Team</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4424,16 +4424,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4444,11 +4444,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：阵容</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Team</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4459,11 +4464,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4474,11 +4484,11 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4489,16 +4499,11 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
-        </is>
-      </c>
-      <c r="C170" s="0" t="inlineStr">
-        <is>
-          <t>Sort: Type</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4509,14 +4514,13 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
-        </is>
-      </c>
-      <c r="C171" s="0" t="n"/>
+          <t>道具名字:{0}</t>
+        </is>
+      </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4525,14 +4529,18 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
-        </is>
-      </c>
-      <c r="C172" s="0" t="n"/>
+          <t>排序：同类</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Type</t>
+        </is>
+      </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4541,11 +4549,11 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="C173" s="0" t="n"/>
@@ -4557,18 +4565,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
-        </is>
-      </c>
-      <c r="C174" s="0" t="inlineStr">
-        <is>
-          <t>No Related Items</t>
-        </is>
-      </c>
+          <t>倒序</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="n"/>
       <c r="D174" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4577,18 +4581,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
-        </is>
-      </c>
-      <c r="C175" s="0" t="inlineStr">
-        <is>
-          <t>No Related Creatures</t>
-        </is>
-      </c>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="n"/>
       <c r="D175" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4597,14 +4597,18 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C176" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4613,16 +4617,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>No Related Creatures</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4633,18 +4637,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
-        </is>
-      </c>
-      <c r="C178" s="0" t="inlineStr">
-        <is>
-          <t>Not Enough Reputation!</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="n"/>
       <c r="D178" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4653,16 +4653,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4673,16 +4673,16 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4693,16 +4693,16 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4713,16 +4713,16 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4733,16 +4733,16 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4753,16 +4753,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4773,16 +4773,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4793,16 +4793,16 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4813,16 +4813,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4833,16 +4833,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4853,19 +4853,99 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>Difficulty {0}</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>{0}h {1}m</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B189" s="0" t="inlineStr">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="C189" s="0" t="inlineStr">
+      <c r="C191" s="0" t="inlineStr">
         <is>
           <t>Total Clears</t>
         </is>
       </c>
-      <c r="D189" s="0" t="inlineStr">
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -9082,360 +9162,360 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>4001001</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>生物猎手</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Creature Slayer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>累计击杀 {Name} 只生物</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Defeat a total of {Name} creatures</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>4002001</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>时光旅人</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>Time Traveler</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>累计游玩 {Time_H} 小时</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Play for a total of {Time_H} hour(s)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>4003001</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度10</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.10</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 10 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 10, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>4003101</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 1 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 1, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>4003201</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度2</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 2 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 2, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>4003301</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度3</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 3 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 3, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>4003401</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度4</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.4</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 4 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 4, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>4003501</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度5</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.5</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 5 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 5, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>4003601</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度6</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 6 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 6, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>4003701</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度7</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 7 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 7, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>4003801</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度8</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 8 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 8, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="0" t="n">
         <v>4003901</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>征服者·剑与魔法·难度9</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>Conqueror Sword&amp;Magic Diff.9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>在剑与魔法世界难度 9 通关 {Name} 次</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Clear Sword&amp;Magic difficulty 9, {Name} time(s)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>excel_achievement_info</t>
         </is>
@@ -16867,7 +16947,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>想要给自己换个新名字！</t>
+          <t>想要给魔王换个新名字！</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4932,20 +4932,20 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="0" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -7224,7 +7224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7736,16 +7736,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>300100000</v>
+        <v>200200001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Crystal Drop Duration +5s</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -7756,16 +7756,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>300100001</v>
+        <v>200300001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Demon Lord Mana Limit +10</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -7776,16 +7776,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>300100002</v>
+        <v>200400001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>魔王魔力恢复+1/秒</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Demon Lord Mana Regen +1/s</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -7796,16 +7796,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>300100003</v>
+        <v>300100000</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -7816,16 +7816,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300100004</v>
+        <v>300100001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -7836,16 +7836,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300100101</v>
+        <v>300100002</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -7856,16 +7856,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>300100102</v>
+        <v>300100003</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -7876,16 +7876,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>300100201</v>
+        <v>300100004</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -7896,16 +7896,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>300100301</v>
+        <v>300100101</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -7916,16 +7916,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>300200000</v>
+        <v>300100102</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -7936,16 +7936,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300200001</v>
+        <v>300100201</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -7956,16 +7956,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300200002</v>
+        <v>300100301</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -7976,16 +7976,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300200003</v>
+        <v>300200000</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -7996,16 +7996,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300200004</v>
+        <v>300200001</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -8016,16 +8016,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300200101</v>
+        <v>300200002</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -8036,16 +8036,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300200102</v>
+        <v>300200003</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -8056,16 +8056,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300200201</v>
+        <v>300200004</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -8076,16 +8076,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300200301</v>
+        <v>300200101</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -8096,16 +8096,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300300000</v>
+        <v>300200102</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -8116,16 +8116,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300300001</v>
+        <v>300200201</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -8136,16 +8136,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300300002</v>
+        <v>300200301</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -8156,16 +8156,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300300003</v>
+        <v>300300000</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -8176,16 +8176,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300300004</v>
+        <v>300300001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -8196,16 +8196,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300300101</v>
+        <v>300300002</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -8216,16 +8216,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300300102</v>
+        <v>300300003</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -8236,16 +8236,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300300201</v>
+        <v>300300004</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8256,16 +8256,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300300301</v>
+        <v>300300101</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8276,16 +8276,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300400000</v>
+        <v>300300102</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8296,16 +8296,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300400001</v>
+        <v>300300201</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8316,16 +8316,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300400002</v>
+        <v>300300301</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8336,16 +8336,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300400003</v>
+        <v>300400000</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8356,16 +8356,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300400004</v>
+        <v>300400001</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8376,16 +8376,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300400005</v>
+        <v>300400002</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8396,16 +8396,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300400101</v>
+        <v>300400003</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8416,16 +8416,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300400102</v>
+        <v>300400004</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8436,16 +8436,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300400201</v>
+        <v>300400005</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8456,16 +8456,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300400301</v>
+        <v>300400101</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8476,16 +8476,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300500000</v>
+        <v>300400102</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8496,16 +8496,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300500001</v>
+        <v>300400201</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8516,16 +8516,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300500002</v>
+        <v>300400301</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8536,16 +8536,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300500003</v>
+        <v>300500000</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8556,16 +8556,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300500004</v>
+        <v>300500001</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8576,16 +8576,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300500101</v>
+        <v>300500002</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8596,16 +8596,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300500102</v>
+        <v>300500003</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8616,16 +8616,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300500201</v>
+        <v>300500004</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8636,16 +8636,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300500301</v>
+        <v>300500101</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8656,16 +8656,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300600000</v>
+        <v>300500102</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8676,16 +8676,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300600001</v>
+        <v>300500201</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -8696,16 +8696,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300600002</v>
+        <v>300500301</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -8716,16 +8716,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300600003</v>
+        <v>300600000</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -8736,16 +8736,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300600004</v>
+        <v>300600001</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -8756,16 +8756,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300600005</v>
+        <v>300600002</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -8776,16 +8776,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300600101</v>
+        <v>300600003</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -8796,16 +8796,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300600102</v>
+        <v>300600004</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -8816,16 +8816,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300600201</v>
+        <v>300600005</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -8836,16 +8836,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300600301</v>
+        <v>300600101</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -8856,16 +8856,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300700000</v>
+        <v>300600102</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -8876,16 +8876,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300700001</v>
+        <v>300600201</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -8896,16 +8896,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300700002</v>
+        <v>300600301</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -8916,16 +8916,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300700003</v>
+        <v>300700000</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -8936,16 +8936,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300700004</v>
+        <v>300700001</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -8956,16 +8956,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>300700101</v>
+        <v>300700002</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -8976,16 +8976,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>300700102</v>
+        <v>300700003</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -8996,16 +8996,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>300700201</v>
+        <v>300700004</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Unlock Class: Orc Ice Mage</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -9016,16 +9016,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>300700301</v>
+        <v>300700101</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Incubate Orcs x5</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -9036,14 +9036,74 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>Incubate Orcs x10</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>终焉议会议案：转生兽人</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>Council: Reincarnate as Orc</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B91" s="0" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C91" s="0" t="inlineStr"/>
+      <c r="C94" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9532,7 +9592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -9661,16 +9721,26 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>2000001001</v>
+        <v>1000002001</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>钱多多Lv.1</t>
+          <t>奖励多多</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>More Rewards</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>每一次击杀有10%的概率多掉落一次魔晶</t>
+          <t>战斗通关时，获得的奖励数量+1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gain 1 extra reward item when clearing a battle</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -9681,16 +9751,26 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>2000001002</v>
+        <v>1000003001</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>钱多多Lv.2</t>
+          <t>再来一瓶</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>One More Pick</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>战斗通关时，可选择的奖励次数+1（超过实际奖励数量时多余次数无效）</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gain 1 extra reward pick (extra picks beyond available rewards have no effect)</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -9701,16 +9781,16 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>2000001003</v>
+        <v>2000001001</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>钱多多Lv.3</t>
+          <t>钱多多Lv.1</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>每一次击杀有30%的概率多掉落一次魔晶</t>
+          <t>每一次击杀有10%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -9721,16 +9801,16 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>2000001004</v>
+        <v>2000001002</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>钱多多Lv.4</t>
+          <t>钱多多Lv.2</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -9741,16 +9821,16 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>2000001005</v>
+        <v>2000001003</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>钱多多Lv.5</t>
+          <t>钱多多Lv.3</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>每一次击杀有50%的概率多掉落一次魔晶</t>
+          <t>每一次击杀有30%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -9761,26 +9841,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>2000002001</v>
+        <v>2000001004</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>强身健体Lv.1</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>Gym Rat Lv.1</t>
+          <t>钱多多Lv.4</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加10%</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>All demons gain 10% HP</t>
+          <t>每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -9791,26 +9861,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>2000002002</v>
+        <v>2000001005</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>强身健体Lv.2</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>Gym Rat Lv.2</t>
+          <t>钱多多Lv.5</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加20%</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>All demons gain 20% HP</t>
+          <t>每一次击杀有50%的概率多掉落一次魔晶</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -9821,26 +9881,26 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>2000002003</v>
+        <v>2000002001</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>强身健体Lv.3</t>
+          <t>强身健体Lv.1</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Gym Rat Lv.3</t>
+          <t>Gym Rat Lv.1</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加30%</t>
+          <t>所有魔物体力增加10%</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 30% HP</t>
+          <t>All demons gain 10% HP</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -9851,26 +9911,26 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>2000002004</v>
+        <v>2000002002</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>强身健体Lv.4</t>
+          <t>强身健体Lv.2</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Gym Rat Lv.4</t>
+          <t>Gym Rat Lv.2</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加40%</t>
+          <t>所有魔物体力增加20%</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 40% HP</t>
+          <t>All demons gain 20% HP</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -9881,26 +9941,26 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>2000002005</v>
+        <v>2000002003</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>强身健体Lv.5</t>
+          <t>强身健体Lv.3</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Gym Rat Lv.5</t>
+          <t>Gym Rat Lv.3</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>所有魔物体力增加50%</t>
+          <t>所有魔物体力增加30%</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 50% HP</t>
+          <t>All demons gain 30% HP</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -9911,26 +9971,26 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>2000003001</v>
+        <v>2000002004</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.1</t>
+          <t>强身健体Lv.4</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Hourglass Lv.1</t>
+          <t>Gym Rat Lv.4</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>减少10%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加40%</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 10%</t>
+          <t>All demons gain 40% HP</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -9941,26 +10001,26 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>2000003002</v>
+        <v>2000002005</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.2</t>
+          <t>强身健体Lv.5</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Hourglass Lv.2</t>
+          <t>Gym Rat Lv.5</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>减少20%所有魔物复活CD时间</t>
+          <t>所有魔物体力增加50%</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 20%</t>
+          <t>All demons gain 50% HP</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -9971,26 +10031,26 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>2000003003</v>
+        <v>2000003001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.3</t>
+          <t>时光沙漏Lv.1</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Hourglass Lv.3</t>
+          <t>Hourglass Lv.1</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>减少30%所有魔物复活CD时间</t>
+          <t>减少10%所有魔物复活CD时间</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 30%</t>
+          <t>All demon revive CD reduced by 10%</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -10001,26 +10061,26 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>2000003004</v>
+        <v>2000003002</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.4</t>
+          <t>时光沙漏Lv.2</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Hourglass Lv.4</t>
+          <t>Hourglass Lv.2</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>减少40%所有魔物复活CD时间</t>
+          <t>减少20%所有魔物复活CD时间</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 40%</t>
+          <t>All demon revive CD reduced by 20%</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -10031,26 +10091,26 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>2000003005</v>
+        <v>2000003003</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>时光沙漏Lv.5</t>
+          <t>时光沙漏Lv.3</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Hourglass Lv.5</t>
+          <t>Hourglass Lv.3</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>减少50%所有魔物复活CD时间</t>
+          <t>减少30%所有魔物复活CD时间</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 50%</t>
+          <t>All demon revive CD reduced by 30%</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -10061,26 +10121,26 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>2000004001</v>
+        <v>2000003004</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强Lv.1</t>
+          <t>时光沙漏Lv.4</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Overwhelming Damage Lv.1</t>
+          <t>Hourglass Lv.4</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击力增加10%</t>
+          <t>减少40%所有魔物复活CD时间</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 10% ATK</t>
+          <t>All demon revive CD reduced by 40%</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -10091,26 +10151,26 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>2000004002</v>
+        <v>2000003005</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强Lv.2</t>
+          <t>时光沙漏Lv.5</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Overwhelming Damage Lv.2</t>
+          <t>Hourglass Lv.5</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击力增加20%</t>
+          <t>减少50%所有魔物复活CD时间</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 20% ATK</t>
+          <t>All demon revive CD reduced by 50%</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -10121,26 +10181,26 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>2000004003</v>
+        <v>2000004001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强Lv.3</t>
+          <t>伤害性极强Lv.1</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Overwhelming Damage Lv.3</t>
+          <t>Overwhelming Damage Lv.1</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击力增加30%</t>
+          <t>所有魔物攻击力增加10%</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 30% ATK</t>
+          <t>All demons gain 10% ATK</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -10151,26 +10211,26 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>2000004004</v>
+        <v>2000004002</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强Lv.4</t>
+          <t>伤害性极强Lv.2</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Overwhelming Damage Lv.4</t>
+          <t>Overwhelming Damage Lv.2</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击力增加40%</t>
+          <t>所有魔物攻击力增加20%</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 40% ATK</t>
+          <t>All demons gain 20% ATK</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -10181,26 +10241,26 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>2000004005</v>
+        <v>2000004003</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>伤害性极强Lv.5</t>
+          <t>伤害性极强Lv.3</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Overwhelming Damage Lv.5</t>
+          <t>Overwhelming Damage Lv.3</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击力增加50%</t>
+          <t>所有魔物攻击力增加30%</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 50% ATK</t>
+          <t>All demons gain 30% ATK</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -10211,26 +10271,26 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>2000005001</v>
+        <v>2000004004</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理Lv.1</t>
+          <t>伤害性极强Lv.4</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Sloth Lv.1</t>
+          <t>Overwhelming Damage Lv.4</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低10%</t>
+          <t>所有魔物攻击力增加40%</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -10%</t>
+          <t>All demons gain 40% ATK</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -10241,26 +10301,26 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>2000005002</v>
+        <v>2000004005</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理Lv.2</t>
+          <t>伤害性极强Lv.5</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Sloth Lv.2</t>
+          <t>Overwhelming Damage Lv.5</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低20%</t>
+          <t>所有魔物攻击力增加50%</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -20%</t>
+          <t>All demons gain 50% ATK</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -10271,26 +10331,26 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>2000005003</v>
+        <v>2000005001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理Lv.3</t>
+          <t>慢条斯理Lv.1</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Sloth Lv.3</t>
+          <t>Sloth Lv.1</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低30%</t>
+          <t>敌方进攻生物移动速度降低10%</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -30%</t>
+          <t>Enemy attackers' MSPD -10%</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -10301,26 +10361,26 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>2000005004</v>
+        <v>2000005002</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理Lv.4</t>
+          <t>慢条斯理Lv.2</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Sloth Lv.4</t>
+          <t>Sloth Lv.2</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低40%</t>
+          <t>敌方进攻生物移动速度降低20%</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -40%</t>
+          <t>Enemy attackers' MSPD -20%</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -10331,26 +10391,26 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>2000005005</v>
+        <v>2000005003</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>慢条斯理Lv.5</t>
+          <t>慢条斯理Lv.3</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Sloth Lv.5</t>
+          <t>Sloth Lv.3</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>敌方进攻生物移动速度降低50%</t>
+          <t>敌方进攻生物移动速度降低30%</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>Enemy attackers' MSPD -50%</t>
+          <t>Enemy attackers' MSPD -30%</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -10361,26 +10421,26 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>2000006001</v>
+        <v>2000005004</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>唯快不破Lv.1</t>
+          <t>慢条斯理Lv.4</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Speed Demon Lv.1</t>
+          <t>Sloth Lv.4</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击速度增加10%</t>
+          <t>敌方进攻生物移动速度降低40%</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 10% ASPD</t>
+          <t>Enemy attackers' MSPD -40%</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -10391,26 +10451,26 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>2000006002</v>
+        <v>2000005005</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>唯快不破Lv.2</t>
+          <t>慢条斯理Lv.5</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Speed Demon Lv.2</t>
+          <t>Sloth Lv.5</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击速度增加20%</t>
+          <t>敌方进攻生物移动速度降低50%</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 20% ASPD</t>
+          <t>Enemy attackers' MSPD -50%</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -10421,26 +10481,26 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>2000006003</v>
+        <v>2000006001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>唯快不破Lv.3</t>
+          <t>唯快不破Lv.1</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Speed Demon Lv.3</t>
+          <t>Speed Demon Lv.1</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击速度增加30%</t>
+          <t>所有魔物攻击速度增加10%</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 30% ASPD</t>
+          <t>All demons gain 10% ASPD</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -10451,26 +10511,26 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>2000006004</v>
+        <v>2000006002</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>唯快不破Lv.4</t>
+          <t>唯快不破Lv.2</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Speed Demon Lv.4</t>
+          <t>Speed Demon Lv.2</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击速度增加40%</t>
+          <t>所有魔物攻击速度增加20%</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 40% ASPD</t>
+          <t>All demons gain 20% ASPD</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -10481,26 +10541,26 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>2000006005</v>
+        <v>2000006003</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>唯快不破Lv.5</t>
+          <t>唯快不破Lv.3</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Speed Demon Lv.5</t>
+          <t>Speed Demon Lv.3</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>所有魔物攻击速度增加50%</t>
+          <t>所有魔物攻击速度增加30%</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 50% ASPD</t>
+          <t>All demons gain 30% ASPD</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -10511,26 +10571,26 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>2000007001</v>
+        <v>2000006004</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧Lv.1</t>
+          <t>唯快不破Lv.4</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Indestructible Lv.1</t>
+          <t>Speed Demon Lv.4</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>所有魔物护甲增加10%（无护甲的魔物不受加成）</t>
+          <t>所有魔物攻击速度增加40%</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 10% DR (no bonus for demons without DR)</t>
+          <t>All demons gain 40% ASPD</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -10541,26 +10601,26 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>2000007002</v>
+        <v>2000006005</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧Lv.2</t>
+          <t>唯快不破Lv.5</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Indestructible Lv.2</t>
+          <t>Speed Demon Lv.5</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>所有魔物护甲增加20%（无护甲的魔物不受加成）</t>
+          <t>所有魔物攻击速度增加50%</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 20% DR (no bonus for demons without DR)</t>
+          <t>All demons gain 50% ASPD</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -10571,26 +10631,26 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>2000007003</v>
+        <v>2000007001</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧Lv.3</t>
+          <t>坚不可摧Lv.1</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Indestructible Lv.3</t>
+          <t>Indestructible Lv.1</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>所有魔物护甲增加30%（无护甲的魔物不受加成）</t>
+          <t>所有魔物护甲增加10%（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 30% DR (no bonus for demons without DR)</t>
+          <t>All demons gain 10% DR (no bonus for demons without DR)</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -10601,26 +10661,26 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>2000007004</v>
+        <v>2000007002</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>坚不可摧Lv.4</t>
+          <t>坚不可摧Lv.2</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Indestructible Lv.4</t>
+          <t>Indestructible Lv.2</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>所有魔物护甲增加40%（无护甲的魔物不受加成）</t>
+          <t>所有魔物护甲增加20%（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>All demons gain 40% DR (no bonus for demons without DR)</t>
+          <t>All demons gain 20% DR (no bonus for demons without DR)</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
@@ -10631,29 +10691,89 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
+        <v>2000007003</v>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.3</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.3</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加30%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 30% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="n">
+        <v>2000007004</v>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>坚不可摧Lv.4</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>Indestructible Lv.4</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>所有魔物护甲增加40%（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>All demons gain 40% DR (no bonus for demons without DR)</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="n">
         <v>2000007005</v>
       </c>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>坚不可摧Lv.5</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>Indestructible Lv.5</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>所有魔物护甲增加50%（无护甲的魔物不受加成）</t>
         </is>
       </c>
-      <c r="E39" s="0" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>All demons gain 50% DR (no bonus for demons without DR)</t>
         </is>
       </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
@@ -15292,7 +15412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="35.375" customWidth="1" style="1" min="1" max="1"/>
@@ -15876,26 +15996,26 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>11000100001</v>
+        <v>3000900001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>奖励多多</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>More Rewards</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>战斗通关获得的奖励数量+1</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>Increase HP by {Percentage}%</t>
+          <t>Gain 1 extra reward item when clearing a battle</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -15906,26 +16026,26 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>11000200001</v>
+        <v>3001000001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>DR+</t>
+          <t>再来一瓶</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>DEF+</t>
+          <t>One More Pick</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>战斗通关可选择的奖励次数+1</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>Increase DEF by {Percentage}%</t>
+          <t>Gain 1 extra reward pick when clearing a battle</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -15936,26 +16056,26 @@
     </row>
     <row r="23" ht="14.25" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>11000300001</v>
+        <v>11000100001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>HP+</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>HP+</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>攻击力增加{Percentage}%</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>Increase ATK by {Percentage}%</t>
+          <t>Increase HP by {Percentage}%</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -15966,26 +16086,26 @@
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000200001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>医者自医</t>
+          <t>DR+</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Self-Heal</t>
+          <t>DEF+</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% HP every {Time_S}s</t>
+          <t>Increase DEF by {Percentage}%</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -15996,26 +16116,26 @@
     </row>
     <row r="25" ht="14.25" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000300001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>护甲保养</t>
+          <t>ATK+</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Armor Polish</t>
+          <t>ATK+</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% DEF every {Time_S}s</t>
+          <t>Increase ATK by {Percentage}%</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -16026,26 +16146,26 @@
     </row>
     <row r="26" ht="14.25" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000400001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>再补一刀</t>
+          <t>ASPD+</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Double Tap</t>
+          <t>ASPD+</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒再攻击一次</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>Extra attack every {Time_S}s</t>
+          <t>Increase ASPD by {Percentage}%</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -16056,26 +16176,26 @@
     </row>
     <row r="27" ht="17.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-HP</t>
+        <v>11000500001</v>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>CD-</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Feast-HP</t>
+          <t>CD-</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP per {KillNum} kills</t>
+          <t>Summon CD {Percentage}%</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -16086,26 +16206,26 @@
     </row>
     <row r="28" ht="17.25" customHeight="1" s="1">
       <c r="A28" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-DR</t>
+        <v>11000600001</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>MP-</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Feast-DEF</t>
+          <t>MP-</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
+          <t>Summon MP cost {Percentage}%</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -16116,26 +16236,26 @@
     </row>
     <row r="29" ht="17.25" customHeight="1" s="1">
       <c r="A29" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-ATK</t>
+        <v>12000100001</v>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>医者自医</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Feast-ATK</t>
+          <t>Self-Heal</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
+          <t>Restore {Percentage}% HP every {Time_S}s</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -16146,26 +16266,26 @@
     </row>
     <row r="30" ht="17.25" customHeight="1" s="1">
       <c r="A30" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-ASPD</t>
+        <v>12000200001</v>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>护甲保养</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Feast-ASPD</t>
+          <t>Armor Polish</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
+          <t>Restore {Percentage}% DEF every {Time_S}s</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -16176,26 +16296,26 @@
     </row>
     <row r="31" ht="17.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>痛楚馈赠-HP</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(HP)</t>
+        <v>12000300001</v>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>再补一刀</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>Double Tap</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒再攻击一次</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
+          <t>Extra attack every {Time_S}s</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -16206,26 +16326,26 @@
     </row>
     <row r="32" ht="17.25" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-DR</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(DR)</t>
+          <t>尸堆养料-HP</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>Feast-HP</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% HP per {KillNum} kills</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -16236,26 +16356,26 @@
     </row>
     <row r="33" ht="17.25" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-ATK</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(ATK)</t>
+          <t>尸堆养料-DR</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>Feast-DEF</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -16266,26 +16386,26 @@
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>痛楚馈赠-ASPD</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(ASPD)</t>
+          <t>尸堆养料-ATK</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>Feast-ATK</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -16296,26 +16416,26 @@
     </row>
     <row r="35" ht="17.25" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-HP</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Feast of the Dying(HP)</t>
+          <t>尸堆养料-ASPD</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>Feast-ASPD</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -16326,26 +16446,26 @@
     </row>
     <row r="36" ht="17.25" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-DR</t>
+          <t>痛楚馈赠-HP</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(DR)</t>
+          <t>Gift of Agony(HP)</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -16356,26 +16476,26 @@
     </row>
     <row r="37" ht="17.25" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-ATK</t>
+          <t>痛楚馈赠-DR</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(ATK)</t>
+          <t>Gift of Agony(DR)</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -16386,26 +16506,26 @@
     </row>
     <row r="38" ht="17.25" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>濒死狂宴-ASPD</t>
+          <t>痛楚馈赠-ATK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Feast of the Dying(ASPD)</t>
+          <t>Gift of Agony(ATK)</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
+          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
@@ -16416,26 +16536,26 @@
     </row>
     <row r="39" ht="17.25" customHeight="1" s="1">
       <c r="A39" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 收尸费</t>
+        <v>12002400001</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>痛楚馈赠-ASPD</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corpse Tax</t>
+          <t>Gift of Agony(ASPD)</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {KillNum} kills</t>
+          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
@@ -16446,26 +16566,26 @@
     </row>
     <row r="40" ht="17.25" customHeight="1" s="1">
       <c r="A40" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>痛觉提款机</t>
+        <v>12003100001</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-HP</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Pain ATM</t>
+          <t>Feast of the Dying(HP)</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
@@ -16476,26 +16596,26 @@
     </row>
     <row r="41" ht="17.25" customHeight="1" s="1">
       <c r="A41" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>暴力小费</t>
+        <v>12003200001</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-DR</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Violence Tip</t>
+          <t>Feast of the Dying(DR)</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>Drop crystal per {AttackDamage} dmg dealt</t>
+          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F41" s="0" t="inlineStr">
@@ -16506,26 +16626,26 @@
     </row>
     <row r="42" ht="17.25" customHeight="1" s="1">
       <c r="A42" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>鞭尸成瘾</t>
+        <v>12003300001</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ATK</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Corpse Kicker</t>
+          <t>Feast of the Dying(ATK)</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>Instant attack per {KillNum} kills</t>
+          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F42" s="0" t="inlineStr">
@@ -16536,26 +16656,26 @@
     </row>
     <row r="43" ht="17.25" customHeight="1" s="1">
       <c r="A43" s="0" t="n">
-        <v>12011200001</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>碰瓷反杀</t>
+        <v>12003400001</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ASPD</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Blood Bait</t>
+          <t>Feast of the Dying(ASPD)</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
         </is>
       </c>
       <c r="F43" s="0" t="inlineStr">
@@ -16566,26 +16686,26 @@
     </row>
     <row r="44" ht="17.25" customHeight="1" s="1">
       <c r="A44" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010100001</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>越打越嗨</t>
+          <t xml:space="preserve"> 收尸费</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rage Spiral </t>
+          <t>Corpse Tax</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {AttackDamage} dmg dealt</t>
+          <t>Drop crystal per {KillNum} kills</t>
         </is>
       </c>
       <c r="F44" s="0" t="inlineStr">
@@ -16596,26 +16716,26 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t>拾晶不昧</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>Honest Finder</t>
+        <v>12010200001</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>痛觉提款机</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Pain ATM</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>Auto-collect crystals every {Time_S}s</t>
+          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
@@ -16626,26 +16746,26 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>13000200001</v>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>有利可图</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>Opportunist</t>
+        <v>12010300001</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>暴力小费</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Violence Tip</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>Resurrect on Death</t>
+          <t>Drop crystal per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F46" s="0" t="inlineStr">
@@ -16656,26 +16776,26 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>死而复生</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>Second Wind</t>
+        <v>12011100001</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>鞭尸成瘾</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Corpse Kicker</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>Explode on Death</t>
+          <t>Instant attack per {KillNum} kills</t>
         </is>
       </c>
       <c r="F47" s="0" t="inlineStr">
@@ -16686,26 +16806,26 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>同归于尽</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>Mutual Destruction</t>
+        <v>12011200001</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>碰瓷反杀</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Blood Bait</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>Heal allies {Percentage}% of max HP on death</t>
+          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F48" s="0" t="inlineStr">
@@ -16716,26 +16836,26 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>死得其所-HP</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>Noble Death-HP</t>
+        <v>12011300001</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>越打越嗨</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rage Spiral </t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Shield allies {Percentage}% of max DEF on death</t>
+          <t>Extra attack per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F49" s="0" t="inlineStr">
@@ -16746,26 +16866,26 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>死得其所-DR</t>
+          <t>拾晶不昧</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Noble Death-DEF</t>
+          <t>Honest Finder</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>Spawn {Percentage}% chance crystal on death</t>
+          <t>Auto-collect crystals every {Time_S}s</t>
         </is>
       </c>
       <c r="F50" s="0" t="inlineStr">
@@ -16776,19 +16896,169 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>有利可图</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>Opportunist</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>Resurrect on Death</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>死而复生</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>Explode on Death</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>同归于尽</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>Mutual Destruction</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>Heal allies {Percentage}% of max HP on death</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-HP</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-HP</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>Shield allies {Percentage}% of max DEF on death</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-DR</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-DEF</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>死亡后{Percentage}%生成魔晶</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>Spawn {Percentage}% chance crystal on death</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="B51" s="0" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>死亡税</t>
         </is>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>Death Tax</t>
         </is>
       </c>
-      <c r="F51" s="0" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2886,40 +2886,40 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="0" t="n">
-        <v>50101</v>
-      </c>
-      <c r="B88" s="0" t="inlineStr">
-        <is>
-          <t>继续</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="inlineStr">
-        <is>
-          <t>Continue</t>
-        </is>
-      </c>
-      <c r="D88" s="0" t="inlineStr">
+      <c r="A88" t="n">
+        <v>50007</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Healing Done</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="0" t="n">
-        <v>51001</v>
-      </c>
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>深渊馈赠</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="inlineStr">
-        <is>
-          <t>Abyssal Blessing</t>
-        </is>
-      </c>
-      <c r="D89" s="0" t="inlineStr">
+      <c r="A89" t="n">
+        <v>50008</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>受疗</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Healing Received</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -2927,16 +2927,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Choose an Abyssal Blessing</t>
+          <t>Continue</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -2947,16 +2947,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Abyssal Blessing</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2967,16 +2967,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>Select Reward</t>
+          <t>Choose an Abyssal Blessing</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -2987,7 +2987,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -3007,16 +3007,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Choices Left: {0}/{1}</t>
+          <t>Select Reward</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -3027,16 +3027,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>No Choices Left</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -3047,16 +3047,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Still have choices! End selection?</t>
+          <t>Choices Left: {0}/{1}</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -3067,16 +3067,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>Doom Council</t>
+          <t>No Choices Left</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -3087,16 +3087,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>Select a Proposal</t>
+          <t>Still have choices! End selection?</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -3107,16 +3107,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>Submit '{0}' to Council of Doom?</t>
+          <t>Doom Council</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -3127,16 +3127,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>Pass Rate: {0}%</t>
+          <t>Select a Proposal</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -3147,16 +3147,16 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>Start Voting</t>
+          <t>Submit '{0}' to Council of Doom?</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -3167,16 +3167,16 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>Leave Council</t>
+          <t>Pass Rate: {0}%</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -3187,16 +3187,16 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>Aye</t>
+          <t>Start Voting</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -3207,16 +3207,16 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>Nay</t>
+          <t>Leave Council</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -3227,16 +3227,16 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Aye</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -3247,16 +3247,16 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Nay</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -3267,16 +3267,16 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>Violent Persuasion</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -3287,16 +3287,16 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>Free Time</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3307,16 +3307,16 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>Submit Proposal '{0}'?</t>
+          <t>Violent Persuasion</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3327,16 +3327,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave the council? Spent resources will not be refunded.</t>
+          <t>Free Time</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3347,16 +3347,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>当前议案通过率:{0}%</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>Current Proposal Approval Rate: {0}%</t>
+          <t>Submit Proposal '{0}'?</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3367,11 +3367,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>Are you sure you want to leave the council? Spent resources will not be refunded.</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3382,16 +3387,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord slayers are approaching...</t>
+          <t>Current Proposal Approval Rate: {0}%</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3402,16 +3407,11 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
-        </is>
-      </c>
-      <c r="C114" s="0" t="inlineStr">
-        <is>
-          <t>A horde of heroes is approaching...</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3422,16 +3422,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>Warning! A hero party is swarming in...</t>
+          <t>Demon Lord slayers are approaching...</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3442,16 +3442,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>Subjugation forces detected approaching...</t>
+          <t>A horde of heroes is approaching...</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3462,16 +3462,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>The Allied Hero Army is closing in...</t>
+          <t>Warning! A hero party is swarming in...</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3482,16 +3482,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>A horde of self-proclaimed heroes has arrived...</t>
+          <t>Subjugation forces detected approaching...</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3502,16 +3502,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>Alert: Allies of justice are approaching...</t>
+          <t>The Allied Hero Army is closing in...</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3522,16 +3522,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Upgrade</t>
+          <t>A horde of self-proclaimed heroes has arrived...</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3542,16 +3542,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Begin Sacrifice</t>
+          <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3562,16 +3562,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Success Rate</t>
+          <t>Sacrifice Upgrade</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3582,16 +3582,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Select Sacrifice First!</t>
+          <t>Begin Sacrifice</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3602,16 +3602,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Too Many Sacrifices!</t>
+          <t>Success Rate</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3622,16 +3622,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Start Sacrifice? Current Rate: {0}</t>
+          <t>Select Sacrifice First!</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3642,16 +3642,16 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Allocate All Points First!</t>
+          <t>Too Many Sacrifices!</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3662,16 +3662,16 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Points Left: {0}</t>
+          <t>Start Sacrifice? Current Rate: {0}</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3682,16 +3682,16 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>Research for x{0} Magic Crystals?</t>
+          <t>Allocate All Points First!</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3702,16 +3702,16 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Points Left: {0}</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3722,16 +3722,16 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Research for x{0} Magic Crystals?</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3742,16 +3742,16 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3762,16 +3762,16 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>Select Rebirth Appearance</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3782,16 +3782,16 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3802,16 +3802,16 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>Confirm Rebirth with this look?</t>
+          <t>Select Rebirth Appearance</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3822,14 +3822,18 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
-        </is>
-      </c>
-      <c r="C135" s="0" t="n"/>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3838,14 +3842,18 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="C136" s="0" t="n"/>
+          <t>是否以此外观完成转生？</t>
+        </is>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>Confirm Rebirth with this look?</t>
+        </is>
+      </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3854,18 +3862,14 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
-        </is>
-      </c>
-      <c r="C137" s="0" t="inlineStr">
-        <is>
-          <t>Bribe</t>
-        </is>
-      </c>
+          <t>成就</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="n"/>
       <c r="D137" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3874,18 +3878,14 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
-        </is>
-      </c>
-      <c r="C138" s="0" t="inlineStr">
-        <is>
-          <t>Start Evolution</t>
-        </is>
-      </c>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="n"/>
       <c r="D138" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>End Evolution</t>
+          <t>Bribe</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3914,16 +3914,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>Complete Evolution</t>
+          <t>Start Evolution</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3934,16 +3934,16 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>End Evolution? Materials won't be refunded!</t>
+          <t>End Evolution</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3954,16 +3954,16 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Complete Evolution</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3974,16 +3974,16 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>Select Evolution Target</t>
+          <t>End Evolution? Materials won't be refunded!</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3994,16 +3994,16 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>Select Support Demon</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
@@ -4014,16 +4014,16 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected</t>
+          <t>Select Evolution Target</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
@@ -4034,16 +4034,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>Speed Up x{0}</t>
+          <t>Select Support Demon</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -4054,16 +4054,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+          <t>No Demon Selected</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -4074,11 +4074,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>加速进阶 x{0}</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>Speed Up x{0}</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -4089,11 +4094,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -4104,16 +4114,11 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
-        </is>
-      </c>
-      <c r="C150" s="0" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4124,16 +4129,11 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C151" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -4144,16 +4144,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -4164,16 +4164,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -4184,16 +4184,16 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -4204,16 +4204,16 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -4224,16 +4224,16 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -4244,16 +4244,16 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -4264,16 +4264,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -4284,16 +4284,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -4304,16 +4304,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4324,16 +4324,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4344,16 +4344,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4364,16 +4364,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4384,16 +4384,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4404,16 +4404,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4424,16 +4424,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4444,16 +4444,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>Sort: Team</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4464,16 +4464,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4484,11 +4484,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：阵容</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Team</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4499,11 +4504,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4514,11 +4524,11 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4529,16 +4539,11 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
-        </is>
-      </c>
-      <c r="C172" s="0" t="inlineStr">
-        <is>
-          <t>Sort: Type</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4549,14 +4554,13 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
-        </is>
-      </c>
-      <c r="C173" s="0" t="n"/>
+          <t>道具名字:{0}</t>
+        </is>
+      </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4565,14 +4569,18 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
-        </is>
-      </c>
-      <c r="C174" s="0" t="n"/>
+          <t>排序：同类</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Type</t>
+        </is>
+      </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4581,11 +4589,11 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="C175" s="0" t="n"/>
@@ -4597,18 +4605,14 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
-        </is>
-      </c>
-      <c r="C176" s="0" t="inlineStr">
-        <is>
-          <t>No Related Items</t>
-        </is>
-      </c>
+          <t>倒序</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="n"/>
       <c r="D176" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4617,18 +4621,14 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
-        </is>
-      </c>
-      <c r="C177" s="0" t="inlineStr">
-        <is>
-          <t>No Related Creatures</t>
-        </is>
-      </c>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="n"/>
       <c r="D177" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4637,14 +4637,18 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C178" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4653,16 +4657,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>No Related Creatures</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4673,18 +4677,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
-        </is>
-      </c>
-      <c r="C180" s="0" t="inlineStr">
-        <is>
-          <t>Not Enough Reputation!</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="n"/>
       <c r="D180" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4693,16 +4693,16 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4713,16 +4713,16 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4733,16 +4733,16 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4753,16 +4753,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4773,16 +4773,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4793,16 +4793,16 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4813,16 +4813,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4833,16 +4833,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4853,16 +4853,16 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4873,16 +4873,16 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4893,16 +4893,16 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>Total Clears</t>
+          <t>Difficulty {0}</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4913,16 +4913,16 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4933,19 +4933,59 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>Total Clears</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B193" s="0" t="inlineStr">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C193" s="0" t="inlineStr">
+      <c r="C195" s="0" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D193" s="0" t="inlineStr">
+      <c r="D195" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -9728,7 +9768,7 @@
           <t>奖励多多</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>More Rewards</t>
         </is>
@@ -9738,7 +9778,7 @@
           <t>战斗通关时，获得的奖励数量+1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Gain 1 extra reward item when clearing a battle</t>
         </is>
@@ -9758,7 +9798,7 @@
           <t>再来一瓶</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>One More Pick</t>
         </is>
@@ -9768,7 +9808,7 @@
           <t>战斗通关时，可选择的奖励次数+1（超过实际奖励数量时多余次数无效）</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Gain 1 extra reward pick (extra picks beyond available rewards have no effect)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -2886,40 +2886,40 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="0" t="n">
         <v>50007</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>治疗</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="0" t="inlineStr">
         <is>
           <t>Healing Done</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="0" t="n">
         <v>50008</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>受疗</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>Healing Received</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>战斗通关时，可选择的奖励次数+1（超过实际奖励数量时多余次数无效）</t>
+          <t>战斗通关时，可选择的奖励次数+1</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>Gain 1 extra reward pick (extra picks beyond available rewards have no effect)</t>
+          <t>Gain 1 extra reward pick</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -10085,12 +10085,12 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>减少10%所有魔物复活CD时间</t>
+          <t>减少10%所有魔物召唤CD时间</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 10%</t>
+          <t>All demon summon CD reduced by 10%</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>减少20%所有魔物复活CD时间</t>
+          <t>减少20%所有魔物召唤CD时间</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 20%</t>
+          <t>All demon summon CD reduced by 20%</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>减少30%所有魔物复活CD时间</t>
+          <t>减少30%所有魔物召唤CD时间</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 30%</t>
+          <t>All demon summon CD reduced by 30%</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>减少40%所有魔物复活CD时间</t>
+          <t>减少40%所有魔物召唤CD时间</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 40%</t>
+          <t>All demon summon CD reduced by 40%</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t>减少50%所有魔物复活CD时间</t>
+          <t>减少50%所有魔物召唤CD时间</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>All demon revive CD reduced by 50%</t>
+          <t>All demon summon CD reduced by 50%</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -7385,12 +7385,12 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>开启献祭设施</t>
+          <t>开启献祭升级设施</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>Unlock Sacrifice Facility</t>
+          <t>Unlock Sacrifice Upgrade Facility</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -7385,7 +7385,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>开启献祭升级设施</t>
+          <t>开启献祭升级设施(经验足够之后在魔物页面升级)</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -4114,12 +4114,12 @@
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>选择素材魔物</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>Select Support Demon</t>
+          <t>Select Material Demon</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4190,46 +4190,41 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>90001</v>
+        <v>80011</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="D154" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
+          <t>素材魔物最多只能选择{0}只</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>Up to {0} material demons can be selected</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="0" t="n">
-        <v>90002</v>
-      </c>
-      <c r="B155" s="0" t="inlineStr">
-        <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
-        </is>
-      </c>
-      <c r="D155" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
+      <c r="A155" t="n">
+        <v>80012</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>还未选择素材魔物</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>No Material Demon Selected</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
-        </is>
-      </c>
-      <c r="C156" s="0" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -4240,16 +4235,11 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C157" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -4260,16 +4250,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -4280,16 +4270,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -4300,16 +4290,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4320,16 +4310,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4340,16 +4330,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4360,16 +4350,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4380,16 +4370,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4400,16 +4390,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4420,16 +4410,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4440,16 +4430,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4460,16 +4450,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4480,16 +4470,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4500,16 +4490,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4520,16 +4510,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4540,16 +4530,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4560,16 +4550,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>Sort: Team</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4580,16 +4570,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4600,11 +4590,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：阵容</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Team</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4615,11 +4610,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4630,11 +4630,11 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4645,16 +4645,11 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
-        </is>
-      </c>
-      <c r="C178" s="0" t="inlineStr">
-        <is>
-          <t>Sort: Type</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4665,14 +4660,13 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
-        </is>
-      </c>
-      <c r="C179" s="0" t="n"/>
+          <t>道具名字:{0}</t>
+        </is>
+      </c>
       <c r="D179" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4681,14 +4675,18 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
-        </is>
-      </c>
-      <c r="C180" s="0" t="n"/>
+          <t>排序：同类</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Type</t>
+        </is>
+      </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4697,11 +4695,11 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="C181" s="0" t="n"/>
@@ -4713,18 +4711,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
-        </is>
-      </c>
-      <c r="C182" s="0" t="inlineStr">
-        <is>
-          <t>No Related Items</t>
-        </is>
-      </c>
+          <t>倒序</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="n"/>
       <c r="D182" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4733,18 +4727,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
-        </is>
-      </c>
-      <c r="C183" s="0" t="inlineStr">
-        <is>
-          <t>No Related Creatures</t>
-        </is>
-      </c>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="n"/>
       <c r="D183" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4753,14 +4743,18 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C184" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D184" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4769,16 +4763,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>No Related Creatures</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4789,18 +4783,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
-        </is>
-      </c>
-      <c r="C186" s="0" t="inlineStr">
-        <is>
-          <t>Not Enough Reputation!</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="n"/>
       <c r="D186" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4809,16 +4799,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4829,16 +4819,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4849,16 +4839,16 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4869,16 +4859,16 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4889,16 +4879,16 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4909,16 +4899,16 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4929,16 +4919,16 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4949,16 +4939,16 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4969,16 +4959,16 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4989,16 +4979,16 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -5009,16 +4999,16 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>Total Clears</t>
+          <t>Difficulty {0}</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -5029,16 +5019,16 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -5049,19 +5039,59 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>Total Clears</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B199" s="0" t="inlineStr">
+      <c r="B201" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C199" s="0" t="inlineStr">
+      <c r="C201" s="0" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D199" s="0" t="inlineStr">
+      <c r="D201" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -9896,120 +9926,120 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>1000004001</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>大力出奇迹</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Roid Rage</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，攻击力翻倍</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's ATK is doubled</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>1000005001</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>膘肥体壮</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Big Boned</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，生命值翻倍</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's HP is doubled</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>1000006001</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>钢铁憨憨</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Tin Can</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，护甲翻倍</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's DR is doubled</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>1000007001</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>急性子</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>Caffeine Rush</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，攻击速度翻倍（攻击间隔减半）</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>A random defending demon attacks twice as fast</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
@@ -16291,120 +16321,120 @@
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" s="1">
-      <c r="A23" t="n">
+      <c r="A23" s="0" t="n">
         <v>3001100001</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>大力出奇迹</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>Roid Rage</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，攻击力翻倍</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's ATK is doubled</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="1">
-      <c r="A24" t="n">
+      <c r="A24" s="0" t="n">
         <v>3001200001</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>膘肥体壮</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>Big Boned</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，生命值翻倍</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's HP is doubled</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="1">
-      <c r="A25" t="n">
+      <c r="A25" s="0" t="n">
         <v>3001300001</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>钢铁憨憨</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>Tin Can</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，护甲翻倍</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>A random defending demon's DR is doubled</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="1">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>3001400001</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>急性子</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>Caffeine Rush</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>随机一只防守魔物，攻击速度翻倍</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>A random defending demon attacks twice as fast</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -4204,15 +4204,15 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" s="0" t="n">
         <v>80012</v>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="0" t="inlineStr">
         <is>
           <t>还未选择素材魔物</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="0" t="inlineStr">
         <is>
           <t>No Material Demon Selected</t>
         </is>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>皮糙肉厚</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>DR+</t>
+          <t>铁布衫</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>力大砖飞</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>ASPD+</t>
+          <t>快到飞起</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>CD-</t>
+          <t>阴魂不散</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>MP-</t>
+          <t>骨折价</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>Sort: Team</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>Sort: Type</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4695,11 +4695,11 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000012</v>
+        <v>2000014</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="C181" s="0" t="n"/>
@@ -4711,14 +4711,18 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000013</v>
+        <v>2000015</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
-        </is>
-      </c>
-      <c r="C182" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D182" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4727,14 +4731,18 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000014</v>
+        <v>2000016</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
-        </is>
-      </c>
-      <c r="C183" s="0" t="n"/>
+          <t>没有相关魔物</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>No Related Creatures</t>
+        </is>
+      </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4743,18 +4751,14 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000015</v>
+        <v>2000017</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
-        </is>
-      </c>
-      <c r="C184" s="0" t="inlineStr">
-        <is>
-          <t>No Related Items</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="n"/>
       <c r="D184" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4763,16 +4767,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000016</v>
+        <v>2000018</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>No Related Creatures</t>
+          <t>Rarity</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4783,14 +4787,18 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000017</v>
+        <v>2000019</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C186" s="0" t="n"/>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4799,16 +4807,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>3000001</v>
+        <v>2000020</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4819,16 +4827,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>3000002</v>
+        <v>2000021</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Reputation!</t>
+          <t>Combat</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4839,16 +4847,16 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>3000003</v>
+        <v>2000022</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4858,40 +4866,40 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="0" t="n">
-        <v>3000004</v>
-      </c>
-      <c r="B190" s="0" t="inlineStr">
-        <is>
-          <t>还未选择魔物！</t>
-        </is>
-      </c>
-      <c r="C190" s="0" t="inlineStr">
-        <is>
-          <t>No Demon Selected!</t>
-        </is>
-      </c>
-      <c r="D190" s="0" t="inlineStr">
+      <c r="A190" t="n">
+        <v>2000023</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>低等级...</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Min Level...</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="0" t="n">
-        <v>3000005</v>
-      </c>
-      <c r="B191" s="0" t="inlineStr">
-        <is>
-          <t>转生成功！</t>
-        </is>
-      </c>
-      <c r="C191" s="0" t="inlineStr">
-        <is>
-          <t>Rebirth Success!</t>
-        </is>
-      </c>
-      <c r="D191" s="0" t="inlineStr">
+      <c r="A191" t="n">
+        <v>2000024</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>高等级...</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Max Level...</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -4899,16 +4907,16 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>4000006</v>
+        <v>3000001</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4919,16 +4927,16 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
-        <v>4000008</v>
+        <v>3000002</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4939,16 +4947,16 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="n">
-        <v>4000010</v>
+        <v>3000003</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4959,16 +4967,16 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="n">
-        <v>4000011</v>
+        <v>3000004</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4979,16 +4987,16 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="n">
-        <v>4000012</v>
+        <v>3000005</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -4999,16 +5007,16 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="n">
-        <v>4000013</v>
+        <v>4000006</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -5019,16 +5027,16 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="n">
-        <v>4000014</v>
+        <v>4000008</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -5039,16 +5047,16 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="n">
-        <v>4000015</v>
+        <v>4000010</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>Total Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -5059,16 +5067,16 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="n">
-        <v>4000016</v>
+        <v>4000011</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -5079,19 +5087,119 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>Conquer Clears</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>Difficulty {0}</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>{0}h {1}m</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>Total Clears</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B201" s="0" t="inlineStr">
+      <c r="B206" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C201" s="0" t="inlineStr">
+      <c r="C206" s="0" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D201" s="0" t="inlineStr">
+      <c r="D206" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D206"/>
+  <dimension ref="A1:D208"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -1761,16 +1761,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>是否退出当前征服之旅，并回到基地？（退出之后会损失所有进度）</t>
+          <t>路径长度</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Exit conquest and return to base? (All progress will be lost!)</t>
+          <t>Road Length</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -1781,16 +1781,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>是否前往？</t>
+          <t>是否退出当前征服之旅，并回到基地？（退出之后会损失所有进度）</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Travel?</t>
+          <t>Exit conquest and return to base? (All progress will be lost!)</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -1801,16 +1801,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>是否结束当前战斗？退出后当前战斗进度将不会保留。</t>
+          <t>是否前往？</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>End the current battle? Your current progress will not be saved.</t>
+          <t>Travel?</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -1821,16 +1821,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>1001</v>
+        <v>503</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>头</t>
+          <t>是否结束当前战斗？退出后当前战斗进度将不会保留。</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>End the current battle? Your current progress will not be saved.</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -1841,16 +1841,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>帽子</t>
+          <t>头</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Hat</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -1861,16 +1861,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>发型</t>
+          <t>帽子</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>Hat</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -1881,16 +1881,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>身体</t>
+          <t>发型</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Hair</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -1901,16 +1901,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>眼睛</t>
+          <t>身体</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Eye</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -1921,16 +1921,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>嘴巴</t>
+          <t>眼睛</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Mouth</t>
+          <t>Eye</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -1941,16 +1941,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>2001</v>
+        <v>1006</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>监视之塔</t>
+          <t>嘴巴</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Watchtower</t>
+          <t>Mouth</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -1961,16 +1961,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>传送门</t>
+          <t>监视之塔</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Watchtower</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -1981,16 +1981,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>传送门</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Council of Doom</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -2001,16 +2001,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>发言席</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Dispatch Box</t>
+          <t>Council of Doom</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -2021,16 +2021,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>议员</t>
+          <t>发言席</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Councilor</t>
+          <t>Dispatch Box</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -2041,16 +2041,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>议员</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Achievement</t>
+          <t>Councilor</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -2061,16 +2061,16 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>10001</v>
+        <v>2006</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>购买</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Achievement</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -2080,20 +2080,20 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="n">
-        <v>10003</v>
-      </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>下一个</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>Next</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="A47" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>刷新次数已用完</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Out of Refreshes</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -2101,16 +2101,16 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>结束</t>
+          <t>购买</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -2121,16 +2121,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>再来一次</t>
+          <t>下一个</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Try Again</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -2141,16 +2141,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>跳过所有</t>
+          <t>结束</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Skip All</t>
+          <t>Ascend</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -2161,16 +2161,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>展示</t>
+          <t>再来一次</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Show</t>
+          <t>Try Again</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -2181,16 +2181,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>重命名</t>
+          <t>跳过所有</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Skip All</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -2201,16 +2201,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>20001</v>
+        <v>10007</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>展示</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Lineup</t>
+          <t>Show</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -2221,16 +2221,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>20002</v>
+        <v>10008</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>孕育</t>
+          <t>重命名</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Incubate</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -2241,16 +2241,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Lineup</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -2261,16 +2261,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>20004</v>
+        <v>20002</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>研究</t>
+          <t>孕育</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Incubate</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -2281,16 +2281,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>20005</v>
+        <v>20003</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -2301,11 +2301,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>20006</v>
+        <v>20004</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>研究</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>Research</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -2316,16 +2321,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>30001</v>
+        <v>20005</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>稀</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Ascend</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2336,16 +2341,11 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>30002</v>
+        <v>20006</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>级</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>Lv</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2356,16 +2356,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>阵</t>
+          <t>稀</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -2376,16 +2376,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>级</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Lv</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2396,16 +2396,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>30005</v>
+        <v>30003</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>阵容 {0}</t>
+          <t>阵</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Lineup {0}</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2416,16 +2416,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>30006</v>
+        <v>30004</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>超过阵容魔物上限！</t>
+          <t>名</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Team Full!</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2436,14 +2436,18 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>30007</v>
+        <v>30005</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>阵容魔物数量 {0}</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="n"/>
+          <t>阵容 {0}</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>Lineup {0}</t>
+        </is>
+      </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -2452,16 +2456,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>超过阵容魔物上限！</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Game</t>
+          <t>Team Full!</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -2472,18 +2476,14 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>40002</v>
+        <v>30007</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
+          <t>阵容魔物数量 {0}</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="n"/>
       <c r="D67" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -2492,16 +2492,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>音频</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -2512,16 +2512,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>40998</v>
+        <v>40002</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>已开启</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2532,16 +2532,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>40999</v>
+        <v>40003</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>已关闭</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2552,16 +2552,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>41001</v>
+        <v>40998</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>已开启</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>On</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2572,16 +2572,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>41002</v>
+        <v>40999</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>按键提示显示</t>
+          <t>已关闭</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Key Hint Display</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -2592,16 +2592,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>42001</v>
+        <v>41001</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>屏幕分辨率</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Screen Resolution</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2612,16 +2612,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>42002</v>
+        <v>41002</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>锁定帧数</t>
+          <t>按键提示显示</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Lock FPS</t>
+          <t>Key Hint Display</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2632,16 +2632,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>42003</v>
+        <v>42001</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>帧数</t>
+          <t>屏幕分辨率</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>FPS</t>
+          <t>Screen Resolution</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2652,16 +2652,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>43001</v>
+        <v>42002</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>锁定帧数</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Music Volume</t>
+          <t>Lock FPS</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2672,16 +2672,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>43002</v>
+        <v>42003</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>帧数</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Sound Volume</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2692,16 +2692,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>49001</v>
+        <v>43001</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>音乐音量</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Music Volume</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -2712,16 +2712,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>49002</v>
+        <v>43002</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>返回主界面</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Main Menu</t>
+          <t>Sound Volume</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -2732,16 +2732,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>49003</v>
+        <v>49001</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>退出游戏</t>
+          <t>游戏设置</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Exit Game</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -2752,11 +2752,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>49004</v>
+        <v>49002</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>退出战斗</t>
+          <t>返回主界面</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>Main Menu</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -2767,16 +2772,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>50001</v>
+        <v>49003</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>退出游戏</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Exit Game</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -2787,16 +2792,11 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>50002</v>
+        <v>49004</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>击杀</t>
-        </is>
-      </c>
-      <c r="C83" s="0" t="inlineStr">
-        <is>
-          <t>Kill</t>
+          <t>退出战斗</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -2807,16 +2807,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>50003</v>
+        <v>50001</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>经验</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>EXP</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -2827,16 +2827,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>50004</v>
+        <v>50002</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>承伤</t>
+          <t>击杀</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Sustain</t>
+          <t>Kill</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -2847,16 +2847,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>当前征程：{0}/{1}</t>
+          <t>经验</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Journey: {0}/{1}</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -2867,16 +2867,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>50006</v>
+        <v>50004</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>魔力不足</t>
+          <t>承伤</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Not enough mana</t>
+          <t>Sustain</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -2887,16 +2887,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>50007</v>
+        <v>50005</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>当前征程：{0}/{1}</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Healing Done</t>
+          <t>Journey: {0}/{1}</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -2907,16 +2907,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>50008</v>
+        <v>50006</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>受疗</t>
+          <t>魔力不足</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>Healing Received</t>
+          <t>Not enough mana</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -2927,16 +2927,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>50101</v>
+        <v>50007</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Healing Done</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -2947,16 +2947,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>51001</v>
+        <v>50008</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠</t>
+          <t>受疗</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>Abyssal Blessing</t>
+          <t>Healing Received</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2967,16 +2967,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>Choose an Abyssal Blessing</t>
+          <t>Continue</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -2987,16 +2987,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Abyssal Blessing</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -3007,16 +3007,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Select Reward</t>
+          <t>Choose an Abyssal Blessing</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Choices Left: {0}/{1}</t>
+          <t>Select Reward</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -3067,16 +3067,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>No Choices Left</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -3087,16 +3087,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>Still have choices! End selection?</t>
+          <t>Choices Left: {0}/{1}</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -3107,16 +3107,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>Doom Council</t>
+          <t>No Choices Left</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -3127,16 +3127,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>Select a Proposal</t>
+          <t>Still have choices! End selection?</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -3147,16 +3147,16 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>Submit '{0}' to Council of Doom?</t>
+          <t>Doom Council</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -3167,16 +3167,16 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>Pass Rate: {0}%</t>
+          <t>Select a Proposal</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -3187,16 +3187,16 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>Start Voting</t>
+          <t>Submit '{0}' to Council of Doom?</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -3207,16 +3207,16 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>Leave Council</t>
+          <t>Pass Rate: {0}%</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -3227,16 +3227,16 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>Aye</t>
+          <t>Start Voting</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -3247,16 +3247,16 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>Nay</t>
+          <t>Leave Council</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -3267,16 +3267,16 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Aye</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -3287,16 +3287,16 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Nay</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3307,16 +3307,16 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>Violent Persuasion</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3327,16 +3327,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>Free Time</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3347,16 +3347,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>Submit Proposal '{0}'?</t>
+          <t>Violent Persuasion</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3367,16 +3367,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave the council? Spent resources will not be refunded.</t>
+          <t>Free Time</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3387,16 +3387,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>当前议案通过率:{0}%</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>Current Proposal Approval Rate: {0}%</t>
+          <t>Submit Proposal '{0}'?</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3407,11 +3407,16 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>Are you sure you want to leave the council? Spent resources will not be refunded.</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3422,16 +3427,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord slayers are approaching...</t>
+          <t>Current Proposal Approval Rate: {0}%</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3442,16 +3447,11 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
-        </is>
-      </c>
-      <c r="C116" s="0" t="inlineStr">
-        <is>
-          <t>A horde of heroes is approaching...</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3462,16 +3462,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>Warning! A hero party is swarming in...</t>
+          <t>Demon Lord slayers are approaching...</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3482,16 +3482,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>Subjugation forces detected approaching...</t>
+          <t>A horde of heroes is approaching...</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3502,16 +3502,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>The Allied Hero Army is closing in...</t>
+          <t>Warning! A hero party is swarming in...</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3522,16 +3522,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>A horde of self-proclaimed heroes has arrived...</t>
+          <t>Subjugation forces detected approaching...</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3542,16 +3542,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Alert: Allies of justice are approaching...</t>
+          <t>The Allied Hero Army is closing in...</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3562,16 +3562,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Upgrade</t>
+          <t>A horde of self-proclaimed heroes has arrived...</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3582,16 +3582,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Begin Sacrifice</t>
+          <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3602,16 +3602,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Success Rate</t>
+          <t>Sacrifice Upgrade</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3622,16 +3622,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Select Sacrifice First!</t>
+          <t>Begin Sacrifice</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3642,16 +3642,16 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Too Many Sacrifices!</t>
+          <t>Success Rate</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3662,16 +3662,16 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Start Sacrifice? Current Rate: {0}</t>
+          <t>Select Sacrifice First!</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3682,16 +3682,16 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>Allocate All Points First!</t>
+          <t>Too Many Sacrifices!</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3702,16 +3702,16 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>Points Left: {0}</t>
+          <t>Start Sacrifice? Current Rate: {0}</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3722,16 +3722,16 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>61006</v>
+        <v>61004</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Confirm this attribute allocation? It cannot be changed afterwards.</t>
+          <t>Allocate All Points First!</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3742,16 +3742,16 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>61007</v>
+        <v>61005</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>献祭成功，等级提升！</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Succeeded, Level Up!</t>
+          <t>Points Left: {0}</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3762,16 +3762,16 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>61008</v>
+        <v>61006</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>献祭失败，祭品已消耗</t>
+          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Failed, Offerings Consumed</t>
+          <t>Confirm this attribute allocation? It cannot be changed afterwards.</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3782,16 +3782,16 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>62001</v>
+        <v>61007</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>献祭成功，等级提升！</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>Research for x{0} Magic Crystals?</t>
+          <t>Sacrifice Succeeded, Level Up!</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3802,16 +3802,16 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>62002</v>
+        <v>61008</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Sacrifice Failed, Offerings Consumed</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3822,16 +3822,16 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Research for x{0} Magic Crystals?</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3842,16 +3842,16 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3862,16 +3862,16 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>Select Rebirth Appearance</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3882,16 +3882,16 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3902,16 +3902,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>Confirm Rebirth with this look?</t>
+          <t>Select Rebirth Appearance</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3922,14 +3922,18 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
-        </is>
-      </c>
-      <c r="C140" s="0" t="n"/>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3938,14 +3942,18 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="C141" s="0" t="n"/>
+          <t>是否以此外观完成转生？</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>Confirm Rebirth with this look?</t>
+        </is>
+      </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3954,11 +3962,11 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>65001</v>
+        <v>64001</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="C142" s="0" t="n"/>
@@ -3970,18 +3978,14 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>70001</v>
+        <v>64002</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
-        </is>
-      </c>
-      <c r="C143" s="0" t="inlineStr">
-        <is>
-          <t>Bribe</t>
-        </is>
-      </c>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="n"/>
       <c r="D143" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3990,18 +3994,14 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80001</v>
+        <v>65001</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
-        </is>
-      </c>
-      <c r="C144" s="0" t="inlineStr">
-        <is>
-          <t>Start Evolution</t>
-        </is>
-      </c>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="n"/>
       <c r="D144" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4010,16 +4010,16 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>End Evolution</t>
+          <t>Bribe</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
@@ -4030,16 +4030,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>Complete Evolution</t>
+          <t>Start Evolution</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -4050,16 +4050,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>End Evolution? Materials won't be refunded!</t>
+          <t>End Evolution</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -4070,16 +4070,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Complete Evolution</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -4090,16 +4090,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>Select Evolution Target</t>
+          <t>End Evolution? Materials won't be refunded!</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -4110,16 +4110,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>选择素材魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>Select Material Demon</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4130,16 +4130,16 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected</t>
+          <t>Select Evolution Target</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -4150,16 +4150,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择素材魔物</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Speed Up x{0}</t>
+          <t>Select Material Demon</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -4170,16 +4170,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+          <t>No Demon Selected</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -4190,76 +4190,81 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>80011</v>
+        <v>80009</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>素材魔物最多只能选择{0}只</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Up to {0} material demons can be selected</t>
+          <t>Speed Up x{0}</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>80012</v>
+        <v>80010</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>还未选择素材魔物</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>No Material Demon Selected</t>
+          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>90001</v>
+        <v>80011</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="D156" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
+          <t>素材魔物最多只能选择{0}只</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>Up to {0} material demons can be selected</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>90002</v>
+        <v>80012</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
-        </is>
-      </c>
-      <c r="D157" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
+          <t>还未选择素材魔物</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>No Material Demon Selected</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
-        </is>
-      </c>
-      <c r="C158" s="0" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -4270,16 +4275,11 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C159" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -4290,16 +4290,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4310,16 +4310,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4330,16 +4330,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4350,16 +4350,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4370,16 +4370,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4390,16 +4390,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4410,16 +4410,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4430,16 +4430,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4450,16 +4450,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4470,16 +4470,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4490,16 +4490,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4510,16 +4510,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4530,16 +4530,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4550,16 +4550,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4570,16 +4570,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4590,16 +4590,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4610,16 +4610,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4630,11 +4630,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>阵容</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>Team</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4645,11 +4650,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4660,11 +4670,11 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4675,16 +4685,11 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
-        </is>
-      </c>
-      <c r="C180" s="0" t="inlineStr">
-        <is>
-          <t>Type</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4695,14 +4700,13 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
-        </is>
-      </c>
-      <c r="C181" s="0" t="n"/>
+          <t>道具名字:{0}</t>
+        </is>
+      </c>
       <c r="D181" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4711,16 +4715,16 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>No Related Items</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4731,18 +4735,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
-        </is>
-      </c>
-      <c r="C183" s="0" t="inlineStr">
-        <is>
-          <t>No Related Creatures</t>
-        </is>
-      </c>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="n"/>
       <c r="D183" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4751,14 +4751,18 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C184" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D184" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4767,16 +4771,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>No Related Creatures</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4787,18 +4791,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="C186" s="0" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="n"/>
       <c r="D186" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4807,16 +4807,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Rarity</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4827,16 +4827,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4847,59 +4847,59 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
+        <v>2000020</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="n">
+        <v>2000021</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="n">
         <v>2000022</v>
       </c>
-      <c r="B189" s="0" t="inlineStr">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="C189" s="0" t="inlineStr">
+      <c r="C191" s="0" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D189" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>2000023</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>低等级...</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Min Level...</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>2000024</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>高等级...</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Max Level...</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -4907,16 +4907,16 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>Min Level...</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4927,16 +4927,16 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Reputation!</t>
+          <t>Max Level...</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4947,16 +4947,16 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4967,16 +4967,16 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4987,16 +4987,16 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -5007,16 +5007,16 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -5027,16 +5027,16 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -5047,16 +5047,16 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -5067,16 +5067,16 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -5087,16 +5087,16 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
@@ -5107,16 +5107,16 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -5127,16 +5127,16 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -5147,16 +5147,16 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>Total Clears</t>
+          <t>Difficulty {0}</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
@@ -5167,16 +5167,16 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="D205" s="0" t="inlineStr">
@@ -5187,19 +5187,59 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>Total Clears</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B206" s="0" t="inlineStr">
+      <c r="B208" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C206" s="0" t="inlineStr">
+      <c r="C208" s="0" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D206" s="0" t="inlineStr">
+      <c r="D208" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -7478,7 +7518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7755,16 +7795,16 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>100310112</v>
+        <v>100300002</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>剑与魔法：征服难度+1</t>
+          <t>线路数预览</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
+          <t>Route Count Preview</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -7775,11 +7815,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>100400000</v>
+        <v>100300003</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>关卡数预览</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Stage Count Preview</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7790,16 +7835,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>100400001</v>
+        <v>100300004</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>路径长度预览</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Incubation Skip</t>
+          <t>Road Length Preview</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -7810,16 +7855,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>100401000</v>
+        <v>100300005</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>奖励预览</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Unlock R Rarity Incubation</t>
+          <t>Reward Preview</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7830,16 +7875,16 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>100401001</v>
+        <v>100300006</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>传送门刷新</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>R Rarity Rate +1%</t>
+          <t>Portal Refresh</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7850,16 +7895,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>100402000</v>
+        <v>100310112</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -7870,16 +7915,11 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>100402001</v>
+        <v>100400000</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>SR Rarity Rate +1%</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -7890,16 +7930,16 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>100403000</v>
+        <v>100400001</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>Unlock SSR Rarity Incubation</t>
+          <t>Incubation Skip</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -7910,16 +7950,16 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>100403001</v>
+        <v>100401000</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>SSR Rarity Rate +1%</t>
+          <t>Unlock R Rarity Incubation</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -7930,16 +7970,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>100404001</v>
+        <v>100401001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>R Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -7950,16 +7990,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>200000001</v>
+        <v>100402000</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Team Limit +1</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -7970,16 +8010,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>200100001</v>
+        <v>100402001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>解锁一个新阵容</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Unlock New Team</t>
+          <t>SR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -7990,16 +8030,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>200200001</v>
+        <v>100403000</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Crystal Drop Duration +5s</t>
+          <t>Unlock SSR Rarity Incubation</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -8010,16 +8050,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>200300001</v>
+        <v>100403001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Limit +10</t>
+          <t>SSR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -8030,16 +8070,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>200400001</v>
+        <v>100404001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力恢复+1/秒</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Regen +1/s</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -8050,16 +8090,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>300100000</v>
+        <v>200000001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Team Limit +1</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -8070,16 +8110,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>300100001</v>
+        <v>200100001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁一个新阵容</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Unlock New Team</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -8090,16 +8130,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>300100002</v>
+        <v>200200001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Crystal Drop Duration +5s</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -8110,16 +8150,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>300100003</v>
+        <v>200300001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Demon Lord Mana Limit +10</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -8130,16 +8170,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>300100004</v>
+        <v>200400001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>魔王魔力恢复+1/秒</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Demon Lord Mana Regen +1/s</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -8150,16 +8190,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>300100101</v>
+        <v>300100000</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -8170,16 +8210,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>300100102</v>
+        <v>300100001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -8190,16 +8230,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300100201</v>
+        <v>300100002</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -8210,16 +8250,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300100301</v>
+        <v>300100003</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -8230,16 +8270,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300200000</v>
+        <v>300100004</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -8250,16 +8290,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300200001</v>
+        <v>300100101</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -8270,16 +8310,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300200002</v>
+        <v>300100102</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -8290,16 +8330,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300200003</v>
+        <v>300100201</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -8310,16 +8350,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300200004</v>
+        <v>300100301</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -8330,16 +8370,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300200101</v>
+        <v>300200000</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -8350,16 +8390,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300200102</v>
+        <v>300200001</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -8370,16 +8410,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300200201</v>
+        <v>300200002</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -8390,16 +8430,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300200301</v>
+        <v>300200003</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -8410,16 +8450,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300300000</v>
+        <v>300200004</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -8430,16 +8470,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300300001</v>
+        <v>300200101</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -8450,16 +8490,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300300002</v>
+        <v>300200102</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -8470,16 +8510,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300300003</v>
+        <v>300200201</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -8490,16 +8530,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300300004</v>
+        <v>300200301</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8510,16 +8550,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300300101</v>
+        <v>300300000</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8530,16 +8570,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300300102</v>
+        <v>300300001</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8550,16 +8590,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300300201</v>
+        <v>300300002</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8570,16 +8610,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300300301</v>
+        <v>300300003</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8590,16 +8630,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300400000</v>
+        <v>300300004</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8610,16 +8650,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300400001</v>
+        <v>300300101</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8630,16 +8670,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300400002</v>
+        <v>300300102</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8650,16 +8690,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300400003</v>
+        <v>300300201</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8670,16 +8710,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300400004</v>
+        <v>300300301</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8690,16 +8730,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300400005</v>
+        <v>300400000</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8710,16 +8750,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300400101</v>
+        <v>300400001</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8730,16 +8770,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300400102</v>
+        <v>300400002</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8750,16 +8790,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300400201</v>
+        <v>300400003</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8770,16 +8810,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300400301</v>
+        <v>300400004</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8790,16 +8830,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300500000</v>
+        <v>300400005</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8810,16 +8850,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300500001</v>
+        <v>300400101</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8830,16 +8870,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300500002</v>
+        <v>300400102</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8850,16 +8890,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300500003</v>
+        <v>300400201</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8870,16 +8910,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300500004</v>
+        <v>300400301</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8890,16 +8930,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300500101</v>
+        <v>300500000</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8910,16 +8950,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300500102</v>
+        <v>300500001</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8930,16 +8970,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300500201</v>
+        <v>300500002</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -8950,16 +8990,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300500301</v>
+        <v>300500003</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -8970,16 +9010,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300600000</v>
+        <v>300500004</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -8990,16 +9030,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300600001</v>
+        <v>300500101</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -9010,16 +9050,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300600002</v>
+        <v>300500102</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -9030,16 +9070,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300600003</v>
+        <v>300500201</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -9050,16 +9090,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300600004</v>
+        <v>300500301</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -9070,16 +9110,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300600005</v>
+        <v>300600000</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -9090,16 +9130,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300600101</v>
+        <v>300600001</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -9110,16 +9150,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300600102</v>
+        <v>300600002</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -9130,16 +9170,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300600201</v>
+        <v>300600003</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -9150,16 +9190,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300600301</v>
+        <v>300600004</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -9170,16 +9210,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300700000</v>
+        <v>300600005</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -9190,16 +9230,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300700001</v>
+        <v>300600101</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -9210,16 +9250,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>300700002</v>
+        <v>300600102</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -9230,16 +9270,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>300700003</v>
+        <v>300600201</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -9250,16 +9290,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>300700004</v>
+        <v>300600301</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -9270,16 +9310,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>300700101</v>
+        <v>300700000</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -9290,16 +9330,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>300700102</v>
+        <v>300700001</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -9310,16 +9350,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>300700201</v>
+        <v>300700002</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -9330,16 +9370,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>300700301</v>
+        <v>300700003</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -9350,14 +9390,114 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
+        <v>300700004</v>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>解锁职业：兽人魔法师（冰）</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>Unlock Class: Orc Ice Mage</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>Incubate Orcs x5</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>Incubate Orcs x10</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>终焉议会议案：转生兽人</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>Council: Reincarnate as Orc</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B94" s="0" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C94" s="0" t="inlineStr"/>
+      <c r="C99" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D208"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2080,20 +2080,20 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>刷新次数已用完</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>Out of Refreshes</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -5240,6 +5240,26 @@
         </is>
       </c>
       <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t>刷新x{0}</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>Refresh x{0}</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -7518,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7635,16 +7655,16 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>100100001</v>
+        <v>100000006</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>开启献祭升级设施(经验足够之后在魔物页面升级)</t>
+          <t>进阶增益范围预览</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>Unlock Sacrifice Upgrade Facility</t>
+          <t>Buff Range Preview</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -7655,16 +7675,16 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>100100002</v>
+        <v>100100001</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>献祭祭品数量+1</t>
+          <t>开启献祭升级设施(经验足够之后在魔物页面升级)</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Fodder +1</t>
+          <t>Unlock Sacrifice Upgrade Facility</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -7675,16 +7695,16 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>100100003</v>
+        <v>100100002</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>献祭失败保底概率提升</t>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Fail Pity Up</t>
+          <t>Sacrifice Fodder +1</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -7695,16 +7715,16 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>100100004</v>
+        <v>100100003</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>不同魔物献祭成功率提升</t>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>Cross-species Sacrifice Rate Up</t>
+          <t>Sacrifice Fail Pity Up</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -7715,16 +7735,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>100200001</v>
+        <v>100100004</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Unlock Council of Doom</t>
+          <t>Cross-species Sacrifice Rate Up</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -7735,16 +7755,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>100200002</v>
+        <v>100200001</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon Renaming</t>
+          <t>Unlock Council of Doom</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -7755,16 +7775,16 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>100200003</v>
+        <v>100200002</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon King Renaming</t>
+          <t>Council: Demon Renaming</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -7775,16 +7795,16 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>100300001</v>
+        <v>100200003</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Portal: +1 World Choice</t>
+          <t>Council: Demon King Renaming</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -7795,16 +7815,16 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>线路数预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Route Count Preview</t>
+          <t>Portal: +1 World Choice</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -7815,16 +7835,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>关卡数预览</t>
+          <t>线路数预览</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Stage Count Preview</t>
+          <t>Route Count Preview</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7835,16 +7855,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>路径长度预览</t>
+          <t>关卡数预览</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Road Length Preview</t>
+          <t>Stage Count Preview</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -7855,16 +7875,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>奖励预览</t>
+          <t>路径长度预览</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Reward Preview</t>
+          <t>Road Length Preview</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7875,16 +7895,16 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>传送门刷新</t>
+          <t>奖励预览</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Portal Refresh</t>
+          <t>Reward Preview</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7895,16 +7915,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>100310112</v>
+        <v>100300006</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>剑与魔法：征服难度+1</t>
+          <t>传送门刷新</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
+          <t>Portal Refresh</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -7915,11 +7935,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>100400000</v>
+        <v>100310112</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>剑与魔法：征服难度+1</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -7930,16 +7955,11 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>Incubation Skip</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -7950,16 +7970,16 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Unlock R Rarity Incubation</t>
+          <t>Incubation Skip</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -7970,16 +7990,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>R Rarity Rate +1%</t>
+          <t>Unlock R Rarity Incubation</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -7990,16 +8010,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>R Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -8010,16 +8030,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>SR Rarity Rate +1%</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -8030,16 +8050,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Unlock SSR Rarity Incubation</t>
+          <t>SR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -8050,16 +8070,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>SSR Rarity Rate +1%</t>
+          <t>Unlock SSR Rarity Incubation</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -8070,16 +8090,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>100404001</v>
+        <v>100403001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>SSR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -8090,16 +8110,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>200000001</v>
+        <v>100404001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Team Limit +1</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -8110,16 +8130,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>200100001</v>
+        <v>200000001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>解锁一个新阵容</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Unlock New Team</t>
+          <t>Team Limit +1</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -8130,16 +8150,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>200200001</v>
+        <v>200100001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁一个新阵容</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Crystal Drop Duration +5s</t>
+          <t>Unlock New Team</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -8150,16 +8170,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Limit +10</t>
+          <t>Crystal Drop Duration +5s</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -8170,16 +8190,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力恢复+1/秒</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Regen +1/s</t>
+          <t>Demon Lord Mana Limit +10</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -8190,16 +8210,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>300100000</v>
+        <v>200400001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔王魔力恢复+1/秒</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Demon Lord Mana Regen +1/s</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -8210,16 +8230,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>300100001</v>
+        <v>200500001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>深渊馈赠刷新次数+1</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Abyssal Blessing Refresh +1</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -8230,16 +8250,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300100002</v>
+        <v>300100000</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -8250,16 +8270,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300100003</v>
+        <v>300100001</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -8270,16 +8290,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300100004</v>
+        <v>300100002</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -8290,16 +8310,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300100101</v>
+        <v>300100003</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -8310,16 +8330,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300100102</v>
+        <v>300100004</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -8330,16 +8350,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300100201</v>
+        <v>300100101</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -8350,16 +8370,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300100301</v>
+        <v>300100102</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -8370,16 +8390,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300200000</v>
+        <v>300100201</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -8390,16 +8410,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300200001</v>
+        <v>300100301</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -8410,16 +8430,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300200002</v>
+        <v>300200000</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -8430,16 +8450,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300200003</v>
+        <v>300200001</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -8450,16 +8470,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300200004</v>
+        <v>300200002</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -8470,16 +8490,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300200101</v>
+        <v>300200003</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -8490,16 +8510,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300200102</v>
+        <v>300200004</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -8510,16 +8530,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300200201</v>
+        <v>300200101</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -8530,16 +8550,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300200301</v>
+        <v>300200102</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8550,16 +8570,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300300000</v>
+        <v>300200201</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8570,16 +8590,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300300001</v>
+        <v>300200301</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8590,16 +8610,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300300002</v>
+        <v>300300000</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8610,16 +8630,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300300003</v>
+        <v>300300001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8630,16 +8650,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300300004</v>
+        <v>300300002</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8650,16 +8670,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300300101</v>
+        <v>300300003</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8670,16 +8690,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300300102</v>
+        <v>300300004</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8690,16 +8710,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300300201</v>
+        <v>300300101</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8710,16 +8730,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300300301</v>
+        <v>300300102</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8730,16 +8750,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300400000</v>
+        <v>300300201</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8750,16 +8770,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300400001</v>
+        <v>300300301</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8770,16 +8790,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300400002</v>
+        <v>300400000</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8790,16 +8810,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300400003</v>
+        <v>300400001</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8810,16 +8830,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300400004</v>
+        <v>300400002</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8830,16 +8850,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300400005</v>
+        <v>300400003</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8850,16 +8870,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300400101</v>
+        <v>300400004</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8870,16 +8890,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300400102</v>
+        <v>300400005</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8890,16 +8910,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300400201</v>
+        <v>300400101</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8910,16 +8930,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300400301</v>
+        <v>300400102</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8930,16 +8950,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300500000</v>
+        <v>300400201</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8950,16 +8970,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300500001</v>
+        <v>300400301</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8970,16 +8990,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300500002</v>
+        <v>300500000</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -8990,16 +9010,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300500003</v>
+        <v>300500001</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -9010,16 +9030,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300500004</v>
+        <v>300500002</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -9030,16 +9050,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300500101</v>
+        <v>300500003</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -9050,16 +9070,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300500102</v>
+        <v>300500004</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -9070,16 +9090,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300500201</v>
+        <v>300500101</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -9090,16 +9110,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300500301</v>
+        <v>300500102</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -9110,16 +9130,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300600000</v>
+        <v>300500201</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -9130,16 +9150,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300600001</v>
+        <v>300500301</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -9150,16 +9170,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300600002</v>
+        <v>300600000</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -9170,16 +9190,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300600003</v>
+        <v>300600001</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -9190,16 +9210,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300600004</v>
+        <v>300600002</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -9210,16 +9230,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300600005</v>
+        <v>300600003</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -9230,16 +9250,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300600101</v>
+        <v>300600004</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -9250,16 +9270,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>300600102</v>
+        <v>300600005</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -9270,16 +9290,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>300600201</v>
+        <v>300600101</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -9290,16 +9310,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>300600301</v>
+        <v>300600102</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -9310,16 +9330,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>300700000</v>
+        <v>300600201</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -9330,16 +9350,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>300700001</v>
+        <v>300600301</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -9350,16 +9370,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>300700002</v>
+        <v>300700000</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -9370,16 +9390,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>300700003</v>
+        <v>300700001</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -9390,16 +9410,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>300700004</v>
+        <v>300700002</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -9410,16 +9430,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>300700101</v>
+        <v>300700003</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -9430,16 +9450,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>300700102</v>
+        <v>300700004</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Unlock Class: Orc Ice Mage</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -9450,16 +9470,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>300700201</v>
+        <v>300700101</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Incubate Orcs x5</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -9470,16 +9490,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>300700301</v>
+        <v>300700102</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Incubate Orcs x10</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -9490,14 +9510,54 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>终焉议会议案：转生兽人</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>Council: Reincarnate as Orc</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B99" s="0" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C99" s="0" t="inlineStr"/>
+      <c r="C101" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9986,7 +10046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -11288,6 +11348,906 @@
         </is>
       </c>
       <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="n">
+        <v>2000008001</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.1</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-ATK Lv.1</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物攻击力增加1%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 1% ATK (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="n">
+        <v>2000008002</v>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.2</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-ATK Lv.2</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物攻击力增加2%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 2% ATK (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="n">
+        <v>2000008003</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.3</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-ATK Lv.3</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物攻击力增加3%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 3% ATK (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="n">
+        <v>2000008004</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.4</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-ATK Lv.4</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物攻击力增加4%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 4% ATK (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="n">
+        <v>2000008005</v>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·攻击Lv.5</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-ATK Lv.5</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物攻击力增加5%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 5% ATK (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="n">
+        <v>2000009001</v>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.1</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-DEF Lv.1</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物护甲增加1%（每只加成、不含自身）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 1% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="n">
+        <v>2000009002</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.2</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-DEF Lv.2</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物护甲增加2%（每只加成、不含自身）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 2% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="n">
+        <v>2000009003</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.3</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-DEF Lv.3</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物护甲增加3%（每只加成、不含自身）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 3% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="n">
+        <v>2000009004</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.4</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-DEF Lv.4</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物护甲增加4%（每只加成、不含自身）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 4% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="n">
+        <v>2000009005</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·护甲Lv.5</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-DEF Lv.5</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物护甲增加5%（每只加成、不含自身）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 5% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="n">
+        <v>2000010001</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.1</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-HP Lv.1</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物生命增加1%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 1% HP (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
+        <v>2000010002</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.2</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-HP Lv.2</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物生命增加2%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 2% HP (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="n">
+        <v>2000010003</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.3</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-HP Lv.3</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物生命增加3%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 3% HP (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="n">
+        <v>2000010004</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.4</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-HP Lv.4</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物生命增加4%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 4% HP (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="n">
+        <v>2000010005</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>都是兄弟·生命Lv.5</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>Band of Brothers-HP Lv.5</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>场上魔物每多1只，全体魔物生命增加5%（每只加成、不含自身）</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>Each extra demon on field grants all demons 5% HP (per demon, excluding self)</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>2000011001</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.1</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-ATK Lv.1</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加1%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 1% ATK (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>2000011002</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.2</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-ATK Lv.2</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加2%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 2% ATK (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>2000011003</v>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.3</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-ATK Lv.3</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加3%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 3% ATK (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
+        <v>2000011004</v>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.4</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-ATK Lv.4</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加4%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 4% ATK (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
+        <v>2000011005</v>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·攻击Lv.5</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-ATK Lv.5</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加5%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 5% ATK (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>2000012001</v>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.1</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-DEF Lv.1</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物护甲永久增加1%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 1% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
+        <v>2000012002</v>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.2</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-DEF Lv.2</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物护甲永久增加2%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 2% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>2000012003</v>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.3</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-DEF Lv.3</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物护甲永久增加3%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 3% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="n">
+        <v>2000012004</v>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.4</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-DEF Lv.4</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物护甲永久增加4%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 4% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="n">
+        <v>2000012005</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·护甲Lv.5</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-DEF Lv.5</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物护甲永久增加5%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 5% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="n">
+        <v>2000013001</v>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.1</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-HP Lv.1</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物生命永久增加1%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 1% HP (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="n">
+        <v>2000013002</v>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.2</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-HP Lv.2</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物生命永久增加2%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 2% HP (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="n">
+        <v>2000013003</v>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.3</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-HP Lv.3</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物生命永久增加3%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 3% HP (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>2000013004</v>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.4</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-HP Lv.4</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物生命永久增加4%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 4% HP (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>excel_abyssal_blessing_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>2000013005</v>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>杀红了眼·生命Lv.5</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>Bloodlust-HP Lv.5</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1只敌人，全体魔物生命永久增加5%（持续至BOSS关）</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>Each enemy killed permanently grants all demons 5% HP (until the boss stage)</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>excel_abyssal_blessing_info</t>
         </is>
@@ -15926,7 +16886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="35.375" customWidth="1" style="1" min="1" max="1"/>
@@ -16690,26 +17650,26 @@
     </row>
     <row r="27" ht="17.25" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>11000100001</v>
+        <v>3001500001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>皮糙肉厚</t>
+          <t>都是兄弟·攻击</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>HP+</t>
+          <t>Band of Brothers-ATK</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>场上魔物每多1只，全体魔物攻击力增加{Percentage}%（每只、不含自身）</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>Increase HP by {Percentage}%</t>
+          <t>Each extra demon grants all demons {Percentage}% ATK (per demon, excluding self)</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -16720,26 +17680,26 @@
     </row>
     <row r="28" ht="17.25" customHeight="1" s="1">
       <c r="A28" s="0" t="n">
-        <v>11000200001</v>
+        <v>3001600001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>铁布衫</t>
+          <t>都是兄弟·护甲</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>DEF+</t>
+          <t>Band of Brothers-DEF</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>场上魔物每多1只，全体魔物护甲增加{Percentage}%（每只、不含自身）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>Increase DEF by {Percentage}%</t>
+          <t>Each extra demon grants all demons {Percentage}% DEF (per demon, excluding self) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -16750,26 +17710,26 @@
     </row>
     <row r="29" ht="17.25" customHeight="1" s="1">
       <c r="A29" s="0" t="n">
-        <v>11000300001</v>
+        <v>3001700001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>力大砖飞</t>
+          <t>都是兄弟·生命</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>ATK+</t>
+          <t>Band of Brothers-HP</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t>攻击力增加{Percentage}%</t>
+          <t>场上魔物每多1只，全体魔物生命增加{Percentage}%（每只、不含自身）</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>Increase ATK by {Percentage}%</t>
+          <t>Each extra demon grants all demons {Percentage}% HP (per demon, excluding self)</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -16780,26 +17740,26 @@
     </row>
     <row r="30" ht="17.25" customHeight="1" s="1">
       <c r="A30" s="0" t="n">
-        <v>11000400001</v>
+        <v>3001800001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>快到飞起</t>
+          <t>杀红了眼·攻击</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>ASPD+</t>
+          <t>Bloodlust-ATK</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>攻击速度增加{Percentage}%</t>
+          <t>每击杀1只敌人，全体魔物攻击力永久增加{Percentage}%</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>Increase ASPD by {Percentage}%</t>
+          <t>Each enemy killed permanently grants all demons {Percentage}% ATK</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -16810,26 +17770,26 @@
     </row>
     <row r="31" ht="17.25" customHeight="1" s="1">
       <c r="A31" s="0" t="n">
-        <v>11000500001</v>
+        <v>3001900001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>阴魂不散</t>
+          <t>杀红了眼·护甲</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>CD-</t>
+          <t>Bloodlust-DEF</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>每击杀1只敌人，全体魔物护甲永久增加{Percentage}%（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Summon CD {Percentage}%</t>
+          <t>Each enemy killed permanently grants all demons {Percentage}% DEF (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -16840,26 +17800,26 @@
     </row>
     <row r="32" ht="17.25" customHeight="1" s="1">
       <c r="A32" s="0" t="n">
-        <v>11000600001</v>
+        <v>3002000001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>骨折价</t>
+          <t>杀红了眼·生命</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>MP-</t>
+          <t>Bloodlust-HP</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>每击杀1只敌人，全体魔物生命永久增加{Percentage}%</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Summon MP cost {Percentage}%</t>
+          <t>Each enemy killed permanently grants all demons {Percentage}% HP</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -16870,26 +17830,26 @@
     </row>
     <row r="33" ht="17.25" customHeight="1" s="1">
       <c r="A33" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000100001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>医者自医</t>
+          <t>皮糙肉厚</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Self-Heal</t>
+          <t>HP+</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% HP every {Time_S}s</t>
+          <t>Increase HP by {Percentage}%</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -16900,26 +17860,26 @@
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
       <c r="A34" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000200001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>护甲保养</t>
+          <t>铁布衫</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Armor Polish</t>
+          <t>DEF+</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>Restore {Percentage}% DEF every {Time_S}s</t>
+          <t>Increase DEF by {Percentage}%</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -16930,26 +17890,26 @@
     </row>
     <row r="35" ht="17.25" customHeight="1" s="1">
       <c r="A35" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000300001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>再补一刀</t>
+          <t>力大砖飞</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Double Tap</t>
+          <t>ATK+</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒再攻击一次</t>
+          <t>攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>Extra attack every {Time_S}s</t>
+          <t>Increase ATK by {Percentage}%</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -16960,26 +17920,26 @@
     </row>
     <row r="36" ht="17.25" customHeight="1" s="1">
       <c r="A36" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000400001</v>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>尸堆养料-HP</t>
+          <t>快到飞起</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Feast-HP</t>
+          <t>ASPD+</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% HP per {KillNum} kills</t>
+          <t>Increase ASPD by {Percentage}%</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -16990,26 +17950,26 @@
     </row>
     <row r="37" ht="17.25" customHeight="1" s="1">
       <c r="A37" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000500001</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>尸堆养料-DR</t>
+          <t>阴魂不散</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Feast-DEF</t>
+          <t>CD-</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
+          <t>Summon CD {Percentage}%</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -17020,26 +17980,26 @@
     </row>
     <row r="38" ht="17.25" customHeight="1" s="1">
       <c r="A38" s="0" t="n">
-        <v>12001300001</v>
+        <v>11000600001</v>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>尸堆养料-ATK</t>
+          <t>骨折价</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Feast-ATK</t>
+          <t>MP-</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
+          <t>Summon MP cost {Percentage}%</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
@@ -17049,360 +18009,360 @@
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" s="1">
-      <c r="A39" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>尸堆养料-ASPD</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>Feast-ASPD</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
+      <c r="A39" t="n">
+        <v>11000700001</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>狂战士-A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Berserker-A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>攻击力增加{Percentage}%，生命减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Increase ATK by {Percentage}%, decrease HP by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" s="1">
-      <c r="A40" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>痛楚馈赠-HP</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(HP)</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
+      <c r="A40" t="n">
+        <v>11000700002</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>狂战士-B</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Berserker-B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>攻击力增加{Percentage}%，护甲减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Increase ATK by {Percentage}%, decrease DEF by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" s="1">
-      <c r="A41" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>痛楚馈赠-DR</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(DR)</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
+      <c r="A41" t="n">
+        <v>11000700003</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>狂战士-C</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Berserker-C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>攻击力增加{Percentage}%，攻击速度减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Increase ATK by {Percentage}%, decrease ASPD by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" s="1">
-      <c r="A42" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>痛楚馈赠-ATK</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(ATK)</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
+      <c r="A42" t="n">
+        <v>11000800001</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>快枪手-A</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gunslinger-A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>攻击速度增加{Percentage}%，护甲减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Increase ASPD by {Percentage}%, decrease DEF by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" s="1">
-      <c r="A43" s="0" t="n">
-        <v>12002400001</v>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>痛楚馈赠-ASPD</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Gift of Agony(ASPD)</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
+      <c r="A43" t="n">
+        <v>11000800002</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>快枪手-B</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gunslinger-B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>攻击速度增加{Percentage}%，生命减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Increase ASPD by {Percentage}%, decrease HP by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" s="1">
-      <c r="A44" s="0" t="n">
-        <v>12003100001</v>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>濒死狂宴-HP</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Feast of the Dying(HP)</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
-        </is>
-      </c>
-      <c r="F44" s="0" t="inlineStr">
+      <c r="A44" t="n">
+        <v>11000800003</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>快枪手-C</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gunslinger-C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>攻击速度增加{Percentage}%，攻击力减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Increase ASPD by {Percentage}%, decrease ATK by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" s="1">
-      <c r="A45" s="0" t="n">
-        <v>12003200001</v>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>濒死狂宴-DR</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Feast of the Dying(DR)</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
-        </is>
-      </c>
-      <c r="F45" s="0" t="inlineStr">
+      <c r="A45" t="n">
+        <v>11000900001</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ironclad-A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%，生命减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Increase DEF by {Percentage}%, decrease HP by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" s="1">
-      <c r="A46" s="0" t="n">
-        <v>12003300001</v>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>濒死狂宴-ATK</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Feast of the Dying(ATK)</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
-        </is>
-      </c>
-      <c r="F46" s="0" t="inlineStr">
+      <c r="A46" t="n">
+        <v>11000900002</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-B</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ironclad-B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%，攻击力减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Increase DEF by {Percentage}%, decrease ATK by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" s="1">
-      <c r="A47" s="0" t="n">
-        <v>12003400001</v>
-      </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>濒死狂宴-ASPD</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Feast of the Dying(ASPD)</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
-        </is>
-      </c>
-      <c r="F47" s="0" t="inlineStr">
+      <c r="A47" t="n">
+        <v>11000900003</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ironclad-C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%，攻击速度减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Increase DEF by {Percentage}%, decrease ASPD by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17.25" customHeight="1" s="1">
-      <c r="A48" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 收尸费</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Corpse Tax</t>
-        </is>
-      </c>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {KillNum} kills</t>
-        </is>
-      </c>
-      <c r="F48" s="0" t="inlineStr">
+      <c r="A48" t="n">
+        <v>11001000001</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>大块头-A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bruiser-A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%，攻击速度减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Increase HP by {Percentage}%, decrease ASPD by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="49" ht="17.25" customHeight="1" s="1">
-      <c r="A49" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>痛觉提款机</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Pain ATM</t>
-        </is>
-      </c>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F49" s="0" t="inlineStr">
+      <c r="A49" t="n">
+        <v>11001000002</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>大块头-B</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bruiser-B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%，护甲减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Increase HP by {Percentage}%, decrease DEF by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>暴力小费</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Violence Tip</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="inlineStr">
-        <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {AttackDamage} dmg dealt</t>
-        </is>
-      </c>
-      <c r="F50" s="0" t="inlineStr">
+      <c r="A50" t="n">
+        <v>11001000003</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>大块头-C</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bruiser-C</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%，攻击力减少{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Increase HP by {Percentage}%, decrease ATK by {Percentage}%</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
@@ -17410,26 +18370,26 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>鞭尸成瘾</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Corpse Kicker</t>
+        <v>12000100001</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>医者自医</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>Self-Heal</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>Instant attack per {KillNum} kills</t>
+          <t>Restore {Percentage}% HP every {Time_S}s</t>
         </is>
       </c>
       <c r="F51" s="0" t="inlineStr">
@@ -17440,26 +18400,26 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>12011200001</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>碰瓷反杀</t>
+        <v>12000200001</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>护甲保养</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Blood Bait</t>
+          <t>Armor Polish</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+          <t>Restore {Percentage}% DEF every {Time_S}s</t>
         </is>
       </c>
       <c r="F52" s="0" t="inlineStr">
@@ -17470,26 +18430,26 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>12011300001</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>越打越嗨</t>
+        <v>12000300001</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>再补一刀</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rage Spiral </t>
+          <t>Double Tap</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>每隔{Time_S}秒再攻击一次</t>
         </is>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {AttackDamage} dmg dealt</t>
+          <t>Extra attack every {Time_S}s</t>
         </is>
       </c>
       <c r="F53" s="0" t="inlineStr">
@@ -17500,26 +18460,26 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>拾晶不昧</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>Honest Finder</t>
+        <v>12001100001</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>尸堆养料-HP</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Feast-HP</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>Auto-collect crystals every {Time_S}s</t>
+          <t>Gain {Percentage}% HP per {KillNum} kills</t>
         </is>
       </c>
       <c r="F54" s="0" t="inlineStr">
@@ -17530,26 +18490,26 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>13000200001</v>
-      </c>
-      <c r="B55" s="0" t="inlineStr">
-        <is>
-          <t>有利可图</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>Opportunist</t>
+        <v>12001200001</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>尸堆养料-DR</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Feast-DEF</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>Resurrect on Death</t>
+          <t>Gain {Percentage}% DEF per {KillNum} kills</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
@@ -17560,26 +18520,26 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>死而复生</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>Second Wind</t>
+        <v>12001300001</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>尸堆养料-ATK</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Feast-ATK</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>Explode on Death</t>
+          <t>Gain {Percentage}% ATK per {KillNum} kills</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
@@ -17590,26 +18550,26 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>同归于尽</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>Mutual Destruction</t>
+        <v>12001400001</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>尸堆养料-ASPD</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Feast-ASPD</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>Heal allies {Percentage}% of max HP on death</t>
+          <t>Gain {Percentage}% ASPD per {KillNum} kills</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
@@ -17620,26 +18580,26 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="B58" s="0" t="inlineStr">
-        <is>
-          <t>死得其所-HP</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>Noble Death-HP</t>
+        <v>12002100001</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>痛楚馈赠-HP</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Gift of Agony(HP)</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>Shield allies {Percentage}% of max DEF on death</t>
+          <t>Gain {Percentage}% HP per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
@@ -17650,26 +18610,26 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>13000600001</v>
-      </c>
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>死得其所-DR</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>Noble Death-DEF</t>
+        <v>12002200001</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>痛楚馈赠-DR</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Gift of Agony(DR)</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>Spawn {Percentage}% chance crystal on death</t>
+          <t>Gain {Percentage}% DEF per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F59" s="0" t="inlineStr">
@@ -17680,19 +18640,559 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>痛楚馈赠-ATK</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Gift of Agony(ATK)</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ATK per {UnderAttackDamage} dmg taken</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>痛楚馈赠-ASPD</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Gift of Agony(ASPD)</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ASPD per {UnderAttackDamage} dmg taken</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>濒死狂宴-HP</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Feast of the Dying(HP)</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% HP when HP &lt; {HPRateLess}%</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>濒死狂宴-DR</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Feast of the Dying(DR)</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% DEF when HP &lt; {HPRateLess}%</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ATK</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Feast of the Dying(ATK)</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ATK when HP &lt; {HPRateLess}%</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>濒死狂宴-ASPD</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Feast of the Dying(ASPD)</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ASPD when HP &lt; {HPRateLess}%</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 收尸费</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>Corpse Tax</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>Drop crystal per {KillNum} kills</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>痛觉提款机</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>Pain ATM</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>暴力小费</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>Violence Tip</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>Drop crystal per {AttackDamage} dmg dealt</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>鞭尸成瘾</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>Corpse Kicker</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>Instant attack per {KillNum} kills</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>碰瓷反杀</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>Blood Bait</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>越打越嗨</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rage Spiral </t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>Extra attack per {AttackDamage} dmg dealt</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>拾晶不昧</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>Honest Finder</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>Auto-collect crystals every {Time_S}s</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>有利可图</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>Opportunist</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>Resurrect on Death</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>死而复生</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>Explode on Death</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>同归于尽</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>Mutual Destruction</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>Heal allies {Percentage}% of max HP on death</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-HP</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-HP</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>Shield allies {Percentage}% of max DEF on death</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-DR</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-DEF</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>死亡后{Percentage}%生成魔晶</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>Spawn {Percentage}% chance crystal on death</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>死亡税</t>
         </is>
       </c>
-      <c r="C60" s="0" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>Death Tax</t>
         </is>
       </c>
-      <c r="F60" s="0" t="inlineStr">
+      <c r="F78" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="723" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="723" firstSheet="1" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" state="visible" r:id="rId1"/>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加1%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加1%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 1% ATK (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 1% ATK (until the boss stage)</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加2%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加2%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 2% ATK (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 2% ATK (until the boss stage)</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加3%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加3%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 3% ATK (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 3% ATK (until the boss stage)</t>
         </is>
       </c>
       <c r="F63" s="0" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加4%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加4%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 4% ATK (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 4% ATK (until the boss stage)</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加5%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加5%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 5% ATK (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 5% ATK (until the boss stage)</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加1%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加1%（持续至BOSS关）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 1% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 1% DEF (until the boss stage) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F66" s="0" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加2%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加2%（持续至BOSS关）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 2% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 2% DEF (until the boss stage) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F67" s="0" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加3%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加3%（持续至BOSS关）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 3% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 3% DEF (until the boss stage) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
@@ -12059,12 +12059,12 @@
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加4%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加4%（持续至BOSS关）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 4% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 4% DEF (until the boss stage) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F69" s="0" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加5%（持续至BOSS关）（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加5%（持续至BOSS关）（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 5% DEF (until the boss stage) (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 5% DEF (until the boss stage) (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
@@ -12119,12 +12119,12 @@
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加1%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加1%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 1% HP (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 1% HP (until the boss stage)</t>
         </is>
       </c>
       <c r="F71" s="0" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加2%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加2%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 2% HP (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 2% HP (until the boss stage)</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
@@ -12179,12 +12179,12 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加3%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加3%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 3% HP (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 3% HP (until the boss stage)</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加4%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加4%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 4% HP (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 4% HP (until the boss stage)</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加5%（持续至BOSS关）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加5%（持续至BOSS关）</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons 5% HP (until the boss stage)</t>
+          <t>A random demon: each enemy it kills permanently grants itself 5% HP (until the boss stage)</t>
         </is>
       </c>
       <c r="F75" s="0" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="35.375" customWidth="1" style="1" min="1" max="1"/>
@@ -17754,12 +17754,12 @@
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物攻击力永久增加{Percentage}%</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身攻击力永久增加{Percentage}%</t>
         </is>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons {Percentage}% ATK</t>
+          <t>A random demon: each enemy it kills permanently grants itself {Percentage}% ATK</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -17784,12 +17784,12 @@
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物护甲永久增加{Percentage}%（无护甲的魔物不受加成）</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身护甲永久增加{Percentage}%（无护甲的魔物不受加成）</t>
         </is>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons {Percentage}% DEF (no bonus for demons without DEF)</t>
+          <t>A random demon: each enemy it kills permanently grants itself {Percentage}% DEF (no bonus for demons without DEF)</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -17814,12 +17814,12 @@
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>每击杀1只敌人，全体魔物生命永久增加{Percentage}%</t>
+          <t>随机1只魔物：它每击杀1只敌人，自身生命永久增加{Percentage}%</t>
         </is>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>Each enemy killed permanently grants all demons {Percentage}% HP</t>
+          <t>A random demon: each enemy it kills permanently grants itself {Percentage}% HP</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -18009,366 +18009,366 @@
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" s="1">
-      <c r="A39" t="n">
+      <c r="A39" s="0" t="n">
         <v>11000700001</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>狂战士-A</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>Berserker-A</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%，生命减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>Increase ATK by {Percentage}%, decrease HP by {Percentage}%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" s="1">
-      <c r="A40" t="n">
+      <c r="A40" s="0" t="n">
         <v>11000700002</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>狂战士-B</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Berserker-B</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%，护甲减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>Increase ATK by {Percentage}%, decrease DEF by {Percentage}%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" s="1">
-      <c r="A41" t="n">
+      <c r="A41" s="0" t="n">
         <v>11000700003</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>狂战士-C</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>Berserker-C</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%，攻击速度减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Increase ATK by {Percentage}%, decrease ASPD by {Percentage}%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" s="1">
-      <c r="A42" t="n">
+      <c r="A42" s="0" t="n">
         <v>11000800001</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>快枪手-A</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>Gunslinger-A</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>攻击速度增加{Percentage}%，护甲减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>Increase ASPD by {Percentage}%, decrease DEF by {Percentage}%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" s="1">
-      <c r="A43" t="n">
+      <c r="A43" s="0" t="n">
         <v>11000800002</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>快枪手-B</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>Gunslinger-B</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>攻击速度增加{Percentage}%，生命减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>Increase ASPD by {Percentage}%, decrease HP by {Percentage}%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" s="1">
-      <c r="A44" t="n">
+      <c r="A44" s="0" t="n">
         <v>11000800003</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>快枪手-C</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>Gunslinger-C</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>攻击速度增加{Percentage}%，攻击力减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>Increase ASPD by {Percentage}%, decrease ATK by {Percentage}%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" s="1">
-      <c r="A45" t="n">
+      <c r="A45" s="0" t="n">
         <v>11000900001</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-A</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>Ironclad-A</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%，生命减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>Increase DEF by {Percentage}%, decrease HP by {Percentage}%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" s="1">
-      <c r="A46" t="n">
+      <c r="A46" s="0" t="n">
         <v>11000900002</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-B</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>Ironclad-B</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%，攻击力减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>Increase DEF by {Percentage}%, decrease ATK by {Percentage}%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" s="1">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>11000900003</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-C</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>Ironclad-C</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%，攻击速度减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>Increase DEF by {Percentage}%, decrease ASPD by {Percentage}%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17.25" customHeight="1" s="1">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>11001000001</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>大块头-A</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>Bruiser-A</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%，攻击速度减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>Increase HP by {Percentage}%, decrease ASPD by {Percentage}%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="49" ht="17.25" customHeight="1" s="1">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>11001000002</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>大块头-B</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>Bruiser-B</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%，护甲减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Increase HP by {Percentage}%, decrease DEF by {Percentage}%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>11001000003</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>大块头-C</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>Bruiser-C</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%，攻击力减少{Percentage}%</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>Increase HP by {Percentage}%, decrease ATK by {Percentage}%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="14.25" customHeight="1" s="1">
       <c r="A51" s="0" t="n">
         <v>12000100001</v>
       </c>
@@ -18398,7 +18398,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="17.25" customHeight="1" s="1">
       <c r="A52" s="0" t="n">
         <v>12000200001</v>
       </c>
@@ -18428,7 +18428,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="17.25" customHeight="1" s="1">
       <c r="A53" s="0" t="n">
         <v>12000300001</v>
       </c>
@@ -18458,7 +18458,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="17.25" customHeight="1" s="1">
       <c r="A54" s="0" t="n">
         <v>12001100001</v>
       </c>
@@ -18488,7 +18488,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="17.25" customHeight="1" s="1">
       <c r="A55" s="0" t="n">
         <v>12001200001</v>
       </c>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="17.25" customHeight="1" s="1">
       <c r="A56" s="0" t="n">
         <v>12001300001</v>
       </c>
@@ -18548,7 +18548,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="17.25" customHeight="1" s="1">
       <c r="A57" s="0" t="n">
         <v>12001400001</v>
       </c>
@@ -18578,7 +18578,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="17.25" customHeight="1" s="1">
       <c r="A58" s="0" t="n">
         <v>12002100001</v>
       </c>
@@ -18608,7 +18608,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="17.25" customHeight="1" s="1">
       <c r="A59" s="0" t="n">
         <v>12002200001</v>
       </c>
@@ -18638,7 +18638,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="17.25" customHeight="1" s="1">
       <c r="A60" s="0" t="n">
         <v>12002300001</v>
       </c>
@@ -18668,7 +18668,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="17.25" customHeight="1" s="1">
       <c r="A61" s="0" t="n">
         <v>12002400001</v>
       </c>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="17.25" customHeight="1" s="1">
       <c r="A62" s="0" t="n">
         <v>12003100001</v>
       </c>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="17.25" customHeight="1" s="1">
       <c r="A63" s="0" t="n">
         <v>12003200001</v>
       </c>
@@ -18758,7 +18758,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="17.25" customHeight="1" s="1">
       <c r="A64" s="0" t="n">
         <v>12003300001</v>
       </c>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="17.25" customHeight="1" s="1">
       <c r="A65" s="0" t="n">
         <v>12003400001</v>
       </c>
@@ -18819,120 +18819,120 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="B66" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 收尸费</t>
-        </is>
-      </c>
-      <c r="C66" s="0" t="inlineStr">
-        <is>
-          <t>Corpse Tax</t>
-        </is>
-      </c>
-      <c r="D66" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E66" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {KillNum} kills</t>
-        </is>
-      </c>
-      <c r="F66" s="0" t="inlineStr">
+      <c r="A66" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>久经沙场-HP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Veteran-HP</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% HP after {OnFieldTime}s on field</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="B67" s="0" t="inlineStr">
-        <is>
-          <t>痛觉提款机</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>Pain ATM</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
-        </is>
-      </c>
-      <c r="F67" s="0" t="inlineStr">
+      <c r="A67" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>久经沙场-DR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Veteran-DEF</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% DEF after {OnFieldTime}s on field</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>暴力小费</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>Violence Tip</t>
-        </is>
-      </c>
-      <c r="D68" s="0" t="inlineStr">
-        <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
-        </is>
-      </c>
-      <c r="E68" s="0" t="inlineStr">
-        <is>
-          <t>Drop crystal per {AttackDamage} dmg dealt</t>
-        </is>
-      </c>
-      <c r="F68" s="0" t="inlineStr">
+      <c r="A68" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>久经沙场-ATK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Veteran-ATK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ATK after {OnFieldTime}s on field</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>鞭尸成瘾</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>Corpse Kicker</t>
-        </is>
-      </c>
-      <c r="D69" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
-        </is>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>Instant attack per {KillNum} kills</t>
-        </is>
-      </c>
-      <c r="F69" s="0" t="inlineStr">
+      <c r="A69" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>久经沙场-ASPD</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Veteran-ASPD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Gain {Percentage}% ASPD after {OnFieldTime}s on field</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
@@ -18940,26 +18940,26 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>碰瓷反杀</t>
+          <t>收尸费</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Blood Bait</t>
+          <t>Corpse Tax</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
+          <t>Drop crystal per {KillNum} kills</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
@@ -18970,26 +18970,26 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010200001</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>越打越嗨</t>
+          <t>痛觉提款机</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rage Spiral </t>
+          <t>Pain ATM</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>Extra attack per {AttackDamage} dmg dealt</t>
+          <t>Drop crystal per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F71" s="0" t="inlineStr">
@@ -19000,26 +19000,26 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010300001</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>拾晶不昧</t>
+          <t>暴力小费</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Honest Finder</t>
+          <t>Violence Tip</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>Auto-collect crystals every {Time_S}s</t>
+          <t>Drop crystal per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
@@ -19030,26 +19030,26 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010400001</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>有利可图</t>
+          <t>医疗账单</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Opportunist</t>
+          <t>Medical Bill</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>Resurrect on Death</t>
+          <t>Drop crystal per {RegainHPReceived} HP healed</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
@@ -19060,26 +19060,26 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>13000300001</v>
+        <v>12010500001</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>死而复生</t>
+          <t>出诊费</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>House Call Fee</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>Explode on Death</t>
+          <t>Drop crystal per {RegainHPCast} HP restored</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
@@ -19090,26 +19090,26 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011100001</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>同归于尽</t>
+          <t>鞭尸成瘾</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Mutual Destruction</t>
+          <t>Corpse Kicker</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>Heal allies {Percentage}% of max HP on death</t>
+          <t>Instant attack per {KillNum} kills</t>
         </is>
       </c>
       <c r="F75" s="0" t="inlineStr">
@@ -19120,26 +19120,26 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011200001</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>死得其所-HP</t>
+          <t>碰瓷反杀</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Noble Death-HP</t>
+          <t>Blood Bait</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>Shield allies {Percentage}% of max DEF on death</t>
+          <t>Extra attack per {UnderAttackDamage} dmg taken</t>
         </is>
       </c>
       <c r="F76" s="0" t="inlineStr">
@@ -19150,26 +19150,26 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>13000600001</v>
+        <v>12011300001</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>死得其所-DR</t>
+          <t>越打越嗨</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Noble Death-DEF</t>
+          <t xml:space="preserve">Rage Spiral </t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>Spawn {Percentage}% chance crystal on death</t>
+          <t>Extra attack per {AttackDamage} dmg dealt</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
@@ -19180,19 +19180,199 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>拾晶不昧</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>Honest Finder</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>Auto-collect crystals every {Time_S}s</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>有利可图</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>Opportunist</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>Resurrect on Death</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>死而复生</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>Explode on Death</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>同归于尽</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>Mutual Destruction</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>Heal allies {Percentage}% of max HP on death</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-HP</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-HP</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>Shield allies {Percentage}% of max DEF on death</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>死得其所-DR</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>Noble Death-DEF</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="inlineStr">
+        <is>
+          <t>死亡后{Percentage}%生成魔晶</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>Spawn {Percentage}% chance crystal on death</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>excel_buff_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="B78" s="0" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>死亡税</t>
         </is>
       </c>
-      <c r="C78" s="0" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>Death Tax</t>
         </is>
       </c>
-      <c r="F78" s="0" t="inlineStr">
+      <c r="F84" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -3447,11 +3447,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>54001</v>
+        <v>53015</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>议案:</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposal: </t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3462,16 +3467,11 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
-        </is>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>Demon Lord slayers are approaching...</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3482,16 +3482,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>A horde of heroes is approaching...</t>
+          <t>Demon Lord slayers are approaching...</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3502,16 +3502,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>Warning! A hero party is swarming in...</t>
+          <t>A horde of heroes is approaching...</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3522,16 +3522,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>Subjugation forces detected approaching...</t>
+          <t>Warning! A hero party is swarming in...</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3542,16 +3542,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>The Allied Hero Army is closing in...</t>
+          <t>Subjugation forces detected approaching...</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3562,16 +3562,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>A horde of self-proclaimed heroes has arrived...</t>
+          <t>The Allied Hero Army is closing in...</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3582,16 +3582,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Alert: Allies of justice are approaching...</t>
+          <t>A horde of self-proclaimed heroes has arrived...</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3602,16 +3602,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Upgrade</t>
+          <t>Alert: Allies of justice are approaching...</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3622,16 +3622,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Begin Sacrifice</t>
+          <t>Sacrifice Upgrade</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3642,16 +3642,16 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Success Rate</t>
+          <t>Begin Sacrifice</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3662,16 +3662,16 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>Select Sacrifice First!</t>
+          <t>Success Rate</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3682,16 +3682,16 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>Too Many Sacrifices!</t>
+          <t>Select Sacrifice First!</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3702,16 +3702,16 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>Start Sacrifice? Current Rate: {0}</t>
+          <t>Too Many Sacrifices!</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3722,16 +3722,16 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>61004</v>
+        <v>61003</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Allocate All Points First!</t>
+          <t>Start Sacrifice? Current Rate: {0}</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3742,16 +3742,16 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>61005</v>
+        <v>61004</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>Points Left: {0}</t>
+          <t>Allocate All Points First!</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3762,16 +3762,16 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>61006</v>
+        <v>61005</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>Confirm this attribute allocation? It cannot be changed afterwards.</t>
+          <t>Points Left: {0}</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3782,16 +3782,16 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>61007</v>
+        <v>61006</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>献祭成功，等级提升！</t>
+          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Succeeded, Level Up!</t>
+          <t>Confirm this attribute allocation? It cannot be changed afterwards.</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3802,16 +3802,16 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>61008</v>
+        <v>61007</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>献祭失败，祭品已消耗</t>
+          <t>献祭成功，等级提升！</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Failed, Offerings Consumed</t>
+          <t>Sacrifice Succeeded, Level Up!</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3822,16 +3822,16 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>62001</v>
+        <v>61008</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>Research for x{0} Magic Crystals?</t>
+          <t>Sacrifice Failed, Offerings Consumed</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3842,16 +3842,16 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Research for x{0} Magic Crystals?</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3862,16 +3862,16 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3882,16 +3882,16 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3902,16 +3902,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>Select Rebirth Appearance</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3922,16 +3922,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Select Rebirth Appearance</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3942,16 +3942,16 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>Confirm Rebirth with this look?</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3962,14 +3962,18 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
-        </is>
-      </c>
-      <c r="C142" s="0" t="n"/>
+          <t>是否以此外观完成转生？</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>Confirm Rebirth with this look?</t>
+        </is>
+      </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -3978,11 +3982,11 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="C143" s="0" t="n"/>
@@ -3994,11 +3998,11 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>65001</v>
+        <v>64002</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="C144" s="0" t="n"/>
@@ -4010,18 +4014,14 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>70001</v>
+        <v>65001</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
-        </is>
-      </c>
-      <c r="C145" s="0" t="inlineStr">
-        <is>
-          <t>Bribe</t>
-        </is>
-      </c>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="n"/>
       <c r="D145" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4030,16 +4030,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>Start Evolution</t>
+          <t>Bribe</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -4050,16 +4050,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>End Evolution</t>
+          <t>Start Evolution</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -4070,16 +4070,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>Complete Evolution</t>
+          <t>End Evolution</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -4090,16 +4090,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>End Evolution? Materials won't be refunded!</t>
+          <t>Complete Evolution</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -4110,16 +4110,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>End Evolution? Materials won't be refunded!</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -4130,16 +4130,16 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>Select Evolution Target</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -4150,16 +4150,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>选择素材魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Select Material Demon</t>
+          <t>Select Evolution Target</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -4170,16 +4170,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择素材魔物</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected</t>
+          <t>Select Material Demon</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -4190,16 +4190,16 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>Speed Up x{0}</t>
+          <t>No Demon Selected</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -4210,16 +4210,16 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>加速进阶 +{0}秒/晶</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+          <t>Speed Up +{0}s/Crystal</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -4230,59 +4230,69 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>80011</v>
+        <v>80010</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>素材魔物最多只能选择{0}只</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>Up to {0} material demons can be selected</t>
+          <t>Dissolve &lt;color=#FF6B6B&gt;{0}&lt;/color&gt; to evolve &lt;color=#4ECDC4&gt;{1}&lt;/color&gt;? Target will vanish!</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>80012</v>
+        <v>80011</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>还未选择素材魔物</t>
+          <t>素材魔物最多只能选择{0}只</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>No Material Demon Selected</t>
+          <t>Up to {0} material demons can be selected</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>90001</v>
+        <v>80012</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="D158" s="0" t="inlineStr">
-        <is>
-          <t>excel_ui_text</t>
+          <t>还未选择素材魔物</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>No Material Demon Selected</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="0" t="n">
-        <v>90002</v>
-      </c>
-      <c r="B159" s="0" t="inlineStr">
-        <is>
-          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
-        </is>
-      </c>
-      <c r="D159" s="0" t="inlineStr">
+      <c r="A159" t="n">
+        <v>80013</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>进阶成功，稀有度提升！</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ascension complete! Rarity increased!</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -4290,16 +4300,11 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
-        </is>
-      </c>
-      <c r="C160" s="0" t="inlineStr">
-        <is>
-          <t>Confirm</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -4310,16 +4315,11 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
-        </is>
-      </c>
-      <c r="C161" s="0" t="inlineStr">
-        <is>
-          <t>Cancel</t>
+          <t>&lt;color=#FF6B6B&gt;(魔王专属)&lt;/color&gt;</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -4330,16 +4330,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -4350,16 +4350,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -4370,16 +4370,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Lv.{0}</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4390,16 +4390,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>Research Lv.{0}</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4410,16 +4410,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>Research Max</t>
+          <t>Discard</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4430,16 +4430,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Research Lv.{0}</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4450,16 +4450,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>Enter name...</t>
+          <t>Research Max</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4470,16 +4470,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>Select Demon</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4490,16 +4490,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>Selected: {0}/{1}</t>
+          <t>Enter name...</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4510,16 +4510,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>Too Many Selected</t>
+          <t>Select Demon</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4530,16 +4530,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>Tip</t>
+          <t>Selected: {0}/{1}</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4550,16 +4550,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>Magic Crystal</t>
+          <t>Too Many Selected</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4570,16 +4570,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4590,16 +4590,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>Sort: Rarity</t>
+          <t>Magic Crystal</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4610,16 +4610,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>Sort: Level</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4630,16 +4630,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Sort: Rarity</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4650,16 +4650,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>Sort: Name</t>
+          <t>Sort: Level</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4670,11 +4670,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>阵容</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>Team</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4685,11 +4690,16 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>所属种族:{0}</t>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>Sort: Name</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4700,11 +4710,11 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4715,16 +4725,11 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
-        </is>
-      </c>
-      <c r="C182" s="0" t="inlineStr">
-        <is>
-          <t>Type</t>
+          <t>所属种族:{0}</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4735,14 +4740,13 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
-        </is>
-      </c>
-      <c r="C183" s="0" t="n"/>
+          <t>道具名字:{0}</t>
+        </is>
+      </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4751,16 +4755,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>No Related Items</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4771,18 +4775,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
-        </is>
-      </c>
-      <c r="C185" s="0" t="inlineStr">
-        <is>
-          <t>No Related Creatures</t>
-        </is>
-      </c>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="n"/>
       <c r="D185" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4791,14 +4791,18 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
-        </is>
-      </c>
-      <c r="C186" s="0" t="n"/>
+          <t>没有相关道具</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>No Related Items</t>
+        </is>
+      </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4807,16 +4811,16 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>Rarity</t>
+          <t>No Related Creatures</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4827,18 +4831,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="C188" s="0" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
+          <t>没有可孕育的生物</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="n"/>
       <c r="D188" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -4847,16 +4847,16 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Rarity</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4867,16 +4867,16 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4887,16 +4887,16 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>2000022</v>
+        <v>2000020</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4907,16 +4907,16 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="n">
-        <v>2000023</v>
+        <v>2000021</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>低等级...</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>Min Level...</t>
+          <t>Combat</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4927,16 +4927,16 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="n">
-        <v>2000024</v>
+        <v>2000022</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>高等级...</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>Max Level...</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4947,16 +4947,16 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Magic Crystals!</t>
+          <t>Min Level...</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4967,16 +4967,16 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>Not Enough Reputation!</t>
+          <t>Max Level...</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4987,16 +4987,16 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>Rename Successful!</t>
+          <t>Not Enough Magic Crystals!</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -5007,16 +5007,16 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>No Demon Selected!</t>
+          <t>Not Enough Reputation!</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -5027,16 +5027,16 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>Rebirth Success!</t>
+          <t>Rename Successful!</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -5047,16 +5047,16 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>No Demon Selected!</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -5067,16 +5067,16 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>Claimed!</t>
+          <t>Rebirth Success!</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -5087,16 +5087,16 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
@@ -5107,16 +5107,16 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>Total Kills</t>
+          <t>Claimed!</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -5127,16 +5127,16 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>Conquer Clears</t>
+          <t>Play Time</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -5147,16 +5147,16 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>Difficulty {0}</t>
+          <t>Total Kills</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
@@ -5167,16 +5167,16 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Conquer Clears</t>
         </is>
       </c>
       <c r="D205" s="0" t="inlineStr">
@@ -5187,16 +5187,16 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>Total Clears</t>
+          <t>Difficulty {0}</t>
         </is>
       </c>
       <c r="D206" s="0" t="inlineStr">
@@ -5207,16 +5207,16 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="D207" s="0" t="inlineStr">
@@ -5227,16 +5227,16 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="n">
-        <v>4000017</v>
+        <v>4000015</v>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>总通关次数</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Total Clears</t>
         </is>
       </c>
       <c r="D208" s="0" t="inlineStr">
@@ -5247,19 +5247,59 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t>excel_ui_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="B209" s="0" t="inlineStr">
+      <c r="B211" s="0" t="inlineStr">
         <is>
           <t>刷新x{0}</t>
         </is>
       </c>
-      <c r="C209" s="0" t="inlineStr">
+      <c r="C211" s="0" t="inlineStr">
         <is>
           <t>Refresh x{0}</t>
         </is>
       </c>
-      <c r="D209" s="0" t="inlineStr">
+      <c r="D211" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
         </is>
@@ -7538,7 +7578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.625" customWidth="1" style="1" min="1" max="1"/>
@@ -7675,16 +7715,16 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>100100001</v>
+        <v>100000007</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>开启献祭升级设施(经验足够之后在魔物页面升级)</t>
+          <t>进阶加速倍率提升</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Unlock Sacrifice Upgrade Facility</t>
+          <t>Evolution Speed-up +1</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -7695,16 +7735,16 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>100100002</v>
+        <v>100000008</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>献祭祭品数量+1</t>
+          <t>进阶素材数量提升</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Fodder +1</t>
+          <t>Evolution Material Slots +1</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -7715,16 +7755,16 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>100100003</v>
+        <v>100100001</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>献祭失败保底概率提升</t>
+          <t>开启献祭升级设施(经验足够之后在魔物页面升级)</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>Sacrifice Fail Pity Up</t>
+          <t>Unlock Sacrifice Upgrade Facility</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -7735,16 +7775,16 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>100100004</v>
+        <v>100100002</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>不同魔物献祭成功率提升</t>
+          <t>献祭祭品数量+1</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Cross-species Sacrifice Rate Up</t>
+          <t>Sacrifice Fodder +1</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -7755,16 +7795,16 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>100200001</v>
+        <v>100100003</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>开启终焉议会</t>
+          <t>献祭失败保底概率提升</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Unlock Council of Doom</t>
+          <t>Sacrifice Fail Pity Up</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -7775,16 +7815,16 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>100200002</v>
+        <v>100100004</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔物重命名</t>
+          <t>不同魔物献祭成功率提升</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon Renaming</t>
+          <t>Cross-species Sacrifice Rate Up</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -7795,16 +7835,16 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>100200003</v>
+        <v>100200001</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：魔王重命名</t>
+          <t>开启终焉议会</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Council: Demon King Renaming</t>
+          <t>Unlock Council of Doom</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -7815,16 +7855,16 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>100300001</v>
+        <v>100200002</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>传送门可选择世界+1</t>
+          <t>终焉议会议案：魔物重命名</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>Portal: +1 World Choice</t>
+          <t>Council: Demon Renaming</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -7835,16 +7875,16 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>100300002</v>
+        <v>100200003</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>线路数预览</t>
+          <t>终焉议会议案：魔王重命名</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Route Count Preview</t>
+          <t>Council: Demon King Renaming</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -7855,16 +7895,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>100300003</v>
+        <v>100300001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>关卡数预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Stage Count Preview</t>
+          <t>Portal: +1 World Choice</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -7875,16 +7915,16 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>100300004</v>
+        <v>100300002</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>路径长度预览</t>
+          <t>线路数预览</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>Road Length Preview</t>
+          <t>Route Count Preview</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -7895,16 +7935,16 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>100300005</v>
+        <v>100300003</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>奖励预览</t>
+          <t>关卡数预览</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Reward Preview</t>
+          <t>Stage Count Preview</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -7915,16 +7955,16 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>100300006</v>
+        <v>100300004</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>传送门刷新</t>
+          <t>路径长度预览</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>Portal Refresh</t>
+          <t>Road Length Preview</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -7935,16 +7975,16 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>100310112</v>
+        <v>100300005</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>剑与魔法：征服难度+1</t>
+          <t>奖励预览</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
+          <t>Reward Preview</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -7955,11 +7995,16 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>100400000</v>
+        <v>100300006</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>传送门刷新</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Portal Refresh</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -7970,16 +8015,16 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>100400001</v>
+        <v>100310112</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>剑与魔法：征服难度+1</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>Incubation Skip</t>
+          <t>Sword &amp; Magic: Conquest Difficulty +1</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -7990,16 +8035,11 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>100401000</v>
+        <v>100400000</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>Unlock R Rarity Incubation</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -8010,16 +8050,16 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>100401001</v>
+        <v>100400001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>R Rarity Rate +1%</t>
+          <t>Incubation Skip</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -8030,16 +8070,16 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="n">
-        <v>100402000</v>
+        <v>100401000</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>Unlock R Rarity Incubation</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -8050,16 +8090,16 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>100402001</v>
+        <v>100401001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>SR Rarity Rate +1%</t>
+          <t>R Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -8070,16 +8110,16 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="n">
-        <v>100403000</v>
+        <v>100402000</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Unlock SSR Rarity Incubation</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -8090,16 +8130,16 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>100403001</v>
+        <v>100402001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>SSR Rarity Rate +1%</t>
+          <t>SR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -8110,16 +8150,16 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>100404001</v>
+        <v>100403000</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Unlock SR Rarity Incubation</t>
+          <t>Unlock SSR Rarity Incubation</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -8130,16 +8170,16 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>200000001</v>
+        <v>100403001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>阵容上限+1</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Team Limit +1</t>
+          <t>SSR Rarity Rate +1%</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -8150,16 +8190,16 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>200100001</v>
+        <v>100404001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>解锁一个新阵容</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Unlock New Team</t>
+          <t>Unlock SR Rarity Incubation</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -8170,16 +8210,16 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>200200001</v>
+        <v>200000001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>阵容上限+1</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>Crystal Drop Duration +5s</t>
+          <t>Team Limit +1</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -8190,16 +8230,16 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>200300001</v>
+        <v>200100001</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>解锁一个新阵容</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Limit +10</t>
+          <t>Unlock New Team</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -8210,16 +8250,16 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>200400001</v>
+        <v>200200001</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>魔王魔力恢复+1/秒</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>Demon Lord Mana Regen +1/s</t>
+          <t>Crystal Drop Duration +5s</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -8230,16 +8270,16 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>200500001</v>
+        <v>200300001</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数+1</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>Abyssal Blessing Refresh +1</t>
+          <t>Demon Lord Mana Limit +10</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -8250,16 +8290,16 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>300100000</v>
+        <v>200400001</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔王魔力恢复+1/秒</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Human</t>
+          <t>Demon Lord Mana Regen +1/s</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -8270,16 +8310,16 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>300100001</v>
+        <v>200500001</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>深渊馈赠刷新次数+1</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Warrior</t>
+          <t>Abyssal Blessing Refresh +1</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -8290,16 +8330,16 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>300100002</v>
+        <v>200600001</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>空格突进</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Archer</t>
+          <t>Space Dash</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -8310,16 +8350,16 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>300100003</v>
+        <v>200700001</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>突进冷却</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Fire Mage</t>
+          <t>Dash Cooldown</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -8330,16 +8370,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>300100004</v>
+        <v>300100000</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Human Ice Mage</t>
+          <t>Unlock Race: Human</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
@@ -8350,16 +8390,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>300100101</v>
+        <v>300100001</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x5</t>
+          <t>Unlock Class: Human Warrior</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
@@ -8370,16 +8410,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>300100102</v>
+        <v>300100002</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>Incubate Humans x10</t>
+          <t>Unlock Class: Human Archer</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -8390,16 +8430,16 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300100201</v>
+        <v>300100003</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为人类</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Human</t>
+          <t>Unlock Class: Human Fire Mage</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -8410,16 +8450,16 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>300100301</v>
+        <v>300100004</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：人类装备</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Human Equipment</t>
+          <t>Unlock Class: Human Ice Mage</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -8430,16 +8470,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>300200000</v>
+        <v>300100101</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Skeleton</t>
+          <t>Incubate Humans x5</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -8450,16 +8490,16 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="1">
       <c r="A46" s="0" t="n">
-        <v>300200001</v>
+        <v>300100102</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Warrior</t>
+          <t>Incubate Humans x10</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
@@ -8470,16 +8510,16 @@
     </row>
     <row r="47" ht="14" customHeight="1" s="1">
       <c r="A47" s="0" t="n">
-        <v>300200002</v>
+        <v>300100201</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>终焉议会议案：转生为人类</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Thrower</t>
+          <t>Council: Reincarnate as Human</t>
         </is>
       </c>
       <c r="D47" s="0" t="inlineStr">
@@ -8490,16 +8530,16 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="1">
       <c r="A48" s="0" t="n">
-        <v>300200003</v>
+        <v>300100301</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>奖励新增：人类装备</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Fire Mage</t>
+          <t>New Reward: Human Equipment</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -8510,16 +8550,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>300200004</v>
+        <v>300200000</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Skeleton Ice Mage</t>
+          <t>Unlock Race: Skeleton</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -8530,16 +8570,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>300200101</v>
+        <v>300200001</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x5</t>
+          <t>Unlock Class: Skeleton Warrior</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -8550,16 +8590,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>300200102</v>
+        <v>300200002</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Incubate Skeletons x10</t>
+          <t>Unlock Class: Skeleton Thrower</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -8570,16 +8610,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>300200201</v>
+        <v>300200003</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为骷髅</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Skeleton</t>
+          <t>Unlock Class: Skeleton Fire Mage</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -8590,16 +8630,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>300200301</v>
+        <v>300200004</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：骷髅装备</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Skeleton Equipment</t>
+          <t>Unlock Class: Skeleton Ice Mage</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -8610,16 +8650,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>300300000</v>
+        <v>300200101</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Slime</t>
+          <t>Incubate Skeletons x5</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -8630,16 +8670,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>300300001</v>
+        <v>300200102</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Guardian Slime</t>
+          <t>Incubate Skeletons x10</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -8650,16 +8690,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>300300002</v>
+        <v>300200201</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>终焉议会议案：转生为骷髅</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Boom Slime</t>
+          <t>Council: Reincarnate as Skeleton</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -8670,16 +8710,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>300300003</v>
+        <v>300200301</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>奖励新增：骷髅装备</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Mud Slime</t>
+          <t>New Reward: Skeleton Equipment</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -8690,16 +8730,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>300300004</v>
+        <v>300300000</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Venom Slime</t>
+          <t>Unlock Race: Slime</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -8710,16 +8750,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>300300101</v>
+        <v>300300001</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x5</t>
+          <t>Unlock Class: Guardian Slime</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -8730,16 +8770,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>300300102</v>
+        <v>300300002</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>Incubate Slimes x10</t>
+          <t>Unlock Class: Boom Slime</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -8750,16 +8790,16 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>300300201</v>
+        <v>300300003</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：生为史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>Council: Be Born as Slime</t>
+          <t>Unlock Class: Mud Slime</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -8770,16 +8810,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>300300301</v>
+        <v>300300004</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：史莱姆装备</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Slime Equipment</t>
+          <t>Unlock Class: Venom Slime</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -8790,16 +8830,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>300400000</v>
+        <v>300300101</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Succubus</t>
+          <t>Incubate Slimes x5</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -8810,16 +8850,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>300400001</v>
+        <v>300300102</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Battle Succubus</t>
+          <t>Incubate Slimes x10</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -8830,16 +8870,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>300400002</v>
+        <v>300300201</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>终焉议会议案：生为史莱姆</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Heal Succubus</t>
+          <t>Council: Be Born as Slime</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -8850,16 +8890,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>300400003</v>
+        <v>300300301</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>奖励新增：史莱姆装备</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Charm Succubus</t>
+          <t>New Reward: Slime Equipment</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -8870,16 +8910,16 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>300400004</v>
+        <v>300400000</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Ao Succubus</t>
+          <t>Unlock Race: Succubus</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -8890,16 +8930,16 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>300400005</v>
+        <v>300400001</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Shield Succubus</t>
+          <t>Unlock Class: Battle Succubus</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -8910,16 +8950,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>300400101</v>
+        <v>300400002</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x5</t>
+          <t>Unlock Class: Heal Succubus</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -8930,16 +8970,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>300400102</v>
+        <v>300400003</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Incubate Succubi x10</t>
+          <t>Unlock Class: Charm Succubus</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -8950,16 +8990,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>300400201</v>
+        <v>300400004</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Succubus</t>
+          <t>Unlock Class: Ao Succubus</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -8970,16 +9010,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>300400301</v>
+        <v>300400005</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：魅魔装备</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Succubus Equipment</t>
+          <t>Unlock Class: Shield Succubus</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -8990,16 +9030,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>300500000</v>
+        <v>300400101</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Minotaur</t>
+          <t>Incubate Succubi x5</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -9010,16 +9050,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>300500001</v>
+        <v>300400102</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Warrior</t>
+          <t>Incubate Succubi x10</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -9030,16 +9070,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>300500002</v>
+        <v>300400201</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>终焉议会议案：转生为魅魔</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Thrower</t>
+          <t>Council: Reincarnate as Succubus</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -9050,16 +9090,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>300500003</v>
+        <v>300400301</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>奖励新增：魅魔装备</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Fire Mage</t>
+          <t>New Reward: Succubus Equipment</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -9070,16 +9110,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>300500004</v>
+        <v>300500000</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Minotaur Ice Mage</t>
+          <t>Unlock Race: Minotaur</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -9090,16 +9130,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>300500101</v>
+        <v>300500001</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x5</t>
+          <t>Unlock Class: Minotaur Warrior</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -9110,16 +9150,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>300500102</v>
+        <v>300500002</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Incubate Minotaurs x10</t>
+          <t>Unlock Class: Minotaur Thrower</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -9130,16 +9170,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>300500201</v>
+        <v>300500003</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为牛头人</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Minotaur</t>
+          <t>Unlock Class: Minotaur Fire Mage</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -9150,16 +9190,16 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>300500301</v>
+        <v>300500004</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：牛头人装备</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Minotaur Equipment</t>
+          <t>Unlock Class: Minotaur Ice Mage</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -9170,16 +9210,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>300600000</v>
+        <v>300500101</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Goblin</t>
+          <t>Incubate Minotaurs x5</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -9190,16 +9230,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>300600001</v>
+        <v>300500102</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Assassin</t>
+          <t>Incubate Minotaurs x10</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
@@ -9210,16 +9250,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>300600002</v>
+        <v>300500201</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>终焉议会议案：转生为牛头人</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Archer</t>
+          <t>Council: Reincarnate as Minotaur</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -9230,16 +9270,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>300600003</v>
+        <v>300500301</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>奖励新增：牛头人装备</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Kamikaze</t>
+          <t>New Reward: Minotaur Equipment</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -9250,16 +9290,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>300600004</v>
+        <v>300600000</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Fire Mage</t>
+          <t>Unlock Race: Goblin</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -9270,16 +9310,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>300600005</v>
+        <v>300600001</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Goblin Ice Mage</t>
+          <t>Unlock Class: Goblin Assassin</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
@@ -9290,16 +9330,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>300600101</v>
+        <v>300600002</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x5</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x5</t>
+          <t>Unlock Class: Goblin Archer</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -9310,16 +9350,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>300600102</v>
+        <v>300600003</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>孕育哥布林x10</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>Incubate Goblins x10</t>
+          <t>Unlock Class: Goblin Kamikaze</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -9330,16 +9370,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>300600201</v>
+        <v>300600004</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生为哥布林</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Goblin</t>
+          <t>Unlock Class: Goblin Fire Mage</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -9350,16 +9390,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>300600301</v>
+        <v>300600005</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：哥布林装备</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Goblin Equipment</t>
+          <t>Unlock Class: Goblin Ice Mage</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -9370,16 +9410,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>300700000</v>
+        <v>300600101</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育哥布林x5</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>Unlock Race: Orc</t>
+          <t>Incubate Goblins x5</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -9390,16 +9430,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>300700001</v>
+        <v>300600102</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育哥布林x10</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Warrior</t>
+          <t>Incubate Goblins x10</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -9410,16 +9450,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>300700002</v>
+        <v>300600201</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>终焉议会议案：转生为哥布林</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Archer</t>
+          <t>Council: Reincarnate as Goblin</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -9430,16 +9470,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>300700003</v>
+        <v>300600301</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>奖励新增：哥布林装备</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Fire Mage</t>
+          <t>New Reward: Goblin Equipment</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -9450,16 +9490,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>300700004</v>
+        <v>300700000</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>Unlock Class: Orc Ice Mage</t>
+          <t>Unlock Race: Orc</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -9470,16 +9510,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>300700101</v>
+        <v>300700001</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x5</t>
+          <t>Unlock Class: Orc Warrior</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -9490,16 +9530,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>300700102</v>
+        <v>300700002</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>Incubate Orcs x10</t>
+          <t>Unlock Class: Orc Archer</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -9510,16 +9550,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>300700201</v>
+        <v>300700003</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>终焉议会议案：转生兽人</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>Council: Reincarnate as Orc</t>
+          <t>Unlock Class: Orc Fire Mage</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -9530,16 +9570,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>300700301</v>
+        <v>300700004</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>奖励新增：兽人装备</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>New Reward: Orc Equipment</t>
+          <t>Unlock Class: Orc Ice Mage</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -9550,14 +9590,94 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>孕育兽人x5</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>Incubate Orcs x5</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="n">
+        <v>300700102</v>
+      </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>孕育兽人x10</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>Incubate Orcs x10</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="n">
+        <v>300700201</v>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>终焉议会议案：转生兽人</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>Council: Reincarnate as Orc</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="n">
+        <v>300700301</v>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>奖励新增：兽人装备</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>New Reward: Orc Equipment</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="inlineStr">
+        <is>
+          <t>excel_research_info</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="n">
         <v>100500001</v>
       </c>
-      <c r="B101" s="0" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>开启成就设施</t>
         </is>
       </c>
-      <c r="C101" s="0" t="inlineStr"/>
+      <c r="C105" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18819,120 +18939,120 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="0" t="n">
         <v>12004100001</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>久经沙场-HP</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>Veteran-HP</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>Gain {Percentage}% HP after {OnFieldTime}s on field</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="0" t="n">
         <v>12004200001</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>久经沙场-DR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>Veteran-DEF</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="0" t="inlineStr">
         <is>
           <t>Gain {Percentage}% DEF after {OnFieldTime}s on field</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="0" t="n">
         <v>12004300001</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>久经沙场-ATK</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>Veteran-ATK</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="0" t="inlineStr">
         <is>
           <t>Gain {Percentage}% ATK after {OnFieldTime}s on field</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="0" t="n">
         <v>12004400001</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>久经沙场-ASPD</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>Veteran-ASPD</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="0" t="inlineStr">
         <is>
           <t>Gain {Percentage}% ASPD after {OnFieldTime}s on field</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="0" t="inlineStr">
         <is>
           <t>excel_buff_info</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_language[多语言_FrameWork].xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="23.25" customWidth="1" style="1" min="1" max="1"/>
@@ -2101,16 +2101,16 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>10001</v>
+        <v>2008</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>购买</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Ascend</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
@@ -2121,16 +2121,16 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>下一个</t>
+          <t>购买</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -2141,16 +2141,16 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>结束</t>
+          <t>下一个</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -2161,16 +2161,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>再来一次</t>
+          <t>结束</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>Try Again</t>
+          <t>Ascend</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -2181,16 +2181,16 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>跳过所有</t>
+          <t>再来一次</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>Skip All</t>
+          <t>Try Again</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -2201,16 +2201,16 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>展示</t>
+          <t>跳过所有</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>Show</t>
+          <t>Skip All</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
@@ -2221,16 +2221,16 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>重命名</t>
+          <t>展示</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Show</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -2241,16 +2241,16 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>20001</v>
+        <v>10008</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>重命名</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>Lineup</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
@@ -2261,16 +2261,16 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>孕育</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>Incubate</t>
+          <t>Lineup</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -2281,16 +2281,16 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>孕育</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Incubate</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -2301,16 +2301,16 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>20004</v>
+        <v>20003</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>研究</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -2321,16 +2321,16 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>研究</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>Ascend</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
@@ -2341,11 +2341,16 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>Ascend</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2356,16 +2361,11 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>30001</v>
+        <v>20006</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>稀</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
@@ -2376,16 +2376,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>级</t>
+          <t>稀</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>Lv</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2396,16 +2396,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>阵</t>
+          <t>级</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Lv</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2416,16 +2416,16 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>阵</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2436,16 +2436,16 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>30005</v>
+        <v>30004</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>阵容 {0}</t>
+          <t>名</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>Lineup {0}</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2456,16 +2456,16 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>30006</v>
+        <v>30005</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>超过阵容魔物上限！</t>
+          <t>阵容 {0}</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>Team Full!</t>
+          <t>Lineup {0}</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -2476,14 +2476,18 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>30007</v>
+        <v>30006</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>阵容魔物数量 {0}</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="n"/>
+          <t>超过阵容魔物上限！</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>Team Full!</t>
+        </is>
+      </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -2492,18 +2496,14 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>40001</v>
+        <v>30007</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>游戏</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>Game</t>
-        </is>
-      </c>
+          <t>阵容魔物数量 {0}</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="n"/>
       <c r="D68" s="0" t="inlineStr">
         <is>
           <t>excel_ui_text</t>
@@ -2512,16 +2512,16 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>40002</v>
+        <v>40001</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Game</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2532,16 +2532,16 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>40003</v>
+        <v>40002</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>音频</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2552,16 +2552,16 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>40998</v>
+        <v>40003</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>已开启</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2572,16 +2572,16 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>40999</v>
+        <v>40998</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>已关闭</t>
+          <t>已开启</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>On</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -2592,16 +2592,16 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>41001</v>
+        <v>40999</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>已关闭</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2612,16 +2612,16 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>41002</v>
+        <v>41001</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>按键提示显示</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>Key Hint Display</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2632,16 +2632,16 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>42001</v>
+        <v>41002</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>屏幕分辨率</t>
+          <t>按键提示显示</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Screen Resolution</t>
+          <t>Key Hint Display</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2652,16 +2652,16 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>42002</v>
+        <v>42001</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>锁定帧数</t>
+          <t>屏幕分辨率</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>Lock FPS</t>
+          <t>Screen Resolution</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2672,16 +2672,16 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>42003</v>
+        <v>42002</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>帧数</t>
+          <t>锁定帧数</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>FPS</t>
+          <t>Lock FPS</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2692,16 +2692,16 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>43001</v>
+        <v>42003</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>帧数</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Music Volume</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -2712,16 +2712,16 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>43002</v>
+        <v>43001</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>音乐音量</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>Sound Volume</t>
+          <t>Music Volume</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -2732,16 +2732,16 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>49001</v>
+        <v>43002</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="C80" s="0" t="in